--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441D9C56-34A5-D340-B5BB-1D9C53ECA835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E39235-0546-E74D-81F2-989A5F8F570F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="850">
   <si>
     <t>Type</t>
   </si>
@@ -2163,9 +2163,6 @@
   </si>
   <si>
     <t>60.5</t>
-  </si>
-  <si>
-    <t>Karahali Souare</t>
   </si>
   <si>
     <t>306.0</t>
@@ -7470,7 +7467,7 @@
         <v>203</v>
       </c>
       <c r="D61" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E61" t="s">
         <v>25</v>
@@ -7547,7 +7544,7 @@
         <v>203</v>
       </c>
       <c r="D62" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E62" t="s">
         <v>42</v>
@@ -7624,7 +7621,7 @@
         <v>203</v>
       </c>
       <c r="D63" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E63" t="s">
         <v>54</v>
@@ -7701,7 +7698,7 @@
         <v>203</v>
       </c>
       <c r="D64" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E64" t="s">
         <v>67</v>
@@ -7778,7 +7775,7 @@
         <v>203</v>
       </c>
       <c r="D65" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E65" t="s">
         <v>79</v>
@@ -7855,7 +7852,7 @@
         <v>203</v>
       </c>
       <c r="D66" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E66" t="s">
         <v>90</v>
@@ -7932,7 +7929,7 @@
         <v>203</v>
       </c>
       <c r="D67" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E67" t="s">
         <v>102</v>
@@ -8009,7 +8006,7 @@
         <v>203</v>
       </c>
       <c r="D68" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -8086,7 +8083,7 @@
         <v>203</v>
       </c>
       <c r="D69" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E69" t="s">
         <v>126</v>
@@ -8163,7 +8160,7 @@
         <v>203</v>
       </c>
       <c r="D70" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E70" t="s">
         <v>137</v>
@@ -8240,7 +8237,7 @@
         <v>203</v>
       </c>
       <c r="D71" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E71" t="s">
         <v>147</v>
@@ -8317,7 +8314,7 @@
         <v>203</v>
       </c>
       <c r="D72" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E72" t="s">
         <v>157</v>
@@ -8394,7 +8391,7 @@
         <v>203</v>
       </c>
       <c r="D73" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E73" t="s">
         <v>168</v>
@@ -8471,7 +8468,7 @@
         <v>203</v>
       </c>
       <c r="D74" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E74" t="s">
         <v>180</v>
@@ -8548,7 +8545,7 @@
         <v>203</v>
       </c>
       <c r="D75" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E75" t="s">
         <v>191</v>
@@ -10014,7 +10011,7 @@
         <v>345</v>
       </c>
       <c r="E94" t="s">
-        <v>709</v>
+        <v>347</v>
       </c>
       <c r="F94" t="s">
         <v>656</v>
@@ -10023,16 +10020,16 @@
         <v>606</v>
       </c>
       <c r="H94" t="s">
+        <v>709</v>
+      </c>
+      <c r="I94" t="s">
         <v>710</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>711</v>
       </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>712</v>
-      </c>
-      <c r="K94" t="s">
-        <v>713</v>
       </c>
       <c r="L94" t="s">
         <v>186</v>
@@ -10047,7 +10044,7 @@
         <v>449</v>
       </c>
       <c r="P94" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="Q94" t="s">
         <v>512</v>
@@ -10094,28 +10091,28 @@
         <v>126</v>
       </c>
       <c r="F95" t="s">
+        <v>714</v>
+      </c>
+      <c r="G95" t="s">
         <v>715</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>716</v>
       </c>
-      <c r="H95" t="s">
+      <c r="I95" t="s">
         <v>717</v>
-      </c>
-      <c r="I95" t="s">
-        <v>718</v>
       </c>
       <c r="J95" t="s">
         <v>161</v>
       </c>
       <c r="K95" t="s">
+        <v>718</v>
+      </c>
+      <c r="L95" t="s">
         <v>719</v>
       </c>
-      <c r="L95" t="s">
+      <c r="M95" t="s">
         <v>720</v>
-      </c>
-      <c r="M95" t="s">
-        <v>721</v>
       </c>
       <c r="N95" t="s">
         <v>123</v>
@@ -10124,10 +10121,10 @@
         <v>66</v>
       </c>
       <c r="P95" t="s">
+        <v>721</v>
+      </c>
+      <c r="Q95" t="s">
         <v>722</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>723</v>
       </c>
       <c r="R95" t="s">
         <v>39</v>
@@ -10174,25 +10171,25 @@
         <v>656</v>
       </c>
       <c r="G96" t="s">
+        <v>723</v>
+      </c>
+      <c r="H96" t="s">
         <v>724</v>
       </c>
-      <c r="H96" t="s">
+      <c r="I96" t="s">
         <v>725</v>
       </c>
-      <c r="I96" t="s">
+      <c r="J96" t="s">
         <v>726</v>
       </c>
-      <c r="J96" t="s">
+      <c r="K96" t="s">
         <v>727</v>
-      </c>
-      <c r="K96" t="s">
-        <v>728</v>
       </c>
       <c r="L96" t="s">
         <v>571</v>
       </c>
       <c r="M96" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="N96" t="s">
         <v>488</v>
@@ -10201,7 +10198,7 @@
         <v>39</v>
       </c>
       <c r="P96" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="Q96" t="s">
         <v>528</v>
@@ -10248,25 +10245,25 @@
         <v>147</v>
       </c>
       <c r="F97" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G97" t="s">
+        <v>730</v>
+      </c>
+      <c r="H97" t="s">
         <v>731</v>
       </c>
-      <c r="H97" t="s">
+      <c r="I97" t="s">
         <v>732</v>
       </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>733</v>
       </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>734</v>
       </c>
-      <c r="K97" t="s">
+      <c r="L97" t="s">
         <v>735</v>
-      </c>
-      <c r="L97" t="s">
-        <v>736</v>
       </c>
       <c r="M97" t="s">
         <v>362</v>
@@ -10278,10 +10275,10 @@
         <v>41</v>
       </c>
       <c r="P97" t="s">
+        <v>736</v>
+      </c>
+      <c r="Q97" t="s">
         <v>737</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>738</v>
       </c>
       <c r="R97" t="s">
         <v>39</v>
@@ -10331,22 +10328,22 @@
         <v>581</v>
       </c>
       <c r="H98" t="s">
+        <v>738</v>
+      </c>
+      <c r="I98" t="s">
         <v>739</v>
       </c>
-      <c r="I98" t="s">
+      <c r="J98" t="s">
         <v>740</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>741</v>
-      </c>
-      <c r="K98" t="s">
-        <v>742</v>
       </c>
       <c r="L98" t="s">
         <v>385</v>
       </c>
       <c r="M98" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="N98" t="s">
         <v>495</v>
@@ -10355,7 +10352,7 @@
         <v>280</v>
       </c>
       <c r="P98" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Q98" t="s">
         <v>326</v>
@@ -10408,22 +10405,22 @@
         <v>198</v>
       </c>
       <c r="H99" t="s">
+        <v>744</v>
+      </c>
+      <c r="I99" t="s">
         <v>745</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>746</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>747</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" t="s">
         <v>748</v>
       </c>
-      <c r="L99" t="s">
+      <c r="M99" t="s">
         <v>749</v>
-      </c>
-      <c r="M99" t="s">
-        <v>750</v>
       </c>
       <c r="N99" t="s">
         <v>134</v>
@@ -10432,7 +10429,7 @@
         <v>280</v>
       </c>
       <c r="P99" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="Q99" t="s">
         <v>572</v>
@@ -10482,25 +10479,25 @@
         <v>665</v>
       </c>
       <c r="G100" t="s">
+        <v>751</v>
+      </c>
+      <c r="H100" t="s">
         <v>752</v>
       </c>
-      <c r="H100" t="s">
+      <c r="I100" t="s">
         <v>753</v>
       </c>
-      <c r="I100" t="s">
+      <c r="J100" t="s">
         <v>754</v>
       </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>755</v>
       </c>
-      <c r="K100" t="s">
+      <c r="L100" t="s">
         <v>756</v>
       </c>
-      <c r="L100" t="s">
+      <c r="M100" t="s">
         <v>757</v>
-      </c>
-      <c r="M100" t="s">
-        <v>758</v>
       </c>
       <c r="N100" t="s">
         <v>495</v>
@@ -10509,10 +10506,10 @@
         <v>40</v>
       </c>
       <c r="P100" t="s">
+        <v>758</v>
+      </c>
+      <c r="Q100" t="s">
         <v>759</v>
-      </c>
-      <c r="Q100" t="s">
-        <v>760</v>
       </c>
       <c r="R100" t="s">
         <v>488</v>
@@ -10562,22 +10559,22 @@
         <v>448</v>
       </c>
       <c r="H101" t="s">
+        <v>760</v>
+      </c>
+      <c r="I101" t="s">
         <v>761</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>762</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>763</v>
       </c>
-      <c r="K101" t="s">
+      <c r="L101" t="s">
         <v>764</v>
       </c>
-      <c r="L101" t="s">
+      <c r="M101" t="s">
         <v>765</v>
-      </c>
-      <c r="M101" t="s">
-        <v>766</v>
       </c>
       <c r="N101" t="s">
         <v>40</v>
@@ -10586,7 +10583,7 @@
         <v>201</v>
       </c>
       <c r="P101" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="Q101" t="s">
         <v>201</v>
@@ -10627,28 +10624,28 @@
         <v>203</v>
       </c>
       <c r="D102" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E102" t="s">
         <v>42</v>
       </c>
       <c r="F102" t="s">
+        <v>767</v>
+      </c>
+      <c r="G102" t="s">
         <v>768</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>769</v>
       </c>
-      <c r="H102" t="s">
+      <c r="I102" t="s">
         <v>770</v>
       </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
         <v>771</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>772</v>
-      </c>
-      <c r="K102" t="s">
-        <v>773</v>
       </c>
       <c r="L102" t="s">
         <v>278</v>
@@ -10663,10 +10660,10 @@
         <v>41</v>
       </c>
       <c r="P102" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q102" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="R102" t="s">
         <v>113</v>
@@ -10704,34 +10701,34 @@
         <v>203</v>
       </c>
       <c r="D103" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E103" t="s">
         <v>54</v>
       </c>
       <c r="F103" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G103" t="s">
+        <v>774</v>
+      </c>
+      <c r="H103" t="s">
         <v>775</v>
       </c>
-      <c r="H103" t="s">
+      <c r="I103" t="s">
         <v>776</v>
       </c>
-      <c r="I103" t="s">
+      <c r="J103" t="s">
         <v>777</v>
       </c>
-      <c r="J103" t="s">
+      <c r="K103" t="s">
         <v>778</v>
-      </c>
-      <c r="K103" t="s">
-        <v>779</v>
       </c>
       <c r="L103" t="s">
         <v>379</v>
       </c>
       <c r="M103" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="N103" t="s">
         <v>99</v>
@@ -10740,10 +10737,10 @@
         <v>41</v>
       </c>
       <c r="P103" t="s">
+        <v>780</v>
+      </c>
+      <c r="Q103" t="s">
         <v>781</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>782</v>
       </c>
       <c r="R103" t="s">
         <v>337</v>
@@ -10781,34 +10778,34 @@
         <v>203</v>
       </c>
       <c r="D104" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E104" t="s">
         <v>67</v>
       </c>
       <c r="F104" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G104" t="s">
+        <v>782</v>
+      </c>
+      <c r="H104" t="s">
         <v>783</v>
       </c>
-      <c r="H104" t="s">
+      <c r="I104" t="s">
         <v>784</v>
       </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>785</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>786</v>
       </c>
-      <c r="K104" t="s">
+      <c r="L104" t="s">
         <v>787</v>
       </c>
-      <c r="L104" t="s">
+      <c r="M104" t="s">
         <v>788</v>
-      </c>
-      <c r="M104" t="s">
-        <v>789</v>
       </c>
       <c r="N104" t="s">
         <v>555</v>
@@ -10817,7 +10814,7 @@
         <v>38</v>
       </c>
       <c r="P104" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="Q104" t="s">
         <v>606</v>
@@ -10858,34 +10855,34 @@
         <v>203</v>
       </c>
       <c r="D105" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E105" t="s">
         <v>79</v>
       </c>
       <c r="F105" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G105" t="s">
         <v>270</v>
       </c>
       <c r="H105" t="s">
+        <v>790</v>
+      </c>
+      <c r="I105" t="s">
         <v>791</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J105" t="s">
         <v>792</v>
       </c>
-      <c r="J105" t="s">
+      <c r="K105" t="s">
         <v>793</v>
       </c>
-      <c r="K105" t="s">
+      <c r="L105" t="s">
         <v>794</v>
       </c>
-      <c r="L105" t="s">
+      <c r="M105" t="s">
         <v>795</v>
-      </c>
-      <c r="M105" t="s">
-        <v>796</v>
       </c>
       <c r="N105" t="s">
         <v>99</v>
@@ -10894,7 +10891,7 @@
         <v>41</v>
       </c>
       <c r="P105" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q105" t="s">
         <v>433</v>
@@ -10935,34 +10932,34 @@
         <v>203</v>
       </c>
       <c r="D106" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E106" t="s">
         <v>90</v>
       </c>
       <c r="F106" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G106" t="s">
         <v>679</v>
       </c>
       <c r="H106" t="s">
+        <v>798</v>
+      </c>
+      <c r="I106" t="s">
         <v>799</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>800</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>801</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" t="s">
         <v>802</v>
       </c>
-      <c r="L106" t="s">
+      <c r="M106" t="s">
         <v>803</v>
-      </c>
-      <c r="M106" t="s">
-        <v>804</v>
       </c>
       <c r="N106" t="s">
         <v>337</v>
@@ -10971,7 +10968,7 @@
         <v>201</v>
       </c>
       <c r="P106" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q106" t="s">
         <v>471</v>
@@ -11012,34 +11009,34 @@
         <v>203</v>
       </c>
       <c r="D107" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E107" t="s">
         <v>102</v>
       </c>
       <c r="F107" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G107" t="s">
         <v>603</v>
       </c>
       <c r="H107" t="s">
+        <v>805</v>
+      </c>
+      <c r="I107" t="s">
         <v>806</v>
       </c>
-      <c r="I107" t="s">
+      <c r="J107" t="s">
         <v>807</v>
       </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>808</v>
-      </c>
-      <c r="K107" t="s">
-        <v>809</v>
       </c>
       <c r="L107" t="s">
         <v>706</v>
       </c>
       <c r="M107" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="N107" t="s">
         <v>35</v>
@@ -11048,10 +11045,10 @@
         <v>41</v>
       </c>
       <c r="P107" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q107" t="s">
         <v>811</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>812</v>
       </c>
       <c r="R107" t="s">
         <v>66</v>
@@ -11089,28 +11086,28 @@
         <v>203</v>
       </c>
       <c r="D108" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E108" t="s">
         <v>347</v>
       </c>
       <c r="F108" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G108" t="s">
         <v>153</v>
       </c>
       <c r="H108" t="s">
+        <v>812</v>
+      </c>
+      <c r="I108" t="s">
         <v>813</v>
       </c>
-      <c r="I108" t="s">
+      <c r="J108" t="s">
         <v>814</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>815</v>
-      </c>
-      <c r="K108" t="s">
-        <v>816</v>
       </c>
       <c r="L108" t="s">
         <v>654</v>
@@ -11125,7 +11122,7 @@
         <v>38</v>
       </c>
       <c r="P108" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="Q108" t="s">
         <v>344</v>
@@ -11166,31 +11163,31 @@
         <v>203</v>
       </c>
       <c r="D109" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E109" t="s">
         <v>126</v>
       </c>
       <c r="F109" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G109" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H109" t="s">
+        <v>817</v>
+      </c>
+      <c r="I109" t="s">
         <v>818</v>
       </c>
-      <c r="I109" t="s">
+      <c r="J109" t="s">
         <v>819</v>
       </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>820</v>
       </c>
-      <c r="K109" t="s">
+      <c r="L109" t="s">
         <v>821</v>
-      </c>
-      <c r="L109" t="s">
-        <v>822</v>
       </c>
       <c r="M109" t="s">
         <v>549</v>
@@ -11202,7 +11199,7 @@
         <v>113</v>
       </c>
       <c r="P109" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="Q109" t="s">
         <v>674</v>
@@ -11243,31 +11240,31 @@
         <v>203</v>
       </c>
       <c r="D110" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E110" t="s">
         <v>137</v>
       </c>
       <c r="F110" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G110" t="s">
+        <v>823</v>
+      </c>
+      <c r="H110" t="s">
         <v>824</v>
       </c>
-      <c r="H110" t="s">
+      <c r="I110" t="s">
         <v>825</v>
       </c>
-      <c r="I110" t="s">
+      <c r="J110" t="s">
         <v>826</v>
       </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
         <v>827</v>
       </c>
-      <c r="K110" t="s">
+      <c r="L110" t="s">
         <v>828</v>
-      </c>
-      <c r="L110" t="s">
-        <v>829</v>
       </c>
       <c r="M110" t="s">
         <v>264</v>
@@ -11279,7 +11276,7 @@
         <v>201</v>
       </c>
       <c r="P110" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="Q110" t="s">
         <v>471</v>
@@ -11320,34 +11317,34 @@
         <v>203</v>
       </c>
       <c r="D111" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E111" t="s">
         <v>157</v>
       </c>
       <c r="F111" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G111" t="s">
         <v>662</v>
       </c>
       <c r="H111" t="s">
+        <v>830</v>
+      </c>
+      <c r="I111" t="s">
         <v>831</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>832</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>833</v>
       </c>
-      <c r="K111" t="s">
+      <c r="L111" t="s">
         <v>834</v>
       </c>
-      <c r="L111" t="s">
-        <v>835</v>
-      </c>
       <c r="M111" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="N111" t="s">
         <v>471</v>
@@ -11356,10 +11353,10 @@
         <v>337</v>
       </c>
       <c r="P111" t="s">
+        <v>835</v>
+      </c>
+      <c r="Q111" t="s">
         <v>836</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>837</v>
       </c>
       <c r="R111" t="s">
         <v>337</v>
@@ -11397,31 +11394,31 @@
         <v>203</v>
       </c>
       <c r="D112" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E112" t="s">
         <v>180</v>
       </c>
       <c r="F112" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G112" t="s">
         <v>541</v>
       </c>
       <c r="H112" t="s">
+        <v>837</v>
+      </c>
+      <c r="I112" t="s">
         <v>838</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>839</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>840</v>
       </c>
-      <c r="K112" t="s">
+      <c r="L112" t="s">
         <v>841</v>
-      </c>
-      <c r="L112" t="s">
-        <v>842</v>
       </c>
       <c r="M112" t="s">
         <v>461</v>
@@ -11474,31 +11471,31 @@
         <v>203</v>
       </c>
       <c r="D113" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E113" t="s">
         <v>191</v>
       </c>
       <c r="F113" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G113" t="s">
+        <v>842</v>
+      </c>
+      <c r="H113" t="s">
         <v>843</v>
       </c>
-      <c r="H113" t="s">
+      <c r="I113" t="s">
         <v>844</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>845</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>846</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" t="s">
         <v>847</v>
-      </c>
-      <c r="L113" t="s">
-        <v>848</v>
       </c>
       <c r="M113" t="s">
         <v>506</v>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E39235-0546-E74D-81F2-989A5F8F570F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3DE3CE-34B5-7645-88AE-88A608188EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="1028">
   <si>
     <t>Type</t>
   </si>
@@ -2586,6 +2586,540 @@
   </si>
   <si>
     <t>J-1</t>
+  </si>
+  <si>
+    <t>74.33</t>
+  </si>
+  <si>
+    <t>8.26</t>
+  </si>
+  <si>
+    <t>897.35</t>
+  </si>
+  <si>
+    <t>363.34</t>
+  </si>
+  <si>
+    <t>31.44</t>
+  </si>
+  <si>
+    <t>111.08</t>
+  </si>
+  <si>
+    <t>8.96</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>109.0</t>
+  </si>
+  <si>
+    <t>29.6</t>
+  </si>
+  <si>
+    <t>88.62</t>
+  </si>
+  <si>
+    <t>9.32</t>
+  </si>
+  <si>
+    <t>733.71</t>
+  </si>
+  <si>
+    <t>433.78</t>
+  </si>
+  <si>
+    <t>32.1</t>
+  </si>
+  <si>
+    <t>105.13</t>
+  </si>
+  <si>
+    <t>6.32</t>
+  </si>
+  <si>
+    <t>6.89</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>87.9</t>
+  </si>
+  <si>
+    <t>99.63</t>
+  </si>
+  <si>
+    <t>10.35</t>
+  </si>
+  <si>
+    <t>1137.9</t>
+  </si>
+  <si>
+    <t>429.16</t>
+  </si>
+  <si>
+    <t>31.6</t>
+  </si>
+  <si>
+    <t>103.88</t>
+  </si>
+  <si>
+    <t>6.64</t>
+  </si>
+  <si>
+    <t>115.4</t>
+  </si>
+  <si>
+    <t>56.1</t>
+  </si>
+  <si>
+    <t>10.38</t>
+  </si>
+  <si>
+    <t>1.44</t>
+  </si>
+  <si>
+    <t>165.23</t>
+  </si>
+  <si>
+    <t>29.7</t>
+  </si>
+  <si>
+    <t>138.24</t>
+  </si>
+  <si>
+    <t>7.83</t>
+  </si>
+  <si>
+    <t>22.0</t>
+  </si>
+  <si>
+    <t>87.92</t>
+  </si>
+  <si>
+    <t>10.47</t>
+  </si>
+  <si>
+    <t>798.69</t>
+  </si>
+  <si>
+    <t>414.5</t>
+  </si>
+  <si>
+    <t>119.04</t>
+  </si>
+  <si>
+    <t>5.76</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>110.9</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>Levy Ndoutoume</t>
+  </si>
+  <si>
+    <t>9.64</t>
+  </si>
+  <si>
+    <t>632.5</t>
+  </si>
+  <si>
+    <t>454.18</t>
+  </si>
+  <si>
+    <t>31.22</t>
+  </si>
+  <si>
+    <t>96.73</t>
+  </si>
+  <si>
+    <t>6.88</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>77.2</t>
+  </si>
+  <si>
+    <t>21.7</t>
+  </si>
+  <si>
+    <t>10.57</t>
+  </si>
+  <si>
+    <t>852.19</t>
+  </si>
+  <si>
+    <t>451.5</t>
+  </si>
+  <si>
+    <t>31.66</t>
+  </si>
+  <si>
+    <t>106.12</t>
+  </si>
+  <si>
+    <t>9.33</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>11.23</t>
+  </si>
+  <si>
+    <t>572.09</t>
+  </si>
+  <si>
+    <t>526.8</t>
+  </si>
+  <si>
+    <t>29.26</t>
+  </si>
+  <si>
+    <t>112.74</t>
+  </si>
+  <si>
+    <t>9.11</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>83.9</t>
+  </si>
+  <si>
+    <t>9.67</t>
+  </si>
+  <si>
+    <t>333.3</t>
+  </si>
+  <si>
+    <t>417.14</t>
+  </si>
+  <si>
+    <t>33.18</t>
+  </si>
+  <si>
+    <t>97.01</t>
+  </si>
+  <si>
+    <t>5.52</t>
+  </si>
+  <si>
+    <t>42.4</t>
+  </si>
+  <si>
+    <t>10.0</t>
+  </si>
+  <si>
+    <t>23.27</t>
+  </si>
+  <si>
+    <t>14.36</t>
+  </si>
+  <si>
+    <t>4.19</t>
+  </si>
+  <si>
+    <t>3.24</t>
+  </si>
+  <si>
+    <t>Sofiane Belkheir</t>
+  </si>
+  <si>
+    <t>11.53</t>
+  </si>
+  <si>
+    <t>1.31</t>
+  </si>
+  <si>
+    <t>154.07</t>
+  </si>
+  <si>
+    <t>60.0</t>
+  </si>
+  <si>
+    <t>31.7</t>
+  </si>
+  <si>
+    <t>113.74</t>
+  </si>
+  <si>
+    <t>6.92</t>
+  </si>
+  <si>
+    <t>16.5</t>
+  </si>
+  <si>
+    <t>79.57</t>
+  </si>
+  <si>
+    <t>8.89</t>
+  </si>
+  <si>
+    <t>767.7</t>
+  </si>
+  <si>
+    <t>358.13</t>
+  </si>
+  <si>
+    <t>30.82</t>
+  </si>
+  <si>
+    <t>111.69</t>
+  </si>
+  <si>
+    <t>8.16</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>96.1</t>
+  </si>
+  <si>
+    <t>9.53</t>
+  </si>
+  <si>
+    <t>404.55</t>
+  </si>
+  <si>
+    <t>394.87</t>
+  </si>
+  <si>
+    <t>95.7</t>
+  </si>
+  <si>
+    <t>6.11</t>
+  </si>
+  <si>
+    <t>54.8</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
+    <t>N1 J5 VS Toulon 19/09/2026</t>
+  </si>
+  <si>
+    <t>93.82</t>
+  </si>
+  <si>
+    <t>5.98</t>
+  </si>
+  <si>
+    <t>75.34</t>
+  </si>
+  <si>
+    <t>298.56</t>
+  </si>
+  <si>
+    <t>24.78</t>
+  </si>
+  <si>
+    <t>63.71</t>
+  </si>
+  <si>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>93.83</t>
+  </si>
+  <si>
+    <t>1.87</t>
+  </si>
+  <si>
+    <t>106.99</t>
+  </si>
+  <si>
+    <t>16.1</t>
+  </si>
+  <si>
+    <t>19.93</t>
+  </si>
+  <si>
+    <t>88.92</t>
+  </si>
+  <si>
+    <t>277.97</t>
+  </si>
+  <si>
+    <t>26.96</t>
+  </si>
+  <si>
+    <t>53.79</t>
+  </si>
+  <si>
+    <t>6.07</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>12.73</t>
+  </si>
+  <si>
+    <t>275.78</t>
+  </si>
+  <si>
+    <t>22.02</t>
+  </si>
+  <si>
+    <t>57.76</t>
+  </si>
+  <si>
+    <t>5.11</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>256.84</t>
+  </si>
+  <si>
+    <t>345.63</t>
+  </si>
+  <si>
+    <t>68.05</t>
+  </si>
+  <si>
+    <t>7.38</t>
+  </si>
+  <si>
+    <t>43.7</t>
+  </si>
+  <si>
+    <t>5.66</t>
+  </si>
+  <si>
+    <t>39.05</t>
+  </si>
+  <si>
+    <t>298.51</t>
+  </si>
+  <si>
+    <t>22.7</t>
+  </si>
+  <si>
+    <t>60.28</t>
+  </si>
+  <si>
+    <t>8.27</t>
+  </si>
+  <si>
+    <t>322.94</t>
+  </si>
+  <si>
+    <t>580.47</t>
+  </si>
+  <si>
+    <t>25.05</t>
+  </si>
+  <si>
+    <t>55.16</t>
+  </si>
+  <si>
+    <t>7.49</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>52.5</t>
+  </si>
+  <si>
+    <t>223.95</t>
+  </si>
+  <si>
+    <t>295.4</t>
+  </si>
+  <si>
+    <t>22.13</t>
+  </si>
+  <si>
+    <t>55.09</t>
+  </si>
+  <si>
+    <t>4.99</t>
+  </si>
+  <si>
+    <t>4.41</t>
+  </si>
+  <si>
+    <t>39.1</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>45.5</t>
+  </si>
+  <si>
+    <t>281.27</t>
+  </si>
+  <si>
+    <t>24.4</t>
+  </si>
+  <si>
+    <t>59.68</t>
+  </si>
+  <si>
+    <t>7.11</t>
+  </si>
+  <si>
+    <t>455.16</t>
+  </si>
+  <si>
+    <t>348.36</t>
+  </si>
+  <si>
+    <t>26.18</t>
+  </si>
+  <si>
+    <t>75.83</t>
+  </si>
+  <si>
+    <t>76.4</t>
+  </si>
+  <si>
+    <t>3.35</t>
+  </si>
+  <si>
+    <t>4.06</t>
+  </si>
+  <si>
+    <t>164.26</t>
+  </si>
+  <si>
+    <t>20.72</t>
+  </si>
+  <si>
+    <t>35.67</t>
+  </si>
+  <si>
+    <t>3.39</t>
+  </si>
+  <si>
+    <t>4.83</t>
+  </si>
+  <si>
+    <t>J+2</t>
   </si>
 </sst>
 </file>
@@ -2964,7 +3498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y113"/>
+  <dimension ref="A1:Y138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
@@ -11537,6 +12071,1931 @@
         <v>3</v>
       </c>
     </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>958</v>
+      </c>
+      <c r="B114" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C114" t="s">
+        <v>203</v>
+      </c>
+      <c r="D114" t="s">
+        <v>348</v>
+      </c>
+      <c r="E114" t="s">
+        <v>42</v>
+      </c>
+      <c r="F114" t="s">
+        <v>850</v>
+      </c>
+      <c r="G114" t="s">
+        <v>851</v>
+      </c>
+      <c r="H114" t="s">
+        <v>852</v>
+      </c>
+      <c r="I114" t="s">
+        <v>853</v>
+      </c>
+      <c r="J114" t="s">
+        <v>854</v>
+      </c>
+      <c r="K114" t="s">
+        <v>855</v>
+      </c>
+      <c r="L114" t="s">
+        <v>856</v>
+      </c>
+      <c r="M114" t="s">
+        <v>289</v>
+      </c>
+      <c r="N114" t="s">
+        <v>857</v>
+      </c>
+      <c r="O114" t="s">
+        <v>63</v>
+      </c>
+      <c r="P114" t="s">
+        <v>858</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>859</v>
+      </c>
+      <c r="R114" t="s">
+        <v>337</v>
+      </c>
+      <c r="S114" t="s">
+        <v>113</v>
+      </c>
+      <c r="T114" t="s">
+        <v>66</v>
+      </c>
+      <c r="U114" t="s">
+        <v>41</v>
+      </c>
+      <c r="V114">
+        <v>51</v>
+      </c>
+      <c r="W114">
+        <v>29</v>
+      </c>
+      <c r="X114">
+        <v>40</v>
+      </c>
+      <c r="Y114">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>958</v>
+      </c>
+      <c r="B115" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C115" t="s">
+        <v>203</v>
+      </c>
+      <c r="D115" t="s">
+        <v>348</v>
+      </c>
+      <c r="E115" t="s">
+        <v>54</v>
+      </c>
+      <c r="F115" t="s">
+        <v>860</v>
+      </c>
+      <c r="G115" t="s">
+        <v>861</v>
+      </c>
+      <c r="H115" t="s">
+        <v>862</v>
+      </c>
+      <c r="I115" t="s">
+        <v>863</v>
+      </c>
+      <c r="J115" t="s">
+        <v>864</v>
+      </c>
+      <c r="K115" t="s">
+        <v>865</v>
+      </c>
+      <c r="L115" t="s">
+        <v>866</v>
+      </c>
+      <c r="M115" t="s">
+        <v>867</v>
+      </c>
+      <c r="N115" t="s">
+        <v>868</v>
+      </c>
+      <c r="O115" t="s">
+        <v>471</v>
+      </c>
+      <c r="P115" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>479</v>
+      </c>
+      <c r="R115" t="s">
+        <v>488</v>
+      </c>
+      <c r="S115" t="s">
+        <v>40</v>
+      </c>
+      <c r="T115" t="s">
+        <v>113</v>
+      </c>
+      <c r="U115" t="s">
+        <v>39</v>
+      </c>
+      <c r="V115">
+        <v>69</v>
+      </c>
+      <c r="W115">
+        <v>30</v>
+      </c>
+      <c r="X115">
+        <v>69</v>
+      </c>
+      <c r="Y115">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>958</v>
+      </c>
+      <c r="B116" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C116" t="s">
+        <v>203</v>
+      </c>
+      <c r="D116" t="s">
+        <v>348</v>
+      </c>
+      <c r="E116" t="s">
+        <v>67</v>
+      </c>
+      <c r="F116" t="s">
+        <v>870</v>
+      </c>
+      <c r="G116" t="s">
+        <v>871</v>
+      </c>
+      <c r="H116" t="s">
+        <v>872</v>
+      </c>
+      <c r="I116" t="s">
+        <v>873</v>
+      </c>
+      <c r="J116" t="s">
+        <v>874</v>
+      </c>
+      <c r="K116" t="s">
+        <v>875</v>
+      </c>
+      <c r="L116" t="s">
+        <v>876</v>
+      </c>
+      <c r="M116" t="s">
+        <v>132</v>
+      </c>
+      <c r="N116" t="s">
+        <v>176</v>
+      </c>
+      <c r="O116" t="s">
+        <v>324</v>
+      </c>
+      <c r="P116" t="s">
+        <v>877</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>878</v>
+      </c>
+      <c r="R116" t="s">
+        <v>449</v>
+      </c>
+      <c r="S116" t="s">
+        <v>40</v>
+      </c>
+      <c r="T116" t="s">
+        <v>337</v>
+      </c>
+      <c r="U116" t="s">
+        <v>39</v>
+      </c>
+      <c r="V116">
+        <v>77</v>
+      </c>
+      <c r="W116">
+        <v>33</v>
+      </c>
+      <c r="X116">
+        <v>48</v>
+      </c>
+      <c r="Y116">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>958</v>
+      </c>
+      <c r="B117" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C117" t="s">
+        <v>203</v>
+      </c>
+      <c r="D117" t="s">
+        <v>348</v>
+      </c>
+      <c r="E117" t="s">
+        <v>90</v>
+      </c>
+      <c r="F117" t="s">
+        <v>879</v>
+      </c>
+      <c r="G117" t="s">
+        <v>880</v>
+      </c>
+      <c r="H117" t="s">
+        <v>881</v>
+      </c>
+      <c r="I117" t="s">
+        <v>827</v>
+      </c>
+      <c r="J117" t="s">
+        <v>882</v>
+      </c>
+      <c r="K117" t="s">
+        <v>883</v>
+      </c>
+      <c r="L117" t="s">
+        <v>884</v>
+      </c>
+      <c r="M117" t="s">
+        <v>497</v>
+      </c>
+      <c r="N117" t="s">
+        <v>51</v>
+      </c>
+      <c r="O117" t="s">
+        <v>38</v>
+      </c>
+      <c r="P117" t="s">
+        <v>885</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>344</v>
+      </c>
+      <c r="R117" t="s">
+        <v>41</v>
+      </c>
+      <c r="S117" t="s">
+        <v>41</v>
+      </c>
+      <c r="T117" t="s">
+        <v>41</v>
+      </c>
+      <c r="U117" t="s">
+        <v>201</v>
+      </c>
+      <c r="V117">
+        <v>9</v>
+      </c>
+      <c r="W117">
+        <v>6</v>
+      </c>
+      <c r="X117">
+        <v>2</v>
+      </c>
+      <c r="Y117">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>958</v>
+      </c>
+      <c r="B118" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C118" t="s">
+        <v>203</v>
+      </c>
+      <c r="D118" t="s">
+        <v>348</v>
+      </c>
+      <c r="E118" t="s">
+        <v>102</v>
+      </c>
+      <c r="F118" t="s">
+        <v>886</v>
+      </c>
+      <c r="G118" t="s">
+        <v>887</v>
+      </c>
+      <c r="H118" t="s">
+        <v>888</v>
+      </c>
+      <c r="I118" t="s">
+        <v>889</v>
+      </c>
+      <c r="J118" t="s">
+        <v>882</v>
+      </c>
+      <c r="K118" t="s">
+        <v>890</v>
+      </c>
+      <c r="L118" t="s">
+        <v>502</v>
+      </c>
+      <c r="M118" t="s">
+        <v>891</v>
+      </c>
+      <c r="N118" t="s">
+        <v>892</v>
+      </c>
+      <c r="O118" t="s">
+        <v>51</v>
+      </c>
+      <c r="P118" t="s">
+        <v>893</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>894</v>
+      </c>
+      <c r="R118" t="s">
+        <v>280</v>
+      </c>
+      <c r="S118" t="s">
+        <v>38</v>
+      </c>
+      <c r="T118" t="s">
+        <v>113</v>
+      </c>
+      <c r="U118" t="s">
+        <v>41</v>
+      </c>
+      <c r="V118">
+        <v>75</v>
+      </c>
+      <c r="W118">
+        <v>25</v>
+      </c>
+      <c r="X118">
+        <v>59</v>
+      </c>
+      <c r="Y118">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>958</v>
+      </c>
+      <c r="B119" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C119" t="s">
+        <v>203</v>
+      </c>
+      <c r="D119" t="s">
+        <v>348</v>
+      </c>
+      <c r="E119" t="s">
+        <v>895</v>
+      </c>
+      <c r="F119" t="s">
+        <v>870</v>
+      </c>
+      <c r="G119" t="s">
+        <v>896</v>
+      </c>
+      <c r="H119" t="s">
+        <v>897</v>
+      </c>
+      <c r="I119" t="s">
+        <v>898</v>
+      </c>
+      <c r="J119" t="s">
+        <v>899</v>
+      </c>
+      <c r="K119" t="s">
+        <v>900</v>
+      </c>
+      <c r="L119" t="s">
+        <v>901</v>
+      </c>
+      <c r="M119" t="s">
+        <v>788</v>
+      </c>
+      <c r="N119" t="s">
+        <v>902</v>
+      </c>
+      <c r="O119" t="s">
+        <v>76</v>
+      </c>
+      <c r="P119" t="s">
+        <v>903</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>904</v>
+      </c>
+      <c r="R119" t="s">
+        <v>488</v>
+      </c>
+      <c r="S119" t="s">
+        <v>66</v>
+      </c>
+      <c r="T119" t="s">
+        <v>35</v>
+      </c>
+      <c r="U119" t="s">
+        <v>39</v>
+      </c>
+      <c r="V119">
+        <v>60</v>
+      </c>
+      <c r="W119">
+        <v>32</v>
+      </c>
+      <c r="X119">
+        <v>50</v>
+      </c>
+      <c r="Y119">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>958</v>
+      </c>
+      <c r="B120" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C120" t="s">
+        <v>203</v>
+      </c>
+      <c r="D120" t="s">
+        <v>348</v>
+      </c>
+      <c r="E120" t="s">
+        <v>126</v>
+      </c>
+      <c r="F120" t="s">
+        <v>870</v>
+      </c>
+      <c r="G120" t="s">
+        <v>905</v>
+      </c>
+      <c r="H120" t="s">
+        <v>906</v>
+      </c>
+      <c r="I120" t="s">
+        <v>907</v>
+      </c>
+      <c r="J120" t="s">
+        <v>908</v>
+      </c>
+      <c r="K120" t="s">
+        <v>909</v>
+      </c>
+      <c r="L120" t="s">
+        <v>910</v>
+      </c>
+      <c r="M120" t="s">
+        <v>612</v>
+      </c>
+      <c r="N120" t="s">
+        <v>911</v>
+      </c>
+      <c r="O120" t="s">
+        <v>912</v>
+      </c>
+      <c r="P120" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>281</v>
+      </c>
+      <c r="R120" t="s">
+        <v>35</v>
+      </c>
+      <c r="S120" t="s">
+        <v>40</v>
+      </c>
+      <c r="T120" t="s">
+        <v>66</v>
+      </c>
+      <c r="U120" t="s">
+        <v>41</v>
+      </c>
+      <c r="V120">
+        <v>46</v>
+      </c>
+      <c r="W120">
+        <v>22</v>
+      </c>
+      <c r="X120">
+        <v>42</v>
+      </c>
+      <c r="Y120">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>958</v>
+      </c>
+      <c r="B121" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C121" t="s">
+        <v>203</v>
+      </c>
+      <c r="D121" t="s">
+        <v>348</v>
+      </c>
+      <c r="E121" t="s">
+        <v>346</v>
+      </c>
+      <c r="F121" t="s">
+        <v>870</v>
+      </c>
+      <c r="G121" t="s">
+        <v>201</v>
+      </c>
+      <c r="H121" t="s">
+        <v>201</v>
+      </c>
+      <c r="I121" t="s">
+        <v>41</v>
+      </c>
+      <c r="J121" t="s">
+        <v>201</v>
+      </c>
+      <c r="K121" t="s">
+        <v>201</v>
+      </c>
+      <c r="L121" t="s">
+        <v>201</v>
+      </c>
+      <c r="M121" t="s">
+        <v>201</v>
+      </c>
+      <c r="N121" t="s">
+        <v>201</v>
+      </c>
+      <c r="O121" t="s">
+        <v>201</v>
+      </c>
+      <c r="P121" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>201</v>
+      </c>
+      <c r="R121" t="s">
+        <v>201</v>
+      </c>
+      <c r="S121" t="s">
+        <v>201</v>
+      </c>
+      <c r="T121" t="s">
+        <v>201</v>
+      </c>
+      <c r="U121" t="s">
+        <v>201</v>
+      </c>
+      <c r="V121">
+        <v>0</v>
+      </c>
+      <c r="W121">
+        <v>0</v>
+      </c>
+      <c r="X121">
+        <v>0</v>
+      </c>
+      <c r="Y121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>958</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C122" t="s">
+        <v>203</v>
+      </c>
+      <c r="D122" t="s">
+        <v>348</v>
+      </c>
+      <c r="E122" t="s">
+        <v>137</v>
+      </c>
+      <c r="F122" t="s">
+        <v>870</v>
+      </c>
+      <c r="G122" t="s">
+        <v>913</v>
+      </c>
+      <c r="H122" t="s">
+        <v>914</v>
+      </c>
+      <c r="I122" t="s">
+        <v>915</v>
+      </c>
+      <c r="J122" t="s">
+        <v>916</v>
+      </c>
+      <c r="K122" t="s">
+        <v>917</v>
+      </c>
+      <c r="L122" t="s">
+        <v>918</v>
+      </c>
+      <c r="M122" t="s">
+        <v>133</v>
+      </c>
+      <c r="N122" t="s">
+        <v>919</v>
+      </c>
+      <c r="O122" t="s">
+        <v>35</v>
+      </c>
+      <c r="P122" t="s">
+        <v>920</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>37</v>
+      </c>
+      <c r="R122" t="s">
+        <v>337</v>
+      </c>
+      <c r="S122" t="s">
+        <v>40</v>
+      </c>
+      <c r="T122" t="s">
+        <v>113</v>
+      </c>
+      <c r="U122" t="s">
+        <v>41</v>
+      </c>
+      <c r="V122">
+        <v>73</v>
+      </c>
+      <c r="W122">
+        <v>27</v>
+      </c>
+      <c r="X122">
+        <v>65</v>
+      </c>
+      <c r="Y122">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>958</v>
+      </c>
+      <c r="B123" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C123" t="s">
+        <v>203</v>
+      </c>
+      <c r="D123" t="s">
+        <v>348</v>
+      </c>
+      <c r="E123" t="s">
+        <v>147</v>
+      </c>
+      <c r="F123" t="s">
+        <v>870</v>
+      </c>
+      <c r="G123" t="s">
+        <v>921</v>
+      </c>
+      <c r="H123" t="s">
+        <v>922</v>
+      </c>
+      <c r="I123" t="s">
+        <v>923</v>
+      </c>
+      <c r="J123" t="s">
+        <v>924</v>
+      </c>
+      <c r="K123" t="s">
+        <v>925</v>
+      </c>
+      <c r="L123" t="s">
+        <v>679</v>
+      </c>
+      <c r="M123" t="s">
+        <v>926</v>
+      </c>
+      <c r="N123" t="s">
+        <v>307</v>
+      </c>
+      <c r="O123" t="s">
+        <v>337</v>
+      </c>
+      <c r="P123" t="s">
+        <v>927</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>928</v>
+      </c>
+      <c r="R123" t="s">
+        <v>40</v>
+      </c>
+      <c r="S123" t="s">
+        <v>38</v>
+      </c>
+      <c r="T123" t="s">
+        <v>40</v>
+      </c>
+      <c r="U123" t="s">
+        <v>41</v>
+      </c>
+      <c r="V123">
+        <v>54</v>
+      </c>
+      <c r="W123">
+        <v>14</v>
+      </c>
+      <c r="X123">
+        <v>27</v>
+      </c>
+      <c r="Y123">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>958</v>
+      </c>
+      <c r="B124" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C124" t="s">
+        <v>203</v>
+      </c>
+      <c r="D124" t="s">
+        <v>348</v>
+      </c>
+      <c r="E124" t="s">
+        <v>157</v>
+      </c>
+      <c r="F124" t="s">
+        <v>870</v>
+      </c>
+      <c r="G124" t="s">
+        <v>377</v>
+      </c>
+      <c r="H124" t="s">
+        <v>201</v>
+      </c>
+      <c r="I124" t="s">
+        <v>929</v>
+      </c>
+      <c r="J124" t="s">
+        <v>930</v>
+      </c>
+      <c r="K124" t="s">
+        <v>931</v>
+      </c>
+      <c r="L124" t="s">
+        <v>201</v>
+      </c>
+      <c r="M124" t="s">
+        <v>932</v>
+      </c>
+      <c r="N124" t="s">
+        <v>201</v>
+      </c>
+      <c r="O124" t="s">
+        <v>201</v>
+      </c>
+      <c r="P124" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>201</v>
+      </c>
+      <c r="R124" t="s">
+        <v>201</v>
+      </c>
+      <c r="S124" t="s">
+        <v>201</v>
+      </c>
+      <c r="T124" t="s">
+        <v>201</v>
+      </c>
+      <c r="U124" t="s">
+        <v>201</v>
+      </c>
+      <c r="V124">
+        <v>1</v>
+      </c>
+      <c r="W124">
+        <v>0</v>
+      </c>
+      <c r="X124">
+        <v>0</v>
+      </c>
+      <c r="Y124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>958</v>
+      </c>
+      <c r="B125" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C125" t="s">
+        <v>203</v>
+      </c>
+      <c r="D125" t="s">
+        <v>348</v>
+      </c>
+      <c r="E125" t="s">
+        <v>933</v>
+      </c>
+      <c r="F125" t="s">
+        <v>934</v>
+      </c>
+      <c r="G125" t="s">
+        <v>935</v>
+      </c>
+      <c r="H125" t="s">
+        <v>936</v>
+      </c>
+      <c r="I125" t="s">
+        <v>937</v>
+      </c>
+      <c r="J125" t="s">
+        <v>938</v>
+      </c>
+      <c r="K125" t="s">
+        <v>939</v>
+      </c>
+      <c r="L125" t="s">
+        <v>940</v>
+      </c>
+      <c r="M125" t="s">
+        <v>264</v>
+      </c>
+      <c r="N125" t="s">
+        <v>488</v>
+      </c>
+      <c r="O125" t="s">
+        <v>66</v>
+      </c>
+      <c r="P125" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>365</v>
+      </c>
+      <c r="R125" t="s">
+        <v>39</v>
+      </c>
+      <c r="S125" t="s">
+        <v>41</v>
+      </c>
+      <c r="T125" t="s">
+        <v>41</v>
+      </c>
+      <c r="U125" t="s">
+        <v>201</v>
+      </c>
+      <c r="V125">
+        <v>11</v>
+      </c>
+      <c r="W125">
+        <v>3</v>
+      </c>
+      <c r="X125">
+        <v>11</v>
+      </c>
+      <c r="Y125">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>958</v>
+      </c>
+      <c r="B126" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C126" t="s">
+        <v>203</v>
+      </c>
+      <c r="D126" t="s">
+        <v>348</v>
+      </c>
+      <c r="E126" t="s">
+        <v>180</v>
+      </c>
+      <c r="F126" t="s">
+        <v>942</v>
+      </c>
+      <c r="G126" t="s">
+        <v>943</v>
+      </c>
+      <c r="H126" t="s">
+        <v>944</v>
+      </c>
+      <c r="I126" t="s">
+        <v>945</v>
+      </c>
+      <c r="J126" t="s">
+        <v>946</v>
+      </c>
+      <c r="K126" t="s">
+        <v>947</v>
+      </c>
+      <c r="L126" t="s">
+        <v>948</v>
+      </c>
+      <c r="M126" t="s">
+        <v>133</v>
+      </c>
+      <c r="N126" t="s">
+        <v>949</v>
+      </c>
+      <c r="O126" t="s">
+        <v>99</v>
+      </c>
+      <c r="P126" t="s">
+        <v>950</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>496</v>
+      </c>
+      <c r="R126" t="s">
+        <v>337</v>
+      </c>
+      <c r="S126" t="s">
+        <v>40</v>
+      </c>
+      <c r="T126" t="s">
+        <v>66</v>
+      </c>
+      <c r="U126" t="s">
+        <v>41</v>
+      </c>
+      <c r="V126">
+        <v>62</v>
+      </c>
+      <c r="W126">
+        <v>21</v>
+      </c>
+      <c r="X126">
+        <v>53</v>
+      </c>
+      <c r="Y126">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>958</v>
+      </c>
+      <c r="B127" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C127" t="s">
+        <v>203</v>
+      </c>
+      <c r="D127" t="s">
+        <v>348</v>
+      </c>
+      <c r="E127" t="s">
+        <v>191</v>
+      </c>
+      <c r="F127" t="s">
+        <v>870</v>
+      </c>
+      <c r="G127" t="s">
+        <v>951</v>
+      </c>
+      <c r="H127" t="s">
+        <v>952</v>
+      </c>
+      <c r="I127" t="s">
+        <v>953</v>
+      </c>
+      <c r="J127" t="s">
+        <v>835</v>
+      </c>
+      <c r="K127" t="s">
+        <v>954</v>
+      </c>
+      <c r="L127" t="s">
+        <v>955</v>
+      </c>
+      <c r="M127" t="s">
+        <v>694</v>
+      </c>
+      <c r="N127" t="s">
+        <v>579</v>
+      </c>
+      <c r="O127" t="s">
+        <v>35</v>
+      </c>
+      <c r="P127" t="s">
+        <v>956</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>957</v>
+      </c>
+      <c r="R127" t="s">
+        <v>66</v>
+      </c>
+      <c r="S127" t="s">
+        <v>41</v>
+      </c>
+      <c r="T127" t="s">
+        <v>40</v>
+      </c>
+      <c r="U127" t="s">
+        <v>41</v>
+      </c>
+      <c r="V127">
+        <v>34</v>
+      </c>
+      <c r="W127">
+        <v>23</v>
+      </c>
+      <c r="X127">
+        <v>33</v>
+      </c>
+      <c r="Y127">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>202</v>
+      </c>
+      <c r="B128" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C128" t="s">
+        <v>203</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E128" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" t="s">
+        <v>959</v>
+      </c>
+      <c r="G128" t="s">
+        <v>960</v>
+      </c>
+      <c r="H128" t="s">
+        <v>961</v>
+      </c>
+      <c r="I128" t="s">
+        <v>962</v>
+      </c>
+      <c r="J128" t="s">
+        <v>963</v>
+      </c>
+      <c r="K128" t="s">
+        <v>964</v>
+      </c>
+      <c r="L128" t="s">
+        <v>73</v>
+      </c>
+      <c r="M128" t="s">
+        <v>392</v>
+      </c>
+      <c r="N128" t="s">
+        <v>35</v>
+      </c>
+      <c r="O128" t="s">
+        <v>201</v>
+      </c>
+      <c r="P128" t="s">
+        <v>965</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>165</v>
+      </c>
+      <c r="R128" t="s">
+        <v>38</v>
+      </c>
+      <c r="S128" t="s">
+        <v>41</v>
+      </c>
+      <c r="T128" t="s">
+        <v>38</v>
+      </c>
+      <c r="U128" t="s">
+        <v>41</v>
+      </c>
+      <c r="V128">
+        <v>46</v>
+      </c>
+      <c r="W128">
+        <v>19</v>
+      </c>
+      <c r="X128">
+        <v>31</v>
+      </c>
+      <c r="Y128">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>202</v>
+      </c>
+      <c r="B129" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C129" t="s">
+        <v>203</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E129" t="s">
+        <v>42</v>
+      </c>
+      <c r="F129" t="s">
+        <v>966</v>
+      </c>
+      <c r="G129" t="s">
+        <v>967</v>
+      </c>
+      <c r="H129" t="s">
+        <v>201</v>
+      </c>
+      <c r="I129" t="s">
+        <v>968</v>
+      </c>
+      <c r="J129" t="s">
+        <v>969</v>
+      </c>
+      <c r="K129" t="s">
+        <v>970</v>
+      </c>
+      <c r="L129" t="s">
+        <v>201</v>
+      </c>
+      <c r="M129" t="s">
+        <v>201</v>
+      </c>
+      <c r="N129" t="s">
+        <v>201</v>
+      </c>
+      <c r="O129" t="s">
+        <v>201</v>
+      </c>
+      <c r="P129" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>201</v>
+      </c>
+      <c r="R129" t="s">
+        <v>201</v>
+      </c>
+      <c r="S129" t="s">
+        <v>201</v>
+      </c>
+      <c r="T129" t="s">
+        <v>201</v>
+      </c>
+      <c r="U129" t="s">
+        <v>201</v>
+      </c>
+      <c r="V129">
+        <v>0</v>
+      </c>
+      <c r="W129">
+        <v>0</v>
+      </c>
+      <c r="X129">
+        <v>0</v>
+      </c>
+      <c r="Y129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>202</v>
+      </c>
+      <c r="B130" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C130" t="s">
+        <v>203</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F130" t="s">
+        <v>966</v>
+      </c>
+      <c r="G130" t="s">
+        <v>283</v>
+      </c>
+      <c r="H130" t="s">
+        <v>971</v>
+      </c>
+      <c r="I130" t="s">
+        <v>972</v>
+      </c>
+      <c r="J130" t="s">
+        <v>973</v>
+      </c>
+      <c r="K130" t="s">
+        <v>974</v>
+      </c>
+      <c r="L130" t="s">
+        <v>975</v>
+      </c>
+      <c r="M130" t="s">
+        <v>181</v>
+      </c>
+      <c r="N130" t="s">
+        <v>35</v>
+      </c>
+      <c r="O130" t="s">
+        <v>39</v>
+      </c>
+      <c r="P130" t="s">
+        <v>976</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>977</v>
+      </c>
+      <c r="R130" t="s">
+        <v>66</v>
+      </c>
+      <c r="S130" t="s">
+        <v>39</v>
+      </c>
+      <c r="T130" t="s">
+        <v>40</v>
+      </c>
+      <c r="U130" t="s">
+        <v>41</v>
+      </c>
+      <c r="V130">
+        <v>49</v>
+      </c>
+      <c r="W130">
+        <v>12</v>
+      </c>
+      <c r="X130">
+        <v>42</v>
+      </c>
+      <c r="Y130">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>202</v>
+      </c>
+      <c r="B131" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C131" t="s">
+        <v>203</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E131" t="s">
+        <v>67</v>
+      </c>
+      <c r="F131" t="s">
+        <v>959</v>
+      </c>
+      <c r="G131" t="s">
+        <v>487</v>
+      </c>
+      <c r="H131" t="s">
+        <v>978</v>
+      </c>
+      <c r="I131" t="s">
+        <v>979</v>
+      </c>
+      <c r="J131" t="s">
+        <v>980</v>
+      </c>
+      <c r="K131" t="s">
+        <v>981</v>
+      </c>
+      <c r="L131" t="s">
+        <v>982</v>
+      </c>
+      <c r="M131" t="s">
+        <v>494</v>
+      </c>
+      <c r="N131" t="s">
+        <v>41</v>
+      </c>
+      <c r="O131" t="s">
+        <v>201</v>
+      </c>
+      <c r="P131" t="s">
+        <v>983</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>201</v>
+      </c>
+      <c r="R131" t="s">
+        <v>39</v>
+      </c>
+      <c r="S131" t="s">
+        <v>41</v>
+      </c>
+      <c r="T131" t="s">
+        <v>39</v>
+      </c>
+      <c r="U131" t="s">
+        <v>41</v>
+      </c>
+      <c r="V131">
+        <v>38</v>
+      </c>
+      <c r="W131">
+        <v>15</v>
+      </c>
+      <c r="X131">
+        <v>26</v>
+      </c>
+      <c r="Y131">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>202</v>
+      </c>
+      <c r="B132" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C132" t="s">
+        <v>203</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E132" t="s">
+        <v>90</v>
+      </c>
+      <c r="F132" t="s">
+        <v>959</v>
+      </c>
+      <c r="G132" t="s">
+        <v>158</v>
+      </c>
+      <c r="H132" t="s">
+        <v>984</v>
+      </c>
+      <c r="I132" t="s">
+        <v>985</v>
+      </c>
+      <c r="J132" t="s">
+        <v>569</v>
+      </c>
+      <c r="K132" t="s">
+        <v>986</v>
+      </c>
+      <c r="L132" t="s">
+        <v>987</v>
+      </c>
+      <c r="M132" t="s">
+        <v>628</v>
+      </c>
+      <c r="N132" t="s">
+        <v>279</v>
+      </c>
+      <c r="O132" t="s">
+        <v>201</v>
+      </c>
+      <c r="P132" t="s">
+        <v>988</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>455</v>
+      </c>
+      <c r="R132" t="s">
+        <v>38</v>
+      </c>
+      <c r="S132" t="s">
+        <v>39</v>
+      </c>
+      <c r="T132" t="s">
+        <v>40</v>
+      </c>
+      <c r="U132" t="s">
+        <v>201</v>
+      </c>
+      <c r="V132">
+        <v>64</v>
+      </c>
+      <c r="W132">
+        <v>11</v>
+      </c>
+      <c r="X132">
+        <v>29</v>
+      </c>
+      <c r="Y132">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>202</v>
+      </c>
+      <c r="B133" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C133" t="s">
+        <v>203</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E133" t="s">
+        <v>102</v>
+      </c>
+      <c r="F133" t="s">
+        <v>959</v>
+      </c>
+      <c r="G133" t="s">
+        <v>989</v>
+      </c>
+      <c r="H133" t="s">
+        <v>990</v>
+      </c>
+      <c r="I133" t="s">
+        <v>991</v>
+      </c>
+      <c r="J133" t="s">
+        <v>992</v>
+      </c>
+      <c r="K133" t="s">
+        <v>993</v>
+      </c>
+      <c r="L133" t="s">
+        <v>994</v>
+      </c>
+      <c r="M133" t="s">
+        <v>663</v>
+      </c>
+      <c r="N133" t="s">
+        <v>40</v>
+      </c>
+      <c r="O133" t="s">
+        <v>201</v>
+      </c>
+      <c r="P133" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>201</v>
+      </c>
+      <c r="R133" t="s">
+        <v>40</v>
+      </c>
+      <c r="S133" t="s">
+        <v>41</v>
+      </c>
+      <c r="T133" t="s">
+        <v>38</v>
+      </c>
+      <c r="U133" t="s">
+        <v>201</v>
+      </c>
+      <c r="V133">
+        <v>39</v>
+      </c>
+      <c r="W133">
+        <v>9</v>
+      </c>
+      <c r="X133">
+        <v>33</v>
+      </c>
+      <c r="Y133">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>202</v>
+      </c>
+      <c r="B134" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C134" t="s">
+        <v>203</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E134" t="s">
+        <v>347</v>
+      </c>
+      <c r="F134" t="s">
+        <v>959</v>
+      </c>
+      <c r="G134" t="s">
+        <v>823</v>
+      </c>
+      <c r="H134" t="s">
+        <v>995</v>
+      </c>
+      <c r="I134" t="s">
+        <v>996</v>
+      </c>
+      <c r="J134" t="s">
+        <v>997</v>
+      </c>
+      <c r="K134" t="s">
+        <v>998</v>
+      </c>
+      <c r="L134" t="s">
+        <v>999</v>
+      </c>
+      <c r="M134" t="s">
+        <v>788</v>
+      </c>
+      <c r="N134" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O134" t="s">
+        <v>41</v>
+      </c>
+      <c r="P134" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>773</v>
+      </c>
+      <c r="R134" t="s">
+        <v>337</v>
+      </c>
+      <c r="S134" t="s">
+        <v>66</v>
+      </c>
+      <c r="T134" t="s">
+        <v>35</v>
+      </c>
+      <c r="U134" t="s">
+        <v>39</v>
+      </c>
+      <c r="V134">
+        <v>72</v>
+      </c>
+      <c r="W134">
+        <v>47</v>
+      </c>
+      <c r="X134">
+        <v>75</v>
+      </c>
+      <c r="Y134">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>202</v>
+      </c>
+      <c r="B135" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C135" t="s">
+        <v>203</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E135" t="s">
+        <v>346</v>
+      </c>
+      <c r="F135" t="s">
+        <v>966</v>
+      </c>
+      <c r="G135" t="s">
+        <v>764</v>
+      </c>
+      <c r="H135" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I135" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J135" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K135" t="s">
+        <v>1005</v>
+      </c>
+      <c r="L135" t="s">
+        <v>1006</v>
+      </c>
+      <c r="M135" t="s">
+        <v>1007</v>
+      </c>
+      <c r="N135" t="s">
+        <v>554</v>
+      </c>
+      <c r="O135" t="s">
+        <v>201</v>
+      </c>
+      <c r="P135" t="s">
+        <v>1008</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>201</v>
+      </c>
+      <c r="R135" t="s">
+        <v>39</v>
+      </c>
+      <c r="S135" t="s">
+        <v>201</v>
+      </c>
+      <c r="T135" t="s">
+        <v>38</v>
+      </c>
+      <c r="U135" t="s">
+        <v>201</v>
+      </c>
+      <c r="V135">
+        <v>45</v>
+      </c>
+      <c r="W135">
+        <v>8</v>
+      </c>
+      <c r="X135">
+        <v>31</v>
+      </c>
+      <c r="Y135">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>202</v>
+      </c>
+      <c r="B136" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C136" t="s">
+        <v>203</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E136" t="s">
+        <v>147</v>
+      </c>
+      <c r="F136" t="s">
+        <v>959</v>
+      </c>
+      <c r="G136" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H136" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I136" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J136" t="s">
+        <v>1012</v>
+      </c>
+      <c r="K136" t="s">
+        <v>1013</v>
+      </c>
+      <c r="L136" t="s">
+        <v>398</v>
+      </c>
+      <c r="M136" t="s">
+        <v>187</v>
+      </c>
+      <c r="N136" t="s">
+        <v>40</v>
+      </c>
+      <c r="O136" t="s">
+        <v>201</v>
+      </c>
+      <c r="P136" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>165</v>
+      </c>
+      <c r="R136" t="s">
+        <v>39</v>
+      </c>
+      <c r="S136" t="s">
+        <v>41</v>
+      </c>
+      <c r="T136" t="s">
+        <v>38</v>
+      </c>
+      <c r="U136" t="s">
+        <v>201</v>
+      </c>
+      <c r="V136">
+        <v>34</v>
+      </c>
+      <c r="W136">
+        <v>14</v>
+      </c>
+      <c r="X136">
+        <v>23</v>
+      </c>
+      <c r="Y136">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>202</v>
+      </c>
+      <c r="B137" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C137" t="s">
+        <v>203</v>
+      </c>
+      <c r="D137" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E137" t="s">
+        <v>157</v>
+      </c>
+      <c r="F137" t="s">
+        <v>959</v>
+      </c>
+      <c r="G137" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H137" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I137" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J137" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K137" t="s">
+        <v>1018</v>
+      </c>
+      <c r="L137" t="s">
+        <v>867</v>
+      </c>
+      <c r="M137" t="s">
+        <v>158</v>
+      </c>
+      <c r="N137" t="s">
+        <v>50</v>
+      </c>
+      <c r="O137" t="s">
+        <v>41</v>
+      </c>
+      <c r="P137" t="s">
+        <v>1019</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>371</v>
+      </c>
+      <c r="R137" t="s">
+        <v>35</v>
+      </c>
+      <c r="S137" t="s">
+        <v>38</v>
+      </c>
+      <c r="T137" t="s">
+        <v>35</v>
+      </c>
+      <c r="U137" t="s">
+        <v>38</v>
+      </c>
+      <c r="V137">
+        <v>71</v>
+      </c>
+      <c r="W137">
+        <v>44</v>
+      </c>
+      <c r="X137">
+        <v>62</v>
+      </c>
+      <c r="Y137">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>202</v>
+      </c>
+      <c r="B138" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C138" t="s">
+        <v>203</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E138" t="s">
+        <v>191</v>
+      </c>
+      <c r="F138" t="s">
+        <v>959</v>
+      </c>
+      <c r="G138" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H138" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I138" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J138" t="s">
+        <v>1023</v>
+      </c>
+      <c r="K138" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L138" t="s">
+        <v>1025</v>
+      </c>
+      <c r="M138" t="s">
+        <v>1026</v>
+      </c>
+      <c r="N138" t="s">
+        <v>201</v>
+      </c>
+      <c r="O138" t="s">
+        <v>201</v>
+      </c>
+      <c r="P138" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>201</v>
+      </c>
+      <c r="R138" t="s">
+        <v>201</v>
+      </c>
+      <c r="S138" t="s">
+        <v>201</v>
+      </c>
+      <c r="T138" t="s">
+        <v>41</v>
+      </c>
+      <c r="U138" t="s">
+        <v>201</v>
+      </c>
+      <c r="V138">
+        <v>10</v>
+      </c>
+      <c r="W138">
+        <v>3</v>
+      </c>
+      <c r="X138">
+        <v>2</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3DE3CE-34B5-7645-88AE-88A608188EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCD8D58-871F-C345-8FE6-4C8157B1EA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="1084">
   <si>
     <t>Type</t>
   </si>
@@ -3119,7 +3119,175 @@
     <t>4.83</t>
   </si>
   <si>
-    <t>J+2</t>
+    <t>81.48</t>
+  </si>
+  <si>
+    <t>36.03</t>
+  </si>
+  <si>
+    <t>280.46</t>
+  </si>
+  <si>
+    <t>25.5</t>
+  </si>
+  <si>
+    <t>68.61</t>
+  </si>
+  <si>
+    <t>111.48</t>
+  </si>
+  <si>
+    <t>289.11</t>
+  </si>
+  <si>
+    <t>26.28</t>
+  </si>
+  <si>
+    <t>70.31</t>
+  </si>
+  <si>
+    <t>7.21</t>
+  </si>
+  <si>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>79.63</t>
+  </si>
+  <si>
+    <t>301.08</t>
+  </si>
+  <si>
+    <t>24.74</t>
+  </si>
+  <si>
+    <t>70.0</t>
+  </si>
+  <si>
+    <t>7.47</t>
+  </si>
+  <si>
+    <t>135.94</t>
+  </si>
+  <si>
+    <t>268.61</t>
+  </si>
+  <si>
+    <t>28.42</t>
+  </si>
+  <si>
+    <t>69.96</t>
+  </si>
+  <si>
+    <t>8.6</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>7.14</t>
+  </si>
+  <si>
+    <t>45.21</t>
+  </si>
+  <si>
+    <t>407.25</t>
+  </si>
+  <si>
+    <t>24.35</t>
+  </si>
+  <si>
+    <t>87.67</t>
+  </si>
+  <si>
+    <t>5.22</t>
+  </si>
+  <si>
+    <t>172.28</t>
+  </si>
+  <si>
+    <t>316.35</t>
+  </si>
+  <si>
+    <t>25.36</t>
+  </si>
+  <si>
+    <t>77.79</t>
+  </si>
+  <si>
+    <t>6.94</t>
+  </si>
+  <si>
+    <t>27.7</t>
+  </si>
+  <si>
+    <t>6.76</t>
+  </si>
+  <si>
+    <t>184.59</t>
+  </si>
+  <si>
+    <t>333.77</t>
+  </si>
+  <si>
+    <t>26.78</t>
+  </si>
+  <si>
+    <t>82.98</t>
+  </si>
+  <si>
+    <t>6.93</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>101.83</t>
+  </si>
+  <si>
+    <t>332.98</t>
+  </si>
+  <si>
+    <t>25.12</t>
+  </si>
+  <si>
+    <t>80.19</t>
+  </si>
+  <si>
+    <t>5.95</t>
+  </si>
+  <si>
+    <t>178.83</t>
+  </si>
+  <si>
+    <t>617.39</t>
+  </si>
+  <si>
+    <t>72.99</t>
+  </si>
+  <si>
+    <t>7.15</t>
+  </si>
+  <si>
+    <t>180.37</t>
+  </si>
+  <si>
+    <t>335.37</t>
+  </si>
+  <si>
+    <t>29.06</t>
+  </si>
+  <si>
+    <t>83.02</t>
+  </si>
+  <si>
+    <t>26.4</t>
   </si>
 </sst>
 </file>
@@ -3498,7 +3666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y138"/>
+  <dimension ref="A1:Y148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
@@ -13159,9 +13327,6 @@
       <c r="C128" t="s">
         <v>203</v>
       </c>
-      <c r="D128" t="s">
-        <v>1027</v>
-      </c>
       <c r="E128" t="s">
         <v>25</v>
       </c>
@@ -13236,9 +13401,6 @@
       <c r="C129" t="s">
         <v>203</v>
       </c>
-      <c r="D129" t="s">
-        <v>1027</v>
-      </c>
       <c r="E129" t="s">
         <v>42</v>
       </c>
@@ -13313,9 +13475,6 @@
       <c r="C130" t="s">
         <v>203</v>
       </c>
-      <c r="D130" t="s">
-        <v>1027</v>
-      </c>
       <c r="E130" t="s">
         <v>54</v>
       </c>
@@ -13390,9 +13549,6 @@
       <c r="C131" t="s">
         <v>203</v>
       </c>
-      <c r="D131" t="s">
-        <v>1027</v>
-      </c>
       <c r="E131" t="s">
         <v>67</v>
       </c>
@@ -13467,9 +13623,6 @@
       <c r="C132" t="s">
         <v>203</v>
       </c>
-      <c r="D132" t="s">
-        <v>1027</v>
-      </c>
       <c r="E132" t="s">
         <v>90</v>
       </c>
@@ -13544,9 +13697,6 @@
       <c r="C133" t="s">
         <v>203</v>
       </c>
-      <c r="D133" t="s">
-        <v>1027</v>
-      </c>
       <c r="E133" t="s">
         <v>102</v>
       </c>
@@ -13621,9 +13771,6 @@
       <c r="C134" t="s">
         <v>203</v>
       </c>
-      <c r="D134" t="s">
-        <v>1027</v>
-      </c>
       <c r="E134" t="s">
         <v>347</v>
       </c>
@@ -13698,9 +13845,6 @@
       <c r="C135" t="s">
         <v>203</v>
       </c>
-      <c r="D135" t="s">
-        <v>1027</v>
-      </c>
       <c r="E135" t="s">
         <v>346</v>
       </c>
@@ -13775,9 +13919,6 @@
       <c r="C136" t="s">
         <v>203</v>
       </c>
-      <c r="D136" t="s">
-        <v>1027</v>
-      </c>
       <c r="E136" t="s">
         <v>147</v>
       </c>
@@ -13852,9 +13993,6 @@
       <c r="C137" t="s">
         <v>203</v>
       </c>
-      <c r="D137" t="s">
-        <v>1027</v>
-      </c>
       <c r="E137" t="s">
         <v>157</v>
       </c>
@@ -13929,9 +14067,6 @@
       <c r="C138" t="s">
         <v>203</v>
       </c>
-      <c r="D138" t="s">
-        <v>1027</v>
-      </c>
       <c r="E138" t="s">
         <v>191</v>
       </c>
@@ -13994,6 +14129,746 @@
       </c>
       <c r="Y138">
         <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>202</v>
+      </c>
+      <c r="B139" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C139" t="s">
+        <v>203</v>
+      </c>
+      <c r="E139" t="s">
+        <v>25</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G139" t="s">
+        <v>707</v>
+      </c>
+      <c r="H139" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I139" t="s">
+        <v>1029</v>
+      </c>
+      <c r="J139" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K139" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L139" t="s">
+        <v>803</v>
+      </c>
+      <c r="M139" t="s">
+        <v>362</v>
+      </c>
+      <c r="N139" t="s">
+        <v>38</v>
+      </c>
+      <c r="O139" t="s">
+        <v>201</v>
+      </c>
+      <c r="P139" t="s">
+        <v>1009</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>165</v>
+      </c>
+      <c r="R139" t="s">
+        <v>40</v>
+      </c>
+      <c r="S139" t="s">
+        <v>39</v>
+      </c>
+      <c r="T139" t="s">
+        <v>40</v>
+      </c>
+      <c r="U139" t="s">
+        <v>41</v>
+      </c>
+      <c r="V139">
+        <v>51</v>
+      </c>
+      <c r="W139">
+        <v>21</v>
+      </c>
+      <c r="X139">
+        <v>49</v>
+      </c>
+      <c r="Y139">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>202</v>
+      </c>
+      <c r="B140" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C140" t="s">
+        <v>203</v>
+      </c>
+      <c r="E140" t="s">
+        <v>42</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G140" t="s">
+        <v>511</v>
+      </c>
+      <c r="H140" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I140" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J140" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K140" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L140" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M140" t="s">
+        <v>362</v>
+      </c>
+      <c r="N140" t="s">
+        <v>449</v>
+      </c>
+      <c r="O140" t="s">
+        <v>201</v>
+      </c>
+      <c r="P140" t="s">
+        <v>1037</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>455</v>
+      </c>
+      <c r="R140" t="s">
+        <v>40</v>
+      </c>
+      <c r="S140" t="s">
+        <v>41</v>
+      </c>
+      <c r="T140" t="s">
+        <v>40</v>
+      </c>
+      <c r="U140" t="s">
+        <v>41</v>
+      </c>
+      <c r="V140">
+        <v>39</v>
+      </c>
+      <c r="W140">
+        <v>21</v>
+      </c>
+      <c r="X140">
+        <v>42</v>
+      </c>
+      <c r="Y140">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>202</v>
+      </c>
+      <c r="B141" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C141" t="s">
+        <v>203</v>
+      </c>
+      <c r="E141" t="s">
+        <v>54</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G141" t="s">
+        <v>603</v>
+      </c>
+      <c r="H141" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I141" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J141" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K141" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L141" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M141" t="s">
+        <v>420</v>
+      </c>
+      <c r="N141" t="s">
+        <v>337</v>
+      </c>
+      <c r="O141" t="s">
+        <v>201</v>
+      </c>
+      <c r="P141" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>165</v>
+      </c>
+      <c r="R141" t="s">
+        <v>113</v>
+      </c>
+      <c r="S141" t="s">
+        <v>39</v>
+      </c>
+      <c r="T141" t="s">
+        <v>113</v>
+      </c>
+      <c r="U141" t="s">
+        <v>39</v>
+      </c>
+      <c r="V141">
+        <v>62</v>
+      </c>
+      <c r="W141">
+        <v>39</v>
+      </c>
+      <c r="X141">
+        <v>61</v>
+      </c>
+      <c r="Y141">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>202</v>
+      </c>
+      <c r="B142" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C142" t="s">
+        <v>203</v>
+      </c>
+      <c r="E142" t="s">
+        <v>67</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G142" t="s">
+        <v>603</v>
+      </c>
+      <c r="H142" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I142" t="s">
+        <v>1044</v>
+      </c>
+      <c r="J142" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K142" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L142" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M142" t="s">
+        <v>80</v>
+      </c>
+      <c r="N142" t="s">
+        <v>449</v>
+      </c>
+      <c r="O142" t="s">
+        <v>39</v>
+      </c>
+      <c r="P142" t="s">
+        <v>1048</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>1049</v>
+      </c>
+      <c r="R142" t="s">
+        <v>38</v>
+      </c>
+      <c r="S142" t="s">
+        <v>39</v>
+      </c>
+      <c r="T142" t="s">
+        <v>40</v>
+      </c>
+      <c r="U142" t="s">
+        <v>41</v>
+      </c>
+      <c r="V142">
+        <v>50</v>
+      </c>
+      <c r="W142">
+        <v>25</v>
+      </c>
+      <c r="X142">
+        <v>23</v>
+      </c>
+      <c r="Y142">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>202</v>
+      </c>
+      <c r="B143" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C143" t="s">
+        <v>203</v>
+      </c>
+      <c r="E143" t="s">
+        <v>90</v>
+      </c>
+      <c r="F143" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G143" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H143" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I143" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J143" t="s">
+        <v>1053</v>
+      </c>
+      <c r="K143" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L143" t="s">
+        <v>982</v>
+      </c>
+      <c r="M143" t="s">
+        <v>1055</v>
+      </c>
+      <c r="N143" t="s">
+        <v>40</v>
+      </c>
+      <c r="O143" t="s">
+        <v>201</v>
+      </c>
+      <c r="P143" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>34</v>
+      </c>
+      <c r="R143" t="s">
+        <v>38</v>
+      </c>
+      <c r="S143" t="s">
+        <v>41</v>
+      </c>
+      <c r="T143" t="s">
+        <v>40</v>
+      </c>
+      <c r="U143" t="s">
+        <v>41</v>
+      </c>
+      <c r="V143">
+        <v>58</v>
+      </c>
+      <c r="W143">
+        <v>24</v>
+      </c>
+      <c r="X143">
+        <v>49</v>
+      </c>
+      <c r="Y143">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>202</v>
+      </c>
+      <c r="B144" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C144" t="s">
+        <v>203</v>
+      </c>
+      <c r="E144" t="s">
+        <v>347</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G144" t="s">
+        <v>27</v>
+      </c>
+      <c r="H144" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I144" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J144" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K144" t="s">
+        <v>1059</v>
+      </c>
+      <c r="L144" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M144" t="s">
+        <v>511</v>
+      </c>
+      <c r="N144" t="s">
+        <v>177</v>
+      </c>
+      <c r="O144" t="s">
+        <v>201</v>
+      </c>
+      <c r="P144" t="s">
+        <v>1061</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>176</v>
+      </c>
+      <c r="R144" t="s">
+        <v>113</v>
+      </c>
+      <c r="S144" t="s">
+        <v>38</v>
+      </c>
+      <c r="T144" t="s">
+        <v>113</v>
+      </c>
+      <c r="U144" t="s">
+        <v>39</v>
+      </c>
+      <c r="V144">
+        <v>57</v>
+      </c>
+      <c r="W144">
+        <v>32</v>
+      </c>
+      <c r="X144">
+        <v>50</v>
+      </c>
+      <c r="Y144">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>202</v>
+      </c>
+      <c r="B145" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C145" t="s">
+        <v>203</v>
+      </c>
+      <c r="E145" t="s">
+        <v>126</v>
+      </c>
+      <c r="F145" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G145" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H145" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I145" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J145" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K145" t="s">
+        <v>1066</v>
+      </c>
+      <c r="L145" t="s">
+        <v>1067</v>
+      </c>
+      <c r="M145" t="s">
+        <v>989</v>
+      </c>
+      <c r="N145" t="s">
+        <v>177</v>
+      </c>
+      <c r="O145" t="s">
+        <v>41</v>
+      </c>
+      <c r="P145" t="s">
+        <v>1068</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R145" t="s">
+        <v>113</v>
+      </c>
+      <c r="S145" t="s">
+        <v>39</v>
+      </c>
+      <c r="T145" t="s">
+        <v>40</v>
+      </c>
+      <c r="U145" t="s">
+        <v>41</v>
+      </c>
+      <c r="V145">
+        <v>65</v>
+      </c>
+      <c r="W145">
+        <v>20</v>
+      </c>
+      <c r="X145">
+        <v>50</v>
+      </c>
+      <c r="Y145">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>202</v>
+      </c>
+      <c r="B146" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C146" t="s">
+        <v>203</v>
+      </c>
+      <c r="E146" t="s">
+        <v>346</v>
+      </c>
+      <c r="F146" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G146" t="s">
+        <v>627</v>
+      </c>
+      <c r="H146" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I146" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J146" t="s">
+        <v>1072</v>
+      </c>
+      <c r="K146" t="s">
+        <v>1073</v>
+      </c>
+      <c r="L146" t="s">
+        <v>73</v>
+      </c>
+      <c r="M146" t="s">
+        <v>133</v>
+      </c>
+      <c r="N146" t="s">
+        <v>488</v>
+      </c>
+      <c r="O146" t="s">
+        <v>201</v>
+      </c>
+      <c r="P146" t="s">
+        <v>969</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>87</v>
+      </c>
+      <c r="R146" t="s">
+        <v>113</v>
+      </c>
+      <c r="S146" t="s">
+        <v>38</v>
+      </c>
+      <c r="T146" t="s">
+        <v>66</v>
+      </c>
+      <c r="U146" t="s">
+        <v>41</v>
+      </c>
+      <c r="V146">
+        <v>56</v>
+      </c>
+      <c r="W146">
+        <v>33</v>
+      </c>
+      <c r="X146">
+        <v>49</v>
+      </c>
+      <c r="Y146">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>202</v>
+      </c>
+      <c r="B147" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C147" t="s">
+        <v>203</v>
+      </c>
+      <c r="E147" t="s">
+        <v>147</v>
+      </c>
+      <c r="F147" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G147" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H147" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I147" t="s">
+        <v>1076</v>
+      </c>
+      <c r="J147" t="s">
+        <v>65</v>
+      </c>
+      <c r="K147" t="s">
+        <v>1077</v>
+      </c>
+      <c r="L147" t="s">
+        <v>1078</v>
+      </c>
+      <c r="M147" t="s">
+        <v>143</v>
+      </c>
+      <c r="N147" t="s">
+        <v>495</v>
+      </c>
+      <c r="O147" t="s">
+        <v>39</v>
+      </c>
+      <c r="P147" t="s">
+        <v>1030</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>581</v>
+      </c>
+      <c r="R147" t="s">
+        <v>280</v>
+      </c>
+      <c r="S147" t="s">
+        <v>35</v>
+      </c>
+      <c r="T147" t="s">
+        <v>35</v>
+      </c>
+      <c r="U147" t="s">
+        <v>38</v>
+      </c>
+      <c r="V147">
+        <v>76</v>
+      </c>
+      <c r="W147">
+        <v>57</v>
+      </c>
+      <c r="X147">
+        <v>75</v>
+      </c>
+      <c r="Y147">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>202</v>
+      </c>
+      <c r="B148" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C148" t="s">
+        <v>203</v>
+      </c>
+      <c r="E148" t="s">
+        <v>157</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G148" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H148" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I148" t="s">
+        <v>1080</v>
+      </c>
+      <c r="J148" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K148" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L148" t="s">
+        <v>564</v>
+      </c>
+      <c r="M148" t="s">
+        <v>635</v>
+      </c>
+      <c r="N148" t="s">
+        <v>76</v>
+      </c>
+      <c r="O148" t="s">
+        <v>39</v>
+      </c>
+      <c r="P148" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>1049</v>
+      </c>
+      <c r="R148" t="s">
+        <v>35</v>
+      </c>
+      <c r="S148" t="s">
+        <v>38</v>
+      </c>
+      <c r="T148" t="s">
+        <v>35</v>
+      </c>
+      <c r="U148" t="s">
+        <v>39</v>
+      </c>
+      <c r="V148">
+        <v>78</v>
+      </c>
+      <c r="W148">
+        <v>35</v>
+      </c>
+      <c r="X148">
+        <v>52</v>
+      </c>
+      <c r="Y148">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCD8D58-871F-C345-8FE6-4C8157B1EA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BC1A6E-043C-2D4C-B733-7C35102A6254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3131" uniqueCount="1226">
   <si>
     <t>Type</t>
   </si>
@@ -3288,6 +3288,432 @@
   </si>
   <si>
     <t>26.4</t>
+  </si>
+  <si>
+    <t>65.72</t>
+  </si>
+  <si>
+    <t>58.71</t>
+  </si>
+  <si>
+    <t>139.68</t>
+  </si>
+  <si>
+    <t>24.18</t>
+  </si>
+  <si>
+    <t>42.68</t>
+  </si>
+  <si>
+    <t>9.6</t>
+  </si>
+  <si>
+    <t>3.25</t>
+  </si>
+  <si>
+    <t>226.53</t>
+  </si>
+  <si>
+    <t>154.67</t>
+  </si>
+  <si>
+    <t>27.17</t>
+  </si>
+  <si>
+    <t>49.43</t>
+  </si>
+  <si>
+    <t>8.76</t>
+  </si>
+  <si>
+    <t>32.2</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>3.06</t>
+  </si>
+  <si>
+    <t>313.93</t>
+  </si>
+  <si>
+    <t>157.23</t>
+  </si>
+  <si>
+    <t>30.31</t>
+  </si>
+  <si>
+    <t>46.53</t>
+  </si>
+  <si>
+    <t>3.96</t>
+  </si>
+  <si>
+    <t>492.7</t>
+  </si>
+  <si>
+    <t>165.57</t>
+  </si>
+  <si>
+    <t>30.5</t>
+  </si>
+  <si>
+    <t>60.19</t>
+  </si>
+  <si>
+    <t>4.36</t>
+  </si>
+  <si>
+    <t>57.1</t>
+  </si>
+  <si>
+    <t>18.8</t>
+  </si>
+  <si>
+    <t>3.09</t>
+  </si>
+  <si>
+    <t>142.18</t>
+  </si>
+  <si>
+    <t>171.28</t>
+  </si>
+  <si>
+    <t>47.0</t>
+  </si>
+  <si>
+    <t>23.5</t>
+  </si>
+  <si>
+    <t>3.74</t>
+  </si>
+  <si>
+    <t>163.24</t>
+  </si>
+  <si>
+    <t>56.97</t>
+  </si>
+  <si>
+    <t>5.97</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>25.1</t>
+  </si>
+  <si>
+    <t>3.84</t>
+  </si>
+  <si>
+    <t>465.31</t>
+  </si>
+  <si>
+    <t>168.05</t>
+  </si>
+  <si>
+    <t>29.79</t>
+  </si>
+  <si>
+    <t>58.49</t>
+  </si>
+  <si>
+    <t>5.27</t>
+  </si>
+  <si>
+    <t>5.14</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>18.7</t>
+  </si>
+  <si>
+    <t>4.05</t>
+  </si>
+  <si>
+    <t>509.32</t>
+  </si>
+  <si>
+    <t>193.21</t>
+  </si>
+  <si>
+    <t>61.66</t>
+  </si>
+  <si>
+    <t>54.3</t>
+  </si>
+  <si>
+    <t>2.64</t>
+  </si>
+  <si>
+    <t>150.79</t>
+  </si>
+  <si>
+    <t>18.13</t>
+  </si>
+  <si>
+    <t>40.16</t>
+  </si>
+  <si>
+    <t>66.05</t>
+  </si>
+  <si>
+    <t>287.72</t>
+  </si>
+  <si>
+    <t>26.17</t>
+  </si>
+  <si>
+    <t>40.1</t>
+  </si>
+  <si>
+    <t>7.66</t>
+  </si>
+  <si>
+    <t>2.85</t>
+  </si>
+  <si>
+    <t>240.31</t>
+  </si>
+  <si>
+    <t>133.73</t>
+  </si>
+  <si>
+    <t>27.57</t>
+  </si>
+  <si>
+    <t>43.42</t>
+  </si>
+  <si>
+    <t>27.5</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>3.49</t>
+  </si>
+  <si>
+    <t>309.69</t>
+  </si>
+  <si>
+    <t>320.77</t>
+  </si>
+  <si>
+    <t>35.17</t>
+  </si>
+  <si>
+    <t>53.18</t>
+  </si>
+  <si>
+    <t>6.59</t>
+  </si>
+  <si>
+    <t>36.6</t>
+  </si>
+  <si>
+    <t>82.88</t>
+  </si>
+  <si>
+    <t>81.08</t>
+  </si>
+  <si>
+    <t>245.83</t>
+  </si>
+  <si>
+    <t>27.27</t>
+  </si>
+  <si>
+    <t>59.31</t>
+  </si>
+  <si>
+    <t>124.61</t>
+  </si>
+  <si>
+    <t>263.3</t>
+  </si>
+  <si>
+    <t>28.45</t>
+  </si>
+  <si>
+    <t>58.21</t>
+  </si>
+  <si>
+    <t>8.36</t>
+  </si>
+  <si>
+    <t>18.5</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>169.27</t>
+  </si>
+  <si>
+    <t>241.9</t>
+  </si>
+  <si>
+    <t>24.93</t>
+  </si>
+  <si>
+    <t>60.58</t>
+  </si>
+  <si>
+    <t>5.47</t>
+  </si>
+  <si>
+    <t>25.6</t>
+  </si>
+  <si>
+    <t>61.12</t>
+  </si>
+  <si>
+    <t>340.55</t>
+  </si>
+  <si>
+    <t>24.53</t>
+  </si>
+  <si>
+    <t>72.74</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
+    <t>107.17</t>
+  </si>
+  <si>
+    <t>264.86</t>
+  </si>
+  <si>
+    <t>62.16</t>
+  </si>
+  <si>
+    <t>16.4</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>71.89</t>
+  </si>
+  <si>
+    <t>258.25</t>
+  </si>
+  <si>
+    <t>25.14</t>
+  </si>
+  <si>
+    <t>60.02</t>
+  </si>
+  <si>
+    <t>208.11</t>
+  </si>
+  <si>
+    <t>283.06</t>
+  </si>
+  <si>
+    <t>26.98</t>
+  </si>
+  <si>
+    <t>65.84</t>
+  </si>
+  <si>
+    <t>5.16</t>
+  </si>
+  <si>
+    <t>Pharell Cafara</t>
+  </si>
+  <si>
+    <t>5.28</t>
+  </si>
+  <si>
+    <t>212.79</t>
+  </si>
+  <si>
+    <t>286.07</t>
+  </si>
+  <si>
+    <t>63.74</t>
+  </si>
+  <si>
+    <t>4.03</t>
+  </si>
+  <si>
+    <t>237.13</t>
+  </si>
+  <si>
+    <t>15.12</t>
+  </si>
+  <si>
+    <t>48.66</t>
+  </si>
+  <si>
+    <t>4.32</t>
+  </si>
+  <si>
+    <t>5.07</t>
+  </si>
+  <si>
+    <t>56.09</t>
+  </si>
+  <si>
+    <t>251.84</t>
+  </si>
+  <si>
+    <t>61.17</t>
+  </si>
+  <si>
+    <t>6.26</t>
+  </si>
+  <si>
+    <t>8.7</t>
+  </si>
+  <si>
+    <t>4.67</t>
+  </si>
+  <si>
+    <t>214.89</t>
+  </si>
+  <si>
+    <t>226.23</t>
+  </si>
+  <si>
+    <t>28.72</t>
+  </si>
+  <si>
+    <t>56.38</t>
+  </si>
+  <si>
+    <t>6.46</t>
+  </si>
+  <si>
+    <t>31.5</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>223.02</t>
+  </si>
+  <si>
+    <t>524.89</t>
+  </si>
+  <si>
+    <t>29.46</t>
+  </si>
+  <si>
+    <t>59.72</t>
+  </si>
+  <si>
+    <t>8.34</t>
+  </si>
+  <si>
+    <t>5.2</t>
   </si>
 </sst>
 </file>
@@ -3666,7 +4092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y148"/>
+  <dimension ref="A1:Y172"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
@@ -14871,6 +15297,1782 @@
         <v>31</v>
       </c>
     </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>202</v>
+      </c>
+      <c r="B149" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C149" t="s">
+        <v>203</v>
+      </c>
+      <c r="E149" t="s">
+        <v>25</v>
+      </c>
+      <c r="F149" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I149" t="s">
+        <v>1086</v>
+      </c>
+      <c r="J149" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K149" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L149" t="s">
+        <v>706</v>
+      </c>
+      <c r="M149" t="s">
+        <v>61</v>
+      </c>
+      <c r="N149" t="s">
+        <v>113</v>
+      </c>
+      <c r="O149" t="s">
+        <v>201</v>
+      </c>
+      <c r="P149" t="s">
+        <v>1089</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>488</v>
+      </c>
+      <c r="R149" t="s">
+        <v>41</v>
+      </c>
+      <c r="S149" t="s">
+        <v>201</v>
+      </c>
+      <c r="T149" t="s">
+        <v>41</v>
+      </c>
+      <c r="U149" t="s">
+        <v>41</v>
+      </c>
+      <c r="V149">
+        <v>18</v>
+      </c>
+      <c r="W149">
+        <v>12</v>
+      </c>
+      <c r="X149">
+        <v>8</v>
+      </c>
+      <c r="Y149">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>202</v>
+      </c>
+      <c r="B150" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C150" t="s">
+        <v>203</v>
+      </c>
+      <c r="E150" t="s">
+        <v>42</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H150" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I150" t="s">
+        <v>1092</v>
+      </c>
+      <c r="J150" t="s">
+        <v>1093</v>
+      </c>
+      <c r="K150" t="s">
+        <v>1094</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1095</v>
+      </c>
+      <c r="M150" t="s">
+        <v>469</v>
+      </c>
+      <c r="N150" t="s">
+        <v>471</v>
+      </c>
+      <c r="O150" t="s">
+        <v>38</v>
+      </c>
+      <c r="P150" t="s">
+        <v>1096</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>1097</v>
+      </c>
+      <c r="R150" t="s">
+        <v>41</v>
+      </c>
+      <c r="S150" t="s">
+        <v>201</v>
+      </c>
+      <c r="T150" t="s">
+        <v>39</v>
+      </c>
+      <c r="U150" t="s">
+        <v>201</v>
+      </c>
+      <c r="V150">
+        <v>17</v>
+      </c>
+      <c r="W150">
+        <v>9</v>
+      </c>
+      <c r="X150">
+        <v>6</v>
+      </c>
+      <c r="Y150">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>202</v>
+      </c>
+      <c r="B151" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C151" t="s">
+        <v>203</v>
+      </c>
+      <c r="E151" t="s">
+        <v>54</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G151" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H151" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I151" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J151" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K151" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L151" t="s">
+        <v>143</v>
+      </c>
+      <c r="M151" t="s">
+        <v>891</v>
+      </c>
+      <c r="N151" t="s">
+        <v>110</v>
+      </c>
+      <c r="O151" t="s">
+        <v>40</v>
+      </c>
+      <c r="P151" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>163</v>
+      </c>
+      <c r="R151" t="s">
+        <v>38</v>
+      </c>
+      <c r="S151" t="s">
+        <v>39</v>
+      </c>
+      <c r="T151" t="s">
+        <v>39</v>
+      </c>
+      <c r="U151" t="s">
+        <v>41</v>
+      </c>
+      <c r="V151">
+        <v>17</v>
+      </c>
+      <c r="W151">
+        <v>19</v>
+      </c>
+      <c r="X151">
+        <v>24</v>
+      </c>
+      <c r="Y151">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>202</v>
+      </c>
+      <c r="B152" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C152" t="s">
+        <v>203</v>
+      </c>
+      <c r="E152" t="s">
+        <v>67</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G152" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H152" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I152" t="s">
+        <v>1105</v>
+      </c>
+      <c r="J152" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K152" t="s">
+        <v>1107</v>
+      </c>
+      <c r="L152" t="s">
+        <v>1108</v>
+      </c>
+      <c r="M152" t="s">
+        <v>955</v>
+      </c>
+      <c r="N152" t="s">
+        <v>641</v>
+      </c>
+      <c r="O152" t="s">
+        <v>555</v>
+      </c>
+      <c r="P152" t="s">
+        <v>1109</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>1110</v>
+      </c>
+      <c r="R152" t="s">
+        <v>38</v>
+      </c>
+      <c r="S152" t="s">
+        <v>201</v>
+      </c>
+      <c r="T152" t="s">
+        <v>38</v>
+      </c>
+      <c r="U152" t="s">
+        <v>41</v>
+      </c>
+      <c r="V152">
+        <v>21</v>
+      </c>
+      <c r="W152">
+        <v>12</v>
+      </c>
+      <c r="X152">
+        <v>18</v>
+      </c>
+      <c r="Y152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>202</v>
+      </c>
+      <c r="B153" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C153" t="s">
+        <v>203</v>
+      </c>
+      <c r="E153" t="s">
+        <v>90</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G153" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H153" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I153" t="s">
+        <v>1113</v>
+      </c>
+      <c r="J153" t="s">
+        <v>625</v>
+      </c>
+      <c r="K153" t="s">
+        <v>1114</v>
+      </c>
+      <c r="L153" t="s">
+        <v>749</v>
+      </c>
+      <c r="M153" t="s">
+        <v>309</v>
+      </c>
+      <c r="N153" t="s">
+        <v>555</v>
+      </c>
+      <c r="O153" t="s">
+        <v>201</v>
+      </c>
+      <c r="P153" t="s">
+        <v>1115</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>165</v>
+      </c>
+      <c r="R153" t="s">
+        <v>41</v>
+      </c>
+      <c r="S153" t="s">
+        <v>201</v>
+      </c>
+      <c r="T153" t="s">
+        <v>41</v>
+      </c>
+      <c r="U153" t="s">
+        <v>201</v>
+      </c>
+      <c r="V153">
+        <v>16</v>
+      </c>
+      <c r="W153">
+        <v>10</v>
+      </c>
+      <c r="X153">
+        <v>10</v>
+      </c>
+      <c r="Y153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>202</v>
+      </c>
+      <c r="B154" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C154" t="s">
+        <v>203</v>
+      </c>
+      <c r="E154" t="s">
+        <v>347</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G154" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H154" t="s">
+        <v>590</v>
+      </c>
+      <c r="I154" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J154" t="s">
+        <v>140</v>
+      </c>
+      <c r="K154" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L154" t="s">
+        <v>823</v>
+      </c>
+      <c r="M154" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N154" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O154" t="s">
+        <v>213</v>
+      </c>
+      <c r="P154" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>1121</v>
+      </c>
+      <c r="R154" t="s">
+        <v>38</v>
+      </c>
+      <c r="S154" t="s">
+        <v>41</v>
+      </c>
+      <c r="T154" t="s">
+        <v>38</v>
+      </c>
+      <c r="U154" t="s">
+        <v>41</v>
+      </c>
+      <c r="V154">
+        <v>16</v>
+      </c>
+      <c r="W154">
+        <v>13</v>
+      </c>
+      <c r="X154">
+        <v>15</v>
+      </c>
+      <c r="Y154">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>202</v>
+      </c>
+      <c r="B155" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C155" t="s">
+        <v>203</v>
+      </c>
+      <c r="E155" t="s">
+        <v>126</v>
+      </c>
+      <c r="F155" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G155" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H155" t="s">
+        <v>1123</v>
+      </c>
+      <c r="I155" t="s">
+        <v>1124</v>
+      </c>
+      <c r="J155" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K155" t="s">
+        <v>1126</v>
+      </c>
+      <c r="L155" t="s">
+        <v>1127</v>
+      </c>
+      <c r="M155" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N155" t="s">
+        <v>290</v>
+      </c>
+      <c r="O155" t="s">
+        <v>555</v>
+      </c>
+      <c r="P155" t="s">
+        <v>1129</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>1130</v>
+      </c>
+      <c r="R155" t="s">
+        <v>41</v>
+      </c>
+      <c r="S155" t="s">
+        <v>201</v>
+      </c>
+      <c r="T155" t="s">
+        <v>39</v>
+      </c>
+      <c r="U155" t="s">
+        <v>41</v>
+      </c>
+      <c r="V155">
+        <v>10</v>
+      </c>
+      <c r="W155">
+        <v>11</v>
+      </c>
+      <c r="X155">
+        <v>15</v>
+      </c>
+      <c r="Y155">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>202</v>
+      </c>
+      <c r="B156" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C156" t="s">
+        <v>203</v>
+      </c>
+      <c r="E156" t="s">
+        <v>346</v>
+      </c>
+      <c r="F156" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G156" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H156" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I156" t="s">
+        <v>1133</v>
+      </c>
+      <c r="J156" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K156" t="s">
+        <v>1134</v>
+      </c>
+      <c r="L156" t="s">
+        <v>306</v>
+      </c>
+      <c r="M156" t="s">
+        <v>1127</v>
+      </c>
+      <c r="N156" t="s">
+        <v>579</v>
+      </c>
+      <c r="O156" t="s">
+        <v>177</v>
+      </c>
+      <c r="P156" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>789</v>
+      </c>
+      <c r="R156" t="s">
+        <v>40</v>
+      </c>
+      <c r="S156" t="s">
+        <v>41</v>
+      </c>
+      <c r="T156" t="s">
+        <v>39</v>
+      </c>
+      <c r="U156" t="s">
+        <v>201</v>
+      </c>
+      <c r="V156">
+        <v>24</v>
+      </c>
+      <c r="W156">
+        <v>9</v>
+      </c>
+      <c r="X156">
+        <v>15</v>
+      </c>
+      <c r="Y156">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>202</v>
+      </c>
+      <c r="B157" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C157" t="s">
+        <v>203</v>
+      </c>
+      <c r="E157" t="s">
+        <v>137</v>
+      </c>
+      <c r="F157" t="s">
+        <v>351</v>
+      </c>
+      <c r="G157" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H157" t="s">
+        <v>201</v>
+      </c>
+      <c r="I157" t="s">
+        <v>1137</v>
+      </c>
+      <c r="J157" t="s">
+        <v>1138</v>
+      </c>
+      <c r="K157" t="s">
+        <v>1139</v>
+      </c>
+      <c r="L157" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M157" t="s">
+        <v>310</v>
+      </c>
+      <c r="N157" t="s">
+        <v>201</v>
+      </c>
+      <c r="O157" t="s">
+        <v>201</v>
+      </c>
+      <c r="P157" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>201</v>
+      </c>
+      <c r="R157" t="s">
+        <v>41</v>
+      </c>
+      <c r="S157" t="s">
+        <v>201</v>
+      </c>
+      <c r="T157" t="s">
+        <v>201</v>
+      </c>
+      <c r="U157" t="s">
+        <v>201</v>
+      </c>
+      <c r="V157">
+        <v>6</v>
+      </c>
+      <c r="W157">
+        <v>5</v>
+      </c>
+      <c r="X157">
+        <v>4</v>
+      </c>
+      <c r="Y157">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>202</v>
+      </c>
+      <c r="B158" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C158" t="s">
+        <v>203</v>
+      </c>
+      <c r="E158" t="s">
+        <v>147</v>
+      </c>
+      <c r="F158" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G158" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H158" t="s">
+        <v>1140</v>
+      </c>
+      <c r="I158" t="s">
+        <v>1141</v>
+      </c>
+      <c r="J158" t="s">
+        <v>1142</v>
+      </c>
+      <c r="K158" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L158" t="s">
+        <v>1144</v>
+      </c>
+      <c r="M158" t="s">
+        <v>497</v>
+      </c>
+      <c r="N158" t="s">
+        <v>113</v>
+      </c>
+      <c r="O158" t="s">
+        <v>41</v>
+      </c>
+      <c r="P158" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>433</v>
+      </c>
+      <c r="R158" t="s">
+        <v>39</v>
+      </c>
+      <c r="S158" t="s">
+        <v>41</v>
+      </c>
+      <c r="T158" t="s">
+        <v>39</v>
+      </c>
+      <c r="U158" t="s">
+        <v>201</v>
+      </c>
+      <c r="V158">
+        <v>25</v>
+      </c>
+      <c r="W158">
+        <v>10</v>
+      </c>
+      <c r="X158">
+        <v>23</v>
+      </c>
+      <c r="Y158">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>202</v>
+      </c>
+      <c r="B159" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C159" t="s">
+        <v>203</v>
+      </c>
+      <c r="E159" t="s">
+        <v>157</v>
+      </c>
+      <c r="F159" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G159" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H159" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I159" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J159" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K159" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L159" t="s">
+        <v>153</v>
+      </c>
+      <c r="M159" t="s">
+        <v>406</v>
+      </c>
+      <c r="N159" t="s">
+        <v>177</v>
+      </c>
+      <c r="O159" t="s">
+        <v>35</v>
+      </c>
+      <c r="P159" t="s">
+        <v>1150</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>1151</v>
+      </c>
+      <c r="R159" t="s">
+        <v>41</v>
+      </c>
+      <c r="S159" t="s">
+        <v>41</v>
+      </c>
+      <c r="T159" t="s">
+        <v>39</v>
+      </c>
+      <c r="U159" t="s">
+        <v>41</v>
+      </c>
+      <c r="V159">
+        <v>19</v>
+      </c>
+      <c r="W159">
+        <v>14</v>
+      </c>
+      <c r="X159">
+        <v>12</v>
+      </c>
+      <c r="Y159">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>202</v>
+      </c>
+      <c r="B160" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C160" t="s">
+        <v>203</v>
+      </c>
+      <c r="E160" t="s">
+        <v>180</v>
+      </c>
+      <c r="F160" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G160" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H160" t="s">
+        <v>1153</v>
+      </c>
+      <c r="I160" t="s">
+        <v>1154</v>
+      </c>
+      <c r="J160" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K160" t="s">
+        <v>1156</v>
+      </c>
+      <c r="L160" t="s">
+        <v>795</v>
+      </c>
+      <c r="M160" t="s">
+        <v>1157</v>
+      </c>
+      <c r="N160" t="s">
+        <v>554</v>
+      </c>
+      <c r="O160" t="s">
+        <v>280</v>
+      </c>
+      <c r="P160" t="s">
+        <v>1158</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>527</v>
+      </c>
+      <c r="R160" t="s">
+        <v>35</v>
+      </c>
+      <c r="S160" t="s">
+        <v>40</v>
+      </c>
+      <c r="T160" t="s">
+        <v>66</v>
+      </c>
+      <c r="U160" t="s">
+        <v>39</v>
+      </c>
+      <c r="V160">
+        <v>45</v>
+      </c>
+      <c r="W160">
+        <v>40</v>
+      </c>
+      <c r="X160">
+        <v>43</v>
+      </c>
+      <c r="Y160">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>202</v>
+      </c>
+      <c r="B161" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C161" t="s">
+        <v>203</v>
+      </c>
+      <c r="E161" t="s">
+        <v>25</v>
+      </c>
+      <c r="F161" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G161" t="s">
+        <v>497</v>
+      </c>
+      <c r="H161" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I161" t="s">
+        <v>1161</v>
+      </c>
+      <c r="J161" t="s">
+        <v>1162</v>
+      </c>
+      <c r="K161" t="s">
+        <v>1163</v>
+      </c>
+      <c r="L161" t="s">
+        <v>757</v>
+      </c>
+      <c r="M161" t="s">
+        <v>133</v>
+      </c>
+      <c r="N161" t="s">
+        <v>35</v>
+      </c>
+      <c r="O161" t="s">
+        <v>41</v>
+      </c>
+      <c r="P161" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>737</v>
+      </c>
+      <c r="R161" t="s">
+        <v>38</v>
+      </c>
+      <c r="S161" t="s">
+        <v>39</v>
+      </c>
+      <c r="T161" t="s">
+        <v>38</v>
+      </c>
+      <c r="U161" t="s">
+        <v>41</v>
+      </c>
+      <c r="V161">
+        <v>40</v>
+      </c>
+      <c r="W161">
+        <v>19</v>
+      </c>
+      <c r="X161">
+        <v>20</v>
+      </c>
+      <c r="Y161">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>202</v>
+      </c>
+      <c r="B162" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C162" t="s">
+        <v>203</v>
+      </c>
+      <c r="E162" t="s">
+        <v>54</v>
+      </c>
+      <c r="F162" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G162" t="s">
+        <v>43</v>
+      </c>
+      <c r="H162" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I162" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J162" t="s">
+        <v>1166</v>
+      </c>
+      <c r="K162" t="s">
+        <v>1167</v>
+      </c>
+      <c r="L162" t="s">
+        <v>1168</v>
+      </c>
+      <c r="M162" t="s">
+        <v>782</v>
+      </c>
+      <c r="N162" t="s">
+        <v>449</v>
+      </c>
+      <c r="O162" t="s">
+        <v>41</v>
+      </c>
+      <c r="P162" t="s">
+        <v>1169</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R162" t="s">
+        <v>113</v>
+      </c>
+      <c r="S162" t="s">
+        <v>38</v>
+      </c>
+      <c r="T162" t="s">
+        <v>113</v>
+      </c>
+      <c r="U162" t="s">
+        <v>39</v>
+      </c>
+      <c r="V162">
+        <v>54</v>
+      </c>
+      <c r="W162">
+        <v>35</v>
+      </c>
+      <c r="X162">
+        <v>47</v>
+      </c>
+      <c r="Y162">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>202</v>
+      </c>
+      <c r="B163" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C163" t="s">
+        <v>203</v>
+      </c>
+      <c r="E163" t="s">
+        <v>67</v>
+      </c>
+      <c r="F163" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G163" t="s">
+        <v>749</v>
+      </c>
+      <c r="H163" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I163" t="s">
+        <v>1172</v>
+      </c>
+      <c r="J163" t="s">
+        <v>1173</v>
+      </c>
+      <c r="K163" t="s">
+        <v>1174</v>
+      </c>
+      <c r="L163" t="s">
+        <v>91</v>
+      </c>
+      <c r="M163" t="s">
+        <v>1175</v>
+      </c>
+      <c r="N163" t="s">
+        <v>495</v>
+      </c>
+      <c r="O163" t="s">
+        <v>39</v>
+      </c>
+      <c r="P163" t="s">
+        <v>1176</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>983</v>
+      </c>
+      <c r="R163" t="s">
+        <v>38</v>
+      </c>
+      <c r="S163" t="s">
+        <v>39</v>
+      </c>
+      <c r="T163" t="s">
+        <v>40</v>
+      </c>
+      <c r="U163" t="s">
+        <v>41</v>
+      </c>
+      <c r="V163">
+        <v>40</v>
+      </c>
+      <c r="W163">
+        <v>23</v>
+      </c>
+      <c r="X163">
+        <v>27</v>
+      </c>
+      <c r="Y163">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>202</v>
+      </c>
+      <c r="B164" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C164" t="s">
+        <v>203</v>
+      </c>
+      <c r="E164" t="s">
+        <v>90</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G164" t="s">
+        <v>503</v>
+      </c>
+      <c r="H164" t="s">
+        <v>1177</v>
+      </c>
+      <c r="I164" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J164" t="s">
+        <v>1179</v>
+      </c>
+      <c r="K164" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L164" t="s">
+        <v>158</v>
+      </c>
+      <c r="M164" t="s">
+        <v>192</v>
+      </c>
+      <c r="N164" t="s">
+        <v>113</v>
+      </c>
+      <c r="O164" t="s">
+        <v>201</v>
+      </c>
+      <c r="P164" t="s">
+        <v>1181</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>165</v>
+      </c>
+      <c r="R164" t="s">
+        <v>38</v>
+      </c>
+      <c r="S164" t="s">
+        <v>41</v>
+      </c>
+      <c r="T164" t="s">
+        <v>38</v>
+      </c>
+      <c r="U164" t="s">
+        <v>41</v>
+      </c>
+      <c r="V164">
+        <v>53</v>
+      </c>
+      <c r="W164">
+        <v>14</v>
+      </c>
+      <c r="X164">
+        <v>30</v>
+      </c>
+      <c r="Y164">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>202</v>
+      </c>
+      <c r="B165" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C165" t="s">
+        <v>203</v>
+      </c>
+      <c r="E165" t="s">
+        <v>347</v>
+      </c>
+      <c r="F165" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G165" t="s">
+        <v>720</v>
+      </c>
+      <c r="H165" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I165" t="s">
+        <v>1183</v>
+      </c>
+      <c r="J165" t="s">
+        <v>195</v>
+      </c>
+      <c r="K165" t="s">
+        <v>1184</v>
+      </c>
+      <c r="L165" t="s">
+        <v>261</v>
+      </c>
+      <c r="M165" t="s">
+        <v>982</v>
+      </c>
+      <c r="N165" t="s">
+        <v>488</v>
+      </c>
+      <c r="O165" t="s">
+        <v>41</v>
+      </c>
+      <c r="P165" t="s">
+        <v>1185</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>1186</v>
+      </c>
+      <c r="R165" t="s">
+        <v>40</v>
+      </c>
+      <c r="S165" t="s">
+        <v>39</v>
+      </c>
+      <c r="T165" t="s">
+        <v>40</v>
+      </c>
+      <c r="U165" t="s">
+        <v>41</v>
+      </c>
+      <c r="V165">
+        <v>40</v>
+      </c>
+      <c r="W165">
+        <v>24</v>
+      </c>
+      <c r="X165">
+        <v>37</v>
+      </c>
+      <c r="Y165">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>202</v>
+      </c>
+      <c r="B166" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C166" t="s">
+        <v>203</v>
+      </c>
+      <c r="E166" t="s">
+        <v>147</v>
+      </c>
+      <c r="F166" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G166" t="s">
+        <v>391</v>
+      </c>
+      <c r="H166" t="s">
+        <v>1187</v>
+      </c>
+      <c r="I166" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J166" t="s">
+        <v>1189</v>
+      </c>
+      <c r="K166" t="s">
+        <v>1190</v>
+      </c>
+      <c r="L166" t="s">
+        <v>1074</v>
+      </c>
+      <c r="M166" t="s">
+        <v>1026</v>
+      </c>
+      <c r="N166" t="s">
+        <v>35</v>
+      </c>
+      <c r="O166" t="s">
+        <v>201</v>
+      </c>
+      <c r="P166" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>488</v>
+      </c>
+      <c r="R166" t="s">
+        <v>39</v>
+      </c>
+      <c r="S166" t="s">
+        <v>41</v>
+      </c>
+      <c r="T166" t="s">
+        <v>39</v>
+      </c>
+      <c r="U166" t="s">
+        <v>201</v>
+      </c>
+      <c r="V166">
+        <v>25</v>
+      </c>
+      <c r="W166">
+        <v>7</v>
+      </c>
+      <c r="X166">
+        <v>24</v>
+      </c>
+      <c r="Y166">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>202</v>
+      </c>
+      <c r="B167" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C167" t="s">
+        <v>203</v>
+      </c>
+      <c r="E167" t="s">
+        <v>346</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G167" t="s">
+        <v>255</v>
+      </c>
+      <c r="H167" t="s">
+        <v>1191</v>
+      </c>
+      <c r="I167" t="s">
+        <v>1192</v>
+      </c>
+      <c r="J167" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K167" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L167" t="s">
+        <v>635</v>
+      </c>
+      <c r="M167" t="s">
+        <v>1195</v>
+      </c>
+      <c r="N167" t="s">
+        <v>213</v>
+      </c>
+      <c r="O167" t="s">
+        <v>39</v>
+      </c>
+      <c r="P167" t="s">
+        <v>713</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>977</v>
+      </c>
+      <c r="R167" t="s">
+        <v>113</v>
+      </c>
+      <c r="S167" t="s">
+        <v>39</v>
+      </c>
+      <c r="T167" t="s">
+        <v>66</v>
+      </c>
+      <c r="U167" t="s">
+        <v>41</v>
+      </c>
+      <c r="V167">
+        <v>54</v>
+      </c>
+      <c r="W167">
+        <v>21</v>
+      </c>
+      <c r="X167">
+        <v>43</v>
+      </c>
+      <c r="Y167">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>202</v>
+      </c>
+      <c r="B168" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C168" t="s">
+        <v>203</v>
+      </c>
+      <c r="E168" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G168" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H168" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I168" t="s">
+        <v>1199</v>
+      </c>
+      <c r="J168" t="s">
+        <v>430</v>
+      </c>
+      <c r="K168" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L168" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M168" t="s">
+        <v>133</v>
+      </c>
+      <c r="N168" t="s">
+        <v>213</v>
+      </c>
+      <c r="O168" t="s">
+        <v>39</v>
+      </c>
+      <c r="P168" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>1049</v>
+      </c>
+      <c r="R168" t="s">
+        <v>113</v>
+      </c>
+      <c r="S168" t="s">
+        <v>40</v>
+      </c>
+      <c r="T168" t="s">
+        <v>66</v>
+      </c>
+      <c r="U168" t="s">
+        <v>41</v>
+      </c>
+      <c r="V168">
+        <v>49</v>
+      </c>
+      <c r="W168">
+        <v>24</v>
+      </c>
+      <c r="X168">
+        <v>37</v>
+      </c>
+      <c r="Y168">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>202</v>
+      </c>
+      <c r="B169" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C169" t="s">
+        <v>203</v>
+      </c>
+      <c r="E169" t="s">
+        <v>137</v>
+      </c>
+      <c r="F169" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G169" t="s">
+        <v>1201</v>
+      </c>
+      <c r="H169" t="s">
+        <v>201</v>
+      </c>
+      <c r="I169" t="s">
+        <v>1202</v>
+      </c>
+      <c r="J169" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K169" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L169" t="s">
+        <v>254</v>
+      </c>
+      <c r="M169" t="s">
+        <v>1205</v>
+      </c>
+      <c r="N169" t="s">
+        <v>201</v>
+      </c>
+      <c r="O169" t="s">
+        <v>201</v>
+      </c>
+      <c r="P169" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>201</v>
+      </c>
+      <c r="R169" t="s">
+        <v>41</v>
+      </c>
+      <c r="S169" t="s">
+        <v>201</v>
+      </c>
+      <c r="T169" t="s">
+        <v>201</v>
+      </c>
+      <c r="U169" t="s">
+        <v>201</v>
+      </c>
+      <c r="V169">
+        <v>4</v>
+      </c>
+      <c r="W169">
+        <v>3</v>
+      </c>
+      <c r="X169">
+        <v>9</v>
+      </c>
+      <c r="Y169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>202</v>
+      </c>
+      <c r="B170" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C170" t="s">
+        <v>203</v>
+      </c>
+      <c r="E170" t="s">
+        <v>126</v>
+      </c>
+      <c r="F170" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G170" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H170" t="s">
+        <v>1207</v>
+      </c>
+      <c r="I170" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J170" t="s">
+        <v>430</v>
+      </c>
+      <c r="K170" t="s">
+        <v>1209</v>
+      </c>
+      <c r="L170" t="s">
+        <v>270</v>
+      </c>
+      <c r="M170" t="s">
+        <v>1210</v>
+      </c>
+      <c r="N170" t="s">
+        <v>66</v>
+      </c>
+      <c r="O170" t="s">
+        <v>201</v>
+      </c>
+      <c r="P170" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>455</v>
+      </c>
+      <c r="R170" t="s">
+        <v>40</v>
+      </c>
+      <c r="S170" t="s">
+        <v>39</v>
+      </c>
+      <c r="T170" t="s">
+        <v>38</v>
+      </c>
+      <c r="U170" t="s">
+        <v>41</v>
+      </c>
+      <c r="V170">
+        <v>37</v>
+      </c>
+      <c r="W170">
+        <v>9</v>
+      </c>
+      <c r="X170">
+        <v>37</v>
+      </c>
+      <c r="Y170">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>202</v>
+      </c>
+      <c r="B171" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C171" t="s">
+        <v>203</v>
+      </c>
+      <c r="E171" t="s">
+        <v>157</v>
+      </c>
+      <c r="F171" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G171" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H171" t="s">
+        <v>1213</v>
+      </c>
+      <c r="I171" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J171" t="s">
+        <v>1215</v>
+      </c>
+      <c r="K171" t="s">
+        <v>1216</v>
+      </c>
+      <c r="L171" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M171" t="s">
+        <v>414</v>
+      </c>
+      <c r="N171" t="s">
+        <v>213</v>
+      </c>
+      <c r="O171" t="s">
+        <v>39</v>
+      </c>
+      <c r="P171" t="s">
+        <v>1218</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>1219</v>
+      </c>
+      <c r="R171" t="s">
+        <v>113</v>
+      </c>
+      <c r="S171" t="s">
+        <v>40</v>
+      </c>
+      <c r="T171" t="s">
+        <v>66</v>
+      </c>
+      <c r="U171" t="s">
+        <v>39</v>
+      </c>
+      <c r="V171">
+        <v>43</v>
+      </c>
+      <c r="W171">
+        <v>31</v>
+      </c>
+      <c r="X171">
+        <v>27</v>
+      </c>
+      <c r="Y171">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>202</v>
+      </c>
+      <c r="B172" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C172" t="s">
+        <v>203</v>
+      </c>
+      <c r="E172" t="s">
+        <v>180</v>
+      </c>
+      <c r="F172" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G172" t="s">
+        <v>671</v>
+      </c>
+      <c r="H172" t="s">
+        <v>1220</v>
+      </c>
+      <c r="I172" t="s">
+        <v>1221</v>
+      </c>
+      <c r="J172" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K172" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L172" t="s">
+        <v>1224</v>
+      </c>
+      <c r="M172" t="s">
+        <v>415</v>
+      </c>
+      <c r="N172" t="s">
+        <v>99</v>
+      </c>
+      <c r="O172" t="s">
+        <v>40</v>
+      </c>
+      <c r="P172" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>1225</v>
+      </c>
+      <c r="R172" t="s">
+        <v>495</v>
+      </c>
+      <c r="S172" t="s">
+        <v>449</v>
+      </c>
+      <c r="T172" t="s">
+        <v>449</v>
+      </c>
+      <c r="U172" t="s">
+        <v>113</v>
+      </c>
+      <c r="V172">
+        <v>85</v>
+      </c>
+      <c r="W172">
+        <v>92</v>
+      </c>
+      <c r="X172">
+        <v>102</v>
+      </c>
+      <c r="Y172">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BC1A6E-043C-2D4C-B733-7C35102A6254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845EAD56-AEA5-3B46-BBA3-E4A0AF67CEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3131" uniqueCount="1226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3846" uniqueCount="1439">
   <si>
     <t>Type</t>
   </si>
@@ -3714,6 +3714,645 @@
   </si>
   <si>
     <t>5.2</t>
+  </si>
+  <si>
+    <t>101.03</t>
+  </si>
+  <si>
+    <t>10.07</t>
+  </si>
+  <si>
+    <t>467.17</t>
+  </si>
+  <si>
+    <t>421.49</t>
+  </si>
+  <si>
+    <t>29.53</t>
+  </si>
+  <si>
+    <t>99.65</t>
+  </si>
+  <si>
+    <t>58.9</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>18.15</t>
+  </si>
+  <si>
+    <t>1.94</t>
+  </si>
+  <si>
+    <t>216.57</t>
+  </si>
+  <si>
+    <t>90.09</t>
+  </si>
+  <si>
+    <t>106.98</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
+    <t>63.33</t>
+  </si>
+  <si>
+    <t>565.06</t>
+  </si>
+  <si>
+    <t>29.76</t>
+  </si>
+  <si>
+    <t>94.32</t>
+  </si>
+  <si>
+    <t>8.17</t>
+  </si>
+  <si>
+    <t>67.1</t>
+  </si>
+  <si>
+    <t>20.1</t>
+  </si>
+  <si>
+    <t>18.12</t>
+  </si>
+  <si>
+    <t>1.89</t>
+  </si>
+  <si>
+    <t>190.69</t>
+  </si>
+  <si>
+    <t>73.57</t>
+  </si>
+  <si>
+    <t>28.63</t>
+  </si>
+  <si>
+    <t>104.25</t>
+  </si>
+  <si>
+    <t>6.96</t>
+  </si>
+  <si>
+    <t>20.6</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>80.2</t>
+  </si>
+  <si>
+    <t>9.59</t>
+  </si>
+  <si>
+    <t>212.15</t>
+  </si>
+  <si>
+    <t>477.07</t>
+  </si>
+  <si>
+    <t>27.23</t>
+  </si>
+  <si>
+    <t>119.62</t>
+  </si>
+  <si>
+    <t>19.4</t>
+  </si>
+  <si>
+    <t>1.88</t>
+  </si>
+  <si>
+    <t>66.07</t>
+  </si>
+  <si>
+    <t>77.42</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>96.82</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>79.48</t>
+  </si>
+  <si>
+    <t>810.73</t>
+  </si>
+  <si>
+    <t>368.54</t>
+  </si>
+  <si>
+    <t>106.94</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>95.0</t>
+  </si>
+  <si>
+    <t>84.45</t>
+  </si>
+  <si>
+    <t>554.75</t>
+  </si>
+  <si>
+    <t>349.37</t>
+  </si>
+  <si>
+    <t>92.75</t>
+  </si>
+  <si>
+    <t>69.3</t>
+  </si>
+  <si>
+    <t>17.2</t>
+  </si>
+  <si>
+    <t>11.16</t>
+  </si>
+  <si>
+    <t>637.35</t>
+  </si>
+  <si>
+    <t>463.26</t>
+  </si>
+  <si>
+    <t>31.65</t>
+  </si>
+  <si>
+    <t>110.47</t>
+  </si>
+  <si>
+    <t>7.71</t>
+  </si>
+  <si>
+    <t>6.19</t>
+  </si>
+  <si>
+    <t>80.9</t>
+  </si>
+  <si>
+    <t>18.4</t>
+  </si>
+  <si>
+    <t>87.82</t>
+  </si>
+  <si>
+    <t>9.63</t>
+  </si>
+  <si>
+    <t>825.25</t>
+  </si>
+  <si>
+    <t>402.21</t>
+  </si>
+  <si>
+    <t>30.01</t>
+  </si>
+  <si>
+    <t>109.71</t>
+  </si>
+  <si>
+    <t>103.6</t>
+  </si>
+  <si>
+    <t>9.65</t>
+  </si>
+  <si>
+    <t>366.98</t>
+  </si>
+  <si>
+    <t>420.12</t>
+  </si>
+  <si>
+    <t>33.02</t>
+  </si>
+  <si>
+    <t>95.5</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>46.5</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>908.11</t>
+  </si>
+  <si>
+    <t>469.2</t>
+  </si>
+  <si>
+    <t>33.1</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>92.3</t>
+  </si>
+  <si>
+    <t>44.0</t>
+  </si>
+  <si>
+    <t>10.51</t>
+  </si>
+  <si>
+    <t>547.84</t>
+  </si>
+  <si>
+    <t>448.09</t>
+  </si>
+  <si>
+    <t>104.06</t>
+  </si>
+  <si>
+    <t>7.89</t>
+  </si>
+  <si>
+    <t>5.53</t>
+  </si>
+  <si>
+    <t>77.4</t>
+  </si>
+  <si>
+    <t>10.2</t>
+  </si>
+  <si>
+    <t>CDF T4 VS Tournon 26/09/2026</t>
+  </si>
+  <si>
+    <t>88.12</t>
+  </si>
+  <si>
+    <t>78.76</t>
+  </si>
+  <si>
+    <t>298.6</t>
+  </si>
+  <si>
+    <t>24.56</t>
+  </si>
+  <si>
+    <t>68.64</t>
+  </si>
+  <si>
+    <t>4.61</t>
+  </si>
+  <si>
+    <t>260.36</t>
+  </si>
+  <si>
+    <t>20.2</t>
+  </si>
+  <si>
+    <t>52.32</t>
+  </si>
+  <si>
+    <t>5.29</t>
+  </si>
+  <si>
+    <t>19.12</t>
+  </si>
+  <si>
+    <t>295.49</t>
+  </si>
+  <si>
+    <t>23.65</t>
+  </si>
+  <si>
+    <t>57.72</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>271.11</t>
+  </si>
+  <si>
+    <t>20.28</t>
+  </si>
+  <si>
+    <t>58.95</t>
+  </si>
+  <si>
+    <t>50.58</t>
+  </si>
+  <si>
+    <t>421.13</t>
+  </si>
+  <si>
+    <t>24.66</t>
+  </si>
+  <si>
+    <t>80.51</t>
+  </si>
+  <si>
+    <t>7.64</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+  <si>
+    <t>7.16</t>
+  </si>
+  <si>
+    <t>1278.46</t>
+  </si>
+  <si>
+    <t>318.72</t>
+  </si>
+  <si>
+    <t>25.09</t>
+  </si>
+  <si>
+    <t>81.3</t>
+  </si>
+  <si>
+    <t>5.81</t>
+  </si>
+  <si>
+    <t>1.27</t>
+  </si>
+  <si>
+    <t>210.8</t>
+  </si>
+  <si>
+    <t>55.7</t>
+  </si>
+  <si>
+    <t>297.6</t>
+  </si>
+  <si>
+    <t>25.58</t>
+  </si>
+  <si>
+    <t>61.51</t>
+  </si>
+  <si>
+    <t>7.54</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>1250.04</t>
+  </si>
+  <si>
+    <t>398.61</t>
+  </si>
+  <si>
+    <t>24.91</t>
+  </si>
+  <si>
+    <t>89.67</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>209.9</t>
+  </si>
+  <si>
+    <t>18.25</t>
+  </si>
+  <si>
+    <t>289.27</t>
+  </si>
+  <si>
+    <t>22.67</t>
+  </si>
+  <si>
+    <t>57.58</t>
+  </si>
+  <si>
+    <t>5.93</t>
+  </si>
+  <si>
+    <t>121.41</t>
+  </si>
+  <si>
+    <t>274.34</t>
+  </si>
+  <si>
+    <t>24.86</t>
+  </si>
+  <si>
+    <t>67.28</t>
+  </si>
+  <si>
+    <t>5.91</t>
+  </si>
+  <si>
+    <t>20.9</t>
+  </si>
+  <si>
+    <t>22.81</t>
+  </si>
+  <si>
+    <t>687.61</t>
+  </si>
+  <si>
+    <t>23.01</t>
+  </si>
+  <si>
+    <t>70.77</t>
+  </si>
+  <si>
+    <t>70.07</t>
+  </si>
+  <si>
+    <t>565.22</t>
+  </si>
+  <si>
+    <t>29.42</t>
+  </si>
+  <si>
+    <t>60.44</t>
+  </si>
+  <si>
+    <t>7.43</t>
+  </si>
+  <si>
+    <t>99.98</t>
+  </si>
+  <si>
+    <t>41.08</t>
+  </si>
+  <si>
+    <t>268.01</t>
+  </si>
+  <si>
+    <t>23.3</t>
+  </si>
+  <si>
+    <t>50.28</t>
+  </si>
+  <si>
+    <t>97.25</t>
+  </si>
+  <si>
+    <t>4.02</t>
+  </si>
+  <si>
+    <t>16.31</t>
+  </si>
+  <si>
+    <t>227.86</t>
+  </si>
+  <si>
+    <t>41.35</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>32.25</t>
+  </si>
+  <si>
+    <t>254.27</t>
+  </si>
+  <si>
+    <t>47.87</t>
+  </si>
+  <si>
+    <t>4.34</t>
+  </si>
+  <si>
+    <t>14.0</t>
+  </si>
+  <si>
+    <t>274.19</t>
+  </si>
+  <si>
+    <t>21.74</t>
+  </si>
+  <si>
+    <t>43.4</t>
+  </si>
+  <si>
+    <t>19.5</t>
+  </si>
+  <si>
+    <t>334.82</t>
+  </si>
+  <si>
+    <t>21.54</t>
+  </si>
+  <si>
+    <t>56.98</t>
+  </si>
+  <si>
+    <t>33.47</t>
+  </si>
+  <si>
+    <t>269.35</t>
+  </si>
+  <si>
+    <t>23.9</t>
+  </si>
+  <si>
+    <t>50.73</t>
+  </si>
+  <si>
+    <t>46.04</t>
+  </si>
+  <si>
+    <t>282.79</t>
+  </si>
+  <si>
+    <t>22.31</t>
+  </si>
+  <si>
+    <t>50.33</t>
+  </si>
+  <si>
+    <t>5.61</t>
+  </si>
+  <si>
+    <t>4.93</t>
+  </si>
+  <si>
+    <t>24.69</t>
+  </si>
+  <si>
+    <t>313.74</t>
+  </si>
+  <si>
+    <t>22.93</t>
+  </si>
+  <si>
+    <t>49.34</t>
+  </si>
+  <si>
+    <t>106.07</t>
+  </si>
+  <si>
+    <t>354.8</t>
+  </si>
+  <si>
+    <t>24.02</t>
+  </si>
+  <si>
+    <t>59.95</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>43.04</t>
+  </si>
+  <si>
+    <t>291.89</t>
+  </si>
+  <si>
+    <t>22.78</t>
+  </si>
+  <si>
+    <t>51.0</t>
+  </si>
+  <si>
+    <t>73.58</t>
+  </si>
+  <si>
+    <t>522.56</t>
+  </si>
+  <si>
+    <t>23.49</t>
+  </si>
+  <si>
+    <t>43.8</t>
+  </si>
+  <si>
+    <t>11.94</t>
+  </si>
+  <si>
+    <t>227.32</t>
+  </si>
+  <si>
+    <t>41.45</t>
   </si>
 </sst>
 </file>
@@ -4092,7 +4731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y172"/>
+  <dimension ref="A1:Y209"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
@@ -17073,6 +17712,2780 @@
         <v>103</v>
       </c>
     </row>
+    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B173" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C173" t="s">
+        <v>203</v>
+      </c>
+      <c r="E173" t="s">
+        <v>25</v>
+      </c>
+      <c r="F173" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G173" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H173" t="s">
+        <v>1228</v>
+      </c>
+      <c r="I173" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J173" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K173" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L173" t="s">
+        <v>446</v>
+      </c>
+      <c r="M173" t="s">
+        <v>362</v>
+      </c>
+      <c r="N173" t="s">
+        <v>232</v>
+      </c>
+      <c r="O173" t="s">
+        <v>449</v>
+      </c>
+      <c r="P173" t="s">
+        <v>1232</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>1233</v>
+      </c>
+      <c r="R173" t="s">
+        <v>66</v>
+      </c>
+      <c r="S173" t="s">
+        <v>38</v>
+      </c>
+      <c r="T173" t="s">
+        <v>113</v>
+      </c>
+      <c r="U173" t="s">
+        <v>41</v>
+      </c>
+      <c r="V173">
+        <v>73</v>
+      </c>
+      <c r="W173">
+        <v>33</v>
+      </c>
+      <c r="X173">
+        <v>54</v>
+      </c>
+      <c r="Y173">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B174" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C174" t="s">
+        <v>203</v>
+      </c>
+      <c r="E174" t="s">
+        <v>42</v>
+      </c>
+      <c r="F174" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G174" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H174" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I174" t="s">
+        <v>1237</v>
+      </c>
+      <c r="J174" t="s">
+        <v>632</v>
+      </c>
+      <c r="K174" t="s">
+        <v>1238</v>
+      </c>
+      <c r="L174" t="s">
+        <v>989</v>
+      </c>
+      <c r="M174" t="s">
+        <v>439</v>
+      </c>
+      <c r="N174" t="s">
+        <v>495</v>
+      </c>
+      <c r="O174" t="s">
+        <v>35</v>
+      </c>
+      <c r="P174" t="s">
+        <v>1239</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>234</v>
+      </c>
+      <c r="R174" t="s">
+        <v>38</v>
+      </c>
+      <c r="S174" t="s">
+        <v>41</v>
+      </c>
+      <c r="T174" t="s">
+        <v>39</v>
+      </c>
+      <c r="U174" t="s">
+        <v>201</v>
+      </c>
+      <c r="V174">
+        <v>13</v>
+      </c>
+      <c r="W174">
+        <v>12</v>
+      </c>
+      <c r="X174">
+        <v>16</v>
+      </c>
+      <c r="Y174">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B175" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C175" t="s">
+        <v>203</v>
+      </c>
+      <c r="E175" t="s">
+        <v>54</v>
+      </c>
+      <c r="F175" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G175" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H175" t="s">
+        <v>1241</v>
+      </c>
+      <c r="I175" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J175" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K175" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L175" t="s">
+        <v>1244</v>
+      </c>
+      <c r="M175" t="s">
+        <v>426</v>
+      </c>
+      <c r="N175" t="s">
+        <v>647</v>
+      </c>
+      <c r="O175" t="s">
+        <v>495</v>
+      </c>
+      <c r="P175" t="s">
+        <v>1245</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>1246</v>
+      </c>
+      <c r="R175" t="s">
+        <v>35</v>
+      </c>
+      <c r="S175" t="s">
+        <v>40</v>
+      </c>
+      <c r="T175" t="s">
+        <v>113</v>
+      </c>
+      <c r="U175" t="s">
+        <v>39</v>
+      </c>
+      <c r="V175">
+        <v>57</v>
+      </c>
+      <c r="W175">
+        <v>28</v>
+      </c>
+      <c r="X175">
+        <v>35</v>
+      </c>
+      <c r="Y175">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B176" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C176" t="s">
+        <v>203</v>
+      </c>
+      <c r="E176" t="s">
+        <v>67</v>
+      </c>
+      <c r="F176" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G176" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H176" t="s">
+        <v>1249</v>
+      </c>
+      <c r="I176" t="s">
+        <v>1250</v>
+      </c>
+      <c r="J176" t="s">
+        <v>1251</v>
+      </c>
+      <c r="K176" t="s">
+        <v>1252</v>
+      </c>
+      <c r="L176" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M176" t="s">
+        <v>503</v>
+      </c>
+      <c r="N176" t="s">
+        <v>51</v>
+      </c>
+      <c r="O176" t="s">
+        <v>113</v>
+      </c>
+      <c r="P176" t="s">
+        <v>1254</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>1255</v>
+      </c>
+      <c r="R176" t="s">
+        <v>41</v>
+      </c>
+      <c r="S176" t="s">
+        <v>41</v>
+      </c>
+      <c r="T176" t="s">
+        <v>41</v>
+      </c>
+      <c r="U176" t="s">
+        <v>41</v>
+      </c>
+      <c r="V176">
+        <v>10</v>
+      </c>
+      <c r="W176">
+        <v>8</v>
+      </c>
+      <c r="X176">
+        <v>4</v>
+      </c>
+      <c r="Y176">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B177" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C177" t="s">
+        <v>203</v>
+      </c>
+      <c r="E177" t="s">
+        <v>90</v>
+      </c>
+      <c r="F177" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G177" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H177" t="s">
+        <v>1258</v>
+      </c>
+      <c r="I177" t="s">
+        <v>1259</v>
+      </c>
+      <c r="J177" t="s">
+        <v>1260</v>
+      </c>
+      <c r="K177" t="s">
+        <v>1261</v>
+      </c>
+      <c r="L177" t="s">
+        <v>143</v>
+      </c>
+      <c r="M177" t="s">
+        <v>511</v>
+      </c>
+      <c r="N177" t="s">
+        <v>213</v>
+      </c>
+      <c r="O177" t="s">
+        <v>39</v>
+      </c>
+      <c r="P177" t="s">
+        <v>713</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>1049</v>
+      </c>
+      <c r="R177" t="s">
+        <v>113</v>
+      </c>
+      <c r="S177" t="s">
+        <v>39</v>
+      </c>
+      <c r="T177" t="s">
+        <v>66</v>
+      </c>
+      <c r="U177" t="s">
+        <v>41</v>
+      </c>
+      <c r="V177">
+        <v>73</v>
+      </c>
+      <c r="W177">
+        <v>27</v>
+      </c>
+      <c r="X177">
+        <v>60</v>
+      </c>
+      <c r="Y177">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B178" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C178" t="s">
+        <v>203</v>
+      </c>
+      <c r="E178" t="s">
+        <v>102</v>
+      </c>
+      <c r="F178" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G178" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H178" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I178" t="s">
+        <v>1265</v>
+      </c>
+      <c r="J178" t="s">
+        <v>1266</v>
+      </c>
+      <c r="K178" t="s">
+        <v>1267</v>
+      </c>
+      <c r="L178" t="s">
+        <v>289</v>
+      </c>
+      <c r="M178" t="s">
+        <v>759</v>
+      </c>
+      <c r="N178" t="s">
+        <v>40</v>
+      </c>
+      <c r="O178" t="s">
+        <v>39</v>
+      </c>
+      <c r="P178" t="s">
+        <v>722</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R178" t="s">
+        <v>41</v>
+      </c>
+      <c r="S178" t="s">
+        <v>201</v>
+      </c>
+      <c r="T178" t="s">
+        <v>41</v>
+      </c>
+      <c r="U178" t="s">
+        <v>201</v>
+      </c>
+      <c r="V178">
+        <v>17</v>
+      </c>
+      <c r="W178">
+        <v>6</v>
+      </c>
+      <c r="X178">
+        <v>8</v>
+      </c>
+      <c r="Y178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B179" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C179" t="s">
+        <v>203</v>
+      </c>
+      <c r="E179" t="s">
+        <v>347</v>
+      </c>
+      <c r="F179" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G179" t="s">
+        <v>1255</v>
+      </c>
+      <c r="H179" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I179" t="s">
+        <v>1271</v>
+      </c>
+      <c r="J179" t="s">
+        <v>140</v>
+      </c>
+      <c r="K179" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L179" t="s">
+        <v>615</v>
+      </c>
+      <c r="M179" t="s">
+        <v>86</v>
+      </c>
+      <c r="N179" t="s">
+        <v>1273</v>
+      </c>
+      <c r="O179" t="s">
+        <v>63</v>
+      </c>
+      <c r="P179" t="s">
+        <v>1274</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>796</v>
+      </c>
+      <c r="R179" t="s">
+        <v>488</v>
+      </c>
+      <c r="S179" t="s">
+        <v>66</v>
+      </c>
+      <c r="T179" t="s">
+        <v>113</v>
+      </c>
+      <c r="U179" t="s">
+        <v>39</v>
+      </c>
+      <c r="V179">
+        <v>61</v>
+      </c>
+      <c r="W179">
+        <v>28</v>
+      </c>
+      <c r="X179">
+        <v>53</v>
+      </c>
+      <c r="Y179">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B180" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C180" t="s">
+        <v>203</v>
+      </c>
+      <c r="E180" t="s">
+        <v>895</v>
+      </c>
+      <c r="F180" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G180" t="s">
+        <v>884</v>
+      </c>
+      <c r="H180" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I180" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J180" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K180" t="s">
+        <v>1278</v>
+      </c>
+      <c r="L180" t="s">
+        <v>867</v>
+      </c>
+      <c r="M180" t="s">
+        <v>1210</v>
+      </c>
+      <c r="N180" t="s">
+        <v>324</v>
+      </c>
+      <c r="O180" t="s">
+        <v>51</v>
+      </c>
+      <c r="P180" t="s">
+        <v>1279</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>1280</v>
+      </c>
+      <c r="R180" t="s">
+        <v>337</v>
+      </c>
+      <c r="S180" t="s">
+        <v>38</v>
+      </c>
+      <c r="T180" t="s">
+        <v>35</v>
+      </c>
+      <c r="U180" t="s">
+        <v>41</v>
+      </c>
+      <c r="V180">
+        <v>62</v>
+      </c>
+      <c r="W180">
+        <v>29</v>
+      </c>
+      <c r="X180">
+        <v>34</v>
+      </c>
+      <c r="Y180">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B181" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C181" t="s">
+        <v>203</v>
+      </c>
+      <c r="E181" t="s">
+        <v>126</v>
+      </c>
+      <c r="F181" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G181" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H181" t="s">
+        <v>1282</v>
+      </c>
+      <c r="I181" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J181" t="s">
+        <v>1284</v>
+      </c>
+      <c r="K181" t="s">
+        <v>1285</v>
+      </c>
+      <c r="L181" t="s">
+        <v>1286</v>
+      </c>
+      <c r="M181" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N181" t="s">
+        <v>455</v>
+      </c>
+      <c r="O181" t="s">
+        <v>555</v>
+      </c>
+      <c r="P181" t="s">
+        <v>1288</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>1289</v>
+      </c>
+      <c r="R181" t="s">
+        <v>449</v>
+      </c>
+      <c r="S181" t="s">
+        <v>40</v>
+      </c>
+      <c r="T181" t="s">
+        <v>113</v>
+      </c>
+      <c r="U181" t="s">
+        <v>39</v>
+      </c>
+      <c r="V181">
+        <v>59</v>
+      </c>
+      <c r="W181">
+        <v>39</v>
+      </c>
+      <c r="X181">
+        <v>65</v>
+      </c>
+      <c r="Y181">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B182" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C182" t="s">
+        <v>203</v>
+      </c>
+      <c r="E182" t="s">
+        <v>346</v>
+      </c>
+      <c r="F182" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G182" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H182" t="s">
+        <v>1292</v>
+      </c>
+      <c r="I182" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J182" t="s">
+        <v>1294</v>
+      </c>
+      <c r="K182" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L182" t="s">
+        <v>802</v>
+      </c>
+      <c r="M182" t="s">
+        <v>289</v>
+      </c>
+      <c r="N182" t="s">
+        <v>62</v>
+      </c>
+      <c r="O182" t="s">
+        <v>213</v>
+      </c>
+      <c r="P182" t="s">
+        <v>1296</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>1030</v>
+      </c>
+      <c r="R182" t="s">
+        <v>337</v>
+      </c>
+      <c r="S182" t="s">
+        <v>113</v>
+      </c>
+      <c r="T182" t="s">
+        <v>113</v>
+      </c>
+      <c r="U182" t="s">
+        <v>41</v>
+      </c>
+      <c r="V182">
+        <v>64</v>
+      </c>
+      <c r="W182">
+        <v>22</v>
+      </c>
+      <c r="X182">
+        <v>50</v>
+      </c>
+      <c r="Y182">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B183" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C183" t="s">
+        <v>203</v>
+      </c>
+      <c r="E183" t="s">
+        <v>147</v>
+      </c>
+      <c r="F183" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G183" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H183" t="s">
+        <v>1298</v>
+      </c>
+      <c r="I183" t="s">
+        <v>1299</v>
+      </c>
+      <c r="J183" t="s">
+        <v>1300</v>
+      </c>
+      <c r="K183" t="s">
+        <v>1301</v>
+      </c>
+      <c r="L183" t="s">
+        <v>1144</v>
+      </c>
+      <c r="M183" t="s">
+        <v>293</v>
+      </c>
+      <c r="N183" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O183" t="s">
+        <v>280</v>
+      </c>
+      <c r="P183" t="s">
+        <v>1303</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>1304</v>
+      </c>
+      <c r="R183" t="s">
+        <v>113</v>
+      </c>
+      <c r="S183" t="s">
+        <v>38</v>
+      </c>
+      <c r="T183" t="s">
+        <v>38</v>
+      </c>
+      <c r="U183" t="s">
+        <v>41</v>
+      </c>
+      <c r="V183">
+        <v>45</v>
+      </c>
+      <c r="W183">
+        <v>16</v>
+      </c>
+      <c r="X183">
+        <v>46</v>
+      </c>
+      <c r="Y183">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B184" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C184" t="s">
+        <v>203</v>
+      </c>
+      <c r="E184" t="s">
+        <v>157</v>
+      </c>
+      <c r="F184" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G184" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H184" t="s">
+        <v>1305</v>
+      </c>
+      <c r="I184" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J184" t="s">
+        <v>1307</v>
+      </c>
+      <c r="K184" t="s">
+        <v>1285</v>
+      </c>
+      <c r="L184" t="s">
+        <v>1308</v>
+      </c>
+      <c r="M184" t="s">
+        <v>1067</v>
+      </c>
+      <c r="N184" t="s">
+        <v>1309</v>
+      </c>
+      <c r="O184" t="s">
+        <v>641</v>
+      </c>
+      <c r="P184" t="s">
+        <v>1310</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>1311</v>
+      </c>
+      <c r="R184" t="s">
+        <v>488</v>
+      </c>
+      <c r="S184" t="s">
+        <v>113</v>
+      </c>
+      <c r="T184" t="s">
+        <v>449</v>
+      </c>
+      <c r="U184" t="s">
+        <v>38</v>
+      </c>
+      <c r="V184">
+        <v>80</v>
+      </c>
+      <c r="W184">
+        <v>45</v>
+      </c>
+      <c r="X184">
+        <v>53</v>
+      </c>
+      <c r="Y184">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B185" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C185" t="s">
+        <v>203</v>
+      </c>
+      <c r="E185" t="s">
+        <v>180</v>
+      </c>
+      <c r="F185" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G185" t="s">
+        <v>1312</v>
+      </c>
+      <c r="H185" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I185" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J185" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K185" t="s">
+        <v>1315</v>
+      </c>
+      <c r="L185" t="s">
+        <v>1316</v>
+      </c>
+      <c r="M185" t="s">
+        <v>1317</v>
+      </c>
+      <c r="N185" t="s">
+        <v>902</v>
+      </c>
+      <c r="O185" t="s">
+        <v>337</v>
+      </c>
+      <c r="P185" t="s">
+        <v>1318</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>1319</v>
+      </c>
+      <c r="R185" t="s">
+        <v>337</v>
+      </c>
+      <c r="S185" t="s">
+        <v>40</v>
+      </c>
+      <c r="T185" t="s">
+        <v>113</v>
+      </c>
+      <c r="U185" t="s">
+        <v>41</v>
+      </c>
+      <c r="V185">
+        <v>67</v>
+      </c>
+      <c r="W185">
+        <v>20</v>
+      </c>
+      <c r="X185">
+        <v>46</v>
+      </c>
+      <c r="Y185">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>202</v>
+      </c>
+      <c r="B186" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C186" t="s">
+        <v>203</v>
+      </c>
+      <c r="E186" t="s">
+        <v>25</v>
+      </c>
+      <c r="F186" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G186" t="s">
+        <v>689</v>
+      </c>
+      <c r="H186" t="s">
+        <v>1322</v>
+      </c>
+      <c r="I186" t="s">
+        <v>1323</v>
+      </c>
+      <c r="J186" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K186" t="s">
+        <v>1325</v>
+      </c>
+      <c r="L186" t="s">
+        <v>270</v>
+      </c>
+      <c r="M186" t="s">
+        <v>221</v>
+      </c>
+      <c r="N186" t="s">
+        <v>337</v>
+      </c>
+      <c r="O186" t="s">
+        <v>201</v>
+      </c>
+      <c r="P186" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>471</v>
+      </c>
+      <c r="R186" t="s">
+        <v>40</v>
+      </c>
+      <c r="S186" t="s">
+        <v>41</v>
+      </c>
+      <c r="T186" t="s">
+        <v>40</v>
+      </c>
+      <c r="U186" t="s">
+        <v>41</v>
+      </c>
+      <c r="V186">
+        <v>48</v>
+      </c>
+      <c r="W186">
+        <v>21</v>
+      </c>
+      <c r="X186">
+        <v>31</v>
+      </c>
+      <c r="Y186">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>202</v>
+      </c>
+      <c r="B187" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C187" t="s">
+        <v>203</v>
+      </c>
+      <c r="E187" t="s">
+        <v>42</v>
+      </c>
+      <c r="F187" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G187" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H187" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I187" t="s">
+        <v>1327</v>
+      </c>
+      <c r="J187" t="s">
+        <v>1328</v>
+      </c>
+      <c r="K187" t="s">
+        <v>1329</v>
+      </c>
+      <c r="L187" t="s">
+        <v>719</v>
+      </c>
+      <c r="M187" t="s">
+        <v>1330</v>
+      </c>
+      <c r="N187" t="s">
+        <v>201</v>
+      </c>
+      <c r="O187" t="s">
+        <v>201</v>
+      </c>
+      <c r="P187" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>201</v>
+      </c>
+      <c r="R187" t="s">
+        <v>39</v>
+      </c>
+      <c r="S187" t="s">
+        <v>201</v>
+      </c>
+      <c r="T187" t="s">
+        <v>41</v>
+      </c>
+      <c r="U187" t="s">
+        <v>201</v>
+      </c>
+      <c r="V187">
+        <v>27</v>
+      </c>
+      <c r="W187">
+        <v>10</v>
+      </c>
+      <c r="X187">
+        <v>18</v>
+      </c>
+      <c r="Y187">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>202</v>
+      </c>
+      <c r="B188" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C188" t="s">
+        <v>203</v>
+      </c>
+      <c r="E188" t="s">
+        <v>54</v>
+      </c>
+      <c r="F188" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G188" t="s">
+        <v>370</v>
+      </c>
+      <c r="H188" t="s">
+        <v>1331</v>
+      </c>
+      <c r="I188" t="s">
+        <v>1332</v>
+      </c>
+      <c r="J188" t="s">
+        <v>1333</v>
+      </c>
+      <c r="K188" t="s">
+        <v>1334</v>
+      </c>
+      <c r="L188" t="s">
+        <v>828</v>
+      </c>
+      <c r="M188" t="s">
+        <v>699</v>
+      </c>
+      <c r="N188" t="s">
+        <v>39</v>
+      </c>
+      <c r="O188" t="s">
+        <v>201</v>
+      </c>
+      <c r="P188" t="s">
+        <v>1335</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>488</v>
+      </c>
+      <c r="R188" t="s">
+        <v>40</v>
+      </c>
+      <c r="S188" t="s">
+        <v>41</v>
+      </c>
+      <c r="T188" t="s">
+        <v>38</v>
+      </c>
+      <c r="U188" t="s">
+        <v>41</v>
+      </c>
+      <c r="V188">
+        <v>45</v>
+      </c>
+      <c r="W188">
+        <v>18</v>
+      </c>
+      <c r="X188">
+        <v>43</v>
+      </c>
+      <c r="Y188">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>202</v>
+      </c>
+      <c r="B189" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C189" t="s">
+        <v>203</v>
+      </c>
+      <c r="E189" t="s">
+        <v>67</v>
+      </c>
+      <c r="F189" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G189" t="s">
+        <v>663</v>
+      </c>
+      <c r="H189" t="s">
+        <v>987</v>
+      </c>
+      <c r="I189" t="s">
+        <v>1336</v>
+      </c>
+      <c r="J189" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K189" t="s">
+        <v>1338</v>
+      </c>
+      <c r="L189" t="s">
+        <v>663</v>
+      </c>
+      <c r="M189" t="s">
+        <v>503</v>
+      </c>
+      <c r="N189" t="s">
+        <v>41</v>
+      </c>
+      <c r="O189" t="s">
+        <v>201</v>
+      </c>
+      <c r="P189" t="s">
+        <v>773</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>201</v>
+      </c>
+      <c r="R189" t="s">
+        <v>39</v>
+      </c>
+      <c r="S189" t="s">
+        <v>201</v>
+      </c>
+      <c r="T189" t="s">
+        <v>39</v>
+      </c>
+      <c r="U189" t="s">
+        <v>41</v>
+      </c>
+      <c r="V189">
+        <v>30</v>
+      </c>
+      <c r="W189">
+        <v>13</v>
+      </c>
+      <c r="X189">
+        <v>18</v>
+      </c>
+      <c r="Y189">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>202</v>
+      </c>
+      <c r="B190" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C190" t="s">
+        <v>203</v>
+      </c>
+      <c r="E190" t="s">
+        <v>90</v>
+      </c>
+      <c r="F190" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G190" t="s">
+        <v>32</v>
+      </c>
+      <c r="H190" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I190" t="s">
+        <v>1340</v>
+      </c>
+      <c r="J190" t="s">
+        <v>1341</v>
+      </c>
+      <c r="K190" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L190" t="s">
+        <v>1343</v>
+      </c>
+      <c r="M190" t="s">
+        <v>241</v>
+      </c>
+      <c r="N190" t="s">
+        <v>66</v>
+      </c>
+      <c r="O190" t="s">
+        <v>201</v>
+      </c>
+      <c r="P190" t="s">
+        <v>1344</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>488</v>
+      </c>
+      <c r="R190" t="s">
+        <v>66</v>
+      </c>
+      <c r="S190" t="s">
+        <v>39</v>
+      </c>
+      <c r="T190" t="s">
+        <v>40</v>
+      </c>
+      <c r="U190" t="s">
+        <v>41</v>
+      </c>
+      <c r="V190">
+        <v>62</v>
+      </c>
+      <c r="W190">
+        <v>30</v>
+      </c>
+      <c r="X190">
+        <v>51</v>
+      </c>
+      <c r="Y190">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>202</v>
+      </c>
+      <c r="B191" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C191" t="s">
+        <v>203</v>
+      </c>
+      <c r="E191" t="s">
+        <v>102</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G191" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H191" t="s">
+        <v>1346</v>
+      </c>
+      <c r="I191" t="s">
+        <v>1347</v>
+      </c>
+      <c r="J191" t="s">
+        <v>1348</v>
+      </c>
+      <c r="K191" t="s">
+        <v>1349</v>
+      </c>
+      <c r="L191" t="s">
+        <v>1350</v>
+      </c>
+      <c r="M191" t="s">
+        <v>1009</v>
+      </c>
+      <c r="N191" t="s">
+        <v>1351</v>
+      </c>
+      <c r="O191" t="s">
+        <v>201</v>
+      </c>
+      <c r="P191" t="s">
+        <v>1352</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>455</v>
+      </c>
+      <c r="R191" t="s">
+        <v>38</v>
+      </c>
+      <c r="S191" t="s">
+        <v>41</v>
+      </c>
+      <c r="T191" t="s">
+        <v>66</v>
+      </c>
+      <c r="U191" t="s">
+        <v>39</v>
+      </c>
+      <c r="V191">
+        <v>43</v>
+      </c>
+      <c r="W191">
+        <v>37</v>
+      </c>
+      <c r="X191">
+        <v>29</v>
+      </c>
+      <c r="Y191">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>202</v>
+      </c>
+      <c r="B192" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C192" t="s">
+        <v>203</v>
+      </c>
+      <c r="E192" t="s">
+        <v>347</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G192" t="s">
+        <v>487</v>
+      </c>
+      <c r="H192" t="s">
+        <v>1353</v>
+      </c>
+      <c r="I192" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J192" t="s">
+        <v>1355</v>
+      </c>
+      <c r="K192" t="s">
+        <v>1356</v>
+      </c>
+      <c r="L192" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M192" t="s">
+        <v>121</v>
+      </c>
+      <c r="N192" t="s">
+        <v>66</v>
+      </c>
+      <c r="O192" t="s">
+        <v>41</v>
+      </c>
+      <c r="P192" t="s">
+        <v>674</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>1358</v>
+      </c>
+      <c r="R192" t="s">
+        <v>40</v>
+      </c>
+      <c r="S192" t="s">
+        <v>39</v>
+      </c>
+      <c r="T192" t="s">
+        <v>38</v>
+      </c>
+      <c r="U192" t="s">
+        <v>41</v>
+      </c>
+      <c r="V192">
+        <v>40</v>
+      </c>
+      <c r="W192">
+        <v>19</v>
+      </c>
+      <c r="X192">
+        <v>35</v>
+      </c>
+      <c r="Y192">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>202</v>
+      </c>
+      <c r="B193" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C193" t="s">
+        <v>203</v>
+      </c>
+      <c r="E193" t="s">
+        <v>137</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G193" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H193" t="s">
+        <v>1360</v>
+      </c>
+      <c r="I193" t="s">
+        <v>1361</v>
+      </c>
+      <c r="J193" t="s">
+        <v>1362</v>
+      </c>
+      <c r="K193" t="s">
+        <v>1363</v>
+      </c>
+      <c r="L193" t="s">
+        <v>757</v>
+      </c>
+      <c r="M193" t="s">
+        <v>278</v>
+      </c>
+      <c r="N193" t="s">
+        <v>1364</v>
+      </c>
+      <c r="O193" t="s">
+        <v>201</v>
+      </c>
+      <c r="P193" t="s">
+        <v>1365</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>165</v>
+      </c>
+      <c r="R193" t="s">
+        <v>66</v>
+      </c>
+      <c r="S193" t="s">
+        <v>39</v>
+      </c>
+      <c r="T193" t="s">
+        <v>66</v>
+      </c>
+      <c r="U193" t="s">
+        <v>39</v>
+      </c>
+      <c r="V193">
+        <v>42</v>
+      </c>
+      <c r="W193">
+        <v>46</v>
+      </c>
+      <c r="X193">
+        <v>51</v>
+      </c>
+      <c r="Y193">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>202</v>
+      </c>
+      <c r="B194" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C194" t="s">
+        <v>203</v>
+      </c>
+      <c r="E194" t="s">
+        <v>346</v>
+      </c>
+      <c r="F194" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G194" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H194" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I194" t="s">
+        <v>1367</v>
+      </c>
+      <c r="J194" t="s">
+        <v>1368</v>
+      </c>
+      <c r="K194" t="s">
+        <v>1369</v>
+      </c>
+      <c r="L194" t="s">
+        <v>379</v>
+      </c>
+      <c r="M194" t="s">
+        <v>774</v>
+      </c>
+      <c r="N194" t="s">
+        <v>39</v>
+      </c>
+      <c r="O194" t="s">
+        <v>201</v>
+      </c>
+      <c r="P194" t="s">
+        <v>1335</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>201</v>
+      </c>
+      <c r="R194" t="s">
+        <v>39</v>
+      </c>
+      <c r="S194" t="s">
+        <v>41</v>
+      </c>
+      <c r="T194" t="s">
+        <v>39</v>
+      </c>
+      <c r="U194" t="s">
+        <v>201</v>
+      </c>
+      <c r="V194">
+        <v>28</v>
+      </c>
+      <c r="W194">
+        <v>12</v>
+      </c>
+      <c r="X194">
+        <v>19</v>
+      </c>
+      <c r="Y194">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>202</v>
+      </c>
+      <c r="B195" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C195" t="s">
+        <v>203</v>
+      </c>
+      <c r="E195" t="s">
+        <v>191</v>
+      </c>
+      <c r="F195" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G195" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H195" t="s">
+        <v>1371</v>
+      </c>
+      <c r="I195" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J195" t="s">
+        <v>1373</v>
+      </c>
+      <c r="K195" t="s">
+        <v>1374</v>
+      </c>
+      <c r="L195" t="s">
+        <v>1375</v>
+      </c>
+      <c r="M195" t="s">
+        <v>364</v>
+      </c>
+      <c r="N195" t="s">
+        <v>188</v>
+      </c>
+      <c r="O195" t="s">
+        <v>201</v>
+      </c>
+      <c r="P195" t="s">
+        <v>1376</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>165</v>
+      </c>
+      <c r="R195" t="s">
+        <v>41</v>
+      </c>
+      <c r="S195" t="s">
+        <v>201</v>
+      </c>
+      <c r="T195" t="s">
+        <v>41</v>
+      </c>
+      <c r="U195" t="s">
+        <v>201</v>
+      </c>
+      <c r="V195">
+        <v>30</v>
+      </c>
+      <c r="W195">
+        <v>6</v>
+      </c>
+      <c r="X195">
+        <v>14</v>
+      </c>
+      <c r="Y195">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>202</v>
+      </c>
+      <c r="B196" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C196" t="s">
+        <v>203</v>
+      </c>
+      <c r="E196" t="s">
+        <v>147</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G196" t="s">
+        <v>788</v>
+      </c>
+      <c r="H196" t="s">
+        <v>1377</v>
+      </c>
+      <c r="I196" t="s">
+        <v>1378</v>
+      </c>
+      <c r="J196" t="s">
+        <v>1379</v>
+      </c>
+      <c r="K196" t="s">
+        <v>1380</v>
+      </c>
+      <c r="L196" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M196" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N196" t="s">
+        <v>39</v>
+      </c>
+      <c r="O196" t="s">
+        <v>201</v>
+      </c>
+      <c r="P196" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>201</v>
+      </c>
+      <c r="R196" t="s">
+        <v>35</v>
+      </c>
+      <c r="S196" t="s">
+        <v>38</v>
+      </c>
+      <c r="T196" t="s">
+        <v>66</v>
+      </c>
+      <c r="U196" t="s">
+        <v>41</v>
+      </c>
+      <c r="V196">
+        <v>70</v>
+      </c>
+      <c r="W196">
+        <v>34</v>
+      </c>
+      <c r="X196">
+        <v>64</v>
+      </c>
+      <c r="Y196">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>202</v>
+      </c>
+      <c r="B197" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C197" t="s">
+        <v>203</v>
+      </c>
+      <c r="E197" t="s">
+        <v>180</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G197" t="s">
+        <v>133</v>
+      </c>
+      <c r="H197" t="s">
+        <v>1381</v>
+      </c>
+      <c r="I197" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J197" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K197" t="s">
+        <v>1384</v>
+      </c>
+      <c r="L197" t="s">
+        <v>1385</v>
+      </c>
+      <c r="M197" t="s">
+        <v>33</v>
+      </c>
+      <c r="N197" t="s">
+        <v>113</v>
+      </c>
+      <c r="O197" t="s">
+        <v>41</v>
+      </c>
+      <c r="P197" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>811</v>
+      </c>
+      <c r="R197" t="s">
+        <v>449</v>
+      </c>
+      <c r="S197" t="s">
+        <v>113</v>
+      </c>
+      <c r="T197" t="s">
+        <v>35</v>
+      </c>
+      <c r="U197" t="s">
+        <v>40</v>
+      </c>
+      <c r="V197">
+        <v>78</v>
+      </c>
+      <c r="W197">
+        <v>55</v>
+      </c>
+      <c r="X197">
+        <v>96</v>
+      </c>
+      <c r="Y197">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>202</v>
+      </c>
+      <c r="B198" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C198" t="s">
+        <v>203</v>
+      </c>
+      <c r="D198" t="s">
+        <v>848</v>
+      </c>
+      <c r="E198" t="s">
+        <v>25</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G198" t="s">
+        <v>521</v>
+      </c>
+      <c r="H198" t="s">
+        <v>1387</v>
+      </c>
+      <c r="I198" t="s">
+        <v>1388</v>
+      </c>
+      <c r="J198" t="s">
+        <v>1389</v>
+      </c>
+      <c r="K198" t="s">
+        <v>1390</v>
+      </c>
+      <c r="L198" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M198" t="s">
+        <v>823</v>
+      </c>
+      <c r="N198" t="s">
+        <v>40</v>
+      </c>
+      <c r="O198" t="s">
+        <v>201</v>
+      </c>
+      <c r="P198" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>488</v>
+      </c>
+      <c r="R198" t="s">
+        <v>40</v>
+      </c>
+      <c r="S198" t="s">
+        <v>39</v>
+      </c>
+      <c r="T198" t="s">
+        <v>66</v>
+      </c>
+      <c r="U198" t="s">
+        <v>41</v>
+      </c>
+      <c r="V198">
+        <v>56</v>
+      </c>
+      <c r="W198">
+        <v>19</v>
+      </c>
+      <c r="X198">
+        <v>35</v>
+      </c>
+      <c r="Y198">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C199" t="s">
+        <v>203</v>
+      </c>
+      <c r="D199" t="s">
+        <v>848</v>
+      </c>
+      <c r="E199" t="s">
+        <v>42</v>
+      </c>
+      <c r="F199" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G199" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H199" t="s">
+        <v>1393</v>
+      </c>
+      <c r="I199" t="s">
+        <v>1394</v>
+      </c>
+      <c r="J199" t="s">
+        <v>374</v>
+      </c>
+      <c r="K199" t="s">
+        <v>1395</v>
+      </c>
+      <c r="L199" t="s">
+        <v>1370</v>
+      </c>
+      <c r="M199" t="s">
+        <v>686</v>
+      </c>
+      <c r="N199" t="s">
+        <v>39</v>
+      </c>
+      <c r="O199" t="s">
+        <v>201</v>
+      </c>
+      <c r="P199" t="s">
+        <v>1396</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>201</v>
+      </c>
+      <c r="R199" t="s">
+        <v>38</v>
+      </c>
+      <c r="S199" t="s">
+        <v>41</v>
+      </c>
+      <c r="T199" t="s">
+        <v>39</v>
+      </c>
+      <c r="U199" t="s">
+        <v>201</v>
+      </c>
+      <c r="V199">
+        <v>34</v>
+      </c>
+      <c r="W199">
+        <v>9</v>
+      </c>
+      <c r="X199">
+        <v>32</v>
+      </c>
+      <c r="Y199">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>202</v>
+      </c>
+      <c r="B200" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C200" t="s">
+        <v>203</v>
+      </c>
+      <c r="D200" t="s">
+        <v>848</v>
+      </c>
+      <c r="E200" t="s">
+        <v>67</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G200" t="s">
+        <v>319</v>
+      </c>
+      <c r="H200" t="s">
+        <v>1397</v>
+      </c>
+      <c r="I200" t="s">
+        <v>1398</v>
+      </c>
+      <c r="J200" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K200" t="s">
+        <v>1399</v>
+      </c>
+      <c r="L200" t="s">
+        <v>306</v>
+      </c>
+      <c r="M200" t="s">
+        <v>187</v>
+      </c>
+      <c r="N200" t="s">
+        <v>38</v>
+      </c>
+      <c r="O200" t="s">
+        <v>201</v>
+      </c>
+      <c r="P200" t="s">
+        <v>1225</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>488</v>
+      </c>
+      <c r="R200" t="s">
+        <v>39</v>
+      </c>
+      <c r="S200" t="s">
+        <v>41</v>
+      </c>
+      <c r="T200" t="s">
+        <v>38</v>
+      </c>
+      <c r="U200" t="s">
+        <v>41</v>
+      </c>
+      <c r="V200">
+        <v>47</v>
+      </c>
+      <c r="W200">
+        <v>18</v>
+      </c>
+      <c r="X200">
+        <v>30</v>
+      </c>
+      <c r="Y200">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>202</v>
+      </c>
+      <c r="B201" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C201" t="s">
+        <v>203</v>
+      </c>
+      <c r="D201" t="s">
+        <v>848</v>
+      </c>
+      <c r="E201" t="s">
+        <v>79</v>
+      </c>
+      <c r="F201" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G201" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H201" t="s">
+        <v>1401</v>
+      </c>
+      <c r="I201" t="s">
+        <v>1402</v>
+      </c>
+      <c r="J201" t="s">
+        <v>1403</v>
+      </c>
+      <c r="K201" t="s">
+        <v>1404</v>
+      </c>
+      <c r="L201" t="s">
+        <v>891</v>
+      </c>
+      <c r="M201" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N201" t="s">
+        <v>41</v>
+      </c>
+      <c r="O201" t="s">
+        <v>201</v>
+      </c>
+      <c r="P201" t="s">
+        <v>977</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>201</v>
+      </c>
+      <c r="R201" t="s">
+        <v>38</v>
+      </c>
+      <c r="S201" t="s">
+        <v>41</v>
+      </c>
+      <c r="T201" t="s">
+        <v>38</v>
+      </c>
+      <c r="U201" t="s">
+        <v>41</v>
+      </c>
+      <c r="V201">
+        <v>49</v>
+      </c>
+      <c r="W201">
+        <v>18</v>
+      </c>
+      <c r="X201">
+        <v>33</v>
+      </c>
+      <c r="Y201">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>202</v>
+      </c>
+      <c r="B202" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C202" t="s">
+        <v>203</v>
+      </c>
+      <c r="D202" t="s">
+        <v>848</v>
+      </c>
+      <c r="E202" t="s">
+        <v>90</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G202" t="s">
+        <v>603</v>
+      </c>
+      <c r="H202" t="s">
+        <v>1405</v>
+      </c>
+      <c r="I202" t="s">
+        <v>1406</v>
+      </c>
+      <c r="J202" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K202" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L202" t="s">
+        <v>288</v>
+      </c>
+      <c r="M202" t="s">
+        <v>834</v>
+      </c>
+      <c r="N202" t="s">
+        <v>39</v>
+      </c>
+      <c r="O202" t="s">
+        <v>201</v>
+      </c>
+      <c r="P202" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>201</v>
+      </c>
+      <c r="R202" t="s">
+        <v>113</v>
+      </c>
+      <c r="S202" t="s">
+        <v>39</v>
+      </c>
+      <c r="T202" t="s">
+        <v>113</v>
+      </c>
+      <c r="U202" t="s">
+        <v>39</v>
+      </c>
+      <c r="V202">
+        <v>89</v>
+      </c>
+      <c r="W202">
+        <v>35</v>
+      </c>
+      <c r="X202">
+        <v>60</v>
+      </c>
+      <c r="Y202">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C203" t="s">
+        <v>203</v>
+      </c>
+      <c r="D203" t="s">
+        <v>848</v>
+      </c>
+      <c r="E203" t="s">
+        <v>102</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G203" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H203" t="s">
+        <v>1409</v>
+      </c>
+      <c r="I203" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J203" t="s">
+        <v>1411</v>
+      </c>
+      <c r="K203" t="s">
+        <v>1412</v>
+      </c>
+      <c r="L203" t="s">
+        <v>32</v>
+      </c>
+      <c r="M203" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N203" t="s">
+        <v>38</v>
+      </c>
+      <c r="O203" t="s">
+        <v>201</v>
+      </c>
+      <c r="P203" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>488</v>
+      </c>
+      <c r="R203" t="s">
+        <v>113</v>
+      </c>
+      <c r="S203" t="s">
+        <v>39</v>
+      </c>
+      <c r="T203" t="s">
+        <v>40</v>
+      </c>
+      <c r="U203" t="s">
+        <v>41</v>
+      </c>
+      <c r="V203">
+        <v>77</v>
+      </c>
+      <c r="W203">
+        <v>32</v>
+      </c>
+      <c r="X203">
+        <v>61</v>
+      </c>
+      <c r="Y203">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>202</v>
+      </c>
+      <c r="B204" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C204" t="s">
+        <v>203</v>
+      </c>
+      <c r="D204" t="s">
+        <v>848</v>
+      </c>
+      <c r="E204" t="s">
+        <v>347</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G204" t="s">
+        <v>521</v>
+      </c>
+      <c r="H204" t="s">
+        <v>1413</v>
+      </c>
+      <c r="I204" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J204" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K204" t="s">
+        <v>1416</v>
+      </c>
+      <c r="L204" t="s">
+        <v>398</v>
+      </c>
+      <c r="M204" t="s">
+        <v>1417</v>
+      </c>
+      <c r="N204" t="s">
+        <v>66</v>
+      </c>
+      <c r="O204" t="s">
+        <v>201</v>
+      </c>
+      <c r="P204" t="s">
+        <v>1308</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>201</v>
+      </c>
+      <c r="R204" t="s">
+        <v>66</v>
+      </c>
+      <c r="S204" t="s">
+        <v>39</v>
+      </c>
+      <c r="T204" t="s">
+        <v>66</v>
+      </c>
+      <c r="U204" t="s">
+        <v>41</v>
+      </c>
+      <c r="V204">
+        <v>69</v>
+      </c>
+      <c r="W204">
+        <v>22</v>
+      </c>
+      <c r="X204">
+        <v>36</v>
+      </c>
+      <c r="Y204">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>202</v>
+      </c>
+      <c r="B205" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C205" t="s">
+        <v>203</v>
+      </c>
+      <c r="D205" t="s">
+        <v>848</v>
+      </c>
+      <c r="E205" t="s">
+        <v>346</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G205" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H205" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I205" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J205" t="s">
+        <v>1421</v>
+      </c>
+      <c r="K205" t="s">
+        <v>1422</v>
+      </c>
+      <c r="L205" t="s">
+        <v>231</v>
+      </c>
+      <c r="M205" t="s">
+        <v>720</v>
+      </c>
+      <c r="N205" t="s">
+        <v>39</v>
+      </c>
+      <c r="O205" t="s">
+        <v>201</v>
+      </c>
+      <c r="P205" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>201</v>
+      </c>
+      <c r="R205" t="s">
+        <v>66</v>
+      </c>
+      <c r="S205" t="s">
+        <v>39</v>
+      </c>
+      <c r="T205" t="s">
+        <v>40</v>
+      </c>
+      <c r="U205" t="s">
+        <v>201</v>
+      </c>
+      <c r="V205">
+        <v>63</v>
+      </c>
+      <c r="W205">
+        <v>11</v>
+      </c>
+      <c r="X205">
+        <v>47</v>
+      </c>
+      <c r="Y205">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>202</v>
+      </c>
+      <c r="B206" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C206" t="s">
+        <v>203</v>
+      </c>
+      <c r="D206" t="s">
+        <v>848</v>
+      </c>
+      <c r="E206" t="s">
+        <v>137</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G206" t="s">
+        <v>269</v>
+      </c>
+      <c r="H206" t="s">
+        <v>1423</v>
+      </c>
+      <c r="I206" t="s">
+        <v>1424</v>
+      </c>
+      <c r="J206" t="s">
+        <v>1425</v>
+      </c>
+      <c r="K206" t="s">
+        <v>1426</v>
+      </c>
+      <c r="L206" t="s">
+        <v>779</v>
+      </c>
+      <c r="M206" t="s">
+        <v>1055</v>
+      </c>
+      <c r="N206" t="s">
+        <v>488</v>
+      </c>
+      <c r="O206" t="s">
+        <v>201</v>
+      </c>
+      <c r="P206" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>165</v>
+      </c>
+      <c r="R206" t="s">
+        <v>35</v>
+      </c>
+      <c r="S206" t="s">
+        <v>38</v>
+      </c>
+      <c r="T206" t="s">
+        <v>66</v>
+      </c>
+      <c r="U206" t="s">
+        <v>41</v>
+      </c>
+      <c r="V206">
+        <v>72</v>
+      </c>
+      <c r="W206">
+        <v>23</v>
+      </c>
+      <c r="X206">
+        <v>62</v>
+      </c>
+      <c r="Y206">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="207" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>202</v>
+      </c>
+      <c r="B207" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C207" t="s">
+        <v>203</v>
+      </c>
+      <c r="D207" t="s">
+        <v>848</v>
+      </c>
+      <c r="E207" t="s">
+        <v>147</v>
+      </c>
+      <c r="F207" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G207" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H207" t="s">
+        <v>1428</v>
+      </c>
+      <c r="I207" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J207" t="s">
+        <v>1430</v>
+      </c>
+      <c r="K207" t="s">
+        <v>1431</v>
+      </c>
+      <c r="L207" t="s">
+        <v>132</v>
+      </c>
+      <c r="M207" t="s">
+        <v>1210</v>
+      </c>
+      <c r="N207" t="s">
+        <v>40</v>
+      </c>
+      <c r="O207" t="s">
+        <v>201</v>
+      </c>
+      <c r="P207" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>201</v>
+      </c>
+      <c r="R207" t="s">
+        <v>66</v>
+      </c>
+      <c r="S207" t="s">
+        <v>39</v>
+      </c>
+      <c r="T207" t="s">
+        <v>38</v>
+      </c>
+      <c r="U207" t="s">
+        <v>41</v>
+      </c>
+      <c r="V207">
+        <v>55</v>
+      </c>
+      <c r="W207">
+        <v>24</v>
+      </c>
+      <c r="X207">
+        <v>38</v>
+      </c>
+      <c r="Y207">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="208" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>202</v>
+      </c>
+      <c r="B208" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C208" t="s">
+        <v>203</v>
+      </c>
+      <c r="D208" t="s">
+        <v>848</v>
+      </c>
+      <c r="E208" t="s">
+        <v>180</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G208" t="s">
+        <v>728</v>
+      </c>
+      <c r="H208" t="s">
+        <v>1432</v>
+      </c>
+      <c r="I208" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J208" t="s">
+        <v>1434</v>
+      </c>
+      <c r="K208" t="s">
+        <v>1435</v>
+      </c>
+      <c r="L208" t="s">
+        <v>876</v>
+      </c>
+      <c r="M208" t="s">
+        <v>884</v>
+      </c>
+      <c r="N208" t="s">
+        <v>35</v>
+      </c>
+      <c r="O208" t="s">
+        <v>41</v>
+      </c>
+      <c r="P208" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>176</v>
+      </c>
+      <c r="R208" t="s">
+        <v>280</v>
+      </c>
+      <c r="S208" t="s">
+        <v>66</v>
+      </c>
+      <c r="T208" t="s">
+        <v>35</v>
+      </c>
+      <c r="U208" t="s">
+        <v>38</v>
+      </c>
+      <c r="V208">
+        <v>67</v>
+      </c>
+      <c r="W208">
+        <v>61</v>
+      </c>
+      <c r="X208">
+        <v>70</v>
+      </c>
+      <c r="Y208">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="209" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>202</v>
+      </c>
+      <c r="B209" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C209" t="s">
+        <v>203</v>
+      </c>
+      <c r="D209" t="s">
+        <v>848</v>
+      </c>
+      <c r="E209" t="s">
+        <v>191</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G209" t="s">
+        <v>300</v>
+      </c>
+      <c r="H209" t="s">
+        <v>1436</v>
+      </c>
+      <c r="I209" t="s">
+        <v>1437</v>
+      </c>
+      <c r="J209" t="s">
+        <v>845</v>
+      </c>
+      <c r="K209" t="s">
+        <v>1438</v>
+      </c>
+      <c r="L209" t="s">
+        <v>926</v>
+      </c>
+      <c r="M209" t="s">
+        <v>571</v>
+      </c>
+      <c r="N209" t="s">
+        <v>41</v>
+      </c>
+      <c r="O209" t="s">
+        <v>201</v>
+      </c>
+      <c r="P209" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>201</v>
+      </c>
+      <c r="R209" t="s">
+        <v>39</v>
+      </c>
+      <c r="S209" t="s">
+        <v>41</v>
+      </c>
+      <c r="T209" t="s">
+        <v>39</v>
+      </c>
+      <c r="U209" t="s">
+        <v>201</v>
+      </c>
+      <c r="V209">
+        <v>25</v>
+      </c>
+      <c r="W209">
+        <v>9</v>
+      </c>
+      <c r="X209">
+        <v>20</v>
+      </c>
+      <c r="Y209">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845EAD56-AEA5-3B46-BBA3-E4A0AF67CEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84370C44-1715-3641-A86B-AAD8958ECDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3846" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5026" uniqueCount="1781">
   <si>
     <t>Type</t>
   </si>
@@ -4353,6 +4353,1032 @@
   </si>
   <si>
     <t>41.45</t>
+  </si>
+  <si>
+    <t>79.22</t>
+  </si>
+  <si>
+    <t>254.41</t>
+  </si>
+  <si>
+    <t>240.15</t>
+  </si>
+  <si>
+    <t>30.77</t>
+  </si>
+  <si>
+    <t>66.83</t>
+  </si>
+  <si>
+    <t>5.55</t>
+  </si>
+  <si>
+    <t>480.51</t>
+  </si>
+  <si>
+    <t>281.54</t>
+  </si>
+  <si>
+    <t>70.12</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>64.2</t>
+  </si>
+  <si>
+    <t>12.4</t>
+  </si>
+  <si>
+    <t>237.19</t>
+  </si>
+  <si>
+    <t>246.95</t>
+  </si>
+  <si>
+    <t>27.45</t>
+  </si>
+  <si>
+    <t>61.67</t>
+  </si>
+  <si>
+    <t>34.8</t>
+  </si>
+  <si>
+    <t>79.2</t>
+  </si>
+  <si>
+    <t>6.52</t>
+  </si>
+  <si>
+    <t>167.6</t>
+  </si>
+  <si>
+    <t>313.1</t>
+  </si>
+  <si>
+    <t>25.76</t>
+  </si>
+  <si>
+    <t>82.34</t>
+  </si>
+  <si>
+    <t>26.5</t>
+  </si>
+  <si>
+    <t>326.71</t>
+  </si>
+  <si>
+    <t>342.74</t>
+  </si>
+  <si>
+    <t>28.37</t>
+  </si>
+  <si>
+    <t>85.38</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>315.79</t>
+  </si>
+  <si>
+    <t>264.22</t>
+  </si>
+  <si>
+    <t>27.14</t>
+  </si>
+  <si>
+    <t>73.96</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>5.41</t>
+  </si>
+  <si>
+    <t>45.6</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>77.72</t>
+  </si>
+  <si>
+    <t>417.3</t>
+  </si>
+  <si>
+    <t>263.51</t>
+  </si>
+  <si>
+    <t>31.01</t>
+  </si>
+  <si>
+    <t>73.08</t>
+  </si>
+  <si>
+    <t>46.2</t>
+  </si>
+  <si>
+    <t>422.08</t>
+  </si>
+  <si>
+    <t>276.45</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
+    <t>78.4</t>
+  </si>
+  <si>
+    <t>41.3</t>
+  </si>
+  <si>
+    <t>327.17</t>
+  </si>
+  <si>
+    <t>273.5</t>
+  </si>
+  <si>
+    <t>32.03</t>
+  </si>
+  <si>
+    <t>71.91</t>
+  </si>
+  <si>
+    <t>5.01</t>
+  </si>
+  <si>
+    <t>42.0</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>116.28</t>
+  </si>
+  <si>
+    <t>319.8</t>
+  </si>
+  <si>
+    <t>25.59</t>
+  </si>
+  <si>
+    <t>79.12</t>
+  </si>
+  <si>
+    <t>326.57</t>
+  </si>
+  <si>
+    <t>281.16</t>
+  </si>
+  <si>
+    <t>30.4</t>
+  </si>
+  <si>
+    <t>76.15</t>
+  </si>
+  <si>
+    <t>42.3</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
+    <t>492.0</t>
+  </si>
+  <si>
+    <t>512.78</t>
+  </si>
+  <si>
+    <t>31.49</t>
+  </si>
+  <si>
+    <t>69.2</t>
+  </si>
+  <si>
+    <t>7.72</t>
+  </si>
+  <si>
+    <t>60.4</t>
+  </si>
+  <si>
+    <t>147.86</t>
+  </si>
+  <si>
+    <t>245.53</t>
+  </si>
+  <si>
+    <t>64.29</t>
+  </si>
+  <si>
+    <t>21.0</t>
+  </si>
+  <si>
+    <t>108.89</t>
+  </si>
+  <si>
+    <t>251.16</t>
+  </si>
+  <si>
+    <t>24.77</t>
+  </si>
+  <si>
+    <t>69.43</t>
+  </si>
+  <si>
+    <t>3.87</t>
+  </si>
+  <si>
+    <t>359.68</t>
+  </si>
+  <si>
+    <t>204.03</t>
+  </si>
+  <si>
+    <t>52.56</t>
+  </si>
+  <si>
+    <t>9.09</t>
+  </si>
+  <si>
+    <t>6.12</t>
+  </si>
+  <si>
+    <t>45.4</t>
+  </si>
+  <si>
+    <t>210.94</t>
+  </si>
+  <si>
+    <t>246.93</t>
+  </si>
+  <si>
+    <t>27.64</t>
+  </si>
+  <si>
+    <t>63.54</t>
+  </si>
+  <si>
+    <t>5.87</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>242.65</t>
+  </si>
+  <si>
+    <t>252.42</t>
+  </si>
+  <si>
+    <t>27.78</t>
+  </si>
+  <si>
+    <t>71.08</t>
+  </si>
+  <si>
+    <t>283.43</t>
+  </si>
+  <si>
+    <t>283.59</t>
+  </si>
+  <si>
+    <t>74.4</t>
+  </si>
+  <si>
+    <t>41.9</t>
+  </si>
+  <si>
+    <t>497.86</t>
+  </si>
+  <si>
+    <t>249.12</t>
+  </si>
+  <si>
+    <t>73.73</t>
+  </si>
+  <si>
+    <t>68.4</t>
+  </si>
+  <si>
+    <t>4.74</t>
+  </si>
+  <si>
+    <t>345.82</t>
+  </si>
+  <si>
+    <t>238.49</t>
+  </si>
+  <si>
+    <t>29.17</t>
+  </si>
+  <si>
+    <t>64.38</t>
+  </si>
+  <si>
+    <t>47.4</t>
+  </si>
+  <si>
+    <t>376.43</t>
+  </si>
+  <si>
+    <t>264.16</t>
+  </si>
+  <si>
+    <t>28.66</t>
+  </si>
+  <si>
+    <t>75.28</t>
+  </si>
+  <si>
+    <t>45.7</t>
+  </si>
+  <si>
+    <t>12.9</t>
+  </si>
+  <si>
+    <t>585.19</t>
+  </si>
+  <si>
+    <t>264.53</t>
+  </si>
+  <si>
+    <t>29.54</t>
+  </si>
+  <si>
+    <t>71.06</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>80.3</t>
+  </si>
+  <si>
+    <t>141.27</t>
+  </si>
+  <si>
+    <t>282.45</t>
+  </si>
+  <si>
+    <t>73.16</t>
+  </si>
+  <si>
+    <t>23.8</t>
+  </si>
+  <si>
+    <t>4.81</t>
+  </si>
+  <si>
+    <t>323.87</t>
+  </si>
+  <si>
+    <t>234.82</t>
+  </si>
+  <si>
+    <t>32.42</t>
+  </si>
+  <si>
+    <t>65.38</t>
+  </si>
+  <si>
+    <t>29.1</t>
+  </si>
+  <si>
+    <t>18.6</t>
+  </si>
+  <si>
+    <t>264.95</t>
+  </si>
+  <si>
+    <t>252.32</t>
+  </si>
+  <si>
+    <t>30.26</t>
+  </si>
+  <si>
+    <t>68.36</t>
+  </si>
+  <si>
+    <t>35.5</t>
+  </si>
+  <si>
+    <t>518.88</t>
+  </si>
+  <si>
+    <t>482.02</t>
+  </si>
+  <si>
+    <t>32.29</t>
+  </si>
+  <si>
+    <t>68.97</t>
+  </si>
+  <si>
+    <t>7.96</t>
+  </si>
+  <si>
+    <t>19.9</t>
+  </si>
+  <si>
+    <t>144.51</t>
+  </si>
+  <si>
+    <t>216.55</t>
+  </si>
+  <si>
+    <t>25.54</t>
+  </si>
+  <si>
+    <t>60.53</t>
+  </si>
+  <si>
+    <t>21.9</t>
+  </si>
+  <si>
+    <t>22.12</t>
+  </si>
+  <si>
+    <t>2.47</t>
+  </si>
+  <si>
+    <t>260.97</t>
+  </si>
+  <si>
+    <t>112.73</t>
+  </si>
+  <si>
+    <t>32.34</t>
+  </si>
+  <si>
+    <t>111.51</t>
+  </si>
+  <si>
+    <t>34.7</t>
+  </si>
+  <si>
+    <t>98.0</t>
+  </si>
+  <si>
+    <t>9.94</t>
+  </si>
+  <si>
+    <t>769.45</t>
+  </si>
+  <si>
+    <t>456.91</t>
+  </si>
+  <si>
+    <t>101.38</t>
+  </si>
+  <si>
+    <t>6.73</t>
+  </si>
+  <si>
+    <t>107.8</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>50.52</t>
+  </si>
+  <si>
+    <t>353.6</t>
+  </si>
+  <si>
+    <t>292.66</t>
+  </si>
+  <si>
+    <t>27.3</t>
+  </si>
+  <si>
+    <t>118.03</t>
+  </si>
+  <si>
+    <t>6.39</t>
+  </si>
+  <si>
+    <t>48.2</t>
+  </si>
+  <si>
+    <t>69.52</t>
+  </si>
+  <si>
+    <t>8.79</t>
+  </si>
+  <si>
+    <t>670.99</t>
+  </si>
+  <si>
+    <t>334.26</t>
+  </si>
+  <si>
+    <t>27.49</t>
+  </si>
+  <si>
+    <t>126.47</t>
+  </si>
+  <si>
+    <t>7.07</t>
+  </si>
+  <si>
+    <t>98.9</t>
+  </si>
+  <si>
+    <t>10.4</t>
+  </si>
+  <si>
+    <t>89.08</t>
+  </si>
+  <si>
+    <t>8.52</t>
+  </si>
+  <si>
+    <t>524.04</t>
+  </si>
+  <si>
+    <t>388.54</t>
+  </si>
+  <si>
+    <t>29.49</t>
+  </si>
+  <si>
+    <t>95.62</t>
+  </si>
+  <si>
+    <t>8.35</t>
+  </si>
+  <si>
+    <t>72.9</t>
+  </si>
+  <si>
+    <t>11.8</t>
+  </si>
+  <si>
+    <t>81.13</t>
+  </si>
+  <si>
+    <t>9.07</t>
+  </si>
+  <si>
+    <t>740.88</t>
+  </si>
+  <si>
+    <t>384.94</t>
+  </si>
+  <si>
+    <t>28.33</t>
+  </si>
+  <si>
+    <t>111.85</t>
+  </si>
+  <si>
+    <t>106.6</t>
+  </si>
+  <si>
+    <t>12.6</t>
+  </si>
+  <si>
+    <t>11.33</t>
+  </si>
+  <si>
+    <t>485.07</t>
+  </si>
+  <si>
+    <t>541.4</t>
+  </si>
+  <si>
+    <t>27.38</t>
+  </si>
+  <si>
+    <t>115.66</t>
+  </si>
+  <si>
+    <t>70.1</t>
+  </si>
+  <si>
+    <t>29.52</t>
+  </si>
+  <si>
+    <t>3.56</t>
+  </si>
+  <si>
+    <t>245.47</t>
+  </si>
+  <si>
+    <t>154.17</t>
+  </si>
+  <si>
+    <t>28.27</t>
+  </si>
+  <si>
+    <t>120.67</t>
+  </si>
+  <si>
+    <t>28.7</t>
+  </si>
+  <si>
+    <t>2.94</t>
+  </si>
+  <si>
+    <t>215.41</t>
+  </si>
+  <si>
+    <t>127.17</t>
+  </si>
+  <si>
+    <t>102.28</t>
+  </si>
+  <si>
+    <t>6.65</t>
+  </si>
+  <si>
+    <t>24.8</t>
+  </si>
+  <si>
+    <t>47.2</t>
+  </si>
+  <si>
+    <t>287.17</t>
+  </si>
+  <si>
+    <t>262.06</t>
+  </si>
+  <si>
+    <t>28.24</t>
+  </si>
+  <si>
+    <t>117.06</t>
+  </si>
+  <si>
+    <t>44.9</t>
+  </si>
+  <si>
+    <t>9.52</t>
+  </si>
+  <si>
+    <t>469.34</t>
+  </si>
+  <si>
+    <t>395.17</t>
+  </si>
+  <si>
+    <t>97.17</t>
+  </si>
+  <si>
+    <t>8.65</t>
+  </si>
+  <si>
+    <t>64.1</t>
+  </si>
+  <si>
+    <t>10.7</t>
+  </si>
+  <si>
+    <t>81.4</t>
+  </si>
+  <si>
+    <t>5.83</t>
+  </si>
+  <si>
+    <t>326.73</t>
+  </si>
+  <si>
+    <t>275.57</t>
+  </si>
+  <si>
+    <t>71.61</t>
+  </si>
+  <si>
+    <t>54.5</t>
+  </si>
+  <si>
+    <t>11.36</t>
+  </si>
+  <si>
+    <t>255.72</t>
+  </si>
+  <si>
+    <t>20.53</t>
+  </si>
+  <si>
+    <t>56.52</t>
+  </si>
+  <si>
+    <t>5.32</t>
+  </si>
+  <si>
+    <t>4.21</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>5.57</t>
+  </si>
+  <si>
+    <t>42.88</t>
+  </si>
+  <si>
+    <t>306.05</t>
+  </si>
+  <si>
+    <t>24.27</t>
+  </si>
+  <si>
+    <t>68.43</t>
+  </si>
+  <si>
+    <t>122.17</t>
+  </si>
+  <si>
+    <t>352.3</t>
+  </si>
+  <si>
+    <t>87.93</t>
+  </si>
+  <si>
+    <t>19.1</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>42.24</t>
+  </si>
+  <si>
+    <t>10.46</t>
+  </si>
+  <si>
+    <t>7.01</t>
+  </si>
+  <si>
+    <t>91.38</t>
+  </si>
+  <si>
+    <t>363.52</t>
+  </si>
+  <si>
+    <t>26.63</t>
+  </si>
+  <si>
+    <t>86.1</t>
+  </si>
+  <si>
+    <t>6.18</t>
+  </si>
+  <si>
+    <t>323.1</t>
+  </si>
+  <si>
+    <t>24.26</t>
+  </si>
+  <si>
+    <t>75.89</t>
+  </si>
+  <si>
+    <t>6.17</t>
+  </si>
+  <si>
+    <t>5.49</t>
+  </si>
+  <si>
+    <t>75.22</t>
+  </si>
+  <si>
+    <t>298.27</t>
+  </si>
+  <si>
+    <t>24.34</t>
+  </si>
+  <si>
+    <t>67.16</t>
+  </si>
+  <si>
+    <t>6.23</t>
+  </si>
+  <si>
+    <t>76.44</t>
+  </si>
+  <si>
+    <t>585.56</t>
+  </si>
+  <si>
+    <t>76.49</t>
+  </si>
+  <si>
+    <t>7.24</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>12.1</t>
+  </si>
+  <si>
+    <t>143.59</t>
+  </si>
+  <si>
+    <t>293.26</t>
+  </si>
+  <si>
+    <t>73.56</t>
+  </si>
+  <si>
+    <t>8.24</t>
+  </si>
+  <si>
+    <t>64.75</t>
+  </si>
+  <si>
+    <t>301.88</t>
+  </si>
+  <si>
+    <t>26.08</t>
+  </si>
+  <si>
+    <t>64.97</t>
+  </si>
+  <si>
+    <t>J+2</t>
+  </si>
+  <si>
+    <t>N1 J6 VS GOAL FC 03/10/2026</t>
+  </si>
+  <si>
+    <t>84.12</t>
+  </si>
+  <si>
+    <t>859.68</t>
+  </si>
+  <si>
+    <t>282.01</t>
+  </si>
+  <si>
+    <t>27.1</t>
+  </si>
+  <si>
+    <t>133.5</t>
+  </si>
+  <si>
+    <t>3.72</t>
+  </si>
+  <si>
+    <t>277.74</t>
+  </si>
+  <si>
+    <t>189.63</t>
+  </si>
+  <si>
+    <t>25.82</t>
+  </si>
+  <si>
+    <t>44.2</t>
+  </si>
+  <si>
+    <t>45.0</t>
+  </si>
+  <si>
+    <t>479.37</t>
+  </si>
+  <si>
+    <t>260.44</t>
+  </si>
+  <si>
+    <t>30.04</t>
+  </si>
+  <si>
+    <t>63.43</t>
+  </si>
+  <si>
+    <t>70.7</t>
+  </si>
+  <si>
+    <t>1130.22</t>
+  </si>
+  <si>
+    <t>282.39</t>
+  </si>
+  <si>
+    <t>29.8</t>
+  </si>
+  <si>
+    <t>77.22</t>
+  </si>
+  <si>
+    <t>8.25</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>161.0</t>
+  </si>
+  <si>
+    <t>306.52</t>
+  </si>
+  <si>
+    <t>230.41</t>
+  </si>
+  <si>
+    <t>27.55</t>
+  </si>
+  <si>
+    <t>58.56</t>
+  </si>
+  <si>
+    <t>44.8</t>
+  </si>
+  <si>
+    <t>907.56</t>
+  </si>
+  <si>
+    <t>235.29</t>
+  </si>
+  <si>
+    <t>62.54</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>134.3</t>
+  </si>
+  <si>
+    <t>700.08</t>
+  </si>
+  <si>
+    <t>322.51</t>
+  </si>
+  <si>
+    <t>27.46</t>
+  </si>
+  <si>
+    <t>76.53</t>
+  </si>
+  <si>
+    <t>112.9</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>979.98</t>
+  </si>
+  <si>
+    <t>323.26</t>
+  </si>
+  <si>
+    <t>29.47</t>
+  </si>
+  <si>
+    <t>77.28</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>149.0</t>
+  </si>
+  <si>
+    <t>617.96</t>
+  </si>
+  <si>
+    <t>483.68</t>
+  </si>
+  <si>
+    <t>33.85</t>
+  </si>
+  <si>
+    <t>60.57</t>
+  </si>
+  <si>
+    <t>84.6</t>
+  </si>
+  <si>
+    <t>266.24</t>
+  </si>
+  <si>
+    <t>261.88</t>
+  </si>
+  <si>
+    <t>27.92</t>
+  </si>
+  <si>
+    <t>68.54</t>
+  </si>
+  <si>
+    <t>4.78</t>
   </si>
 </sst>
 </file>
@@ -4731,7 +5757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y209"/>
+  <dimension ref="A1:Y268"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
@@ -20486,6 +21512,4549 @@
         <v>8</v>
       </c>
     </row>
+    <row r="210" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>202</v>
+      </c>
+      <c r="B210" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C210" t="s">
+        <v>203</v>
+      </c>
+      <c r="D210" t="s">
+        <v>204</v>
+      </c>
+      <c r="E210" t="s">
+        <v>25</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G210" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H210" t="s">
+        <v>1440</v>
+      </c>
+      <c r="I210" t="s">
+        <v>1441</v>
+      </c>
+      <c r="J210" t="s">
+        <v>1442</v>
+      </c>
+      <c r="K210" t="s">
+        <v>1443</v>
+      </c>
+      <c r="L210" t="s">
+        <v>55</v>
+      </c>
+      <c r="M210" t="s">
+        <v>397</v>
+      </c>
+      <c r="N210" t="s">
+        <v>99</v>
+      </c>
+      <c r="O210" t="s">
+        <v>35</v>
+      </c>
+      <c r="P210" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>1089</v>
+      </c>
+      <c r="R210" t="s">
+        <v>38</v>
+      </c>
+      <c r="S210" t="s">
+        <v>39</v>
+      </c>
+      <c r="T210" t="s">
+        <v>38</v>
+      </c>
+      <c r="U210" t="s">
+        <v>41</v>
+      </c>
+      <c r="V210">
+        <v>50</v>
+      </c>
+      <c r="W210">
+        <v>24</v>
+      </c>
+      <c r="X210">
+        <v>30</v>
+      </c>
+      <c r="Y210">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="211" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>202</v>
+      </c>
+      <c r="B211" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C211" t="s">
+        <v>203</v>
+      </c>
+      <c r="D211" t="s">
+        <v>204</v>
+      </c>
+      <c r="E211" t="s">
+        <v>42</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G211" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H211" t="s">
+        <v>1445</v>
+      </c>
+      <c r="I211" t="s">
+        <v>1446</v>
+      </c>
+      <c r="J211" t="s">
+        <v>711</v>
+      </c>
+      <c r="K211" t="s">
+        <v>1447</v>
+      </c>
+      <c r="L211" t="s">
+        <v>186</v>
+      </c>
+      <c r="M211" t="s">
+        <v>749</v>
+      </c>
+      <c r="N211" t="s">
+        <v>1448</v>
+      </c>
+      <c r="O211" t="s">
+        <v>280</v>
+      </c>
+      <c r="P211" t="s">
+        <v>1449</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>1450</v>
+      </c>
+      <c r="R211" t="s">
+        <v>66</v>
+      </c>
+      <c r="S211" t="s">
+        <v>39</v>
+      </c>
+      <c r="T211" t="s">
+        <v>38</v>
+      </c>
+      <c r="U211" t="s">
+        <v>201</v>
+      </c>
+      <c r="V211">
+        <v>44</v>
+      </c>
+      <c r="W211">
+        <v>10</v>
+      </c>
+      <c r="X211">
+        <v>36</v>
+      </c>
+      <c r="Y211">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="212" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>202</v>
+      </c>
+      <c r="B212" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C212" t="s">
+        <v>203</v>
+      </c>
+      <c r="D212" t="s">
+        <v>204</v>
+      </c>
+      <c r="E212" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G212" t="s">
+        <v>404</v>
+      </c>
+      <c r="H212" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I212" t="s">
+        <v>1452</v>
+      </c>
+      <c r="J212" t="s">
+        <v>1453</v>
+      </c>
+      <c r="K212" t="s">
+        <v>1454</v>
+      </c>
+      <c r="L212" t="s">
+        <v>1014</v>
+      </c>
+      <c r="M212" t="s">
+        <v>251</v>
+      </c>
+      <c r="N212" t="s">
+        <v>672</v>
+      </c>
+      <c r="O212" t="s">
+        <v>38</v>
+      </c>
+      <c r="P212" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>606</v>
+      </c>
+      <c r="R212" t="s">
+        <v>66</v>
+      </c>
+      <c r="S212" t="s">
+        <v>38</v>
+      </c>
+      <c r="T212" t="s">
+        <v>38</v>
+      </c>
+      <c r="U212" t="s">
+        <v>39</v>
+      </c>
+      <c r="V212">
+        <v>31</v>
+      </c>
+      <c r="W212">
+        <v>20</v>
+      </c>
+      <c r="X212">
+        <v>29</v>
+      </c>
+      <c r="Y212">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="213" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>202</v>
+      </c>
+      <c r="B213" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C213" t="s">
+        <v>203</v>
+      </c>
+      <c r="D213" t="s">
+        <v>204</v>
+      </c>
+      <c r="E213" t="s">
+        <v>79</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G213" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H213" t="s">
+        <v>1458</v>
+      </c>
+      <c r="I213" t="s">
+        <v>1459</v>
+      </c>
+      <c r="J213" t="s">
+        <v>1460</v>
+      </c>
+      <c r="K213" t="s">
+        <v>1461</v>
+      </c>
+      <c r="L213" t="s">
+        <v>132</v>
+      </c>
+      <c r="M213" t="s">
+        <v>487</v>
+      </c>
+      <c r="N213" t="s">
+        <v>76</v>
+      </c>
+      <c r="O213" t="s">
+        <v>41</v>
+      </c>
+      <c r="P213" t="s">
+        <v>1462</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>773</v>
+      </c>
+      <c r="R213" t="s">
+        <v>66</v>
+      </c>
+      <c r="S213" t="s">
+        <v>39</v>
+      </c>
+      <c r="T213" t="s">
+        <v>40</v>
+      </c>
+      <c r="U213" t="s">
+        <v>41</v>
+      </c>
+      <c r="V213">
+        <v>48</v>
+      </c>
+      <c r="W213">
+        <v>27</v>
+      </c>
+      <c r="X213">
+        <v>40</v>
+      </c>
+      <c r="Y213">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="214" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>202</v>
+      </c>
+      <c r="B214" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C214" t="s">
+        <v>203</v>
+      </c>
+      <c r="D214" t="s">
+        <v>204</v>
+      </c>
+      <c r="E214" t="s">
+        <v>90</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G214" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H214" t="s">
+        <v>1463</v>
+      </c>
+      <c r="I214" t="s">
+        <v>1464</v>
+      </c>
+      <c r="J214" t="s">
+        <v>1465</v>
+      </c>
+      <c r="K214" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L214" t="s">
+        <v>1457</v>
+      </c>
+      <c r="M214" t="s">
+        <v>385</v>
+      </c>
+      <c r="N214" t="s">
+        <v>165</v>
+      </c>
+      <c r="O214" t="s">
+        <v>38</v>
+      </c>
+      <c r="P214" t="s">
+        <v>1467</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>1468</v>
+      </c>
+      <c r="R214" t="s">
+        <v>113</v>
+      </c>
+      <c r="S214" t="s">
+        <v>39</v>
+      </c>
+      <c r="T214" t="s">
+        <v>66</v>
+      </c>
+      <c r="U214" t="s">
+        <v>41</v>
+      </c>
+      <c r="V214">
+        <v>61</v>
+      </c>
+      <c r="W214">
+        <v>18</v>
+      </c>
+      <c r="X214">
+        <v>50</v>
+      </c>
+      <c r="Y214">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="215" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>202</v>
+      </c>
+      <c r="B215" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C215" t="s">
+        <v>203</v>
+      </c>
+      <c r="D215" t="s">
+        <v>204</v>
+      </c>
+      <c r="E215" t="s">
+        <v>102</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G215" t="s">
+        <v>55</v>
+      </c>
+      <c r="H215" t="s">
+        <v>1469</v>
+      </c>
+      <c r="I215" t="s">
+        <v>1470</v>
+      </c>
+      <c r="J215" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K215" t="s">
+        <v>1472</v>
+      </c>
+      <c r="L215" t="s">
+        <v>1473</v>
+      </c>
+      <c r="M215" t="s">
+        <v>1474</v>
+      </c>
+      <c r="N215" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O215" t="s">
+        <v>40</v>
+      </c>
+      <c r="P215" t="s">
+        <v>1475</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>1476</v>
+      </c>
+      <c r="R215" t="s">
+        <v>113</v>
+      </c>
+      <c r="S215" t="s">
+        <v>39</v>
+      </c>
+      <c r="T215" t="s">
+        <v>38</v>
+      </c>
+      <c r="U215" t="s">
+        <v>201</v>
+      </c>
+      <c r="V215">
+        <v>46</v>
+      </c>
+      <c r="W215">
+        <v>10</v>
+      </c>
+      <c r="X215">
+        <v>39</v>
+      </c>
+      <c r="Y215">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="216" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>202</v>
+      </c>
+      <c r="B216" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C216" t="s">
+        <v>203</v>
+      </c>
+      <c r="D216" t="s">
+        <v>204</v>
+      </c>
+      <c r="E216" t="s">
+        <v>347</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G216" t="s">
+        <v>362</v>
+      </c>
+      <c r="H216" t="s">
+        <v>1478</v>
+      </c>
+      <c r="I216" t="s">
+        <v>1479</v>
+      </c>
+      <c r="J216" t="s">
+        <v>1480</v>
+      </c>
+      <c r="K216" t="s">
+        <v>1481</v>
+      </c>
+      <c r="L216" t="s">
+        <v>834</v>
+      </c>
+      <c r="M216" t="s">
+        <v>1444</v>
+      </c>
+      <c r="N216" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O216" t="s">
+        <v>555</v>
+      </c>
+      <c r="P216" t="s">
+        <v>1482</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>822</v>
+      </c>
+      <c r="R216" t="s">
+        <v>66</v>
+      </c>
+      <c r="S216" t="s">
+        <v>40</v>
+      </c>
+      <c r="T216" t="s">
+        <v>38</v>
+      </c>
+      <c r="U216" t="s">
+        <v>41</v>
+      </c>
+      <c r="V216">
+        <v>48</v>
+      </c>
+      <c r="W216">
+        <v>15</v>
+      </c>
+      <c r="X216">
+        <v>28</v>
+      </c>
+      <c r="Y216">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="217" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>202</v>
+      </c>
+      <c r="B217" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C217" t="s">
+        <v>203</v>
+      </c>
+      <c r="D217" t="s">
+        <v>204</v>
+      </c>
+      <c r="E217" t="s">
+        <v>126</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G217" t="s">
+        <v>706</v>
+      </c>
+      <c r="H217" t="s">
+        <v>1483</v>
+      </c>
+      <c r="I217" t="s">
+        <v>1484</v>
+      </c>
+      <c r="J217" t="s">
+        <v>1485</v>
+      </c>
+      <c r="K217" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L217" t="s">
+        <v>1175</v>
+      </c>
+      <c r="M217" t="s">
+        <v>187</v>
+      </c>
+      <c r="N217" t="s">
+        <v>279</v>
+      </c>
+      <c r="O217" t="s">
+        <v>177</v>
+      </c>
+      <c r="P217" t="s">
+        <v>1487</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>643</v>
+      </c>
+      <c r="R217" t="s">
+        <v>40</v>
+      </c>
+      <c r="S217" t="s">
+        <v>41</v>
+      </c>
+      <c r="T217" t="s">
+        <v>39</v>
+      </c>
+      <c r="U217" t="s">
+        <v>201</v>
+      </c>
+      <c r="V217">
+        <v>38</v>
+      </c>
+      <c r="W217">
+        <v>9</v>
+      </c>
+      <c r="X217">
+        <v>36</v>
+      </c>
+      <c r="Y217">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="218" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>202</v>
+      </c>
+      <c r="B218" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C218" t="s">
+        <v>203</v>
+      </c>
+      <c r="D218" t="s">
+        <v>204</v>
+      </c>
+      <c r="E218" t="s">
+        <v>346</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G218" t="s">
+        <v>603</v>
+      </c>
+      <c r="H218" t="s">
+        <v>1488</v>
+      </c>
+      <c r="I218" t="s">
+        <v>1489</v>
+      </c>
+      <c r="J218" t="s">
+        <v>1490</v>
+      </c>
+      <c r="K218" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L218" t="s">
+        <v>533</v>
+      </c>
+      <c r="M218" t="s">
+        <v>1492</v>
+      </c>
+      <c r="N218" t="s">
+        <v>279</v>
+      </c>
+      <c r="O218" t="s">
+        <v>35</v>
+      </c>
+      <c r="P218" t="s">
+        <v>1493</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>1494</v>
+      </c>
+      <c r="R218" t="s">
+        <v>113</v>
+      </c>
+      <c r="S218" t="s">
+        <v>38</v>
+      </c>
+      <c r="T218" t="s">
+        <v>38</v>
+      </c>
+      <c r="U218" t="s">
+        <v>41</v>
+      </c>
+      <c r="V218">
+        <v>45</v>
+      </c>
+      <c r="W218">
+        <v>13</v>
+      </c>
+      <c r="X218">
+        <v>45</v>
+      </c>
+      <c r="Y218">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="219" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>202</v>
+      </c>
+      <c r="B219" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C219" t="s">
+        <v>203</v>
+      </c>
+      <c r="D219" t="s">
+        <v>204</v>
+      </c>
+      <c r="E219" t="s">
+        <v>137</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G219" t="s">
+        <v>231</v>
+      </c>
+      <c r="H219" t="s">
+        <v>1495</v>
+      </c>
+      <c r="I219" t="s">
+        <v>1496</v>
+      </c>
+      <c r="J219" t="s">
+        <v>1497</v>
+      </c>
+      <c r="K219" t="s">
+        <v>1498</v>
+      </c>
+      <c r="L219" t="s">
+        <v>32</v>
+      </c>
+      <c r="M219" t="s">
+        <v>298</v>
+      </c>
+      <c r="N219" t="s">
+        <v>449</v>
+      </c>
+      <c r="O219" t="s">
+        <v>201</v>
+      </c>
+      <c r="P219" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>176</v>
+      </c>
+      <c r="R219" t="s">
+        <v>66</v>
+      </c>
+      <c r="S219" t="s">
+        <v>38</v>
+      </c>
+      <c r="T219" t="s">
+        <v>39</v>
+      </c>
+      <c r="U219" t="s">
+        <v>41</v>
+      </c>
+      <c r="V219">
+        <v>31</v>
+      </c>
+      <c r="W219">
+        <v>19</v>
+      </c>
+      <c r="X219">
+        <v>50</v>
+      </c>
+      <c r="Y219">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="220" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>202</v>
+      </c>
+      <c r="B220" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C220" t="s">
+        <v>203</v>
+      </c>
+      <c r="D220" t="s">
+        <v>204</v>
+      </c>
+      <c r="E220" t="s">
+        <v>147</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G220" t="s">
+        <v>503</v>
+      </c>
+      <c r="H220" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I220" t="s">
+        <v>1500</v>
+      </c>
+      <c r="J220" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K220" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L220" t="s">
+        <v>766</v>
+      </c>
+      <c r="M220" t="s">
+        <v>1253</v>
+      </c>
+      <c r="N220" t="s">
+        <v>307</v>
+      </c>
+      <c r="O220" t="s">
+        <v>35</v>
+      </c>
+      <c r="P220" t="s">
+        <v>1503</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>1504</v>
+      </c>
+      <c r="R220" t="s">
+        <v>66</v>
+      </c>
+      <c r="S220" t="s">
+        <v>39</v>
+      </c>
+      <c r="T220" t="s">
+        <v>40</v>
+      </c>
+      <c r="U220" t="s">
+        <v>41</v>
+      </c>
+      <c r="V220">
+        <v>39</v>
+      </c>
+      <c r="W220">
+        <v>15</v>
+      </c>
+      <c r="X220">
+        <v>26</v>
+      </c>
+      <c r="Y220">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="221" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>202</v>
+      </c>
+      <c r="B221" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C221" t="s">
+        <v>203</v>
+      </c>
+      <c r="D221" t="s">
+        <v>204</v>
+      </c>
+      <c r="E221" t="s">
+        <v>180</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G221" t="s">
+        <v>148</v>
+      </c>
+      <c r="H221" t="s">
+        <v>1505</v>
+      </c>
+      <c r="I221" t="s">
+        <v>1506</v>
+      </c>
+      <c r="J221" t="s">
+        <v>1507</v>
+      </c>
+      <c r="K221" t="s">
+        <v>1508</v>
+      </c>
+      <c r="L221" t="s">
+        <v>1509</v>
+      </c>
+      <c r="M221" t="s">
+        <v>96</v>
+      </c>
+      <c r="N221" t="s">
+        <v>604</v>
+      </c>
+      <c r="O221" t="s">
+        <v>188</v>
+      </c>
+      <c r="P221" t="s">
+        <v>1510</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>969</v>
+      </c>
+      <c r="R221" t="s">
+        <v>495</v>
+      </c>
+      <c r="S221" t="s">
+        <v>449</v>
+      </c>
+      <c r="T221" t="s">
+        <v>188</v>
+      </c>
+      <c r="U221" t="s">
+        <v>66</v>
+      </c>
+      <c r="V221">
+        <v>85</v>
+      </c>
+      <c r="W221">
+        <v>80</v>
+      </c>
+      <c r="X221">
+        <v>98</v>
+      </c>
+      <c r="Y221">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="222" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>202</v>
+      </c>
+      <c r="B222" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C222" t="s">
+        <v>203</v>
+      </c>
+      <c r="D222" t="s">
+        <v>204</v>
+      </c>
+      <c r="E222" t="s">
+        <v>191</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G222" t="s">
+        <v>370</v>
+      </c>
+      <c r="H222" t="s">
+        <v>1511</v>
+      </c>
+      <c r="I222" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J222" t="s">
+        <v>380</v>
+      </c>
+      <c r="K222" t="s">
+        <v>1513</v>
+      </c>
+      <c r="L222" t="s">
+        <v>426</v>
+      </c>
+      <c r="M222" t="s">
+        <v>306</v>
+      </c>
+      <c r="N222" t="s">
+        <v>51</v>
+      </c>
+      <c r="O222" t="s">
+        <v>39</v>
+      </c>
+      <c r="P222" t="s">
+        <v>1514</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>1396</v>
+      </c>
+      <c r="R222" t="s">
+        <v>39</v>
+      </c>
+      <c r="S222" t="s">
+        <v>41</v>
+      </c>
+      <c r="T222" t="s">
+        <v>39</v>
+      </c>
+      <c r="U222" t="s">
+        <v>41</v>
+      </c>
+      <c r="V222">
+        <v>20</v>
+      </c>
+      <c r="W222">
+        <v>16</v>
+      </c>
+      <c r="X222">
+        <v>24</v>
+      </c>
+      <c r="Y222">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>202</v>
+      </c>
+      <c r="B223" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C223" t="s">
+        <v>203</v>
+      </c>
+      <c r="D223" t="s">
+        <v>849</v>
+      </c>
+      <c r="E223" t="s">
+        <v>25</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G223" t="s">
+        <v>982</v>
+      </c>
+      <c r="H223" t="s">
+        <v>1515</v>
+      </c>
+      <c r="I223" t="s">
+        <v>1516</v>
+      </c>
+      <c r="J223" t="s">
+        <v>1517</v>
+      </c>
+      <c r="K223" t="s">
+        <v>1518</v>
+      </c>
+      <c r="L223" t="s">
+        <v>261</v>
+      </c>
+      <c r="M223" t="s">
+        <v>511</v>
+      </c>
+      <c r="N223" t="s">
+        <v>449</v>
+      </c>
+      <c r="O223" t="s">
+        <v>201</v>
+      </c>
+      <c r="P223" t="s">
+        <v>1037</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>471</v>
+      </c>
+      <c r="R223" t="s">
+        <v>38</v>
+      </c>
+      <c r="S223" t="s">
+        <v>39</v>
+      </c>
+      <c r="T223" t="s">
+        <v>38</v>
+      </c>
+      <c r="U223" t="s">
+        <v>41</v>
+      </c>
+      <c r="V223">
+        <v>37</v>
+      </c>
+      <c r="W223">
+        <v>11</v>
+      </c>
+      <c r="X223">
+        <v>24</v>
+      </c>
+      <c r="Y223">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="224" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>202</v>
+      </c>
+      <c r="B224" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C224" t="s">
+        <v>203</v>
+      </c>
+      <c r="D224" t="s">
+        <v>849</v>
+      </c>
+      <c r="E224" t="s">
+        <v>42</v>
+      </c>
+      <c r="F224" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G224" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H224" t="s">
+        <v>1520</v>
+      </c>
+      <c r="I224" t="s">
+        <v>1521</v>
+      </c>
+      <c r="J224" t="s">
+        <v>684</v>
+      </c>
+      <c r="K224" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L224" t="s">
+        <v>1523</v>
+      </c>
+      <c r="M224" t="s">
+        <v>1524</v>
+      </c>
+      <c r="N224" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O224" t="s">
+        <v>337</v>
+      </c>
+      <c r="P224" t="s">
+        <v>1525</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>427</v>
+      </c>
+      <c r="R224" t="s">
+        <v>38</v>
+      </c>
+      <c r="S224" t="s">
+        <v>39</v>
+      </c>
+      <c r="T224" t="s">
+        <v>39</v>
+      </c>
+      <c r="U224" t="s">
+        <v>41</v>
+      </c>
+      <c r="V224">
+        <v>16</v>
+      </c>
+      <c r="W224">
+        <v>11</v>
+      </c>
+      <c r="X224">
+        <v>18</v>
+      </c>
+      <c r="Y224">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>202</v>
+      </c>
+      <c r="B225" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C225" t="s">
+        <v>203</v>
+      </c>
+      <c r="D225" t="s">
+        <v>849</v>
+      </c>
+      <c r="E225" t="s">
+        <v>54</v>
+      </c>
+      <c r="F225" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G225" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H225" t="s">
+        <v>1526</v>
+      </c>
+      <c r="I225" t="s">
+        <v>1527</v>
+      </c>
+      <c r="J225" t="s">
+        <v>1528</v>
+      </c>
+      <c r="K225" t="s">
+        <v>1529</v>
+      </c>
+      <c r="L225" t="s">
+        <v>1530</v>
+      </c>
+      <c r="M225" t="s">
+        <v>788</v>
+      </c>
+      <c r="N225" t="s">
+        <v>177</v>
+      </c>
+      <c r="O225" t="s">
+        <v>40</v>
+      </c>
+      <c r="P225" t="s">
+        <v>1531</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>1225</v>
+      </c>
+      <c r="R225" t="s">
+        <v>38</v>
+      </c>
+      <c r="S225" t="s">
+        <v>41</v>
+      </c>
+      <c r="T225" t="s">
+        <v>40</v>
+      </c>
+      <c r="U225" t="s">
+        <v>41</v>
+      </c>
+      <c r="V225">
+        <v>29</v>
+      </c>
+      <c r="W225">
+        <v>18</v>
+      </c>
+      <c r="X225">
+        <v>32</v>
+      </c>
+      <c r="Y225">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="226" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>202</v>
+      </c>
+      <c r="B226" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C226" t="s">
+        <v>203</v>
+      </c>
+      <c r="D226" t="s">
+        <v>849</v>
+      </c>
+      <c r="E226" t="s">
+        <v>79</v>
+      </c>
+      <c r="F226" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G226" t="s">
+        <v>211</v>
+      </c>
+      <c r="H226" t="s">
+        <v>1532</v>
+      </c>
+      <c r="I226" t="s">
+        <v>1533</v>
+      </c>
+      <c r="J226" t="s">
+        <v>1534</v>
+      </c>
+      <c r="K226" t="s">
+        <v>1535</v>
+      </c>
+      <c r="L226" t="s">
+        <v>121</v>
+      </c>
+      <c r="M226" t="s">
+        <v>1127</v>
+      </c>
+      <c r="N226" t="s">
+        <v>672</v>
+      </c>
+      <c r="O226" t="s">
+        <v>38</v>
+      </c>
+      <c r="P226" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>454</v>
+      </c>
+      <c r="R226" t="s">
+        <v>38</v>
+      </c>
+      <c r="S226" t="s">
+        <v>41</v>
+      </c>
+      <c r="T226" t="s">
+        <v>38</v>
+      </c>
+      <c r="U226" t="s">
+        <v>41</v>
+      </c>
+      <c r="V226">
+        <v>21</v>
+      </c>
+      <c r="W226">
+        <v>17</v>
+      </c>
+      <c r="X226">
+        <v>23</v>
+      </c>
+      <c r="Y226">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="227" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>202</v>
+      </c>
+      <c r="B227" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C227" t="s">
+        <v>203</v>
+      </c>
+      <c r="D227" t="s">
+        <v>849</v>
+      </c>
+      <c r="E227" t="s">
+        <v>90</v>
+      </c>
+      <c r="F227" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G227" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H227" t="s">
+        <v>1536</v>
+      </c>
+      <c r="I227" t="s">
+        <v>1537</v>
+      </c>
+      <c r="J227" t="s">
+        <v>258</v>
+      </c>
+      <c r="K227" t="s">
+        <v>1538</v>
+      </c>
+      <c r="L227" t="s">
+        <v>662</v>
+      </c>
+      <c r="M227" t="s">
+        <v>774</v>
+      </c>
+      <c r="N227" t="s">
+        <v>307</v>
+      </c>
+      <c r="O227" t="s">
+        <v>39</v>
+      </c>
+      <c r="P227" t="s">
+        <v>1539</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>829</v>
+      </c>
+      <c r="R227" t="s">
+        <v>38</v>
+      </c>
+      <c r="S227" t="s">
+        <v>41</v>
+      </c>
+      <c r="T227" t="s">
+        <v>38</v>
+      </c>
+      <c r="U227" t="s">
+        <v>41</v>
+      </c>
+      <c r="V227">
+        <v>38</v>
+      </c>
+      <c r="W227">
+        <v>10</v>
+      </c>
+      <c r="X227">
+        <v>32</v>
+      </c>
+      <c r="Y227">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="228" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>202</v>
+      </c>
+      <c r="B228" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C228" t="s">
+        <v>203</v>
+      </c>
+      <c r="D228" t="s">
+        <v>849</v>
+      </c>
+      <c r="E228" t="s">
+        <v>102</v>
+      </c>
+      <c r="F228" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G228" t="s">
+        <v>487</v>
+      </c>
+      <c r="H228" t="s">
+        <v>1540</v>
+      </c>
+      <c r="I228" t="s">
+        <v>1541</v>
+      </c>
+      <c r="J228" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K228" t="s">
+        <v>1542</v>
+      </c>
+      <c r="L228" t="s">
+        <v>595</v>
+      </c>
+      <c r="M228" t="s">
+        <v>891</v>
+      </c>
+      <c r="N228" t="s">
+        <v>377</v>
+      </c>
+      <c r="O228" t="s">
+        <v>337</v>
+      </c>
+      <c r="P228" t="s">
+        <v>1543</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>836</v>
+      </c>
+      <c r="R228" t="s">
+        <v>66</v>
+      </c>
+      <c r="S228" t="s">
+        <v>38</v>
+      </c>
+      <c r="T228" t="s">
+        <v>40</v>
+      </c>
+      <c r="U228" t="s">
+        <v>41</v>
+      </c>
+      <c r="V228">
+        <v>43</v>
+      </c>
+      <c r="W228">
+        <v>20</v>
+      </c>
+      <c r="X228">
+        <v>34</v>
+      </c>
+      <c r="Y228">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="229" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>202</v>
+      </c>
+      <c r="B229" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C229" t="s">
+        <v>203</v>
+      </c>
+      <c r="D229" t="s">
+        <v>849</v>
+      </c>
+      <c r="E229" t="s">
+        <v>347</v>
+      </c>
+      <c r="F229" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G229" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H229" t="s">
+        <v>1545</v>
+      </c>
+      <c r="I229" t="s">
+        <v>1546</v>
+      </c>
+      <c r="J229" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K229" t="s">
+        <v>1548</v>
+      </c>
+      <c r="L229" t="s">
+        <v>867</v>
+      </c>
+      <c r="M229" t="s">
+        <v>192</v>
+      </c>
+      <c r="N229" t="s">
+        <v>134</v>
+      </c>
+      <c r="O229" t="s">
+        <v>66</v>
+      </c>
+      <c r="P229" t="s">
+        <v>1549</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>169</v>
+      </c>
+      <c r="R229" t="s">
+        <v>66</v>
+      </c>
+      <c r="S229" t="s">
+        <v>39</v>
+      </c>
+      <c r="T229" t="s">
+        <v>40</v>
+      </c>
+      <c r="U229" t="s">
+        <v>41</v>
+      </c>
+      <c r="V229">
+        <v>29</v>
+      </c>
+      <c r="W229">
+        <v>20</v>
+      </c>
+      <c r="X229">
+        <v>25</v>
+      </c>
+      <c r="Y229">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="230" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>202</v>
+      </c>
+      <c r="B230" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C230" t="s">
+        <v>203</v>
+      </c>
+      <c r="D230" t="s">
+        <v>849</v>
+      </c>
+      <c r="E230" t="s">
+        <v>126</v>
+      </c>
+      <c r="F230" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G230" t="s">
+        <v>548</v>
+      </c>
+      <c r="H230" t="s">
+        <v>1550</v>
+      </c>
+      <c r="I230" t="s">
+        <v>1551</v>
+      </c>
+      <c r="J230" t="s">
+        <v>1552</v>
+      </c>
+      <c r="K230" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L230" t="s">
+        <v>426</v>
+      </c>
+      <c r="M230" t="s">
+        <v>1530</v>
+      </c>
+      <c r="N230" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O230" t="s">
+        <v>488</v>
+      </c>
+      <c r="P230" t="s">
+        <v>1554</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>1555</v>
+      </c>
+      <c r="R230" t="s">
+        <v>66</v>
+      </c>
+      <c r="S230" t="s">
+        <v>41</v>
+      </c>
+      <c r="T230" t="s">
+        <v>40</v>
+      </c>
+      <c r="U230" t="s">
+        <v>41</v>
+      </c>
+      <c r="V230">
+        <v>47</v>
+      </c>
+      <c r="W230">
+        <v>17</v>
+      </c>
+      <c r="X230">
+        <v>42</v>
+      </c>
+      <c r="Y230">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="231" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>202</v>
+      </c>
+      <c r="B231" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C231" t="s">
+        <v>203</v>
+      </c>
+      <c r="D231" t="s">
+        <v>849</v>
+      </c>
+      <c r="E231" t="s">
+        <v>346</v>
+      </c>
+      <c r="F231" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G231" t="s">
+        <v>211</v>
+      </c>
+      <c r="H231" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I231" t="s">
+        <v>1557</v>
+      </c>
+      <c r="J231" t="s">
+        <v>1558</v>
+      </c>
+      <c r="K231" t="s">
+        <v>1559</v>
+      </c>
+      <c r="L231" t="s">
+        <v>564</v>
+      </c>
+      <c r="M231" t="s">
+        <v>891</v>
+      </c>
+      <c r="N231" t="s">
+        <v>1560</v>
+      </c>
+      <c r="O231" t="s">
+        <v>280</v>
+      </c>
+      <c r="P231" t="s">
+        <v>1561</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>572</v>
+      </c>
+      <c r="R231" t="s">
+        <v>66</v>
+      </c>
+      <c r="S231" t="s">
+        <v>39</v>
+      </c>
+      <c r="T231" t="s">
+        <v>66</v>
+      </c>
+      <c r="U231" t="s">
+        <v>41</v>
+      </c>
+      <c r="V231">
+        <v>45</v>
+      </c>
+      <c r="W231">
+        <v>18</v>
+      </c>
+      <c r="X231">
+        <v>38</v>
+      </c>
+      <c r="Y231">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="232" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>202</v>
+      </c>
+      <c r="B232" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C232" t="s">
+        <v>203</v>
+      </c>
+      <c r="D232" t="s">
+        <v>849</v>
+      </c>
+      <c r="E232" t="s">
+        <v>137</v>
+      </c>
+      <c r="F232" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G232" t="s">
+        <v>774</v>
+      </c>
+      <c r="H232" t="s">
+        <v>1562</v>
+      </c>
+      <c r="I232" t="s">
+        <v>1563</v>
+      </c>
+      <c r="J232" t="s">
+        <v>1341</v>
+      </c>
+      <c r="K232" t="s">
+        <v>1564</v>
+      </c>
+      <c r="L232" t="s">
+        <v>1014</v>
+      </c>
+      <c r="M232" t="s">
+        <v>774</v>
+      </c>
+      <c r="N232" t="s">
+        <v>555</v>
+      </c>
+      <c r="O232" t="s">
+        <v>201</v>
+      </c>
+      <c r="P232" t="s">
+        <v>1565</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>488</v>
+      </c>
+      <c r="R232" t="s">
+        <v>40</v>
+      </c>
+      <c r="S232" t="s">
+        <v>39</v>
+      </c>
+      <c r="T232" t="s">
+        <v>39</v>
+      </c>
+      <c r="U232" t="s">
+        <v>201</v>
+      </c>
+      <c r="V232">
+        <v>36</v>
+      </c>
+      <c r="W232">
+        <v>6</v>
+      </c>
+      <c r="X232">
+        <v>34</v>
+      </c>
+      <c r="Y232">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="233" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>202</v>
+      </c>
+      <c r="B233" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C233" t="s">
+        <v>203</v>
+      </c>
+      <c r="D233" t="s">
+        <v>849</v>
+      </c>
+      <c r="E233" t="s">
+        <v>147</v>
+      </c>
+      <c r="F233" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G233" t="s">
+        <v>1566</v>
+      </c>
+      <c r="H233" t="s">
+        <v>1567</v>
+      </c>
+      <c r="I233" t="s">
+        <v>1568</v>
+      </c>
+      <c r="J233" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K233" t="s">
+        <v>1570</v>
+      </c>
+      <c r="L233" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M233" t="s">
+        <v>487</v>
+      </c>
+      <c r="N233" t="s">
+        <v>99</v>
+      </c>
+      <c r="O233" t="s">
+        <v>555</v>
+      </c>
+      <c r="P233" t="s">
+        <v>1571</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>1572</v>
+      </c>
+      <c r="R233" t="s">
+        <v>40</v>
+      </c>
+      <c r="S233" t="s">
+        <v>39</v>
+      </c>
+      <c r="T233" t="s">
+        <v>39</v>
+      </c>
+      <c r="U233" t="s">
+        <v>41</v>
+      </c>
+      <c r="V233">
+        <v>18</v>
+      </c>
+      <c r="W233">
+        <v>11</v>
+      </c>
+      <c r="X233">
+        <v>23</v>
+      </c>
+      <c r="Y233">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="234" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>202</v>
+      </c>
+      <c r="B234" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C234" t="s">
+        <v>203</v>
+      </c>
+      <c r="D234" t="s">
+        <v>849</v>
+      </c>
+      <c r="E234" t="s">
+        <v>157</v>
+      </c>
+      <c r="F234" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G234" t="s">
+        <v>521</v>
+      </c>
+      <c r="H234" t="s">
+        <v>1573</v>
+      </c>
+      <c r="I234" t="s">
+        <v>1574</v>
+      </c>
+      <c r="J234" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K234" t="s">
+        <v>1576</v>
+      </c>
+      <c r="L234" t="s">
+        <v>55</v>
+      </c>
+      <c r="M234" t="s">
+        <v>261</v>
+      </c>
+      <c r="N234" t="s">
+        <v>672</v>
+      </c>
+      <c r="O234" t="s">
+        <v>66</v>
+      </c>
+      <c r="P234" t="s">
+        <v>1577</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>766</v>
+      </c>
+      <c r="R234" t="s">
+        <v>38</v>
+      </c>
+      <c r="S234" t="s">
+        <v>41</v>
+      </c>
+      <c r="T234" t="s">
+        <v>40</v>
+      </c>
+      <c r="U234" t="s">
+        <v>41</v>
+      </c>
+      <c r="V234">
+        <v>31</v>
+      </c>
+      <c r="W234">
+        <v>20</v>
+      </c>
+      <c r="X234">
+        <v>34</v>
+      </c>
+      <c r="Y234">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="235" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>202</v>
+      </c>
+      <c r="B235" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C235" t="s">
+        <v>203</v>
+      </c>
+      <c r="D235" t="s">
+        <v>849</v>
+      </c>
+      <c r="E235" t="s">
+        <v>180</v>
+      </c>
+      <c r="F235" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G235" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H235" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I235" t="s">
+        <v>1579</v>
+      </c>
+      <c r="J235" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K235" t="s">
+        <v>1581</v>
+      </c>
+      <c r="L235" t="s">
+        <v>602</v>
+      </c>
+      <c r="M235" t="s">
+        <v>1582</v>
+      </c>
+      <c r="N235" t="s">
+        <v>232</v>
+      </c>
+      <c r="O235" t="s">
+        <v>76</v>
+      </c>
+      <c r="P235" t="s">
+        <v>588</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>1583</v>
+      </c>
+      <c r="R235" t="s">
+        <v>555</v>
+      </c>
+      <c r="S235" t="s">
+        <v>35</v>
+      </c>
+      <c r="T235" t="s">
+        <v>488</v>
+      </c>
+      <c r="U235" t="s">
+        <v>66</v>
+      </c>
+      <c r="V235">
+        <v>83</v>
+      </c>
+      <c r="W235">
+        <v>70</v>
+      </c>
+      <c r="X235">
+        <v>94</v>
+      </c>
+      <c r="Y235">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="236" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>202</v>
+      </c>
+      <c r="B236" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C236" t="s">
+        <v>203</v>
+      </c>
+      <c r="D236" t="s">
+        <v>849</v>
+      </c>
+      <c r="E236" t="s">
+        <v>191</v>
+      </c>
+      <c r="F236" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G236" t="s">
+        <v>719</v>
+      </c>
+      <c r="H236" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I236" t="s">
+        <v>1585</v>
+      </c>
+      <c r="J236" t="s">
+        <v>1586</v>
+      </c>
+      <c r="K236" t="s">
+        <v>1587</v>
+      </c>
+      <c r="L236" t="s">
+        <v>686</v>
+      </c>
+      <c r="M236" t="s">
+        <v>370</v>
+      </c>
+      <c r="N236" t="s">
+        <v>555</v>
+      </c>
+      <c r="O236" t="s">
+        <v>41</v>
+      </c>
+      <c r="P236" t="s">
+        <v>1588</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>371</v>
+      </c>
+      <c r="R236" t="s">
+        <v>41</v>
+      </c>
+      <c r="S236" t="s">
+        <v>41</v>
+      </c>
+      <c r="T236" t="s">
+        <v>41</v>
+      </c>
+      <c r="U236" t="s">
+        <v>201</v>
+      </c>
+      <c r="V236">
+        <v>19</v>
+      </c>
+      <c r="W236">
+        <v>9</v>
+      </c>
+      <c r="X236">
+        <v>11</v>
+      </c>
+      <c r="Y236">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B237" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C237" t="s">
+        <v>203</v>
+      </c>
+      <c r="D237" t="s">
+        <v>348</v>
+      </c>
+      <c r="E237" t="s">
+        <v>42</v>
+      </c>
+      <c r="F237" t="s">
+        <v>1589</v>
+      </c>
+      <c r="G237" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H237" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I237" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J237" t="s">
+        <v>1593</v>
+      </c>
+      <c r="K237" t="s">
+        <v>1594</v>
+      </c>
+      <c r="L237" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M237" t="s">
+        <v>1350</v>
+      </c>
+      <c r="N237" t="s">
+        <v>672</v>
+      </c>
+      <c r="O237" t="s">
+        <v>66</v>
+      </c>
+      <c r="P237" t="s">
+        <v>1595</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>834</v>
+      </c>
+      <c r="R237" t="s">
+        <v>38</v>
+      </c>
+      <c r="S237" t="s">
+        <v>39</v>
+      </c>
+      <c r="T237" t="s">
+        <v>39</v>
+      </c>
+      <c r="U237" t="s">
+        <v>41</v>
+      </c>
+      <c r="V237">
+        <v>17</v>
+      </c>
+      <c r="W237">
+        <v>13</v>
+      </c>
+      <c r="X237">
+        <v>13</v>
+      </c>
+      <c r="Y237">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B238" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C238" t="s">
+        <v>203</v>
+      </c>
+      <c r="D238" t="s">
+        <v>348</v>
+      </c>
+      <c r="E238" t="s">
+        <v>54</v>
+      </c>
+      <c r="F238" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G238" t="s">
+        <v>1597</v>
+      </c>
+      <c r="H238" t="s">
+        <v>1598</v>
+      </c>
+      <c r="I238" t="s">
+        <v>1599</v>
+      </c>
+      <c r="J238" t="s">
+        <v>916</v>
+      </c>
+      <c r="K238" t="s">
+        <v>1600</v>
+      </c>
+      <c r="L238" t="s">
+        <v>1601</v>
+      </c>
+      <c r="M238" t="s">
+        <v>251</v>
+      </c>
+      <c r="N238" t="s">
+        <v>892</v>
+      </c>
+      <c r="O238" t="s">
+        <v>449</v>
+      </c>
+      <c r="P238" t="s">
+        <v>1602</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>1603</v>
+      </c>
+      <c r="R238" t="s">
+        <v>488</v>
+      </c>
+      <c r="S238" t="s">
+        <v>113</v>
+      </c>
+      <c r="T238" t="s">
+        <v>337</v>
+      </c>
+      <c r="U238" t="s">
+        <v>39</v>
+      </c>
+      <c r="V238">
+        <v>79</v>
+      </c>
+      <c r="W238">
+        <v>42</v>
+      </c>
+      <c r="X238">
+        <v>46</v>
+      </c>
+      <c r="Y238">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="239" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B239" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C239" t="s">
+        <v>203</v>
+      </c>
+      <c r="D239" t="s">
+        <v>348</v>
+      </c>
+      <c r="E239" t="s">
+        <v>90</v>
+      </c>
+      <c r="F239" t="s">
+        <v>1604</v>
+      </c>
+      <c r="G239" t="s">
+        <v>186</v>
+      </c>
+      <c r="H239" t="s">
+        <v>1605</v>
+      </c>
+      <c r="I239" t="s">
+        <v>1606</v>
+      </c>
+      <c r="J239" t="s">
+        <v>1607</v>
+      </c>
+      <c r="K239" t="s">
+        <v>1608</v>
+      </c>
+      <c r="L239" t="s">
+        <v>1609</v>
+      </c>
+      <c r="M239" t="s">
+        <v>246</v>
+      </c>
+      <c r="N239" t="s">
+        <v>134</v>
+      </c>
+      <c r="O239" t="s">
+        <v>35</v>
+      </c>
+      <c r="P239" t="s">
+        <v>1610</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>1504</v>
+      </c>
+      <c r="R239" t="s">
+        <v>40</v>
+      </c>
+      <c r="S239" t="s">
+        <v>41</v>
+      </c>
+      <c r="T239" t="s">
+        <v>39</v>
+      </c>
+      <c r="U239" t="s">
+        <v>201</v>
+      </c>
+      <c r="V239">
+        <v>30</v>
+      </c>
+      <c r="W239">
+        <v>4</v>
+      </c>
+      <c r="X239">
+        <v>15</v>
+      </c>
+      <c r="Y239">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="240" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B240" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C240" t="s">
+        <v>203</v>
+      </c>
+      <c r="D240" t="s">
+        <v>348</v>
+      </c>
+      <c r="E240" t="s">
+        <v>102</v>
+      </c>
+      <c r="F240" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G240" t="s">
+        <v>1612</v>
+      </c>
+      <c r="H240" t="s">
+        <v>1613</v>
+      </c>
+      <c r="I240" t="s">
+        <v>1614</v>
+      </c>
+      <c r="J240" t="s">
+        <v>1615</v>
+      </c>
+      <c r="K240" t="s">
+        <v>1616</v>
+      </c>
+      <c r="L240" t="s">
+        <v>1617</v>
+      </c>
+      <c r="M240" t="s">
+        <v>525</v>
+      </c>
+      <c r="N240" t="s">
+        <v>87</v>
+      </c>
+      <c r="O240" t="s">
+        <v>337</v>
+      </c>
+      <c r="P240" t="s">
+        <v>1618</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>1619</v>
+      </c>
+      <c r="R240" t="s">
+        <v>337</v>
+      </c>
+      <c r="S240" t="s">
+        <v>38</v>
+      </c>
+      <c r="T240" t="s">
+        <v>66</v>
+      </c>
+      <c r="U240" t="s">
+        <v>41</v>
+      </c>
+      <c r="V240">
+        <v>72</v>
+      </c>
+      <c r="W240">
+        <v>25</v>
+      </c>
+      <c r="X240">
+        <v>67</v>
+      </c>
+      <c r="Y240">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="241" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B241" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C241" t="s">
+        <v>203</v>
+      </c>
+      <c r="D241" t="s">
+        <v>348</v>
+      </c>
+      <c r="E241" t="s">
+        <v>895</v>
+      </c>
+      <c r="F241" t="s">
+        <v>1620</v>
+      </c>
+      <c r="G241" t="s">
+        <v>1621</v>
+      </c>
+      <c r="H241" t="s">
+        <v>1622</v>
+      </c>
+      <c r="I241" t="s">
+        <v>1623</v>
+      </c>
+      <c r="J241" t="s">
+        <v>1624</v>
+      </c>
+      <c r="K241" t="s">
+        <v>1625</v>
+      </c>
+      <c r="L241" t="s">
+        <v>1626</v>
+      </c>
+      <c r="M241" t="s">
+        <v>80</v>
+      </c>
+      <c r="N241" t="s">
+        <v>411</v>
+      </c>
+      <c r="O241" t="s">
+        <v>280</v>
+      </c>
+      <c r="P241" t="s">
+        <v>1627</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>1628</v>
+      </c>
+      <c r="R241" t="s">
+        <v>488</v>
+      </c>
+      <c r="S241" t="s">
+        <v>66</v>
+      </c>
+      <c r="T241" t="s">
+        <v>113</v>
+      </c>
+      <c r="U241" t="s">
+        <v>41</v>
+      </c>
+      <c r="V241">
+        <v>56</v>
+      </c>
+      <c r="W241">
+        <v>22</v>
+      </c>
+      <c r="X241">
+        <v>59</v>
+      </c>
+      <c r="Y241">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="242" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B242" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C242" t="s">
+        <v>203</v>
+      </c>
+      <c r="D242" t="s">
+        <v>348</v>
+      </c>
+      <c r="E242" t="s">
+        <v>346</v>
+      </c>
+      <c r="F242" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G242" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H242" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I242" t="s">
+        <v>1632</v>
+      </c>
+      <c r="J242" t="s">
+        <v>1633</v>
+      </c>
+      <c r="K242" t="s">
+        <v>1634</v>
+      </c>
+      <c r="L242" t="s">
+        <v>386</v>
+      </c>
+      <c r="M242" t="s">
+        <v>1127</v>
+      </c>
+      <c r="N242" t="s">
+        <v>122</v>
+      </c>
+      <c r="O242" t="s">
+        <v>280</v>
+      </c>
+      <c r="P242" t="s">
+        <v>1635</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>1636</v>
+      </c>
+      <c r="R242" t="s">
+        <v>337</v>
+      </c>
+      <c r="S242" t="s">
+        <v>40</v>
+      </c>
+      <c r="T242" t="s">
+        <v>35</v>
+      </c>
+      <c r="U242" t="s">
+        <v>39</v>
+      </c>
+      <c r="V242">
+        <v>60</v>
+      </c>
+      <c r="W242">
+        <v>35</v>
+      </c>
+      <c r="X242">
+        <v>67</v>
+      </c>
+      <c r="Y242">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="243" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B243" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C243" t="s">
+        <v>203</v>
+      </c>
+      <c r="D243" t="s">
+        <v>348</v>
+      </c>
+      <c r="E243" t="s">
+        <v>137</v>
+      </c>
+      <c r="F243" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G243" t="s">
+        <v>1637</v>
+      </c>
+      <c r="H243" t="s">
+        <v>1638</v>
+      </c>
+      <c r="I243" t="s">
+        <v>1639</v>
+      </c>
+      <c r="J243" t="s">
+        <v>1640</v>
+      </c>
+      <c r="K243" t="s">
+        <v>1641</v>
+      </c>
+      <c r="L243" t="s">
+        <v>288</v>
+      </c>
+      <c r="M243" t="s">
+        <v>663</v>
+      </c>
+      <c r="N243" t="s">
+        <v>377</v>
+      </c>
+      <c r="O243" t="s">
+        <v>113</v>
+      </c>
+      <c r="P243" t="s">
+        <v>1642</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>957</v>
+      </c>
+      <c r="R243" t="s">
+        <v>449</v>
+      </c>
+      <c r="S243" t="s">
+        <v>40</v>
+      </c>
+      <c r="T243" t="s">
+        <v>113</v>
+      </c>
+      <c r="U243" t="s">
+        <v>41</v>
+      </c>
+      <c r="V243">
+        <v>83</v>
+      </c>
+      <c r="W243">
+        <v>28</v>
+      </c>
+      <c r="X243">
+        <v>71</v>
+      </c>
+      <c r="Y243">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="244" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B244" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C244" t="s">
+        <v>203</v>
+      </c>
+      <c r="D244" t="s">
+        <v>348</v>
+      </c>
+      <c r="E244" t="s">
+        <v>157</v>
+      </c>
+      <c r="F244" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G244" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H244" t="s">
+        <v>1645</v>
+      </c>
+      <c r="I244" t="s">
+        <v>1646</v>
+      </c>
+      <c r="J244" t="s">
+        <v>1647</v>
+      </c>
+      <c r="K244" t="s">
+        <v>1648</v>
+      </c>
+      <c r="L244" t="s">
+        <v>960</v>
+      </c>
+      <c r="M244" t="s">
+        <v>404</v>
+      </c>
+      <c r="N244" t="s">
+        <v>213</v>
+      </c>
+      <c r="O244" t="s">
+        <v>113</v>
+      </c>
+      <c r="P244" t="s">
+        <v>1501</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>398</v>
+      </c>
+      <c r="R244" t="s">
+        <v>40</v>
+      </c>
+      <c r="S244" t="s">
+        <v>39</v>
+      </c>
+      <c r="T244" t="s">
+        <v>39</v>
+      </c>
+      <c r="U244" t="s">
+        <v>41</v>
+      </c>
+      <c r="V244">
+        <v>22</v>
+      </c>
+      <c r="W244">
+        <v>14</v>
+      </c>
+      <c r="X244">
+        <v>15</v>
+      </c>
+      <c r="Y244">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="245" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B245" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C245" t="s">
+        <v>203</v>
+      </c>
+      <c r="D245" t="s">
+        <v>348</v>
+      </c>
+      <c r="E245" t="s">
+        <v>933</v>
+      </c>
+      <c r="F245" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G245" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H245" t="s">
+        <v>1651</v>
+      </c>
+      <c r="I245" t="s">
+        <v>1652</v>
+      </c>
+      <c r="J245" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K245" t="s">
+        <v>1653</v>
+      </c>
+      <c r="L245" t="s">
+        <v>706</v>
+      </c>
+      <c r="M245" t="s">
+        <v>1654</v>
+      </c>
+      <c r="N245" t="s">
+        <v>495</v>
+      </c>
+      <c r="O245" t="s">
+        <v>113</v>
+      </c>
+      <c r="P245" t="s">
+        <v>1655</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>1255</v>
+      </c>
+      <c r="R245" t="s">
+        <v>38</v>
+      </c>
+      <c r="S245" t="s">
+        <v>41</v>
+      </c>
+      <c r="T245" t="s">
+        <v>39</v>
+      </c>
+      <c r="U245" t="s">
+        <v>41</v>
+      </c>
+      <c r="V245">
+        <v>21</v>
+      </c>
+      <c r="W245">
+        <v>9</v>
+      </c>
+      <c r="X245">
+        <v>22</v>
+      </c>
+      <c r="Y245">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B246" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C246" t="s">
+        <v>203</v>
+      </c>
+      <c r="D246" t="s">
+        <v>348</v>
+      </c>
+      <c r="E246" t="s">
+        <v>180</v>
+      </c>
+      <c r="F246" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G246" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H246" t="s">
+        <v>1657</v>
+      </c>
+      <c r="I246" t="s">
+        <v>1658</v>
+      </c>
+      <c r="J246" t="s">
+        <v>1659</v>
+      </c>
+      <c r="K246" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L246" t="s">
+        <v>420</v>
+      </c>
+      <c r="M246" t="s">
+        <v>748</v>
+      </c>
+      <c r="N246" t="s">
+        <v>110</v>
+      </c>
+      <c r="O246" t="s">
+        <v>39</v>
+      </c>
+      <c r="P246" t="s">
+        <v>1661</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>977</v>
+      </c>
+      <c r="R246" t="s">
+        <v>113</v>
+      </c>
+      <c r="S246" t="s">
+        <v>39</v>
+      </c>
+      <c r="T246" t="s">
+        <v>40</v>
+      </c>
+      <c r="U246" t="s">
+        <v>41</v>
+      </c>
+      <c r="V246">
+        <v>56</v>
+      </c>
+      <c r="W246">
+        <v>23</v>
+      </c>
+      <c r="X246">
+        <v>46</v>
+      </c>
+      <c r="Y246">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="247" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B247" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C247" t="s">
+        <v>203</v>
+      </c>
+      <c r="D247" t="s">
+        <v>348</v>
+      </c>
+      <c r="E247" t="s">
+        <v>191</v>
+      </c>
+      <c r="F247" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G247" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H247" t="s">
+        <v>1663</v>
+      </c>
+      <c r="I247" t="s">
+        <v>1664</v>
+      </c>
+      <c r="J247" t="s">
+        <v>30</v>
+      </c>
+      <c r="K247" t="s">
+        <v>1665</v>
+      </c>
+      <c r="L247" t="s">
+        <v>1666</v>
+      </c>
+      <c r="M247" t="s">
+        <v>866</v>
+      </c>
+      <c r="N247" t="s">
+        <v>1448</v>
+      </c>
+      <c r="O247" t="s">
+        <v>337</v>
+      </c>
+      <c r="P247" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>1668</v>
+      </c>
+      <c r="R247" t="s">
+        <v>113</v>
+      </c>
+      <c r="S247" t="s">
+        <v>39</v>
+      </c>
+      <c r="T247" t="s">
+        <v>40</v>
+      </c>
+      <c r="U247" t="s">
+        <v>41</v>
+      </c>
+      <c r="V247">
+        <v>45</v>
+      </c>
+      <c r="W247">
+        <v>27</v>
+      </c>
+      <c r="X247">
+        <v>49</v>
+      </c>
+      <c r="Y247">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="248" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>202</v>
+      </c>
+      <c r="B248" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C248" t="s">
+        <v>203</v>
+      </c>
+      <c r="D248" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F248" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G248" t="s">
+        <v>1670</v>
+      </c>
+      <c r="H248" t="s">
+        <v>1671</v>
+      </c>
+      <c r="I248" t="s">
+        <v>1672</v>
+      </c>
+      <c r="J248" t="s">
+        <v>1260</v>
+      </c>
+      <c r="K248" t="s">
+        <v>1673</v>
+      </c>
+      <c r="L248" t="s">
+        <v>583</v>
+      </c>
+      <c r="M248" t="s">
+        <v>1350</v>
+      </c>
+      <c r="N248" t="s">
+        <v>290</v>
+      </c>
+      <c r="O248" t="s">
+        <v>41</v>
+      </c>
+      <c r="P248" t="s">
+        <v>1674</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R248" t="s">
+        <v>40</v>
+      </c>
+      <c r="S248" t="s">
+        <v>39</v>
+      </c>
+      <c r="T248" t="s">
+        <v>40</v>
+      </c>
+      <c r="U248" t="s">
+        <v>41</v>
+      </c>
+      <c r="V248">
+        <v>50</v>
+      </c>
+      <c r="W248">
+        <v>27</v>
+      </c>
+      <c r="X248">
+        <v>27</v>
+      </c>
+      <c r="Y248">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="249" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>202</v>
+      </c>
+      <c r="B249" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C249" t="s">
+        <v>203</v>
+      </c>
+      <c r="D249" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E249" t="s">
+        <v>42</v>
+      </c>
+      <c r="F249" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G249" t="s">
+        <v>272</v>
+      </c>
+      <c r="H249" t="s">
+        <v>1675</v>
+      </c>
+      <c r="I249" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J249" t="s">
+        <v>1677</v>
+      </c>
+      <c r="K249" t="s">
+        <v>1678</v>
+      </c>
+      <c r="L249" t="s">
+        <v>1679</v>
+      </c>
+      <c r="M249" t="s">
+        <v>1680</v>
+      </c>
+      <c r="N249" t="s">
+        <v>41</v>
+      </c>
+      <c r="O249" t="s">
+        <v>201</v>
+      </c>
+      <c r="P249" t="s">
+        <v>1681</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>201</v>
+      </c>
+      <c r="R249" t="s">
+        <v>201</v>
+      </c>
+      <c r="S249" t="s">
+        <v>201</v>
+      </c>
+      <c r="T249" t="s">
+        <v>41</v>
+      </c>
+      <c r="U249" t="s">
+        <v>201</v>
+      </c>
+      <c r="V249">
+        <v>11</v>
+      </c>
+      <c r="W249">
+        <v>3</v>
+      </c>
+      <c r="X249">
+        <v>6</v>
+      </c>
+      <c r="Y249">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>202</v>
+      </c>
+      <c r="B250" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C250" t="s">
+        <v>203</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E250" t="s">
+        <v>54</v>
+      </c>
+      <c r="F250" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G250" t="s">
+        <v>1682</v>
+      </c>
+      <c r="H250" t="s">
+        <v>1683</v>
+      </c>
+      <c r="I250" t="s">
+        <v>1684</v>
+      </c>
+      <c r="J250" t="s">
+        <v>1685</v>
+      </c>
+      <c r="K250" t="s">
+        <v>1686</v>
+      </c>
+      <c r="L250" t="s">
+        <v>1417</v>
+      </c>
+      <c r="M250" t="s">
+        <v>278</v>
+      </c>
+      <c r="N250" t="s">
+        <v>40</v>
+      </c>
+      <c r="O250" t="s">
+        <v>201</v>
+      </c>
+      <c r="P250" t="s">
+        <v>766</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>471</v>
+      </c>
+      <c r="R250" t="s">
+        <v>38</v>
+      </c>
+      <c r="S250" t="s">
+        <v>39</v>
+      </c>
+      <c r="T250" t="s">
+        <v>40</v>
+      </c>
+      <c r="U250" t="s">
+        <v>41</v>
+      </c>
+      <c r="V250">
+        <v>42</v>
+      </c>
+      <c r="W250">
+        <v>24</v>
+      </c>
+      <c r="X250">
+        <v>30</v>
+      </c>
+      <c r="Y250">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="251" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>202</v>
+      </c>
+      <c r="B251" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C251" t="s">
+        <v>203</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E251" t="s">
+        <v>102</v>
+      </c>
+      <c r="F251" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G251" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H251" t="s">
+        <v>1687</v>
+      </c>
+      <c r="I251" t="s">
+        <v>1688</v>
+      </c>
+      <c r="J251" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K251" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L251" t="s">
+        <v>679</v>
+      </c>
+      <c r="M251" t="s">
+        <v>1417</v>
+      </c>
+      <c r="N251" t="s">
+        <v>449</v>
+      </c>
+      <c r="O251" t="s">
+        <v>41</v>
+      </c>
+      <c r="P251" t="s">
+        <v>1690</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>781</v>
+      </c>
+      <c r="R251" t="s">
+        <v>35</v>
+      </c>
+      <c r="S251" t="s">
+        <v>39</v>
+      </c>
+      <c r="T251" t="s">
+        <v>66</v>
+      </c>
+      <c r="U251" t="s">
+        <v>41</v>
+      </c>
+      <c r="V251">
+        <v>59</v>
+      </c>
+      <c r="W251">
+        <v>25</v>
+      </c>
+      <c r="X251">
+        <v>51</v>
+      </c>
+      <c r="Y251">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="252" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>202</v>
+      </c>
+      <c r="B252" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C252" t="s">
+        <v>203</v>
+      </c>
+      <c r="D252" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E252" t="s">
+        <v>895</v>
+      </c>
+      <c r="F252" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G252" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H252" t="s">
+        <v>201</v>
+      </c>
+      <c r="I252" t="s">
+        <v>1692</v>
+      </c>
+      <c r="J252" t="s">
+        <v>1693</v>
+      </c>
+      <c r="K252" t="s">
+        <v>1523</v>
+      </c>
+      <c r="L252" t="s">
+        <v>201</v>
+      </c>
+      <c r="M252" t="s">
+        <v>201</v>
+      </c>
+      <c r="N252" t="s">
+        <v>201</v>
+      </c>
+      <c r="O252" t="s">
+        <v>201</v>
+      </c>
+      <c r="P252" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>201</v>
+      </c>
+      <c r="R252" t="s">
+        <v>201</v>
+      </c>
+      <c r="S252" t="s">
+        <v>201</v>
+      </c>
+      <c r="T252" t="s">
+        <v>201</v>
+      </c>
+      <c r="U252" t="s">
+        <v>201</v>
+      </c>
+      <c r="V252">
+        <v>0</v>
+      </c>
+      <c r="W252">
+        <v>0</v>
+      </c>
+      <c r="X252">
+        <v>0</v>
+      </c>
+      <c r="Y252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>202</v>
+      </c>
+      <c r="B253" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C253" t="s">
+        <v>203</v>
+      </c>
+      <c r="D253" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E253" t="s">
+        <v>126</v>
+      </c>
+      <c r="F253" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G253" t="s">
+        <v>1694</v>
+      </c>
+      <c r="H253" t="s">
+        <v>1695</v>
+      </c>
+      <c r="I253" t="s">
+        <v>1696</v>
+      </c>
+      <c r="J253" t="s">
+        <v>1697</v>
+      </c>
+      <c r="K253" t="s">
+        <v>1698</v>
+      </c>
+      <c r="L253" t="s">
+        <v>603</v>
+      </c>
+      <c r="M253" t="s">
+        <v>749</v>
+      </c>
+      <c r="N253" t="s">
+        <v>337</v>
+      </c>
+      <c r="O253" t="s">
+        <v>41</v>
+      </c>
+      <c r="P253" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>1681</v>
+      </c>
+      <c r="R253" t="s">
+        <v>40</v>
+      </c>
+      <c r="S253" t="s">
+        <v>41</v>
+      </c>
+      <c r="T253" t="s">
+        <v>38</v>
+      </c>
+      <c r="U253" t="s">
+        <v>41</v>
+      </c>
+      <c r="V253">
+        <v>36</v>
+      </c>
+      <c r="W253">
+        <v>20</v>
+      </c>
+      <c r="X253">
+        <v>43</v>
+      </c>
+      <c r="Y253">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>202</v>
+      </c>
+      <c r="B254" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C254" t="s">
+        <v>203</v>
+      </c>
+      <c r="D254" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E254" t="s">
+        <v>346</v>
+      </c>
+      <c r="F254" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G254" t="s">
+        <v>1699</v>
+      </c>
+      <c r="H254" t="s">
+        <v>327</v>
+      </c>
+      <c r="I254" t="s">
+        <v>1700</v>
+      </c>
+      <c r="J254" t="s">
+        <v>1701</v>
+      </c>
+      <c r="K254" t="s">
+        <v>1702</v>
+      </c>
+      <c r="L254" t="s">
+        <v>1703</v>
+      </c>
+      <c r="M254" t="s">
+        <v>1704</v>
+      </c>
+      <c r="N254" t="s">
+        <v>113</v>
+      </c>
+      <c r="O254" t="s">
+        <v>201</v>
+      </c>
+      <c r="P254" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>201</v>
+      </c>
+      <c r="R254" t="s">
+        <v>40</v>
+      </c>
+      <c r="S254" t="s">
+        <v>41</v>
+      </c>
+      <c r="T254" t="s">
+        <v>38</v>
+      </c>
+      <c r="U254" t="s">
+        <v>41</v>
+      </c>
+      <c r="V254">
+        <v>54</v>
+      </c>
+      <c r="W254">
+        <v>14</v>
+      </c>
+      <c r="X254">
+        <v>36</v>
+      </c>
+      <c r="Y254">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="255" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>202</v>
+      </c>
+      <c r="B255" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C255" t="s">
+        <v>203</v>
+      </c>
+      <c r="D255" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E255" t="s">
+        <v>137</v>
+      </c>
+      <c r="F255" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G255" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H255" t="s">
+        <v>1705</v>
+      </c>
+      <c r="I255" t="s">
+        <v>1706</v>
+      </c>
+      <c r="J255" t="s">
+        <v>1707</v>
+      </c>
+      <c r="K255" t="s">
+        <v>1708</v>
+      </c>
+      <c r="L255" t="s">
+        <v>1704</v>
+      </c>
+      <c r="M255" t="s">
+        <v>270</v>
+      </c>
+      <c r="N255" t="s">
+        <v>35</v>
+      </c>
+      <c r="O255" t="s">
+        <v>201</v>
+      </c>
+      <c r="P255" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>165</v>
+      </c>
+      <c r="R255" t="s">
+        <v>113</v>
+      </c>
+      <c r="S255" t="s">
+        <v>41</v>
+      </c>
+      <c r="T255" t="s">
+        <v>40</v>
+      </c>
+      <c r="U255" t="s">
+        <v>41</v>
+      </c>
+      <c r="V255">
+        <v>53</v>
+      </c>
+      <c r="W255">
+        <v>23</v>
+      </c>
+      <c r="X255">
+        <v>68</v>
+      </c>
+      <c r="Y255">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="256" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>202</v>
+      </c>
+      <c r="B256" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C256" t="s">
+        <v>203</v>
+      </c>
+      <c r="D256" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E256" t="s">
+        <v>147</v>
+      </c>
+      <c r="F256" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G256" t="s">
+        <v>1709</v>
+      </c>
+      <c r="H256" t="s">
+        <v>1710</v>
+      </c>
+      <c r="I256" t="s">
+        <v>1711</v>
+      </c>
+      <c r="J256" t="s">
+        <v>1012</v>
+      </c>
+      <c r="K256" t="s">
+        <v>1712</v>
+      </c>
+      <c r="L256" t="s">
+        <v>1713</v>
+      </c>
+      <c r="M256" t="s">
+        <v>1714</v>
+      </c>
+      <c r="N256" t="s">
+        <v>35</v>
+      </c>
+      <c r="O256" t="s">
+        <v>201</v>
+      </c>
+      <c r="P256" t="s">
+        <v>1715</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>34</v>
+      </c>
+      <c r="R256" t="s">
+        <v>113</v>
+      </c>
+      <c r="S256" t="s">
+        <v>38</v>
+      </c>
+      <c r="T256" t="s">
+        <v>66</v>
+      </c>
+      <c r="U256" t="s">
+        <v>39</v>
+      </c>
+      <c r="V256">
+        <v>55</v>
+      </c>
+      <c r="W256">
+        <v>25</v>
+      </c>
+      <c r="X256">
+        <v>67</v>
+      </c>
+      <c r="Y256">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="257" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>202</v>
+      </c>
+      <c r="B257" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C257" t="s">
+        <v>203</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E257" t="s">
+        <v>157</v>
+      </c>
+      <c r="F257" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G257" t="s">
+        <v>269</v>
+      </c>
+      <c r="H257" t="s">
+        <v>1716</v>
+      </c>
+      <c r="I257" t="s">
+        <v>1717</v>
+      </c>
+      <c r="J257" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K257" t="s">
+        <v>1718</v>
+      </c>
+      <c r="L257" t="s">
+        <v>1719</v>
+      </c>
+      <c r="M257" t="s">
+        <v>1375</v>
+      </c>
+      <c r="N257" t="s">
+        <v>555</v>
+      </c>
+      <c r="O257" t="s">
+        <v>201</v>
+      </c>
+      <c r="P257" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>87</v>
+      </c>
+      <c r="R257" t="s">
+        <v>113</v>
+      </c>
+      <c r="S257" t="s">
+        <v>39</v>
+      </c>
+      <c r="T257" t="s">
+        <v>66</v>
+      </c>
+      <c r="U257" t="s">
+        <v>41</v>
+      </c>
+      <c r="V257">
+        <v>50</v>
+      </c>
+      <c r="W257">
+        <v>37</v>
+      </c>
+      <c r="X257">
+        <v>61</v>
+      </c>
+      <c r="Y257">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="258" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>202</v>
+      </c>
+      <c r="B258" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C258" t="s">
+        <v>203</v>
+      </c>
+      <c r="D258" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E258" t="s">
+        <v>933</v>
+      </c>
+      <c r="F258" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G258" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H258" t="s">
+        <v>1720</v>
+      </c>
+      <c r="I258" t="s">
+        <v>1721</v>
+      </c>
+      <c r="J258" t="s">
+        <v>1722</v>
+      </c>
+      <c r="K258" t="s">
+        <v>1723</v>
+      </c>
+      <c r="L258" t="s">
+        <v>866</v>
+      </c>
+      <c r="M258" t="s">
+        <v>1195</v>
+      </c>
+      <c r="N258" t="s">
+        <v>113</v>
+      </c>
+      <c r="O258" t="s">
+        <v>41</v>
+      </c>
+      <c r="P258" t="s">
+        <v>1181</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>433</v>
+      </c>
+      <c r="R258" t="s">
+        <v>40</v>
+      </c>
+      <c r="S258" t="s">
+        <v>39</v>
+      </c>
+      <c r="T258" t="s">
+        <v>40</v>
+      </c>
+      <c r="U258" t="s">
+        <v>41</v>
+      </c>
+      <c r="V258">
+        <v>54</v>
+      </c>
+      <c r="W258">
+        <v>23</v>
+      </c>
+      <c r="X258">
+        <v>32</v>
+      </c>
+      <c r="Y258">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="259" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>202</v>
+      </c>
+      <c r="B259" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C259" t="s">
+        <v>203</v>
+      </c>
+      <c r="D259" t="s">
+        <v>848</v>
+      </c>
+      <c r="E259" t="s">
+        <v>25</v>
+      </c>
+      <c r="F259" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G259" t="s">
+        <v>955</v>
+      </c>
+      <c r="H259" t="s">
+        <v>1727</v>
+      </c>
+      <c r="I259" t="s">
+        <v>1728</v>
+      </c>
+      <c r="J259" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K259" t="s">
+        <v>390</v>
+      </c>
+      <c r="L259" t="s">
+        <v>689</v>
+      </c>
+      <c r="M259" t="s">
+        <v>74</v>
+      </c>
+      <c r="N259" t="s">
+        <v>1358</v>
+      </c>
+      <c r="O259" t="s">
+        <v>66</v>
+      </c>
+      <c r="P259" t="s">
+        <v>1730</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>533</v>
+      </c>
+      <c r="R259" t="s">
+        <v>40</v>
+      </c>
+      <c r="S259" t="s">
+        <v>38</v>
+      </c>
+      <c r="T259" t="s">
+        <v>66</v>
+      </c>
+      <c r="U259" t="s">
+        <v>39</v>
+      </c>
+      <c r="V259">
+        <v>49</v>
+      </c>
+      <c r="W259">
+        <v>34</v>
+      </c>
+      <c r="X259">
+        <v>31</v>
+      </c>
+      <c r="Y259">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="260" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>202</v>
+      </c>
+      <c r="B260" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C260" t="s">
+        <v>203</v>
+      </c>
+      <c r="D260" t="s">
+        <v>848</v>
+      </c>
+      <c r="E260" t="s">
+        <v>42</v>
+      </c>
+      <c r="F260" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G260" t="s">
+        <v>1731</v>
+      </c>
+      <c r="H260" t="s">
+        <v>1732</v>
+      </c>
+      <c r="I260" t="s">
+        <v>1733</v>
+      </c>
+      <c r="J260" t="s">
+        <v>1734</v>
+      </c>
+      <c r="K260" t="s">
+        <v>1735</v>
+      </c>
+      <c r="L260" t="s">
+        <v>821</v>
+      </c>
+      <c r="M260" t="s">
+        <v>225</v>
+      </c>
+      <c r="N260" t="s">
+        <v>110</v>
+      </c>
+      <c r="O260" t="s">
+        <v>41</v>
+      </c>
+      <c r="P260" t="s">
+        <v>1736</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>1186</v>
+      </c>
+      <c r="R260" t="s">
+        <v>39</v>
+      </c>
+      <c r="S260" t="s">
+        <v>41</v>
+      </c>
+      <c r="T260" t="s">
+        <v>41</v>
+      </c>
+      <c r="U260" t="s">
+        <v>201</v>
+      </c>
+      <c r="V260">
+        <v>23</v>
+      </c>
+      <c r="W260">
+        <v>6</v>
+      </c>
+      <c r="X260">
+        <v>10</v>
+      </c>
+      <c r="Y260">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>202</v>
+      </c>
+      <c r="B261" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C261" t="s">
+        <v>203</v>
+      </c>
+      <c r="D261" t="s">
+        <v>848</v>
+      </c>
+      <c r="E261" t="s">
+        <v>54</v>
+      </c>
+      <c r="F261" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G261" t="s">
+        <v>541</v>
+      </c>
+      <c r="H261" t="s">
+        <v>1737</v>
+      </c>
+      <c r="I261" t="s">
+        <v>1738</v>
+      </c>
+      <c r="J261" t="s">
+        <v>1739</v>
+      </c>
+      <c r="K261" t="s">
+        <v>1740</v>
+      </c>
+      <c r="L261" t="s">
+        <v>1530</v>
+      </c>
+      <c r="M261" t="s">
+        <v>768</v>
+      </c>
+      <c r="N261" t="s">
+        <v>377</v>
+      </c>
+      <c r="O261" t="s">
+        <v>113</v>
+      </c>
+      <c r="P261" t="s">
+        <v>1741</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>1047</v>
+      </c>
+      <c r="R261" t="s">
+        <v>66</v>
+      </c>
+      <c r="S261" t="s">
+        <v>39</v>
+      </c>
+      <c r="T261" t="s">
+        <v>38</v>
+      </c>
+      <c r="U261" t="s">
+        <v>41</v>
+      </c>
+      <c r="V261">
+        <v>45</v>
+      </c>
+      <c r="W261">
+        <v>22</v>
+      </c>
+      <c r="X261">
+        <v>27</v>
+      </c>
+      <c r="Y261">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="262" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>202</v>
+      </c>
+      <c r="B262" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C262" t="s">
+        <v>203</v>
+      </c>
+      <c r="D262" t="s">
+        <v>848</v>
+      </c>
+      <c r="E262" t="s">
+        <v>102</v>
+      </c>
+      <c r="F262" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G262" t="s">
+        <v>834</v>
+      </c>
+      <c r="H262" t="s">
+        <v>1742</v>
+      </c>
+      <c r="I262" t="s">
+        <v>1743</v>
+      </c>
+      <c r="J262" t="s">
+        <v>1744</v>
+      </c>
+      <c r="K262" t="s">
+        <v>1745</v>
+      </c>
+      <c r="L262" t="s">
+        <v>1746</v>
+      </c>
+      <c r="M262" t="s">
+        <v>108</v>
+      </c>
+      <c r="N262" t="s">
+        <v>1747</v>
+      </c>
+      <c r="O262" t="s">
+        <v>495</v>
+      </c>
+      <c r="P262" t="s">
+        <v>1748</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>1583</v>
+      </c>
+      <c r="R262" t="s">
+        <v>113</v>
+      </c>
+      <c r="S262" t="s">
+        <v>38</v>
+      </c>
+      <c r="T262" t="s">
+        <v>35</v>
+      </c>
+      <c r="U262" t="s">
+        <v>39</v>
+      </c>
+      <c r="V262">
+        <v>76</v>
+      </c>
+      <c r="W262">
+        <v>37</v>
+      </c>
+      <c r="X262">
+        <v>43</v>
+      </c>
+      <c r="Y262">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="263" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>202</v>
+      </c>
+      <c r="B263" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C263" t="s">
+        <v>203</v>
+      </c>
+      <c r="D263" t="s">
+        <v>848</v>
+      </c>
+      <c r="E263" t="s">
+        <v>347</v>
+      </c>
+      <c r="F263" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G263" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H263" t="s">
+        <v>1749</v>
+      </c>
+      <c r="I263" t="s">
+        <v>1750</v>
+      </c>
+      <c r="J263" t="s">
+        <v>1751</v>
+      </c>
+      <c r="K263" t="s">
+        <v>1752</v>
+      </c>
+      <c r="L263" t="s">
+        <v>876</v>
+      </c>
+      <c r="M263" t="s">
+        <v>1330</v>
+      </c>
+      <c r="N263" t="s">
+        <v>110</v>
+      </c>
+      <c r="O263" t="s">
+        <v>40</v>
+      </c>
+      <c r="P263" t="s">
+        <v>1753</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>526</v>
+      </c>
+      <c r="R263" t="s">
+        <v>38</v>
+      </c>
+      <c r="S263" t="s">
+        <v>39</v>
+      </c>
+      <c r="T263" t="s">
+        <v>38</v>
+      </c>
+      <c r="U263" t="s">
+        <v>201</v>
+      </c>
+      <c r="V263">
+        <v>36</v>
+      </c>
+      <c r="W263">
+        <v>13</v>
+      </c>
+      <c r="X263">
+        <v>26</v>
+      </c>
+      <c r="Y263">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="264" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>202</v>
+      </c>
+      <c r="B264" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C264" t="s">
+        <v>203</v>
+      </c>
+      <c r="D264" t="s">
+        <v>848</v>
+      </c>
+      <c r="E264" t="s">
+        <v>126</v>
+      </c>
+      <c r="F264" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G264" t="s">
+        <v>628</v>
+      </c>
+      <c r="H264" t="s">
+        <v>1754</v>
+      </c>
+      <c r="I264" t="s">
+        <v>1755</v>
+      </c>
+      <c r="J264" t="s">
+        <v>313</v>
+      </c>
+      <c r="K264" t="s">
+        <v>1756</v>
+      </c>
+      <c r="L264" t="s">
+        <v>221</v>
+      </c>
+      <c r="M264" t="s">
+        <v>231</v>
+      </c>
+      <c r="N264" t="s">
+        <v>1757</v>
+      </c>
+      <c r="O264" t="s">
+        <v>280</v>
+      </c>
+      <c r="P264" t="s">
+        <v>1758</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>1628</v>
+      </c>
+      <c r="R264" t="s">
+        <v>40</v>
+      </c>
+      <c r="S264" t="s">
+        <v>41</v>
+      </c>
+      <c r="T264" t="s">
+        <v>40</v>
+      </c>
+      <c r="U264" t="s">
+        <v>41</v>
+      </c>
+      <c r="V264">
+        <v>36</v>
+      </c>
+      <c r="W264">
+        <v>19</v>
+      </c>
+      <c r="X264">
+        <v>30</v>
+      </c>
+      <c r="Y264">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="265" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>202</v>
+      </c>
+      <c r="B265" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C265" t="s">
+        <v>203</v>
+      </c>
+      <c r="D265" t="s">
+        <v>848</v>
+      </c>
+      <c r="E265" t="s">
+        <v>346</v>
+      </c>
+      <c r="F265" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G265" t="s">
+        <v>742</v>
+      </c>
+      <c r="H265" t="s">
+        <v>1759</v>
+      </c>
+      <c r="I265" t="s">
+        <v>1760</v>
+      </c>
+      <c r="J265" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K265" t="s">
+        <v>1762</v>
+      </c>
+      <c r="L265" t="s">
+        <v>1719</v>
+      </c>
+      <c r="M265" t="s">
+        <v>1679</v>
+      </c>
+      <c r="N265" t="s">
+        <v>857</v>
+      </c>
+      <c r="O265" t="s">
+        <v>38</v>
+      </c>
+      <c r="P265" t="s">
+        <v>1763</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>1764</v>
+      </c>
+      <c r="R265" t="s">
+        <v>40</v>
+      </c>
+      <c r="S265" t="s">
+        <v>40</v>
+      </c>
+      <c r="T265" t="s">
+        <v>40</v>
+      </c>
+      <c r="U265" t="s">
+        <v>41</v>
+      </c>
+      <c r="V265">
+        <v>47</v>
+      </c>
+      <c r="W265">
+        <v>22</v>
+      </c>
+      <c r="X265">
+        <v>36</v>
+      </c>
+      <c r="Y265">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="266" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>202</v>
+      </c>
+      <c r="B266" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C266" t="s">
+        <v>203</v>
+      </c>
+      <c r="D266" t="s">
+        <v>848</v>
+      </c>
+      <c r="E266" t="s">
+        <v>137</v>
+      </c>
+      <c r="F266" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G266" t="s">
+        <v>834</v>
+      </c>
+      <c r="H266" t="s">
+        <v>1765</v>
+      </c>
+      <c r="I266" t="s">
+        <v>1766</v>
+      </c>
+      <c r="J266" t="s">
+        <v>1767</v>
+      </c>
+      <c r="K266" t="s">
+        <v>1768</v>
+      </c>
+      <c r="L266" t="s">
+        <v>1062</v>
+      </c>
+      <c r="M266" t="s">
+        <v>309</v>
+      </c>
+      <c r="N266" t="s">
+        <v>1769</v>
+      </c>
+      <c r="O266" t="s">
+        <v>280</v>
+      </c>
+      <c r="P266" t="s">
+        <v>1770</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>282</v>
+      </c>
+      <c r="R266" t="s">
+        <v>66</v>
+      </c>
+      <c r="S266" t="s">
+        <v>39</v>
+      </c>
+      <c r="T266" t="s">
+        <v>40</v>
+      </c>
+      <c r="U266" t="s">
+        <v>41</v>
+      </c>
+      <c r="V266">
+        <v>47</v>
+      </c>
+      <c r="W266">
+        <v>26</v>
+      </c>
+      <c r="X266">
+        <v>48</v>
+      </c>
+      <c r="Y266">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="267" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>202</v>
+      </c>
+      <c r="B267" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C267" t="s">
+        <v>203</v>
+      </c>
+      <c r="D267" t="s">
+        <v>848</v>
+      </c>
+      <c r="E267" t="s">
+        <v>147</v>
+      </c>
+      <c r="F267" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G267" t="s">
+        <v>370</v>
+      </c>
+      <c r="H267" t="s">
+        <v>1771</v>
+      </c>
+      <c r="I267" t="s">
+        <v>1772</v>
+      </c>
+      <c r="J267" t="s">
+        <v>1773</v>
+      </c>
+      <c r="K267" t="s">
+        <v>1774</v>
+      </c>
+      <c r="L267" t="s">
+        <v>525</v>
+      </c>
+      <c r="M267" t="s">
+        <v>511</v>
+      </c>
+      <c r="N267" t="s">
+        <v>919</v>
+      </c>
+      <c r="O267" t="s">
+        <v>449</v>
+      </c>
+      <c r="P267" t="s">
+        <v>1775</v>
+      </c>
+      <c r="Q267" t="s">
+        <v>1401</v>
+      </c>
+      <c r="R267" t="s">
+        <v>66</v>
+      </c>
+      <c r="S267" t="s">
+        <v>38</v>
+      </c>
+      <c r="T267" t="s">
+        <v>40</v>
+      </c>
+      <c r="U267" t="s">
+        <v>41</v>
+      </c>
+      <c r="V267">
+        <v>44</v>
+      </c>
+      <c r="W267">
+        <v>21</v>
+      </c>
+      <c r="X267">
+        <v>44</v>
+      </c>
+      <c r="Y267">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>202</v>
+      </c>
+      <c r="B268" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C268" t="s">
+        <v>203</v>
+      </c>
+      <c r="D268" t="s">
+        <v>848</v>
+      </c>
+      <c r="E268" t="s">
+        <v>191</v>
+      </c>
+      <c r="F268" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G268" t="s">
+        <v>399</v>
+      </c>
+      <c r="H268" t="s">
+        <v>1776</v>
+      </c>
+      <c r="I268" t="s">
+        <v>1777</v>
+      </c>
+      <c r="J268" t="s">
+        <v>1778</v>
+      </c>
+      <c r="K268" t="s">
+        <v>1779</v>
+      </c>
+      <c r="L268" t="s">
+        <v>1780</v>
+      </c>
+      <c r="M268" t="s">
+        <v>391</v>
+      </c>
+      <c r="N268" t="s">
+        <v>554</v>
+      </c>
+      <c r="O268" t="s">
+        <v>40</v>
+      </c>
+      <c r="P268" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q268" t="s">
+        <v>603</v>
+      </c>
+      <c r="R268" t="s">
+        <v>39</v>
+      </c>
+      <c r="S268" t="s">
+        <v>201</v>
+      </c>
+      <c r="T268" t="s">
+        <v>39</v>
+      </c>
+      <c r="U268" t="s">
+        <v>201</v>
+      </c>
+      <c r="V268">
+        <v>35</v>
+      </c>
+      <c r="W268">
+        <v>13</v>
+      </c>
+      <c r="X268">
+        <v>24</v>
+      </c>
+      <c r="Y268">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84370C44-1715-3641-A86B-AAD8958ECDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6398683-F1E7-BD47-9680-A428F7E67655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5026" uniqueCount="1781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5546" uniqueCount="1918">
   <si>
     <t>Type</t>
   </si>
@@ -5379,6 +5379,417 @@
   </si>
   <si>
     <t>4.78</t>
+  </si>
+  <si>
+    <t>69.83</t>
+  </si>
+  <si>
+    <t>325.43</t>
+  </si>
+  <si>
+    <t>266.06</t>
+  </si>
+  <si>
+    <t>76.99</t>
+  </si>
+  <si>
+    <t>249.93</t>
+  </si>
+  <si>
+    <t>368.96</t>
+  </si>
+  <si>
+    <t>26.54</t>
+  </si>
+  <si>
+    <t>35.2</t>
+  </si>
+  <si>
+    <t>69.85</t>
+  </si>
+  <si>
+    <t>6.31</t>
+  </si>
+  <si>
+    <t>478.19</t>
+  </si>
+  <si>
+    <t>282.92</t>
+  </si>
+  <si>
+    <t>29.58</t>
+  </si>
+  <si>
+    <t>90.35</t>
+  </si>
+  <si>
+    <t>7.28</t>
+  </si>
+  <si>
+    <t>5.36</t>
+  </si>
+  <si>
+    <t>59.0</t>
+  </si>
+  <si>
+    <t>15.6</t>
+  </si>
+  <si>
+    <t>47.57</t>
+  </si>
+  <si>
+    <t>3.34</t>
+  </si>
+  <si>
+    <t>269.49</t>
+  </si>
+  <si>
+    <t>320.04</t>
+  </si>
+  <si>
+    <t>30.43</t>
+  </si>
+  <si>
+    <t>70.24</t>
+  </si>
+  <si>
+    <t>9.39</t>
+  </si>
+  <si>
+    <t>6.47</t>
+  </si>
+  <si>
+    <t>31.2</t>
+  </si>
+  <si>
+    <t>286.15</t>
+  </si>
+  <si>
+    <t>235.94</t>
+  </si>
+  <si>
+    <t>27.12</t>
+  </si>
+  <si>
+    <t>66.06</t>
+  </si>
+  <si>
+    <t>38.0</t>
+  </si>
+  <si>
+    <t>549.43</t>
+  </si>
+  <si>
+    <t>299.92</t>
+  </si>
+  <si>
+    <t>29.48</t>
+  </si>
+  <si>
+    <t>95.34</t>
+  </si>
+  <si>
+    <t>70.8</t>
+  </si>
+  <si>
+    <t>341.11</t>
+  </si>
+  <si>
+    <t>295.82</t>
+  </si>
+  <si>
+    <t>28.62</t>
+  </si>
+  <si>
+    <t>49.3</t>
+  </si>
+  <si>
+    <t>138.55</t>
+  </si>
+  <si>
+    <t>318.35</t>
+  </si>
+  <si>
+    <t>89.68</t>
+  </si>
+  <si>
+    <t>5.56</t>
+  </si>
+  <si>
+    <t>23.6</t>
+  </si>
+  <si>
+    <t>225.89</t>
+  </si>
+  <si>
+    <t>471.63</t>
+  </si>
+  <si>
+    <t>70.9</t>
+  </si>
+  <si>
+    <t>7.37</t>
+  </si>
+  <si>
+    <t>269.22</t>
+  </si>
+  <si>
+    <t>253.86</t>
+  </si>
+  <si>
+    <t>29.86</t>
+  </si>
+  <si>
+    <t>80.68</t>
+  </si>
+  <si>
+    <t>6.25</t>
+  </si>
+  <si>
+    <t>130.62</t>
+  </si>
+  <si>
+    <t>237.74</t>
+  </si>
+  <si>
+    <t>4.87</t>
+  </si>
+  <si>
+    <t>6.95</t>
+  </si>
+  <si>
+    <t>20.7</t>
+  </si>
+  <si>
+    <t>55.95</t>
+  </si>
+  <si>
+    <t>205.51</t>
+  </si>
+  <si>
+    <t>24.31</t>
+  </si>
+  <si>
+    <t>61.03</t>
+  </si>
+  <si>
+    <t>495.67</t>
+  </si>
+  <si>
+    <t>256.04</t>
+  </si>
+  <si>
+    <t>30.32</t>
+  </si>
+  <si>
+    <t>57.81</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>92.0</t>
+  </si>
+  <si>
+    <t>287.8</t>
+  </si>
+  <si>
+    <t>222.38</t>
+  </si>
+  <si>
+    <t>44.56</t>
+  </si>
+  <si>
+    <t>6.84</t>
+  </si>
+  <si>
+    <t>34.4</t>
+  </si>
+  <si>
+    <t>10.3</t>
+  </si>
+  <si>
+    <t>Gibril Djahl</t>
+  </si>
+  <si>
+    <t>294.47</t>
+  </si>
+  <si>
+    <t>258.1</t>
+  </si>
+  <si>
+    <t>25.83</t>
+  </si>
+  <si>
+    <t>56.22</t>
+  </si>
+  <si>
+    <t>8.19</t>
+  </si>
+  <si>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>5.25</t>
+  </si>
+  <si>
+    <t>281.04</t>
+  </si>
+  <si>
+    <t>292.02</t>
+  </si>
+  <si>
+    <t>30.69</t>
+  </si>
+  <si>
+    <t>57.03</t>
+  </si>
+  <si>
+    <t>38.1</t>
+  </si>
+  <si>
+    <t>453.22</t>
+  </si>
+  <si>
+    <t>240.68</t>
+  </si>
+  <si>
+    <t>27.77</t>
+  </si>
+  <si>
+    <t>54.83</t>
+  </si>
+  <si>
+    <t>59.8</t>
+  </si>
+  <si>
+    <t>672.53</t>
+  </si>
+  <si>
+    <t>344.23</t>
+  </si>
+  <si>
+    <t>25.52</t>
+  </si>
+  <si>
+    <t>53.34</t>
+  </si>
+  <si>
+    <t>6.33</t>
+  </si>
+  <si>
+    <t>104.3</t>
+  </si>
+  <si>
+    <t>3.37</t>
+  </si>
+  <si>
+    <t>140.05</t>
+  </si>
+  <si>
+    <t>30.81</t>
+  </si>
+  <si>
+    <t>36.66</t>
+  </si>
+  <si>
+    <t>278.35</t>
+  </si>
+  <si>
+    <t>226.96</t>
+  </si>
+  <si>
+    <t>31.1</t>
+  </si>
+  <si>
+    <t>51.69</t>
+  </si>
+  <si>
+    <t>321.41</t>
+  </si>
+  <si>
+    <t>249.75</t>
+  </si>
+  <si>
+    <t>28.67</t>
+  </si>
+  <si>
+    <t>52.06</t>
+  </si>
+  <si>
+    <t>41.2</t>
+  </si>
+  <si>
+    <t>466.77</t>
+  </si>
+  <si>
+    <t>289.71</t>
+  </si>
+  <si>
+    <t>32.37</t>
+  </si>
+  <si>
+    <t>60.31</t>
+  </si>
+  <si>
+    <t>229.29</t>
+  </si>
+  <si>
+    <t>290.19</t>
+  </si>
+  <si>
+    <t>27.65</t>
+  </si>
+  <si>
+    <t>57.46</t>
+  </si>
+  <si>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>394.16</t>
+  </si>
+  <si>
+    <t>443.4</t>
+  </si>
+  <si>
+    <t>31.46</t>
+  </si>
+  <si>
+    <t>52.08</t>
+  </si>
+  <si>
+    <t>4.56</t>
+  </si>
+  <si>
+    <t>340.75</t>
+  </si>
+  <si>
+    <t>254.72</t>
+  </si>
+  <si>
+    <t>49.53</t>
+  </si>
+  <si>
+    <t>19.7</t>
+  </si>
+  <si>
+    <t>122.6</t>
+  </si>
+  <si>
+    <t>181.35</t>
+  </si>
+  <si>
+    <t>38.58</t>
+  </si>
+  <si>
+    <t>16.8</t>
+  </si>
+  <si>
+    <t>Glenn Manga-Tabi</t>
   </si>
 </sst>
 </file>
@@ -5757,7 +6168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y268"/>
+  <dimension ref="A1:Y294"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
@@ -26055,6 +26466,2008 @@
         <v>4</v>
       </c>
     </row>
+    <row r="269" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>202</v>
+      </c>
+      <c r="B269" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C269" t="s">
+        <v>203</v>
+      </c>
+      <c r="D269" t="s">
+        <v>204</v>
+      </c>
+      <c r="E269" t="s">
+        <v>54</v>
+      </c>
+      <c r="F269" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G269" t="s">
+        <v>774</v>
+      </c>
+      <c r="H269" t="s">
+        <v>1782</v>
+      </c>
+      <c r="I269" t="s">
+        <v>1783</v>
+      </c>
+      <c r="J269" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K269" t="s">
+        <v>1784</v>
+      </c>
+      <c r="L269" t="s">
+        <v>278</v>
+      </c>
+      <c r="M269" t="s">
+        <v>420</v>
+      </c>
+      <c r="N269" t="s">
+        <v>307</v>
+      </c>
+      <c r="O269" t="s">
+        <v>113</v>
+      </c>
+      <c r="P269" t="s">
+        <v>988</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>384</v>
+      </c>
+      <c r="R269" t="s">
+        <v>66</v>
+      </c>
+      <c r="S269" t="s">
+        <v>38</v>
+      </c>
+      <c r="T269" t="s">
+        <v>66</v>
+      </c>
+      <c r="U269" t="s">
+        <v>41</v>
+      </c>
+      <c r="V269">
+        <v>53</v>
+      </c>
+      <c r="W269">
+        <v>23</v>
+      </c>
+      <c r="X269">
+        <v>30</v>
+      </c>
+      <c r="Y269">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="270" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>202</v>
+      </c>
+      <c r="B270" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C270" t="s">
+        <v>203</v>
+      </c>
+      <c r="D270" t="s">
+        <v>204</v>
+      </c>
+      <c r="E270" t="s">
+        <v>90</v>
+      </c>
+      <c r="F270" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G270" t="s">
+        <v>766</v>
+      </c>
+      <c r="H270" t="s">
+        <v>1785</v>
+      </c>
+      <c r="I270" t="s">
+        <v>1786</v>
+      </c>
+      <c r="J270" t="s">
+        <v>1787</v>
+      </c>
+      <c r="K270" t="s">
+        <v>665</v>
+      </c>
+      <c r="L270" t="s">
+        <v>548</v>
+      </c>
+      <c r="M270" t="s">
+        <v>230</v>
+      </c>
+      <c r="N270" t="s">
+        <v>672</v>
+      </c>
+      <c r="O270" t="s">
+        <v>40</v>
+      </c>
+      <c r="P270" t="s">
+        <v>1788</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>759</v>
+      </c>
+      <c r="R270" t="s">
+        <v>66</v>
+      </c>
+      <c r="S270" t="s">
+        <v>41</v>
+      </c>
+      <c r="T270" t="s">
+        <v>38</v>
+      </c>
+      <c r="U270" t="s">
+        <v>41</v>
+      </c>
+      <c r="V270">
+        <v>63</v>
+      </c>
+      <c r="W270">
+        <v>21</v>
+      </c>
+      <c r="X270">
+        <v>46</v>
+      </c>
+      <c r="Y270">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="271" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>202</v>
+      </c>
+      <c r="B271" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C271" t="s">
+        <v>203</v>
+      </c>
+      <c r="D271" t="s">
+        <v>204</v>
+      </c>
+      <c r="E271" t="s">
+        <v>102</v>
+      </c>
+      <c r="F271" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G271" t="s">
+        <v>1790</v>
+      </c>
+      <c r="H271" t="s">
+        <v>1791</v>
+      </c>
+      <c r="I271" t="s">
+        <v>1792</v>
+      </c>
+      <c r="J271" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K271" t="s">
+        <v>1794</v>
+      </c>
+      <c r="L271" t="s">
+        <v>1795</v>
+      </c>
+      <c r="M271" t="s">
+        <v>1796</v>
+      </c>
+      <c r="N271" t="s">
+        <v>232</v>
+      </c>
+      <c r="O271" t="s">
+        <v>188</v>
+      </c>
+      <c r="P271" t="s">
+        <v>1797</v>
+      </c>
+      <c r="Q271" t="s">
+        <v>1798</v>
+      </c>
+      <c r="R271" t="s">
+        <v>35</v>
+      </c>
+      <c r="S271" t="s">
+        <v>38</v>
+      </c>
+      <c r="T271" t="s">
+        <v>66</v>
+      </c>
+      <c r="U271" t="s">
+        <v>41</v>
+      </c>
+      <c r="V271">
+        <v>64</v>
+      </c>
+      <c r="W271">
+        <v>18</v>
+      </c>
+      <c r="X271">
+        <v>45</v>
+      </c>
+      <c r="Y271">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="272" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>202</v>
+      </c>
+      <c r="B272" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C272" t="s">
+        <v>203</v>
+      </c>
+      <c r="D272" t="s">
+        <v>204</v>
+      </c>
+      <c r="E272" t="s">
+        <v>347</v>
+      </c>
+      <c r="F272" t="s">
+        <v>1799</v>
+      </c>
+      <c r="G272" t="s">
+        <v>1800</v>
+      </c>
+      <c r="H272" t="s">
+        <v>1801</v>
+      </c>
+      <c r="I272" t="s">
+        <v>1802</v>
+      </c>
+      <c r="J272" t="s">
+        <v>1803</v>
+      </c>
+      <c r="K272" t="s">
+        <v>1804</v>
+      </c>
+      <c r="L272" t="s">
+        <v>1805</v>
+      </c>
+      <c r="M272" t="s">
+        <v>1806</v>
+      </c>
+      <c r="N272" t="s">
+        <v>213</v>
+      </c>
+      <c r="O272" t="s">
+        <v>337</v>
+      </c>
+      <c r="P272" t="s">
+        <v>1807</v>
+      </c>
+      <c r="Q272" t="s">
+        <v>1619</v>
+      </c>
+      <c r="R272" t="s">
+        <v>337</v>
+      </c>
+      <c r="S272" t="s">
+        <v>113</v>
+      </c>
+      <c r="T272" t="s">
+        <v>113</v>
+      </c>
+      <c r="U272" t="s">
+        <v>38</v>
+      </c>
+      <c r="V272">
+        <v>50</v>
+      </c>
+      <c r="W272">
+        <v>40</v>
+      </c>
+      <c r="X272">
+        <v>55</v>
+      </c>
+      <c r="Y272">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="273" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>202</v>
+      </c>
+      <c r="B273" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C273" t="s">
+        <v>203</v>
+      </c>
+      <c r="D273" t="s">
+        <v>204</v>
+      </c>
+      <c r="E273" t="s">
+        <v>895</v>
+      </c>
+      <c r="F273" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G273" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H273" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I273" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J273" t="s">
+        <v>1810</v>
+      </c>
+      <c r="K273" t="s">
+        <v>1811</v>
+      </c>
+      <c r="L273" t="s">
+        <v>298</v>
+      </c>
+      <c r="M273" t="s">
+        <v>1370</v>
+      </c>
+      <c r="N273" t="s">
+        <v>63</v>
+      </c>
+      <c r="O273" t="s">
+        <v>66</v>
+      </c>
+      <c r="P273" t="s">
+        <v>1812</v>
+      </c>
+      <c r="Q273" t="s">
+        <v>277</v>
+      </c>
+      <c r="R273" t="s">
+        <v>66</v>
+      </c>
+      <c r="S273" t="s">
+        <v>39</v>
+      </c>
+      <c r="T273" t="s">
+        <v>40</v>
+      </c>
+      <c r="U273" t="s">
+        <v>41</v>
+      </c>
+      <c r="V273">
+        <v>44</v>
+      </c>
+      <c r="W273">
+        <v>27</v>
+      </c>
+      <c r="X273">
+        <v>42</v>
+      </c>
+      <c r="Y273">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="274" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>202</v>
+      </c>
+      <c r="B274" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C274" t="s">
+        <v>203</v>
+      </c>
+      <c r="D274" t="s">
+        <v>204</v>
+      </c>
+      <c r="E274" t="s">
+        <v>126</v>
+      </c>
+      <c r="F274" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G274" t="s">
+        <v>787</v>
+      </c>
+      <c r="H274" t="s">
+        <v>1813</v>
+      </c>
+      <c r="I274" t="s">
+        <v>1814</v>
+      </c>
+      <c r="J274" t="s">
+        <v>1815</v>
+      </c>
+      <c r="K274" t="s">
+        <v>1816</v>
+      </c>
+      <c r="L274" t="s">
+        <v>73</v>
+      </c>
+      <c r="M274" t="s">
+        <v>794</v>
+      </c>
+      <c r="N274" t="s">
+        <v>324</v>
+      </c>
+      <c r="O274" t="s">
+        <v>188</v>
+      </c>
+      <c r="P274" t="s">
+        <v>1817</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>1798</v>
+      </c>
+      <c r="R274" t="s">
+        <v>113</v>
+      </c>
+      <c r="S274" t="s">
+        <v>39</v>
+      </c>
+      <c r="T274" t="s">
+        <v>40</v>
+      </c>
+      <c r="U274" t="s">
+        <v>41</v>
+      </c>
+      <c r="V274">
+        <v>44</v>
+      </c>
+      <c r="W274">
+        <v>19</v>
+      </c>
+      <c r="X274">
+        <v>45</v>
+      </c>
+      <c r="Y274">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="275" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>202</v>
+      </c>
+      <c r="B275" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C275" t="s">
+        <v>203</v>
+      </c>
+      <c r="D275" t="s">
+        <v>204</v>
+      </c>
+      <c r="E275" t="s">
+        <v>346</v>
+      </c>
+      <c r="F275" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G275" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H275" t="s">
+        <v>1818</v>
+      </c>
+      <c r="I275" t="s">
+        <v>1819</v>
+      </c>
+      <c r="J275" t="s">
+        <v>1820</v>
+      </c>
+      <c r="K275" t="s">
+        <v>860</v>
+      </c>
+      <c r="L275" t="s">
+        <v>867</v>
+      </c>
+      <c r="M275" t="s">
+        <v>521</v>
+      </c>
+      <c r="N275" t="s">
+        <v>165</v>
+      </c>
+      <c r="O275" t="s">
+        <v>40</v>
+      </c>
+      <c r="P275" t="s">
+        <v>1821</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>603</v>
+      </c>
+      <c r="R275" t="s">
+        <v>113</v>
+      </c>
+      <c r="S275" t="s">
+        <v>38</v>
+      </c>
+      <c r="T275" t="s">
+        <v>40</v>
+      </c>
+      <c r="U275" t="s">
+        <v>41</v>
+      </c>
+      <c r="V275">
+        <v>56</v>
+      </c>
+      <c r="W275">
+        <v>19</v>
+      </c>
+      <c r="X275">
+        <v>36</v>
+      </c>
+      <c r="Y275">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="276" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>202</v>
+      </c>
+      <c r="B276" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C276" t="s">
+        <v>203</v>
+      </c>
+      <c r="D276" t="s">
+        <v>204</v>
+      </c>
+      <c r="E276" t="s">
+        <v>137</v>
+      </c>
+      <c r="F276" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G276" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H276" t="s">
+        <v>1822</v>
+      </c>
+      <c r="I276" t="s">
+        <v>1823</v>
+      </c>
+      <c r="J276" t="s">
+        <v>437</v>
+      </c>
+      <c r="K276" t="s">
+        <v>1824</v>
+      </c>
+      <c r="L276" t="s">
+        <v>379</v>
+      </c>
+      <c r="M276" t="s">
+        <v>1825</v>
+      </c>
+      <c r="N276" t="s">
+        <v>555</v>
+      </c>
+      <c r="O276" t="s">
+        <v>201</v>
+      </c>
+      <c r="P276" t="s">
+        <v>1826</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>201</v>
+      </c>
+      <c r="R276" t="s">
+        <v>113</v>
+      </c>
+      <c r="S276" t="s">
+        <v>38</v>
+      </c>
+      <c r="T276" t="s">
+        <v>38</v>
+      </c>
+      <c r="U276" t="s">
+        <v>201</v>
+      </c>
+      <c r="V276">
+        <v>46</v>
+      </c>
+      <c r="W276">
+        <v>14</v>
+      </c>
+      <c r="X276">
+        <v>46</v>
+      </c>
+      <c r="Y276">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="277" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>202</v>
+      </c>
+      <c r="B277" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C277" t="s">
+        <v>203</v>
+      </c>
+      <c r="D277" t="s">
+        <v>204</v>
+      </c>
+      <c r="E277" t="s">
+        <v>147</v>
+      </c>
+      <c r="F277" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G277" t="s">
+        <v>671</v>
+      </c>
+      <c r="H277" t="s">
+        <v>1827</v>
+      </c>
+      <c r="I277" t="s">
+        <v>1828</v>
+      </c>
+      <c r="J277" t="s">
+        <v>58</v>
+      </c>
+      <c r="K277" t="s">
+        <v>1829</v>
+      </c>
+      <c r="L277" t="s">
+        <v>1830</v>
+      </c>
+      <c r="M277" t="s">
+        <v>541</v>
+      </c>
+      <c r="N277" t="s">
+        <v>177</v>
+      </c>
+      <c r="O277" t="s">
+        <v>113</v>
+      </c>
+      <c r="P277" t="s">
+        <v>1729</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>1714</v>
+      </c>
+      <c r="R277" t="s">
+        <v>35</v>
+      </c>
+      <c r="S277" t="s">
+        <v>38</v>
+      </c>
+      <c r="T277" t="s">
+        <v>66</v>
+      </c>
+      <c r="U277" t="s">
+        <v>39</v>
+      </c>
+      <c r="V277">
+        <v>48</v>
+      </c>
+      <c r="W277">
+        <v>39</v>
+      </c>
+      <c r="X277">
+        <v>60</v>
+      </c>
+      <c r="Y277">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="278" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>202</v>
+      </c>
+      <c r="B278" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C278" t="s">
+        <v>203</v>
+      </c>
+      <c r="D278" t="s">
+        <v>204</v>
+      </c>
+      <c r="E278" t="s">
+        <v>157</v>
+      </c>
+      <c r="F278" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G278" t="s">
+        <v>334</v>
+      </c>
+      <c r="H278" t="s">
+        <v>1831</v>
+      </c>
+      <c r="I278" t="s">
+        <v>1832</v>
+      </c>
+      <c r="J278" t="s">
+        <v>1833</v>
+      </c>
+      <c r="K278" t="s">
+        <v>1834</v>
+      </c>
+      <c r="L278" t="s">
+        <v>133</v>
+      </c>
+      <c r="M278" t="s">
+        <v>1835</v>
+      </c>
+      <c r="N278" t="s">
+        <v>99</v>
+      </c>
+      <c r="O278" t="s">
+        <v>280</v>
+      </c>
+      <c r="P278" t="s">
+        <v>882</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>810</v>
+      </c>
+      <c r="R278" t="s">
+        <v>66</v>
+      </c>
+      <c r="S278" t="s">
+        <v>41</v>
+      </c>
+      <c r="T278" t="s">
+        <v>40</v>
+      </c>
+      <c r="U278" t="s">
+        <v>41</v>
+      </c>
+      <c r="V278">
+        <v>41</v>
+      </c>
+      <c r="W278">
+        <v>15</v>
+      </c>
+      <c r="X278">
+        <v>34</v>
+      </c>
+      <c r="Y278">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="279" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>202</v>
+      </c>
+      <c r="B279" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C279" t="s">
+        <v>203</v>
+      </c>
+      <c r="D279" t="s">
+        <v>204</v>
+      </c>
+      <c r="E279" t="s">
+        <v>933</v>
+      </c>
+      <c r="F279" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G279" t="s">
+        <v>759</v>
+      </c>
+      <c r="H279" t="s">
+        <v>1836</v>
+      </c>
+      <c r="I279" t="s">
+        <v>1837</v>
+      </c>
+      <c r="J279" t="s">
+        <v>1348</v>
+      </c>
+      <c r="K279" t="s">
+        <v>1447</v>
+      </c>
+      <c r="L279" t="s">
+        <v>1838</v>
+      </c>
+      <c r="M279" t="s">
+        <v>1839</v>
+      </c>
+      <c r="N279" t="s">
+        <v>51</v>
+      </c>
+      <c r="O279" t="s">
+        <v>41</v>
+      </c>
+      <c r="P279" t="s">
+        <v>1840</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>176</v>
+      </c>
+      <c r="R279" t="s">
+        <v>38</v>
+      </c>
+      <c r="S279" t="s">
+        <v>41</v>
+      </c>
+      <c r="T279" t="s">
+        <v>39</v>
+      </c>
+      <c r="U279" t="s">
+        <v>41</v>
+      </c>
+      <c r="V279">
+        <v>32</v>
+      </c>
+      <c r="W279">
+        <v>20</v>
+      </c>
+      <c r="X279">
+        <v>20</v>
+      </c>
+      <c r="Y279">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="280" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>202</v>
+      </c>
+      <c r="B280" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C280" t="s">
+        <v>203</v>
+      </c>
+      <c r="D280" t="s">
+        <v>204</v>
+      </c>
+      <c r="E280" t="s">
+        <v>191</v>
+      </c>
+      <c r="F280" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G280" t="s">
+        <v>273</v>
+      </c>
+      <c r="H280" t="s">
+        <v>1841</v>
+      </c>
+      <c r="I280" t="s">
+        <v>1842</v>
+      </c>
+      <c r="J280" t="s">
+        <v>1843</v>
+      </c>
+      <c r="K280" t="s">
+        <v>1844</v>
+      </c>
+      <c r="L280" t="s">
+        <v>809</v>
+      </c>
+      <c r="M280" t="s">
+        <v>774</v>
+      </c>
+      <c r="N280" t="s">
+        <v>113</v>
+      </c>
+      <c r="O280" t="s">
+        <v>201</v>
+      </c>
+      <c r="P280" t="s">
+        <v>1504</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>488</v>
+      </c>
+      <c r="R280" t="s">
+        <v>41</v>
+      </c>
+      <c r="S280" t="s">
+        <v>41</v>
+      </c>
+      <c r="T280" t="s">
+        <v>39</v>
+      </c>
+      <c r="U280" t="s">
+        <v>201</v>
+      </c>
+      <c r="V280">
+        <v>28</v>
+      </c>
+      <c r="W280">
+        <v>6</v>
+      </c>
+      <c r="X280">
+        <v>11</v>
+      </c>
+      <c r="Y280">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>202</v>
+      </c>
+      <c r="B281" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C281" t="s">
+        <v>203</v>
+      </c>
+      <c r="D281" t="s">
+        <v>345</v>
+      </c>
+      <c r="E281" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F281" t="s">
+        <v>173</v>
+      </c>
+      <c r="G281" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H281" t="s">
+        <v>1845</v>
+      </c>
+      <c r="I281" t="s">
+        <v>1846</v>
+      </c>
+      <c r="J281" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K281" t="s">
+        <v>1848</v>
+      </c>
+      <c r="L281" t="s">
+        <v>1343</v>
+      </c>
+      <c r="M281" t="s">
+        <v>521</v>
+      </c>
+      <c r="N281" t="s">
+        <v>290</v>
+      </c>
+      <c r="O281" t="s">
+        <v>177</v>
+      </c>
+      <c r="P281" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>1849</v>
+      </c>
+      <c r="R281" t="s">
+        <v>66</v>
+      </c>
+      <c r="S281" t="s">
+        <v>39</v>
+      </c>
+      <c r="T281" t="s">
+        <v>40</v>
+      </c>
+      <c r="U281" t="s">
+        <v>41</v>
+      </c>
+      <c r="V281">
+        <v>39</v>
+      </c>
+      <c r="W281">
+        <v>16</v>
+      </c>
+      <c r="X281">
+        <v>29</v>
+      </c>
+      <c r="Y281">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="282" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>202</v>
+      </c>
+      <c r="B282" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C282" t="s">
+        <v>203</v>
+      </c>
+      <c r="D282" t="s">
+        <v>345</v>
+      </c>
+      <c r="E282" t="s">
+        <v>54</v>
+      </c>
+      <c r="F282" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G282" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H282" t="s">
+        <v>1851</v>
+      </c>
+      <c r="I282" t="s">
+        <v>1852</v>
+      </c>
+      <c r="J282" t="s">
+        <v>509</v>
+      </c>
+      <c r="K282" t="s">
+        <v>1853</v>
+      </c>
+      <c r="L282" t="s">
+        <v>1854</v>
+      </c>
+      <c r="M282" t="s">
+        <v>251</v>
+      </c>
+      <c r="N282" t="s">
+        <v>672</v>
+      </c>
+      <c r="O282" t="s">
+        <v>337</v>
+      </c>
+      <c r="P282" t="s">
+        <v>1855</v>
+      </c>
+      <c r="Q282" t="s">
+        <v>1856</v>
+      </c>
+      <c r="R282" t="s">
+        <v>38</v>
+      </c>
+      <c r="S282" t="s">
+        <v>41</v>
+      </c>
+      <c r="T282" t="s">
+        <v>38</v>
+      </c>
+      <c r="U282" t="s">
+        <v>41</v>
+      </c>
+      <c r="V282">
+        <v>23</v>
+      </c>
+      <c r="W282">
+        <v>17</v>
+      </c>
+      <c r="X282">
+        <v>19</v>
+      </c>
+      <c r="Y282">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="283" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>202</v>
+      </c>
+      <c r="B283" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C283" t="s">
+        <v>203</v>
+      </c>
+      <c r="D283" t="s">
+        <v>345</v>
+      </c>
+      <c r="E283" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F283" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G283" t="s">
+        <v>764</v>
+      </c>
+      <c r="H283" t="s">
+        <v>1858</v>
+      </c>
+      <c r="I283" t="s">
+        <v>1859</v>
+      </c>
+      <c r="J283" t="s">
+        <v>1860</v>
+      </c>
+      <c r="K283" t="s">
+        <v>1861</v>
+      </c>
+      <c r="L283" t="s">
+        <v>1862</v>
+      </c>
+      <c r="M283" t="s">
+        <v>794</v>
+      </c>
+      <c r="N283" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O283" t="s">
+        <v>41</v>
+      </c>
+      <c r="P283" t="s">
+        <v>1863</v>
+      </c>
+      <c r="Q283" t="s">
+        <v>1681</v>
+      </c>
+      <c r="R283" t="s">
+        <v>39</v>
+      </c>
+      <c r="S283" t="s">
+        <v>41</v>
+      </c>
+      <c r="T283" t="s">
+        <v>39</v>
+      </c>
+      <c r="U283" t="s">
+        <v>201</v>
+      </c>
+      <c r="V283">
+        <v>18</v>
+      </c>
+      <c r="W283">
+        <v>7</v>
+      </c>
+      <c r="X283">
+        <v>18</v>
+      </c>
+      <c r="Y283">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>202</v>
+      </c>
+      <c r="B284" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C284" t="s">
+        <v>203</v>
+      </c>
+      <c r="D284" t="s">
+        <v>345</v>
+      </c>
+      <c r="E284" t="s">
+        <v>90</v>
+      </c>
+      <c r="F284" t="s">
+        <v>173</v>
+      </c>
+      <c r="G284" t="s">
+        <v>1864</v>
+      </c>
+      <c r="H284" t="s">
+        <v>1865</v>
+      </c>
+      <c r="I284" t="s">
+        <v>1866</v>
+      </c>
+      <c r="J284" t="s">
+        <v>1867</v>
+      </c>
+      <c r="K284" t="s">
+        <v>1868</v>
+      </c>
+      <c r="L284" t="s">
+        <v>152</v>
+      </c>
+      <c r="M284" t="s">
+        <v>620</v>
+      </c>
+      <c r="N284" t="s">
+        <v>63</v>
+      </c>
+      <c r="O284" t="s">
+        <v>66</v>
+      </c>
+      <c r="P284" t="s">
+        <v>1869</v>
+      </c>
+      <c r="Q284" t="s">
+        <v>834</v>
+      </c>
+      <c r="R284" t="s">
+        <v>38</v>
+      </c>
+      <c r="S284" t="s">
+        <v>39</v>
+      </c>
+      <c r="T284" t="s">
+        <v>40</v>
+      </c>
+      <c r="U284" t="s">
+        <v>41</v>
+      </c>
+      <c r="V284">
+        <v>39</v>
+      </c>
+      <c r="W284">
+        <v>31</v>
+      </c>
+      <c r="X284">
+        <v>20</v>
+      </c>
+      <c r="Y284">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="285" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>202</v>
+      </c>
+      <c r="B285" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C285" t="s">
+        <v>203</v>
+      </c>
+      <c r="D285" t="s">
+        <v>345</v>
+      </c>
+      <c r="E285" t="s">
+        <v>102</v>
+      </c>
+      <c r="F285" t="s">
+        <v>173</v>
+      </c>
+      <c r="G285" t="s">
+        <v>283</v>
+      </c>
+      <c r="H285" t="s">
+        <v>1870</v>
+      </c>
+      <c r="I285" t="s">
+        <v>1871</v>
+      </c>
+      <c r="J285" t="s">
+        <v>1872</v>
+      </c>
+      <c r="K285" t="s">
+        <v>1873</v>
+      </c>
+      <c r="L285" t="s">
+        <v>847</v>
+      </c>
+      <c r="M285" t="s">
+        <v>186</v>
+      </c>
+      <c r="N285" t="s">
+        <v>604</v>
+      </c>
+      <c r="O285" t="s">
+        <v>337</v>
+      </c>
+      <c r="P285" t="s">
+        <v>1874</v>
+      </c>
+      <c r="Q285" t="s">
+        <v>470</v>
+      </c>
+      <c r="R285" t="s">
+        <v>38</v>
+      </c>
+      <c r="S285" t="s">
+        <v>201</v>
+      </c>
+      <c r="T285" t="s">
+        <v>38</v>
+      </c>
+      <c r="U285" t="s">
+        <v>41</v>
+      </c>
+      <c r="V285">
+        <v>36</v>
+      </c>
+      <c r="W285">
+        <v>17</v>
+      </c>
+      <c r="X285">
+        <v>21</v>
+      </c>
+      <c r="Y285">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>202</v>
+      </c>
+      <c r="B286" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C286" t="s">
+        <v>203</v>
+      </c>
+      <c r="D286" t="s">
+        <v>345</v>
+      </c>
+      <c r="E286" t="s">
+        <v>347</v>
+      </c>
+      <c r="F286" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G286" t="s">
+        <v>701</v>
+      </c>
+      <c r="H286" t="s">
+        <v>1875</v>
+      </c>
+      <c r="I286" t="s">
+        <v>1876</v>
+      </c>
+      <c r="J286" t="s">
+        <v>1877</v>
+      </c>
+      <c r="K286" t="s">
+        <v>1878</v>
+      </c>
+      <c r="L286" t="s">
+        <v>728</v>
+      </c>
+      <c r="M286" t="s">
+        <v>1879</v>
+      </c>
+      <c r="N286" t="s">
+        <v>122</v>
+      </c>
+      <c r="O286" t="s">
+        <v>39</v>
+      </c>
+      <c r="P286" t="s">
+        <v>1880</v>
+      </c>
+      <c r="Q286" t="s">
+        <v>581</v>
+      </c>
+      <c r="R286" t="s">
+        <v>41</v>
+      </c>
+      <c r="S286" t="s">
+        <v>201</v>
+      </c>
+      <c r="T286" t="s">
+        <v>39</v>
+      </c>
+      <c r="U286" t="s">
+        <v>41</v>
+      </c>
+      <c r="V286">
+        <v>18</v>
+      </c>
+      <c r="W286">
+        <v>15</v>
+      </c>
+      <c r="X286">
+        <v>9</v>
+      </c>
+      <c r="Y286">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>202</v>
+      </c>
+      <c r="B287" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C287" t="s">
+        <v>203</v>
+      </c>
+      <c r="D287" t="s">
+        <v>345</v>
+      </c>
+      <c r="E287" t="s">
+        <v>895</v>
+      </c>
+      <c r="F287" t="s">
+        <v>173</v>
+      </c>
+      <c r="G287" t="s">
+        <v>1881</v>
+      </c>
+      <c r="H287" t="s">
+        <v>1882</v>
+      </c>
+      <c r="I287" t="s">
+        <v>490</v>
+      </c>
+      <c r="J287" t="s">
+        <v>1883</v>
+      </c>
+      <c r="K287" t="s">
+        <v>1884</v>
+      </c>
+      <c r="L287" t="s">
+        <v>420</v>
+      </c>
+      <c r="M287" t="s">
+        <v>264</v>
+      </c>
+      <c r="N287" t="s">
+        <v>337</v>
+      </c>
+      <c r="O287" t="s">
+        <v>113</v>
+      </c>
+      <c r="P287" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>1359</v>
+      </c>
+      <c r="R287" t="s">
+        <v>39</v>
+      </c>
+      <c r="S287" t="s">
+        <v>41</v>
+      </c>
+      <c r="T287" t="s">
+        <v>41</v>
+      </c>
+      <c r="U287" t="s">
+        <v>201</v>
+      </c>
+      <c r="V287">
+        <v>28</v>
+      </c>
+      <c r="W287">
+        <v>7</v>
+      </c>
+      <c r="X287">
+        <v>10</v>
+      </c>
+      <c r="Y287">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>202</v>
+      </c>
+      <c r="B288" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C288" t="s">
+        <v>203</v>
+      </c>
+      <c r="D288" t="s">
+        <v>345</v>
+      </c>
+      <c r="E288" t="s">
+        <v>126</v>
+      </c>
+      <c r="F288" t="s">
+        <v>173</v>
+      </c>
+      <c r="G288" t="s">
+        <v>115</v>
+      </c>
+      <c r="H288" t="s">
+        <v>1885</v>
+      </c>
+      <c r="I288" t="s">
+        <v>1886</v>
+      </c>
+      <c r="J288" t="s">
+        <v>1887</v>
+      </c>
+      <c r="K288" t="s">
+        <v>1888</v>
+      </c>
+      <c r="L288" t="s">
+        <v>241</v>
+      </c>
+      <c r="M288" t="s">
+        <v>505</v>
+      </c>
+      <c r="N288" t="s">
+        <v>471</v>
+      </c>
+      <c r="O288" t="s">
+        <v>337</v>
+      </c>
+      <c r="P288" t="s">
+        <v>864</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>1619</v>
+      </c>
+      <c r="R288" t="s">
+        <v>38</v>
+      </c>
+      <c r="S288" t="s">
+        <v>41</v>
+      </c>
+      <c r="T288" t="s">
+        <v>39</v>
+      </c>
+      <c r="U288" t="s">
+        <v>201</v>
+      </c>
+      <c r="V288">
+        <v>23</v>
+      </c>
+      <c r="W288">
+        <v>7</v>
+      </c>
+      <c r="X288">
+        <v>13</v>
+      </c>
+      <c r="Y288">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="289" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>202</v>
+      </c>
+      <c r="B289" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C289" t="s">
+        <v>203</v>
+      </c>
+      <c r="D289" t="s">
+        <v>345</v>
+      </c>
+      <c r="E289" t="s">
+        <v>346</v>
+      </c>
+      <c r="F289" t="s">
+        <v>173</v>
+      </c>
+      <c r="G289" t="s">
+        <v>319</v>
+      </c>
+      <c r="H289" t="s">
+        <v>1889</v>
+      </c>
+      <c r="I289" t="s">
+        <v>1890</v>
+      </c>
+      <c r="J289" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K289" t="s">
+        <v>1892</v>
+      </c>
+      <c r="L289" t="s">
+        <v>1862</v>
+      </c>
+      <c r="M289" t="s">
+        <v>192</v>
+      </c>
+      <c r="N289" t="s">
+        <v>279</v>
+      </c>
+      <c r="O289" t="s">
+        <v>35</v>
+      </c>
+      <c r="P289" t="s">
+        <v>1893</v>
+      </c>
+      <c r="Q289" t="s">
+        <v>1151</v>
+      </c>
+      <c r="R289" t="s">
+        <v>39</v>
+      </c>
+      <c r="S289" t="s">
+        <v>201</v>
+      </c>
+      <c r="T289" t="s">
+        <v>38</v>
+      </c>
+      <c r="U289" t="s">
+        <v>41</v>
+      </c>
+      <c r="V289">
+        <v>31</v>
+      </c>
+      <c r="W289">
+        <v>12</v>
+      </c>
+      <c r="X289">
+        <v>18</v>
+      </c>
+      <c r="Y289">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>202</v>
+      </c>
+      <c r="B290" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C290" t="s">
+        <v>203</v>
+      </c>
+      <c r="D290" t="s">
+        <v>345</v>
+      </c>
+      <c r="E290" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F290" t="s">
+        <v>173</v>
+      </c>
+      <c r="G290" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H290" t="s">
+        <v>1894</v>
+      </c>
+      <c r="I290" t="s">
+        <v>1895</v>
+      </c>
+      <c r="J290" t="s">
+        <v>1896</v>
+      </c>
+      <c r="K290" t="s">
+        <v>1897</v>
+      </c>
+      <c r="L290" t="s">
+        <v>1476</v>
+      </c>
+      <c r="M290" t="s">
+        <v>926</v>
+      </c>
+      <c r="N290" t="s">
+        <v>134</v>
+      </c>
+      <c r="O290" t="s">
+        <v>99</v>
+      </c>
+      <c r="P290" t="s">
+        <v>1482</v>
+      </c>
+      <c r="Q290" t="s">
+        <v>1115</v>
+      </c>
+      <c r="R290" t="s">
+        <v>40</v>
+      </c>
+      <c r="S290" t="s">
+        <v>41</v>
+      </c>
+      <c r="T290" t="s">
+        <v>113</v>
+      </c>
+      <c r="U290" t="s">
+        <v>41</v>
+      </c>
+      <c r="V290">
+        <v>49</v>
+      </c>
+      <c r="W290">
+        <v>22</v>
+      </c>
+      <c r="X290">
+        <v>34</v>
+      </c>
+      <c r="Y290">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="291" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>202</v>
+      </c>
+      <c r="B291" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C291" t="s">
+        <v>203</v>
+      </c>
+      <c r="D291" t="s">
+        <v>345</v>
+      </c>
+      <c r="E291" t="s">
+        <v>137</v>
+      </c>
+      <c r="F291" t="s">
+        <v>173</v>
+      </c>
+      <c r="G291" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H291" t="s">
+        <v>1898</v>
+      </c>
+      <c r="I291" t="s">
+        <v>1899</v>
+      </c>
+      <c r="J291" t="s">
+        <v>1900</v>
+      </c>
+      <c r="K291" t="s">
+        <v>1901</v>
+      </c>
+      <c r="L291" t="s">
+        <v>1175</v>
+      </c>
+      <c r="M291" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N291" t="s">
+        <v>99</v>
+      </c>
+      <c r="O291" t="s">
+        <v>66</v>
+      </c>
+      <c r="P291" t="s">
+        <v>1902</v>
+      </c>
+      <c r="Q291" t="s">
+        <v>1903</v>
+      </c>
+      <c r="R291" t="s">
+        <v>40</v>
+      </c>
+      <c r="S291" t="s">
+        <v>41</v>
+      </c>
+      <c r="T291" t="s">
+        <v>39</v>
+      </c>
+      <c r="U291" t="s">
+        <v>201</v>
+      </c>
+      <c r="V291">
+        <v>35</v>
+      </c>
+      <c r="W291">
+        <v>9</v>
+      </c>
+      <c r="X291">
+        <v>27</v>
+      </c>
+      <c r="Y291">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="292" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>202</v>
+      </c>
+      <c r="B292" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C292" t="s">
+        <v>203</v>
+      </c>
+      <c r="D292" t="s">
+        <v>345</v>
+      </c>
+      <c r="E292" t="s">
+        <v>147</v>
+      </c>
+      <c r="F292" t="s">
+        <v>173</v>
+      </c>
+      <c r="G292" t="s">
+        <v>319</v>
+      </c>
+      <c r="H292" t="s">
+        <v>1904</v>
+      </c>
+      <c r="I292" t="s">
+        <v>1905</v>
+      </c>
+      <c r="J292" t="s">
+        <v>1906</v>
+      </c>
+      <c r="K292" t="s">
+        <v>1907</v>
+      </c>
+      <c r="L292" t="s">
+        <v>1370</v>
+      </c>
+      <c r="M292" t="s">
+        <v>434</v>
+      </c>
+      <c r="N292" t="s">
+        <v>123</v>
+      </c>
+      <c r="O292" t="s">
+        <v>76</v>
+      </c>
+      <c r="P292" t="s">
+        <v>1869</v>
+      </c>
+      <c r="Q292" t="s">
+        <v>1328</v>
+      </c>
+      <c r="R292" t="s">
+        <v>113</v>
+      </c>
+      <c r="S292" t="s">
+        <v>39</v>
+      </c>
+      <c r="T292" t="s">
+        <v>66</v>
+      </c>
+      <c r="U292" t="s">
+        <v>39</v>
+      </c>
+      <c r="V292">
+        <v>50</v>
+      </c>
+      <c r="W292">
+        <v>27</v>
+      </c>
+      <c r="X292">
+        <v>44</v>
+      </c>
+      <c r="Y292">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="293" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>202</v>
+      </c>
+      <c r="B293" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C293" t="s">
+        <v>203</v>
+      </c>
+      <c r="D293" t="s">
+        <v>345</v>
+      </c>
+      <c r="E293" t="s">
+        <v>933</v>
+      </c>
+      <c r="F293" t="s">
+        <v>173</v>
+      </c>
+      <c r="G293" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H293" t="s">
+        <v>1909</v>
+      </c>
+      <c r="I293" t="s">
+        <v>1910</v>
+      </c>
+      <c r="J293" t="s">
+        <v>1442</v>
+      </c>
+      <c r="K293" t="s">
+        <v>1911</v>
+      </c>
+      <c r="L293" t="s">
+        <v>241</v>
+      </c>
+      <c r="M293" t="s">
+        <v>251</v>
+      </c>
+      <c r="N293" t="s">
+        <v>213</v>
+      </c>
+      <c r="O293" t="s">
+        <v>495</v>
+      </c>
+      <c r="P293" t="s">
+        <v>1106</v>
+      </c>
+      <c r="Q293" t="s">
+        <v>1912</v>
+      </c>
+      <c r="R293" t="s">
+        <v>39</v>
+      </c>
+      <c r="S293" t="s">
+        <v>41</v>
+      </c>
+      <c r="T293" t="s">
+        <v>38</v>
+      </c>
+      <c r="U293" t="s">
+        <v>41</v>
+      </c>
+      <c r="V293">
+        <v>29</v>
+      </c>
+      <c r="W293">
+        <v>13</v>
+      </c>
+      <c r="X293">
+        <v>18</v>
+      </c>
+      <c r="Y293">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>202</v>
+      </c>
+      <c r="B294" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C294" t="s">
+        <v>203</v>
+      </c>
+      <c r="D294" t="s">
+        <v>345</v>
+      </c>
+      <c r="E294" t="s">
+        <v>191</v>
+      </c>
+      <c r="F294" t="s">
+        <v>173</v>
+      </c>
+      <c r="G294" t="s">
+        <v>482</v>
+      </c>
+      <c r="H294" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I294" t="s">
+        <v>1914</v>
+      </c>
+      <c r="J294" t="s">
+        <v>1534</v>
+      </c>
+      <c r="K294" t="s">
+        <v>1915</v>
+      </c>
+      <c r="L294" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M294" t="s">
+        <v>1175</v>
+      </c>
+      <c r="N294" t="s">
+        <v>488</v>
+      </c>
+      <c r="O294" t="s">
+        <v>39</v>
+      </c>
+      <c r="P294" t="s">
+        <v>1916</v>
+      </c>
+      <c r="Q294" t="s">
+        <v>1396</v>
+      </c>
+      <c r="R294" t="s">
+        <v>201</v>
+      </c>
+      <c r="S294" t="s">
+        <v>201</v>
+      </c>
+      <c r="T294" t="s">
+        <v>41</v>
+      </c>
+      <c r="U294" t="s">
+        <v>201</v>
+      </c>
+      <c r="V294">
+        <v>10</v>
+      </c>
+      <c r="W294">
+        <v>3</v>
+      </c>
+      <c r="X294">
+        <v>7</v>
+      </c>
+      <c r="Y294">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6398683-F1E7-BD47-9680-A428F7E67655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135A491B-597F-534B-8658-CEE850FFF595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5546" uniqueCount="1918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6515" uniqueCount="2159">
   <si>
     <t>Type</t>
   </si>
@@ -5790,6 +5790,729 @@
   </si>
   <si>
     <t>Glenn Manga-Tabi</t>
+  </si>
+  <si>
+    <t>79.37</t>
+  </si>
+  <si>
+    <t>64.98</t>
+  </si>
+  <si>
+    <t>247.19</t>
+  </si>
+  <si>
+    <t>62.61</t>
+  </si>
+  <si>
+    <t>79.38</t>
+  </si>
+  <si>
+    <t>142.05</t>
+  </si>
+  <si>
+    <t>274.96</t>
+  </si>
+  <si>
+    <t>28.05</t>
+  </si>
+  <si>
+    <t>65.12</t>
+  </si>
+  <si>
+    <t>22.82</t>
+  </si>
+  <si>
+    <t>330.28</t>
+  </si>
+  <si>
+    <t>21.88</t>
+  </si>
+  <si>
+    <t>73.69</t>
+  </si>
+  <si>
+    <t>111.74</t>
+  </si>
+  <si>
+    <t>281.98</t>
+  </si>
+  <si>
+    <t>24.99</t>
+  </si>
+  <si>
+    <t>18.3</t>
+  </si>
+  <si>
+    <t>44.09</t>
+  </si>
+  <si>
+    <t>229.28</t>
+  </si>
+  <si>
+    <t>23.44</t>
+  </si>
+  <si>
+    <t>54.63</t>
+  </si>
+  <si>
+    <t>59.12</t>
+  </si>
+  <si>
+    <t>229.33</t>
+  </si>
+  <si>
+    <t>51.16</t>
+  </si>
+  <si>
+    <t>112.55</t>
+  </si>
+  <si>
+    <t>251.83</t>
+  </si>
+  <si>
+    <t>27.6</t>
+  </si>
+  <si>
+    <t>66.92</t>
+  </si>
+  <si>
+    <t>120.66</t>
+  </si>
+  <si>
+    <t>498.57</t>
+  </si>
+  <si>
+    <t>27.84</t>
+  </si>
+  <si>
+    <t>65.43</t>
+  </si>
+  <si>
+    <t>7.77</t>
+  </si>
+  <si>
+    <t>60.91</t>
+  </si>
+  <si>
+    <t>262.77</t>
+  </si>
+  <si>
+    <t>25.7</t>
+  </si>
+  <si>
+    <t>63.17</t>
+  </si>
+  <si>
+    <t>40.58</t>
+  </si>
+  <si>
+    <t>308.9</t>
+  </si>
+  <si>
+    <t>22.08</t>
+  </si>
+  <si>
+    <t>61.68</t>
+  </si>
+  <si>
+    <t>274.37</t>
+  </si>
+  <si>
+    <t>64.55</t>
+  </si>
+  <si>
+    <t>7.56</t>
+  </si>
+  <si>
+    <t>62.67</t>
+  </si>
+  <si>
+    <t>414.75</t>
+  </si>
+  <si>
+    <t>24.7</t>
+  </si>
+  <si>
+    <t>49.9</t>
+  </si>
+  <si>
+    <t>7.05</t>
+  </si>
+  <si>
+    <t>9.2</t>
+  </si>
+  <si>
+    <t>98.12</t>
+  </si>
+  <si>
+    <t>675.69</t>
+  </si>
+  <si>
+    <t>403.74</t>
+  </si>
+  <si>
+    <t>103.97</t>
+  </si>
+  <si>
+    <t>80.1</t>
+  </si>
+  <si>
+    <t>7.92</t>
+  </si>
+  <si>
+    <t>1.36</t>
+  </si>
+  <si>
+    <t>31.26</t>
+  </si>
+  <si>
+    <t>168.38</t>
+  </si>
+  <si>
+    <t>13.84</t>
+  </si>
+  <si>
+    <t>81.35</t>
+  </si>
+  <si>
+    <t>9.55</t>
+  </si>
+  <si>
+    <t>447.36</t>
+  </si>
+  <si>
+    <t>455.02</t>
+  </si>
+  <si>
+    <t>26.56</t>
+  </si>
+  <si>
+    <t>117.35</t>
+  </si>
+  <si>
+    <t>8.66</t>
+  </si>
+  <si>
+    <t>66.4</t>
+  </si>
+  <si>
+    <t>84.93</t>
+  </si>
+  <si>
+    <t>10.22</t>
+  </si>
+  <si>
+    <t>905.08</t>
+  </si>
+  <si>
+    <t>386.8</t>
+  </si>
+  <si>
+    <t>120.28</t>
+  </si>
+  <si>
+    <t>7.84</t>
+  </si>
+  <si>
+    <t>132.4</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>70.28</t>
+  </si>
+  <si>
+    <t>753.07</t>
+  </si>
+  <si>
+    <t>332.19</t>
+  </si>
+  <si>
+    <t>32.38</t>
+  </si>
+  <si>
+    <t>110.69</t>
+  </si>
+  <si>
+    <t>25.0</t>
+  </si>
+  <si>
+    <t>9.15</t>
+  </si>
+  <si>
+    <t>726.54</t>
+  </si>
+  <si>
+    <t>401.5</t>
+  </si>
+  <si>
+    <t>30.48</t>
+  </si>
+  <si>
+    <t>93.24</t>
+  </si>
+  <si>
+    <t>83.2</t>
+  </si>
+  <si>
+    <t>28.6</t>
+  </si>
+  <si>
+    <t>10.96</t>
+  </si>
+  <si>
+    <t>932.22</t>
+  </si>
+  <si>
+    <t>479.01</t>
+  </si>
+  <si>
+    <t>111.7</t>
+  </si>
+  <si>
+    <t>5.84</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>101.5</t>
+  </si>
+  <si>
+    <t>40.8</t>
+  </si>
+  <si>
+    <t>1159.55</t>
+  </si>
+  <si>
+    <t>486.67</t>
+  </si>
+  <si>
+    <t>29.63</t>
+  </si>
+  <si>
+    <t>117.23</t>
+  </si>
+  <si>
+    <t>165.2</t>
+  </si>
+  <si>
+    <t>84.72</t>
+  </si>
+  <si>
+    <t>9.48</t>
+  </si>
+  <si>
+    <t>1007.63</t>
+  </si>
+  <si>
+    <t>395.7</t>
+  </si>
+  <si>
+    <t>111.9</t>
+  </si>
+  <si>
+    <t>121.3</t>
+  </si>
+  <si>
+    <t>317.53</t>
+  </si>
+  <si>
+    <t>147.37</t>
+  </si>
+  <si>
+    <t>32.13</t>
+  </si>
+  <si>
+    <t>96.71</t>
+  </si>
+  <si>
+    <t>8.59</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
+    <t>9.43</t>
+  </si>
+  <si>
+    <t>725.05</t>
+  </si>
+  <si>
+    <t>391.35</t>
+  </si>
+  <si>
+    <t>96.16</t>
+  </si>
+  <si>
+    <t>7.85</t>
+  </si>
+  <si>
+    <t>9.04</t>
+  </si>
+  <si>
+    <t>416.32</t>
+  </si>
+  <si>
+    <t>350.01</t>
+  </si>
+  <si>
+    <t>32.19</t>
+  </si>
+  <si>
+    <t>92.1</t>
+  </si>
+  <si>
+    <t>49.1</t>
+  </si>
+  <si>
+    <t>15.5</t>
+  </si>
+  <si>
+    <t>CDF T5 VS Revermontoise 11/10/2026</t>
+  </si>
+  <si>
+    <t>119.17</t>
+  </si>
+  <si>
+    <t>226.08</t>
+  </si>
+  <si>
+    <t>374.1</t>
+  </si>
+  <si>
+    <t>54.17</t>
+  </si>
+  <si>
+    <t>192.91</t>
+  </si>
+  <si>
+    <t>340.32</t>
+  </si>
+  <si>
+    <t>28.94</t>
+  </si>
+  <si>
+    <t>55.91</t>
+  </si>
+  <si>
+    <t>74.83</t>
+  </si>
+  <si>
+    <t>3.22</t>
+  </si>
+  <si>
+    <t>70.65</t>
+  </si>
+  <si>
+    <t>198.2</t>
+  </si>
+  <si>
+    <t>27.44</t>
+  </si>
+  <si>
+    <t>42.99</t>
+  </si>
+  <si>
+    <t>93.98</t>
+  </si>
+  <si>
+    <t>339.72</t>
+  </si>
+  <si>
+    <t>30.62</t>
+  </si>
+  <si>
+    <t>44.74</t>
+  </si>
+  <si>
+    <t>120.52</t>
+  </si>
+  <si>
+    <t>358.49</t>
+  </si>
+  <si>
+    <t>27.88</t>
+  </si>
+  <si>
+    <t>119.15</t>
+  </si>
+  <si>
+    <t>204.96</t>
+  </si>
+  <si>
+    <t>636.04</t>
+  </si>
+  <si>
+    <t>26.58</t>
+  </si>
+  <si>
+    <t>53.07</t>
+  </si>
+  <si>
+    <t>26.7</t>
+  </si>
+  <si>
+    <t>409.77</t>
+  </si>
+  <si>
+    <t>392.88</t>
+  </si>
+  <si>
+    <t>30.42</t>
+  </si>
+  <si>
+    <t>58.87</t>
+  </si>
+  <si>
+    <t>36.8</t>
+  </si>
+  <si>
+    <t>7.13</t>
+  </si>
+  <si>
+    <t>247.86</t>
+  </si>
+  <si>
+    <t>705.36</t>
+  </si>
+  <si>
+    <t>59.86</t>
+  </si>
+  <si>
+    <t>8.04</t>
+  </si>
+  <si>
+    <t>136.61</t>
+  </si>
+  <si>
+    <t>364.44</t>
+  </si>
+  <si>
+    <t>56.73</t>
+  </si>
+  <si>
+    <t>15.1</t>
+  </si>
+  <si>
+    <t>324.39</t>
+  </si>
+  <si>
+    <t>601.24</t>
+  </si>
+  <si>
+    <t>33.09</t>
+  </si>
+  <si>
+    <t>49.11</t>
+  </si>
+  <si>
+    <t>6.8</t>
+  </si>
+  <si>
+    <t>7.17</t>
+  </si>
+  <si>
+    <t>101.58</t>
+  </si>
+  <si>
+    <t>271.67</t>
+  </si>
+  <si>
+    <t>25.49</t>
+  </si>
+  <si>
+    <t>46.55</t>
+  </si>
+  <si>
+    <t>14.9</t>
+  </si>
+  <si>
+    <t>2.27</t>
+  </si>
+  <si>
+    <t>58.24</t>
+  </si>
+  <si>
+    <t>123.75</t>
+  </si>
+  <si>
+    <t>28.96</t>
+  </si>
+  <si>
+    <t>78.42</t>
+  </si>
+  <si>
+    <t>628.1</t>
+  </si>
+  <si>
+    <t>319.76</t>
+  </si>
+  <si>
+    <t>30.89</t>
+  </si>
+  <si>
+    <t>82.77</t>
+  </si>
+  <si>
+    <t>8.37</t>
+  </si>
+  <si>
+    <t>406.75</t>
+  </si>
+  <si>
+    <t>410.58</t>
+  </si>
+  <si>
+    <t>27.04</t>
+  </si>
+  <si>
+    <t>106.73</t>
+  </si>
+  <si>
+    <t>9.18</t>
+  </si>
+  <si>
+    <t>62.2</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>8.11</t>
+  </si>
+  <si>
+    <t>760.07</t>
+  </si>
+  <si>
+    <t>335.12</t>
+  </si>
+  <si>
+    <t>103.46</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>105.8</t>
+  </si>
+  <si>
+    <t>285.93</t>
+  </si>
+  <si>
+    <t>268.15</t>
+  </si>
+  <si>
+    <t>28.8</t>
+  </si>
+  <si>
+    <t>32.9</t>
+  </si>
+  <si>
+    <t>601.03</t>
+  </si>
+  <si>
+    <t>320.51</t>
+  </si>
+  <si>
+    <t>94.83</t>
+  </si>
+  <si>
+    <t>76.2</t>
+  </si>
+  <si>
+    <t>442.78</t>
+  </si>
+  <si>
+    <t>599.0</t>
+  </si>
+  <si>
+    <t>87.11</t>
+  </si>
+  <si>
+    <t>57.3</t>
+  </si>
+  <si>
+    <t>230.27</t>
+  </si>
+  <si>
+    <t>366.24</t>
+  </si>
+  <si>
+    <t>96.12</t>
+  </si>
+  <si>
+    <t>38.6</t>
+  </si>
+  <si>
+    <t>107.85</t>
+  </si>
+  <si>
+    <t>467.76</t>
+  </si>
+  <si>
+    <t>73.48</t>
+  </si>
+  <si>
+    <t>717.98</t>
+  </si>
+  <si>
+    <t>30.73</t>
+  </si>
+  <si>
+    <t>87.88</t>
+  </si>
+  <si>
+    <t>89.7</t>
+  </si>
+  <si>
+    <t>22.2</t>
+  </si>
+  <si>
+    <t>156.57</t>
+  </si>
+  <si>
+    <t>255.44</t>
+  </si>
+  <si>
+    <t>29.62</t>
+  </si>
+  <si>
+    <t>67.68</t>
+  </si>
+  <si>
+    <t>15.2</t>
+  </si>
+  <si>
+    <t>751.71</t>
+  </si>
+  <si>
+    <t>684.28</t>
+  </si>
+  <si>
+    <t>86.74</t>
+  </si>
+  <si>
+    <t>9.41</t>
+  </si>
+  <si>
+    <t>92.7</t>
+  </si>
+  <si>
+    <t>24.2</t>
+  </si>
+  <si>
+    <t>180.19</t>
+  </si>
+  <si>
+    <t>271.87</t>
+  </si>
+  <si>
+    <t>73.15</t>
+  </si>
+  <si>
+    <t>Jeremy Romany</t>
   </si>
 </sst>
 </file>
@@ -6168,10 +6891,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y294"/>
+  <dimension ref="A1:Y343"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.83203125" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28468,6 +29191,3746 @@
         <v>0</v>
       </c>
     </row>
+    <row r="295" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>202</v>
+      </c>
+      <c r="B295" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C295" t="s">
+        <v>203</v>
+      </c>
+      <c r="D295" t="s">
+        <v>849</v>
+      </c>
+      <c r="E295" t="s">
+        <v>25</v>
+      </c>
+      <c r="F295" t="s">
+        <v>1918</v>
+      </c>
+      <c r="G295" t="s">
+        <v>391</v>
+      </c>
+      <c r="H295" t="s">
+        <v>1919</v>
+      </c>
+      <c r="I295" t="s">
+        <v>1920</v>
+      </c>
+      <c r="J295" t="s">
+        <v>963</v>
+      </c>
+      <c r="K295" t="s">
+        <v>1921</v>
+      </c>
+      <c r="L295" t="s">
+        <v>987</v>
+      </c>
+      <c r="M295" t="s">
+        <v>241</v>
+      </c>
+      <c r="N295" t="s">
+        <v>113</v>
+      </c>
+      <c r="O295" t="s">
+        <v>201</v>
+      </c>
+      <c r="P295" t="s">
+        <v>1856</v>
+      </c>
+      <c r="Q295" t="s">
+        <v>34</v>
+      </c>
+      <c r="R295" t="s">
+        <v>40</v>
+      </c>
+      <c r="S295" t="s">
+        <v>39</v>
+      </c>
+      <c r="T295" t="s">
+        <v>40</v>
+      </c>
+      <c r="U295" t="s">
+        <v>41</v>
+      </c>
+      <c r="V295">
+        <v>48</v>
+      </c>
+      <c r="W295">
+        <v>22</v>
+      </c>
+      <c r="X295">
+        <v>31</v>
+      </c>
+      <c r="Y295">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="296" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>202</v>
+      </c>
+      <c r="B296" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C296" t="s">
+        <v>203</v>
+      </c>
+      <c r="D296" t="s">
+        <v>849</v>
+      </c>
+      <c r="E296" t="s">
+        <v>54</v>
+      </c>
+      <c r="F296" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G296" t="s">
+        <v>764</v>
+      </c>
+      <c r="H296" t="s">
+        <v>1923</v>
+      </c>
+      <c r="I296" t="s">
+        <v>1924</v>
+      </c>
+      <c r="J296" t="s">
+        <v>1925</v>
+      </c>
+      <c r="K296" t="s">
+        <v>1926</v>
+      </c>
+      <c r="L296" t="s">
+        <v>1074</v>
+      </c>
+      <c r="M296" t="s">
+        <v>1375</v>
+      </c>
+      <c r="N296" t="s">
+        <v>51</v>
+      </c>
+      <c r="O296" t="s">
+        <v>41</v>
+      </c>
+      <c r="P296" t="s">
+        <v>643</v>
+      </c>
+      <c r="Q296" t="s">
+        <v>737</v>
+      </c>
+      <c r="R296" t="s">
+        <v>66</v>
+      </c>
+      <c r="S296" t="s">
+        <v>39</v>
+      </c>
+      <c r="T296" t="s">
+        <v>66</v>
+      </c>
+      <c r="U296" t="s">
+        <v>41</v>
+      </c>
+      <c r="V296">
+        <v>64</v>
+      </c>
+      <c r="W296">
+        <v>29</v>
+      </c>
+      <c r="X296">
+        <v>45</v>
+      </c>
+      <c r="Y296">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="297" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>202</v>
+      </c>
+      <c r="B297" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C297" t="s">
+        <v>203</v>
+      </c>
+      <c r="D297" t="s">
+        <v>849</v>
+      </c>
+      <c r="E297" t="s">
+        <v>90</v>
+      </c>
+      <c r="F297" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G297" t="s">
+        <v>61</v>
+      </c>
+      <c r="H297" t="s">
+        <v>1927</v>
+      </c>
+      <c r="I297" t="s">
+        <v>1928</v>
+      </c>
+      <c r="J297" t="s">
+        <v>1929</v>
+      </c>
+      <c r="K297" t="s">
+        <v>1930</v>
+      </c>
+      <c r="L297" t="s">
+        <v>548</v>
+      </c>
+      <c r="M297" t="s">
+        <v>1530</v>
+      </c>
+      <c r="N297" t="s">
+        <v>39</v>
+      </c>
+      <c r="O297" t="s">
+        <v>201</v>
+      </c>
+      <c r="P297" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q297" t="s">
+        <v>201</v>
+      </c>
+      <c r="R297" t="s">
+        <v>40</v>
+      </c>
+      <c r="S297" t="s">
+        <v>41</v>
+      </c>
+      <c r="T297" t="s">
+        <v>66</v>
+      </c>
+      <c r="U297" t="s">
+        <v>39</v>
+      </c>
+      <c r="V297">
+        <v>68</v>
+      </c>
+      <c r="W297">
+        <v>29</v>
+      </c>
+      <c r="X297">
+        <v>57</v>
+      </c>
+      <c r="Y297">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="298" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>202</v>
+      </c>
+      <c r="B298" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C298" t="s">
+        <v>203</v>
+      </c>
+      <c r="D298" t="s">
+        <v>849</v>
+      </c>
+      <c r="E298" t="s">
+        <v>102</v>
+      </c>
+      <c r="F298" t="s">
+        <v>1918</v>
+      </c>
+      <c r="G298" t="s">
+        <v>1825</v>
+      </c>
+      <c r="H298" t="s">
+        <v>1931</v>
+      </c>
+      <c r="I298" t="s">
+        <v>1932</v>
+      </c>
+      <c r="J298" t="s">
+        <v>1933</v>
+      </c>
+      <c r="K298" t="s">
+        <v>1381</v>
+      </c>
+      <c r="L298" t="s">
+        <v>121</v>
+      </c>
+      <c r="M298" t="s">
+        <v>774</v>
+      </c>
+      <c r="N298" t="s">
+        <v>449</v>
+      </c>
+      <c r="O298" t="s">
+        <v>201</v>
+      </c>
+      <c r="P298" t="s">
+        <v>1934</v>
+      </c>
+      <c r="Q298" t="s">
+        <v>488</v>
+      </c>
+      <c r="R298" t="s">
+        <v>113</v>
+      </c>
+      <c r="S298" t="s">
+        <v>39</v>
+      </c>
+      <c r="T298" t="s">
+        <v>66</v>
+      </c>
+      <c r="U298" t="s">
+        <v>41</v>
+      </c>
+      <c r="V298">
+        <v>70</v>
+      </c>
+      <c r="W298">
+        <v>29</v>
+      </c>
+      <c r="X298">
+        <v>65</v>
+      </c>
+      <c r="Y298">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="299" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>202</v>
+      </c>
+      <c r="B299" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C299" t="s">
+        <v>203</v>
+      </c>
+      <c r="D299" t="s">
+        <v>849</v>
+      </c>
+      <c r="E299" t="s">
+        <v>347</v>
+      </c>
+      <c r="F299" t="s">
+        <v>1918</v>
+      </c>
+      <c r="G299" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H299" t="s">
+        <v>1935</v>
+      </c>
+      <c r="I299" t="s">
+        <v>1936</v>
+      </c>
+      <c r="J299" t="s">
+        <v>1937</v>
+      </c>
+      <c r="K299" t="s">
+        <v>1938</v>
+      </c>
+      <c r="L299" t="s">
+        <v>689</v>
+      </c>
+      <c r="M299" t="s">
+        <v>794</v>
+      </c>
+      <c r="N299" t="s">
+        <v>40</v>
+      </c>
+      <c r="O299" t="s">
+        <v>201</v>
+      </c>
+      <c r="P299" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q299" t="s">
+        <v>201</v>
+      </c>
+      <c r="R299" t="s">
+        <v>40</v>
+      </c>
+      <c r="S299" t="s">
+        <v>41</v>
+      </c>
+      <c r="T299" t="s">
+        <v>38</v>
+      </c>
+      <c r="U299" t="s">
+        <v>41</v>
+      </c>
+      <c r="V299">
+        <v>41</v>
+      </c>
+      <c r="W299">
+        <v>16</v>
+      </c>
+      <c r="X299">
+        <v>39</v>
+      </c>
+      <c r="Y299">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="300" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>202</v>
+      </c>
+      <c r="B300" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C300" t="s">
+        <v>203</v>
+      </c>
+      <c r="D300" t="s">
+        <v>849</v>
+      </c>
+      <c r="E300" t="s">
+        <v>895</v>
+      </c>
+      <c r="F300" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G300" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H300" t="s">
+        <v>1939</v>
+      </c>
+      <c r="I300" t="s">
+        <v>1940</v>
+      </c>
+      <c r="J300" t="s">
+        <v>517</v>
+      </c>
+      <c r="K300" t="s">
+        <v>1941</v>
+      </c>
+      <c r="L300" t="s">
+        <v>1444</v>
+      </c>
+      <c r="M300" t="s">
+        <v>549</v>
+      </c>
+      <c r="N300" t="s">
+        <v>66</v>
+      </c>
+      <c r="O300" t="s">
+        <v>41</v>
+      </c>
+      <c r="P300" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Q300" t="s">
+        <v>433</v>
+      </c>
+      <c r="R300" t="s">
+        <v>38</v>
+      </c>
+      <c r="S300" t="s">
+        <v>41</v>
+      </c>
+      <c r="T300" t="s">
+        <v>38</v>
+      </c>
+      <c r="U300" t="s">
+        <v>41</v>
+      </c>
+      <c r="V300">
+        <v>42</v>
+      </c>
+      <c r="W300">
+        <v>21</v>
+      </c>
+      <c r="X300">
+        <v>36</v>
+      </c>
+      <c r="Y300">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="301" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>202</v>
+      </c>
+      <c r="B301" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C301" t="s">
+        <v>203</v>
+      </c>
+      <c r="D301" t="s">
+        <v>849</v>
+      </c>
+      <c r="E301" t="s">
+        <v>126</v>
+      </c>
+      <c r="F301" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G301" t="s">
+        <v>212</v>
+      </c>
+      <c r="H301" t="s">
+        <v>1942</v>
+      </c>
+      <c r="I301" t="s">
+        <v>1943</v>
+      </c>
+      <c r="J301" t="s">
+        <v>1944</v>
+      </c>
+      <c r="K301" t="s">
+        <v>1945</v>
+      </c>
+      <c r="L301" t="s">
+        <v>1157</v>
+      </c>
+      <c r="M301" t="s">
+        <v>153</v>
+      </c>
+      <c r="N301" t="s">
+        <v>488</v>
+      </c>
+      <c r="O301" t="s">
+        <v>41</v>
+      </c>
+      <c r="P301" t="s">
+        <v>969</v>
+      </c>
+      <c r="Q301" t="s">
+        <v>811</v>
+      </c>
+      <c r="R301" t="s">
+        <v>66</v>
+      </c>
+      <c r="S301" t="s">
+        <v>41</v>
+      </c>
+      <c r="T301" t="s">
+        <v>38</v>
+      </c>
+      <c r="U301" t="s">
+        <v>41</v>
+      </c>
+      <c r="V301">
+        <v>42</v>
+      </c>
+      <c r="W301">
+        <v>25</v>
+      </c>
+      <c r="X301">
+        <v>45</v>
+      </c>
+      <c r="Y301">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="302" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>202</v>
+      </c>
+      <c r="B302" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C302" t="s">
+        <v>203</v>
+      </c>
+      <c r="D302" t="s">
+        <v>849</v>
+      </c>
+      <c r="E302" t="s">
+        <v>346</v>
+      </c>
+      <c r="F302" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G302" t="s">
+        <v>663</v>
+      </c>
+      <c r="H302" t="s">
+        <v>1946</v>
+      </c>
+      <c r="I302" t="s">
+        <v>1947</v>
+      </c>
+      <c r="J302" t="s">
+        <v>1948</v>
+      </c>
+      <c r="K302" t="s">
+        <v>1949</v>
+      </c>
+      <c r="L302" t="s">
+        <v>1950</v>
+      </c>
+      <c r="M302" t="s">
+        <v>426</v>
+      </c>
+      <c r="N302" t="s">
+        <v>488</v>
+      </c>
+      <c r="O302" t="s">
+        <v>39</v>
+      </c>
+      <c r="P302" t="s">
+        <v>664</v>
+      </c>
+      <c r="Q302" t="s">
+        <v>1396</v>
+      </c>
+      <c r="R302" t="s">
+        <v>488</v>
+      </c>
+      <c r="S302" t="s">
+        <v>66</v>
+      </c>
+      <c r="T302" t="s">
+        <v>337</v>
+      </c>
+      <c r="U302" t="s">
+        <v>39</v>
+      </c>
+      <c r="V302">
+        <v>80</v>
+      </c>
+      <c r="W302">
+        <v>43</v>
+      </c>
+      <c r="X302">
+        <v>72</v>
+      </c>
+      <c r="Y302">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="303" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>202</v>
+      </c>
+      <c r="B303" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C303" t="s">
+        <v>203</v>
+      </c>
+      <c r="D303" t="s">
+        <v>849</v>
+      </c>
+      <c r="E303" t="s">
+        <v>147</v>
+      </c>
+      <c r="F303" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G303" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H303" t="s">
+        <v>1951</v>
+      </c>
+      <c r="I303" t="s">
+        <v>1952</v>
+      </c>
+      <c r="J303" t="s">
+        <v>1953</v>
+      </c>
+      <c r="K303" t="s">
+        <v>1954</v>
+      </c>
+      <c r="L303" t="s">
+        <v>251</v>
+      </c>
+      <c r="M303" t="s">
+        <v>891</v>
+      </c>
+      <c r="N303" t="s">
+        <v>113</v>
+      </c>
+      <c r="O303" t="s">
+        <v>201</v>
+      </c>
+      <c r="P303" t="s">
+        <v>1494</v>
+      </c>
+      <c r="Q303" t="s">
+        <v>455</v>
+      </c>
+      <c r="R303" t="s">
+        <v>40</v>
+      </c>
+      <c r="S303" t="s">
+        <v>39</v>
+      </c>
+      <c r="T303" t="s">
+        <v>38</v>
+      </c>
+      <c r="U303" t="s">
+        <v>41</v>
+      </c>
+      <c r="V303">
+        <v>42</v>
+      </c>
+      <c r="W303">
+        <v>19</v>
+      </c>
+      <c r="X303">
+        <v>29</v>
+      </c>
+      <c r="Y303">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="304" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>202</v>
+      </c>
+      <c r="B304" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C304" t="s">
+        <v>203</v>
+      </c>
+      <c r="D304" t="s">
+        <v>849</v>
+      </c>
+      <c r="E304" t="s">
+        <v>157</v>
+      </c>
+      <c r="F304" t="s">
+        <v>26</v>
+      </c>
+      <c r="G304" t="s">
+        <v>55</v>
+      </c>
+      <c r="H304" t="s">
+        <v>1955</v>
+      </c>
+      <c r="I304" t="s">
+        <v>1956</v>
+      </c>
+      <c r="J304" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K304" t="s">
+        <v>59</v>
+      </c>
+      <c r="L304" t="s">
+        <v>503</v>
+      </c>
+      <c r="M304" t="s">
+        <v>369</v>
+      </c>
+      <c r="N304" t="s">
+        <v>40</v>
+      </c>
+      <c r="O304" t="s">
+        <v>201</v>
+      </c>
+      <c r="P304" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q304" t="s">
+        <v>201</v>
+      </c>
+      <c r="R304" t="s">
+        <v>113</v>
+      </c>
+      <c r="S304" t="s">
+        <v>39</v>
+      </c>
+      <c r="T304" t="s">
+        <v>113</v>
+      </c>
+      <c r="U304" t="s">
+        <v>39</v>
+      </c>
+      <c r="V304">
+        <v>68</v>
+      </c>
+      <c r="W304">
+        <v>38</v>
+      </c>
+      <c r="X304">
+        <v>58</v>
+      </c>
+      <c r="Y304">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="305" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>202</v>
+      </c>
+      <c r="B305" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C305" t="s">
+        <v>203</v>
+      </c>
+      <c r="D305" t="s">
+        <v>849</v>
+      </c>
+      <c r="E305" t="s">
+        <v>933</v>
+      </c>
+      <c r="F305" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G305" t="s">
+        <v>694</v>
+      </c>
+      <c r="H305" t="s">
+        <v>1958</v>
+      </c>
+      <c r="I305" t="s">
+        <v>1959</v>
+      </c>
+      <c r="J305" t="s">
+        <v>1434</v>
+      </c>
+      <c r="K305" t="s">
+        <v>1960</v>
+      </c>
+      <c r="L305" t="s">
+        <v>1961</v>
+      </c>
+      <c r="M305" t="s">
+        <v>891</v>
+      </c>
+      <c r="N305" t="s">
+        <v>113</v>
+      </c>
+      <c r="O305" t="s">
+        <v>201</v>
+      </c>
+      <c r="P305" t="s">
+        <v>1319</v>
+      </c>
+      <c r="Q305" t="s">
+        <v>488</v>
+      </c>
+      <c r="R305" t="s">
+        <v>40</v>
+      </c>
+      <c r="S305" t="s">
+        <v>41</v>
+      </c>
+      <c r="T305" t="s">
+        <v>40</v>
+      </c>
+      <c r="U305" t="s">
+        <v>39</v>
+      </c>
+      <c r="V305">
+        <v>42</v>
+      </c>
+      <c r="W305">
+        <v>26</v>
+      </c>
+      <c r="X305">
+        <v>33</v>
+      </c>
+      <c r="Y305">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="306" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>202</v>
+      </c>
+      <c r="B306" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C306" t="s">
+        <v>203</v>
+      </c>
+      <c r="D306" t="s">
+        <v>849</v>
+      </c>
+      <c r="E306" t="s">
+        <v>191</v>
+      </c>
+      <c r="F306" t="s">
+        <v>1918</v>
+      </c>
+      <c r="G306" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H306" t="s">
+        <v>1962</v>
+      </c>
+      <c r="I306" t="s">
+        <v>1963</v>
+      </c>
+      <c r="J306" t="s">
+        <v>1964</v>
+      </c>
+      <c r="K306" t="s">
+        <v>1965</v>
+      </c>
+      <c r="L306" t="s">
+        <v>1966</v>
+      </c>
+      <c r="M306" t="s">
+        <v>766</v>
+      </c>
+      <c r="N306" t="s">
+        <v>113</v>
+      </c>
+      <c r="O306" t="s">
+        <v>41</v>
+      </c>
+      <c r="P306" t="s">
+        <v>1967</v>
+      </c>
+      <c r="Q306" t="s">
+        <v>433</v>
+      </c>
+      <c r="R306" t="s">
+        <v>35</v>
+      </c>
+      <c r="S306" t="s">
+        <v>38</v>
+      </c>
+      <c r="T306" t="s">
+        <v>40</v>
+      </c>
+      <c r="U306" t="s">
+        <v>39</v>
+      </c>
+      <c r="V306">
+        <v>48</v>
+      </c>
+      <c r="W306">
+        <v>31</v>
+      </c>
+      <c r="X306">
+        <v>51</v>
+      </c>
+      <c r="Y306">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="307" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B307" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C307" t="s">
+        <v>203</v>
+      </c>
+      <c r="D307" t="s">
+        <v>348</v>
+      </c>
+      <c r="E307" t="s">
+        <v>25</v>
+      </c>
+      <c r="F307" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G307" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H307" t="s">
+        <v>1969</v>
+      </c>
+      <c r="I307" t="s">
+        <v>1970</v>
+      </c>
+      <c r="J307" t="s">
+        <v>363</v>
+      </c>
+      <c r="K307" t="s">
+        <v>1971</v>
+      </c>
+      <c r="L307" t="s">
+        <v>33</v>
+      </c>
+      <c r="M307" t="s">
+        <v>1370</v>
+      </c>
+      <c r="N307" t="s">
+        <v>1560</v>
+      </c>
+      <c r="O307" t="s">
+        <v>213</v>
+      </c>
+      <c r="P307" t="s">
+        <v>1972</v>
+      </c>
+      <c r="Q307" t="s">
+        <v>1121</v>
+      </c>
+      <c r="R307" t="s">
+        <v>35</v>
+      </c>
+      <c r="S307" t="s">
+        <v>40</v>
+      </c>
+      <c r="T307" t="s">
+        <v>35</v>
+      </c>
+      <c r="U307" t="s">
+        <v>39</v>
+      </c>
+      <c r="V307">
+        <v>74</v>
+      </c>
+      <c r="W307">
+        <v>36</v>
+      </c>
+      <c r="X307">
+        <v>48</v>
+      </c>
+      <c r="Y307">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="308" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B308" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C308" t="s">
+        <v>203</v>
+      </c>
+      <c r="D308" t="s">
+        <v>348</v>
+      </c>
+      <c r="E308" t="s">
+        <v>54</v>
+      </c>
+      <c r="F308" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G308" t="s">
+        <v>66</v>
+      </c>
+      <c r="H308" t="s">
+        <v>201</v>
+      </c>
+      <c r="I308" t="s">
+        <v>198</v>
+      </c>
+      <c r="J308" t="s">
+        <v>1973</v>
+      </c>
+      <c r="K308" t="s">
+        <v>455</v>
+      </c>
+      <c r="L308" t="s">
+        <v>201</v>
+      </c>
+      <c r="M308" t="s">
+        <v>201</v>
+      </c>
+      <c r="N308" t="s">
+        <v>201</v>
+      </c>
+      <c r="O308" t="s">
+        <v>201</v>
+      </c>
+      <c r="P308" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q308" t="s">
+        <v>201</v>
+      </c>
+      <c r="R308" t="s">
+        <v>201</v>
+      </c>
+      <c r="S308" t="s">
+        <v>201</v>
+      </c>
+      <c r="T308" t="s">
+        <v>201</v>
+      </c>
+      <c r="U308" t="s">
+        <v>201</v>
+      </c>
+      <c r="V308">
+        <v>0</v>
+      </c>
+      <c r="W308">
+        <v>0</v>
+      </c>
+      <c r="X308">
+        <v>0</v>
+      </c>
+      <c r="Y308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B309" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C309" t="s">
+        <v>203</v>
+      </c>
+      <c r="D309" t="s">
+        <v>348</v>
+      </c>
+      <c r="E309" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F309" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G309" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H309" t="s">
+        <v>1975</v>
+      </c>
+      <c r="I309" t="s">
+        <v>1976</v>
+      </c>
+      <c r="J309" t="s">
+        <v>546</v>
+      </c>
+      <c r="K309" t="s">
+        <v>1977</v>
+      </c>
+      <c r="L309" t="s">
+        <v>293</v>
+      </c>
+      <c r="M309" t="s">
+        <v>293</v>
+      </c>
+      <c r="N309" t="s">
+        <v>38</v>
+      </c>
+      <c r="O309" t="s">
+        <v>201</v>
+      </c>
+      <c r="P309" t="s">
+        <v>1225</v>
+      </c>
+      <c r="Q309" t="s">
+        <v>488</v>
+      </c>
+      <c r="R309" t="s">
+        <v>39</v>
+      </c>
+      <c r="S309" t="s">
+        <v>41</v>
+      </c>
+      <c r="T309" t="s">
+        <v>39</v>
+      </c>
+      <c r="U309" t="s">
+        <v>41</v>
+      </c>
+      <c r="V309">
+        <v>13</v>
+      </c>
+      <c r="W309">
+        <v>11</v>
+      </c>
+      <c r="X309">
+        <v>13</v>
+      </c>
+      <c r="Y309">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="310" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B310" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C310" t="s">
+        <v>203</v>
+      </c>
+      <c r="D310" t="s">
+        <v>348</v>
+      </c>
+      <c r="E310" t="s">
+        <v>90</v>
+      </c>
+      <c r="F310" t="s">
+        <v>1978</v>
+      </c>
+      <c r="G310" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H310" t="s">
+        <v>1980</v>
+      </c>
+      <c r="I310" t="s">
+        <v>1981</v>
+      </c>
+      <c r="J310" t="s">
+        <v>1982</v>
+      </c>
+      <c r="K310" t="s">
+        <v>1983</v>
+      </c>
+      <c r="L310" t="s">
+        <v>1984</v>
+      </c>
+      <c r="M310" t="s">
+        <v>1175</v>
+      </c>
+      <c r="N310" t="s">
+        <v>34</v>
+      </c>
+      <c r="O310" t="s">
+        <v>66</v>
+      </c>
+      <c r="P310" t="s">
+        <v>1985</v>
+      </c>
+      <c r="Q310" t="s">
+        <v>505</v>
+      </c>
+      <c r="R310" t="s">
+        <v>113</v>
+      </c>
+      <c r="S310" t="s">
+        <v>38</v>
+      </c>
+      <c r="T310" t="s">
+        <v>113</v>
+      </c>
+      <c r="U310" t="s">
+        <v>41</v>
+      </c>
+      <c r="V310">
+        <v>77</v>
+      </c>
+      <c r="W310">
+        <v>36</v>
+      </c>
+      <c r="X310">
+        <v>62</v>
+      </c>
+      <c r="Y310">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="311" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B311" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C311" t="s">
+        <v>203</v>
+      </c>
+      <c r="D311" t="s">
+        <v>348</v>
+      </c>
+      <c r="E311" t="s">
+        <v>102</v>
+      </c>
+      <c r="F311" t="s">
+        <v>1986</v>
+      </c>
+      <c r="G311" t="s">
+        <v>1987</v>
+      </c>
+      <c r="H311" t="s">
+        <v>1988</v>
+      </c>
+      <c r="I311" t="s">
+        <v>1989</v>
+      </c>
+      <c r="J311" t="s">
+        <v>1902</v>
+      </c>
+      <c r="K311" t="s">
+        <v>1990</v>
+      </c>
+      <c r="L311" t="s">
+        <v>1991</v>
+      </c>
+      <c r="M311" t="s">
+        <v>975</v>
+      </c>
+      <c r="N311" t="s">
+        <v>1358</v>
+      </c>
+      <c r="O311" t="s">
+        <v>449</v>
+      </c>
+      <c r="P311" t="s">
+        <v>1992</v>
+      </c>
+      <c r="Q311" t="s">
+        <v>1993</v>
+      </c>
+      <c r="R311" t="s">
+        <v>35</v>
+      </c>
+      <c r="S311" t="s">
+        <v>40</v>
+      </c>
+      <c r="T311" t="s">
+        <v>66</v>
+      </c>
+      <c r="U311" t="s">
+        <v>41</v>
+      </c>
+      <c r="V311">
+        <v>71</v>
+      </c>
+      <c r="W311">
+        <v>28</v>
+      </c>
+      <c r="X311">
+        <v>57</v>
+      </c>
+      <c r="Y311">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="312" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A312" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B312" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C312" t="s">
+        <v>203</v>
+      </c>
+      <c r="D312" t="s">
+        <v>348</v>
+      </c>
+      <c r="E312" t="s">
+        <v>347</v>
+      </c>
+      <c r="F312" t="s">
+        <v>1994</v>
+      </c>
+      <c r="G312" t="s">
+        <v>607</v>
+      </c>
+      <c r="H312" t="s">
+        <v>1995</v>
+      </c>
+      <c r="I312" t="s">
+        <v>1996</v>
+      </c>
+      <c r="J312" t="s">
+        <v>1997</v>
+      </c>
+      <c r="K312" t="s">
+        <v>1998</v>
+      </c>
+      <c r="L312" t="s">
+        <v>1457</v>
+      </c>
+      <c r="M312" t="s">
+        <v>503</v>
+      </c>
+      <c r="N312" t="s">
+        <v>1309</v>
+      </c>
+      <c r="O312" t="s">
+        <v>471</v>
+      </c>
+      <c r="P312" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q312" t="s">
+        <v>1999</v>
+      </c>
+      <c r="R312" t="s">
+        <v>488</v>
+      </c>
+      <c r="S312" t="s">
+        <v>66</v>
+      </c>
+      <c r="T312" t="s">
+        <v>280</v>
+      </c>
+      <c r="U312" t="s">
+        <v>39</v>
+      </c>
+      <c r="V312">
+        <v>71</v>
+      </c>
+      <c r="W312">
+        <v>41</v>
+      </c>
+      <c r="X312">
+        <v>43</v>
+      </c>
+      <c r="Y312">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="313" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A313" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B313" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C313" t="s">
+        <v>203</v>
+      </c>
+      <c r="D313" t="s">
+        <v>348</v>
+      </c>
+      <c r="E313" t="s">
+        <v>895</v>
+      </c>
+      <c r="F313" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G313" t="s">
+        <v>2000</v>
+      </c>
+      <c r="H313" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I313" t="s">
+        <v>2002</v>
+      </c>
+      <c r="J313" t="s">
+        <v>2003</v>
+      </c>
+      <c r="K313" t="s">
+        <v>2004</v>
+      </c>
+      <c r="L313" t="s">
+        <v>788</v>
+      </c>
+      <c r="M313" t="s">
+        <v>251</v>
+      </c>
+      <c r="N313" t="s">
+        <v>919</v>
+      </c>
+      <c r="O313" t="s">
+        <v>672</v>
+      </c>
+      <c r="P313" t="s">
+        <v>2005</v>
+      </c>
+      <c r="Q313" t="s">
+        <v>2006</v>
+      </c>
+      <c r="R313" t="s">
+        <v>488</v>
+      </c>
+      <c r="S313" t="s">
+        <v>40</v>
+      </c>
+      <c r="T313" t="s">
+        <v>35</v>
+      </c>
+      <c r="U313" t="s">
+        <v>39</v>
+      </c>
+      <c r="V313">
+        <v>66</v>
+      </c>
+      <c r="W313">
+        <v>34</v>
+      </c>
+      <c r="X313">
+        <v>61</v>
+      </c>
+      <c r="Y313">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="314" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A314" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B314" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C314" t="s">
+        <v>203</v>
+      </c>
+      <c r="D314" t="s">
+        <v>348</v>
+      </c>
+      <c r="E314" t="s">
+        <v>126</v>
+      </c>
+      <c r="F314" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G314" t="s">
+        <v>2007</v>
+      </c>
+      <c r="H314" t="s">
+        <v>2008</v>
+      </c>
+      <c r="I314" t="s">
+        <v>2009</v>
+      </c>
+      <c r="J314" t="s">
+        <v>303</v>
+      </c>
+      <c r="K314" t="s">
+        <v>2010</v>
+      </c>
+      <c r="L314" t="s">
+        <v>132</v>
+      </c>
+      <c r="M314" t="s">
+        <v>2011</v>
+      </c>
+      <c r="N314" t="s">
+        <v>2012</v>
+      </c>
+      <c r="O314" t="s">
+        <v>1000</v>
+      </c>
+      <c r="P314" t="s">
+        <v>2013</v>
+      </c>
+      <c r="Q314" t="s">
+        <v>2014</v>
+      </c>
+      <c r="R314" t="s">
+        <v>35</v>
+      </c>
+      <c r="S314" t="s">
+        <v>38</v>
+      </c>
+      <c r="T314" t="s">
+        <v>66</v>
+      </c>
+      <c r="U314" t="s">
+        <v>41</v>
+      </c>
+      <c r="V314">
+        <v>46</v>
+      </c>
+      <c r="W314">
+        <v>27</v>
+      </c>
+      <c r="X314">
+        <v>47</v>
+      </c>
+      <c r="Y314">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="315" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A315" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B315" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C315" t="s">
+        <v>203</v>
+      </c>
+      <c r="D315" t="s">
+        <v>348</v>
+      </c>
+      <c r="E315" t="s">
+        <v>346</v>
+      </c>
+      <c r="F315" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G315" t="s">
+        <v>976</v>
+      </c>
+      <c r="H315" t="s">
+        <v>2015</v>
+      </c>
+      <c r="I315" t="s">
+        <v>2016</v>
+      </c>
+      <c r="J315" t="s">
+        <v>2017</v>
+      </c>
+      <c r="K315" t="s">
+        <v>2018</v>
+      </c>
+      <c r="L315" t="s">
+        <v>1062</v>
+      </c>
+      <c r="M315" t="s">
+        <v>192</v>
+      </c>
+      <c r="N315" t="s">
+        <v>1186</v>
+      </c>
+      <c r="O315" t="s">
+        <v>76</v>
+      </c>
+      <c r="P315" t="s">
+        <v>2019</v>
+      </c>
+      <c r="Q315" t="s">
+        <v>1376</v>
+      </c>
+      <c r="R315" t="s">
+        <v>449</v>
+      </c>
+      <c r="S315" t="s">
+        <v>40</v>
+      </c>
+      <c r="T315" t="s">
+        <v>337</v>
+      </c>
+      <c r="U315" t="s">
+        <v>39</v>
+      </c>
+      <c r="V315">
+        <v>65</v>
+      </c>
+      <c r="W315">
+        <v>40</v>
+      </c>
+      <c r="X315">
+        <v>67</v>
+      </c>
+      <c r="Y315">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="316" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A316" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B316" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C316" t="s">
+        <v>203</v>
+      </c>
+      <c r="D316" t="s">
+        <v>348</v>
+      </c>
+      <c r="E316" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F316" t="s">
+        <v>2020</v>
+      </c>
+      <c r="G316" t="s">
+        <v>2021</v>
+      </c>
+      <c r="H316" t="s">
+        <v>2022</v>
+      </c>
+      <c r="I316" t="s">
+        <v>2023</v>
+      </c>
+      <c r="J316" t="s">
+        <v>1906</v>
+      </c>
+      <c r="K316" t="s">
+        <v>2024</v>
+      </c>
+      <c r="L316" t="s">
+        <v>735</v>
+      </c>
+      <c r="M316" t="s">
+        <v>699</v>
+      </c>
+      <c r="N316" t="s">
+        <v>1691</v>
+      </c>
+      <c r="O316" t="s">
+        <v>110</v>
+      </c>
+      <c r="P316" t="s">
+        <v>2025</v>
+      </c>
+      <c r="Q316" t="s">
+        <v>1595</v>
+      </c>
+      <c r="R316" t="s">
+        <v>488</v>
+      </c>
+      <c r="S316" t="s">
+        <v>38</v>
+      </c>
+      <c r="T316" t="s">
+        <v>40</v>
+      </c>
+      <c r="U316" t="s">
+        <v>41</v>
+      </c>
+      <c r="V316">
+        <v>48</v>
+      </c>
+      <c r="W316">
+        <v>19</v>
+      </c>
+      <c r="X316">
+        <v>62</v>
+      </c>
+      <c r="Y316">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="317" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A317" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B317" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C317" t="s">
+        <v>203</v>
+      </c>
+      <c r="D317" t="s">
+        <v>348</v>
+      </c>
+      <c r="E317" t="s">
+        <v>157</v>
+      </c>
+      <c r="F317" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G317" t="s">
+        <v>829</v>
+      </c>
+      <c r="H317" t="s">
+        <v>2026</v>
+      </c>
+      <c r="I317" t="s">
+        <v>2027</v>
+      </c>
+      <c r="J317" t="s">
+        <v>2028</v>
+      </c>
+      <c r="K317" t="s">
+        <v>2029</v>
+      </c>
+      <c r="L317" t="s">
+        <v>2030</v>
+      </c>
+      <c r="M317" t="s">
+        <v>97</v>
+      </c>
+      <c r="N317" t="s">
+        <v>554</v>
+      </c>
+      <c r="O317" t="s">
+        <v>488</v>
+      </c>
+      <c r="P317" t="s">
+        <v>2031</v>
+      </c>
+      <c r="Q317" t="s">
+        <v>542</v>
+      </c>
+      <c r="R317" t="s">
+        <v>39</v>
+      </c>
+      <c r="S317" t="s">
+        <v>39</v>
+      </c>
+      <c r="T317" t="s">
+        <v>38</v>
+      </c>
+      <c r="U317" t="s">
+        <v>41</v>
+      </c>
+      <c r="V317">
+        <v>25</v>
+      </c>
+      <c r="W317">
+        <v>9</v>
+      </c>
+      <c r="X317">
+        <v>6</v>
+      </c>
+      <c r="Y317">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="318" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A318" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B318" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C318" t="s">
+        <v>203</v>
+      </c>
+      <c r="D318" t="s">
+        <v>348</v>
+      </c>
+      <c r="E318" t="s">
+        <v>933</v>
+      </c>
+      <c r="F318" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G318" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H318" t="s">
+        <v>2033</v>
+      </c>
+      <c r="I318" t="s">
+        <v>2034</v>
+      </c>
+      <c r="J318" t="s">
+        <v>646</v>
+      </c>
+      <c r="K318" t="s">
+        <v>2035</v>
+      </c>
+      <c r="L318" t="s">
+        <v>2036</v>
+      </c>
+      <c r="M318" t="s">
+        <v>270</v>
+      </c>
+      <c r="N318" t="s">
+        <v>919</v>
+      </c>
+      <c r="O318" t="s">
+        <v>554</v>
+      </c>
+      <c r="P318" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q318" t="s">
+        <v>1649</v>
+      </c>
+      <c r="R318" t="s">
+        <v>337</v>
+      </c>
+      <c r="S318" t="s">
+        <v>38</v>
+      </c>
+      <c r="T318" t="s">
+        <v>113</v>
+      </c>
+      <c r="U318" t="s">
+        <v>39</v>
+      </c>
+      <c r="V318">
+        <v>57</v>
+      </c>
+      <c r="W318">
+        <v>32</v>
+      </c>
+      <c r="X318">
+        <v>44</v>
+      </c>
+      <c r="Y318">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="319" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A319" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B319" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C319" t="s">
+        <v>203</v>
+      </c>
+      <c r="D319" t="s">
+        <v>348</v>
+      </c>
+      <c r="E319" t="s">
+        <v>191</v>
+      </c>
+      <c r="F319" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G319" t="s">
+        <v>2037</v>
+      </c>
+      <c r="H319" t="s">
+        <v>2038</v>
+      </c>
+      <c r="I319" t="s">
+        <v>2039</v>
+      </c>
+      <c r="J319" t="s">
+        <v>2040</v>
+      </c>
+      <c r="K319" t="s">
+        <v>2041</v>
+      </c>
+      <c r="L319" t="s">
+        <v>521</v>
+      </c>
+      <c r="M319" t="s">
+        <v>982</v>
+      </c>
+      <c r="N319" t="s">
+        <v>165</v>
+      </c>
+      <c r="O319" t="s">
+        <v>188</v>
+      </c>
+      <c r="P319" t="s">
+        <v>2042</v>
+      </c>
+      <c r="Q319" t="s">
+        <v>2043</v>
+      </c>
+      <c r="R319" t="s">
+        <v>38</v>
+      </c>
+      <c r="S319" t="s">
+        <v>41</v>
+      </c>
+      <c r="T319" t="s">
+        <v>66</v>
+      </c>
+      <c r="U319" t="s">
+        <v>41</v>
+      </c>
+      <c r="V319">
+        <v>61</v>
+      </c>
+      <c r="W319">
+        <v>17</v>
+      </c>
+      <c r="X319">
+        <v>26</v>
+      </c>
+      <c r="Y319">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="320" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A320" t="s">
+        <v>202</v>
+      </c>
+      <c r="B320" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C320" t="s">
+        <v>203</v>
+      </c>
+      <c r="E320" t="s">
+        <v>54</v>
+      </c>
+      <c r="F320" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G320" t="s">
+        <v>525</v>
+      </c>
+      <c r="H320" t="s">
+        <v>2046</v>
+      </c>
+      <c r="I320" t="s">
+        <v>2047</v>
+      </c>
+      <c r="J320" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K320" t="s">
+        <v>2048</v>
+      </c>
+      <c r="L320" t="s">
+        <v>1966</v>
+      </c>
+      <c r="M320" t="s">
+        <v>27</v>
+      </c>
+      <c r="N320" t="s">
+        <v>177</v>
+      </c>
+      <c r="O320" t="s">
+        <v>66</v>
+      </c>
+      <c r="P320" t="s">
+        <v>1266</v>
+      </c>
+      <c r="Q320" t="s">
+        <v>446</v>
+      </c>
+      <c r="R320" t="s">
+        <v>35</v>
+      </c>
+      <c r="S320" t="s">
+        <v>38</v>
+      </c>
+      <c r="T320" t="s">
+        <v>66</v>
+      </c>
+      <c r="U320" t="s">
+        <v>39</v>
+      </c>
+      <c r="V320">
+        <v>62</v>
+      </c>
+      <c r="W320">
+        <v>43</v>
+      </c>
+      <c r="X320">
+        <v>61</v>
+      </c>
+      <c r="Y320">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="321" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A321" t="s">
+        <v>202</v>
+      </c>
+      <c r="B321" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C321" t="s">
+        <v>203</v>
+      </c>
+      <c r="E321" t="s">
+        <v>102</v>
+      </c>
+      <c r="F321" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G321" t="s">
+        <v>787</v>
+      </c>
+      <c r="H321" t="s">
+        <v>2049</v>
+      </c>
+      <c r="I321" t="s">
+        <v>2050</v>
+      </c>
+      <c r="J321" t="s">
+        <v>2051</v>
+      </c>
+      <c r="K321" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L321" t="s">
+        <v>86</v>
+      </c>
+      <c r="M321" t="s">
+        <v>74</v>
+      </c>
+      <c r="N321" t="s">
+        <v>188</v>
+      </c>
+      <c r="O321" t="s">
+        <v>35</v>
+      </c>
+      <c r="P321" t="s">
+        <v>1262</v>
+      </c>
+      <c r="Q321" t="s">
+        <v>292</v>
+      </c>
+      <c r="R321" t="s">
+        <v>66</v>
+      </c>
+      <c r="S321" t="s">
+        <v>39</v>
+      </c>
+      <c r="T321" t="s">
+        <v>113</v>
+      </c>
+      <c r="U321" t="s">
+        <v>41</v>
+      </c>
+      <c r="V321">
+        <v>76</v>
+      </c>
+      <c r="W321">
+        <v>40</v>
+      </c>
+      <c r="X321">
+        <v>49</v>
+      </c>
+      <c r="Y321">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="322" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A322" t="s">
+        <v>202</v>
+      </c>
+      <c r="B322" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C322" t="s">
+        <v>203</v>
+      </c>
+      <c r="E322" t="s">
+        <v>895</v>
+      </c>
+      <c r="F322" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G322" t="s">
+        <v>2054</v>
+      </c>
+      <c r="H322" t="s">
+        <v>2055</v>
+      </c>
+      <c r="I322" t="s">
+        <v>2056</v>
+      </c>
+      <c r="J322" t="s">
+        <v>2057</v>
+      </c>
+      <c r="K322" t="s">
+        <v>2058</v>
+      </c>
+      <c r="L322" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M322" t="s">
+        <v>478</v>
+      </c>
+      <c r="N322" t="s">
+        <v>66</v>
+      </c>
+      <c r="O322" t="s">
+        <v>39</v>
+      </c>
+      <c r="P322" t="s">
+        <v>1714</v>
+      </c>
+      <c r="Q322" t="s">
+        <v>1335</v>
+      </c>
+      <c r="R322" t="s">
+        <v>39</v>
+      </c>
+      <c r="S322" t="s">
+        <v>41</v>
+      </c>
+      <c r="T322" t="s">
+        <v>39</v>
+      </c>
+      <c r="U322" t="s">
+        <v>201</v>
+      </c>
+      <c r="V322">
+        <v>28</v>
+      </c>
+      <c r="W322">
+        <v>7</v>
+      </c>
+      <c r="X322">
+        <v>14</v>
+      </c>
+      <c r="Y322">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="323" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A323" t="s">
+        <v>202</v>
+      </c>
+      <c r="B323" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C323" t="s">
+        <v>203</v>
+      </c>
+      <c r="E323" t="s">
+        <v>114</v>
+      </c>
+      <c r="F323" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G323" t="s">
+        <v>133</v>
+      </c>
+      <c r="H323" t="s">
+        <v>2059</v>
+      </c>
+      <c r="I323" t="s">
+        <v>2060</v>
+      </c>
+      <c r="J323" t="s">
+        <v>2061</v>
+      </c>
+      <c r="K323" t="s">
+        <v>2062</v>
+      </c>
+      <c r="L323" t="s">
+        <v>252</v>
+      </c>
+      <c r="M323" t="s">
+        <v>1417</v>
+      </c>
+      <c r="N323" t="s">
+        <v>35</v>
+      </c>
+      <c r="O323" t="s">
+        <v>38</v>
+      </c>
+      <c r="P323" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q323" t="s">
+        <v>413</v>
+      </c>
+      <c r="R323" t="s">
+        <v>39</v>
+      </c>
+      <c r="S323" t="s">
+        <v>41</v>
+      </c>
+      <c r="T323" t="s">
+        <v>40</v>
+      </c>
+      <c r="U323" t="s">
+        <v>41</v>
+      </c>
+      <c r="V323">
+        <v>37</v>
+      </c>
+      <c r="W323">
+        <v>19</v>
+      </c>
+      <c r="X323">
+        <v>20</v>
+      </c>
+      <c r="Y323">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="324" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A324" t="s">
+        <v>202</v>
+      </c>
+      <c r="B324" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C324" t="s">
+        <v>203</v>
+      </c>
+      <c r="E324" t="s">
+        <v>126</v>
+      </c>
+      <c r="F324" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G324" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H324" t="s">
+        <v>2063</v>
+      </c>
+      <c r="I324" t="s">
+        <v>2064</v>
+      </c>
+      <c r="J324" t="s">
+        <v>2065</v>
+      </c>
+      <c r="K324" t="s">
+        <v>1939</v>
+      </c>
+      <c r="L324" t="s">
+        <v>866</v>
+      </c>
+      <c r="M324" t="s">
+        <v>1375</v>
+      </c>
+      <c r="N324" t="s">
+        <v>488</v>
+      </c>
+      <c r="O324" t="s">
+        <v>39</v>
+      </c>
+      <c r="P324" t="s">
+        <v>1185</v>
+      </c>
+      <c r="Q324" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R324" t="s">
+        <v>66</v>
+      </c>
+      <c r="S324" t="s">
+        <v>39</v>
+      </c>
+      <c r="T324" t="s">
+        <v>40</v>
+      </c>
+      <c r="U324" t="s">
+        <v>41</v>
+      </c>
+      <c r="V324">
+        <v>57</v>
+      </c>
+      <c r="W324">
+        <v>25</v>
+      </c>
+      <c r="X324">
+        <v>45</v>
+      </c>
+      <c r="Y324">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="325" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A325" t="s">
+        <v>202</v>
+      </c>
+      <c r="B325" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C325" t="s">
+        <v>203</v>
+      </c>
+      <c r="E325" t="s">
+        <v>346</v>
+      </c>
+      <c r="F325" t="s">
+        <v>2066</v>
+      </c>
+      <c r="G325" t="s">
+        <v>866</v>
+      </c>
+      <c r="H325" t="s">
+        <v>2067</v>
+      </c>
+      <c r="I325" t="s">
+        <v>2068</v>
+      </c>
+      <c r="J325" t="s">
+        <v>2069</v>
+      </c>
+      <c r="K325" t="s">
+        <v>2070</v>
+      </c>
+      <c r="L325" t="s">
+        <v>1609</v>
+      </c>
+      <c r="M325" t="s">
+        <v>742</v>
+      </c>
+      <c r="N325" t="s">
+        <v>177</v>
+      </c>
+      <c r="O325" t="s">
+        <v>40</v>
+      </c>
+      <c r="P325" t="s">
+        <v>2071</v>
+      </c>
+      <c r="Q325" t="s">
+        <v>1225</v>
+      </c>
+      <c r="R325" t="s">
+        <v>337</v>
+      </c>
+      <c r="S325" t="s">
+        <v>38</v>
+      </c>
+      <c r="T325" t="s">
+        <v>113</v>
+      </c>
+      <c r="U325" t="s">
+        <v>39</v>
+      </c>
+      <c r="V325">
+        <v>80</v>
+      </c>
+      <c r="W325">
+        <v>34</v>
+      </c>
+      <c r="X325">
+        <v>70</v>
+      </c>
+      <c r="Y325">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="326" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A326" t="s">
+        <v>202</v>
+      </c>
+      <c r="B326" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C326" t="s">
+        <v>203</v>
+      </c>
+      <c r="E326" t="s">
+        <v>137</v>
+      </c>
+      <c r="F326" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G326" t="s">
+        <v>622</v>
+      </c>
+      <c r="H326" t="s">
+        <v>2072</v>
+      </c>
+      <c r="I326" t="s">
+        <v>2073</v>
+      </c>
+      <c r="J326" t="s">
+        <v>2074</v>
+      </c>
+      <c r="K326" t="s">
+        <v>2075</v>
+      </c>
+      <c r="L326" t="s">
+        <v>867</v>
+      </c>
+      <c r="M326" t="s">
+        <v>289</v>
+      </c>
+      <c r="N326" t="s">
+        <v>63</v>
+      </c>
+      <c r="O326" t="s">
+        <v>99</v>
+      </c>
+      <c r="P326" t="s">
+        <v>2076</v>
+      </c>
+      <c r="Q326" t="s">
+        <v>496</v>
+      </c>
+      <c r="R326" t="s">
+        <v>35</v>
+      </c>
+      <c r="S326" t="s">
+        <v>40</v>
+      </c>
+      <c r="T326" t="s">
+        <v>66</v>
+      </c>
+      <c r="U326" t="s">
+        <v>41</v>
+      </c>
+      <c r="V326">
+        <v>76</v>
+      </c>
+      <c r="W326">
+        <v>30</v>
+      </c>
+      <c r="X326">
+        <v>52</v>
+      </c>
+      <c r="Y326">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="327" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A327" t="s">
+        <v>202</v>
+      </c>
+      <c r="B327" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C327" t="s">
+        <v>203</v>
+      </c>
+      <c r="E327" t="s">
+        <v>147</v>
+      </c>
+      <c r="F327" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G327" t="s">
+        <v>2077</v>
+      </c>
+      <c r="H327" t="s">
+        <v>2078</v>
+      </c>
+      <c r="I327" t="s">
+        <v>2079</v>
+      </c>
+      <c r="J327" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K327" t="s">
+        <v>2080</v>
+      </c>
+      <c r="L327" t="s">
+        <v>2081</v>
+      </c>
+      <c r="M327" t="s">
+        <v>622</v>
+      </c>
+      <c r="N327" t="s">
+        <v>76</v>
+      </c>
+      <c r="O327" t="s">
+        <v>280</v>
+      </c>
+      <c r="P327" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q327" t="s">
+        <v>1668</v>
+      </c>
+      <c r="R327" t="s">
+        <v>449</v>
+      </c>
+      <c r="S327" t="s">
+        <v>35</v>
+      </c>
+      <c r="T327" t="s">
+        <v>280</v>
+      </c>
+      <c r="U327" t="s">
+        <v>40</v>
+      </c>
+      <c r="V327">
+        <v>95</v>
+      </c>
+      <c r="W327">
+        <v>71</v>
+      </c>
+      <c r="X327">
+        <v>90</v>
+      </c>
+      <c r="Y327">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="328" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A328" t="s">
+        <v>202</v>
+      </c>
+      <c r="B328" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C328" t="s">
+        <v>203</v>
+      </c>
+      <c r="E328" t="s">
+        <v>157</v>
+      </c>
+      <c r="F328" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G328" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H328" t="s">
+        <v>2082</v>
+      </c>
+      <c r="I328" t="s">
+        <v>2083</v>
+      </c>
+      <c r="J328" t="s">
+        <v>711</v>
+      </c>
+      <c r="K328" t="s">
+        <v>2084</v>
+      </c>
+      <c r="L328" t="s">
+        <v>152</v>
+      </c>
+      <c r="M328" t="s">
+        <v>362</v>
+      </c>
+      <c r="N328" t="s">
+        <v>280</v>
+      </c>
+      <c r="O328" t="s">
+        <v>40</v>
+      </c>
+      <c r="P328" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Q328" t="s">
+        <v>640</v>
+      </c>
+      <c r="R328" t="s">
+        <v>66</v>
+      </c>
+      <c r="S328" t="s">
+        <v>38</v>
+      </c>
+      <c r="T328" t="s">
+        <v>113</v>
+      </c>
+      <c r="U328" t="s">
+        <v>39</v>
+      </c>
+      <c r="V328">
+        <v>67</v>
+      </c>
+      <c r="W328">
+        <v>32</v>
+      </c>
+      <c r="X328">
+        <v>33</v>
+      </c>
+      <c r="Y328">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="329" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A329" t="s">
+        <v>202</v>
+      </c>
+      <c r="B329" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C329" t="s">
+        <v>203</v>
+      </c>
+      <c r="E329" t="s">
+        <v>180</v>
+      </c>
+      <c r="F329" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G329" t="s">
+        <v>61</v>
+      </c>
+      <c r="H329" t="s">
+        <v>2086</v>
+      </c>
+      <c r="I329" t="s">
+        <v>2087</v>
+      </c>
+      <c r="J329" t="s">
+        <v>2088</v>
+      </c>
+      <c r="K329" t="s">
+        <v>2089</v>
+      </c>
+      <c r="L329" t="s">
+        <v>2090</v>
+      </c>
+      <c r="M329" t="s">
+        <v>2091</v>
+      </c>
+      <c r="N329" t="s">
+        <v>213</v>
+      </c>
+      <c r="O329" t="s">
+        <v>51</v>
+      </c>
+      <c r="P329" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q329" t="s">
+        <v>1185</v>
+      </c>
+      <c r="R329" t="s">
+        <v>555</v>
+      </c>
+      <c r="S329" t="s">
+        <v>35</v>
+      </c>
+      <c r="T329" t="s">
+        <v>280</v>
+      </c>
+      <c r="U329" t="s">
+        <v>113</v>
+      </c>
+      <c r="V329">
+        <v>82</v>
+      </c>
+      <c r="W329">
+        <v>82</v>
+      </c>
+      <c r="X329">
+        <v>100</v>
+      </c>
+      <c r="Y329">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="330" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A330" t="s">
+        <v>202</v>
+      </c>
+      <c r="B330" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C330" t="s">
+        <v>203</v>
+      </c>
+      <c r="E330" t="s">
+        <v>191</v>
+      </c>
+      <c r="F330" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G330" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H330" t="s">
+        <v>2092</v>
+      </c>
+      <c r="I330" t="s">
+        <v>2093</v>
+      </c>
+      <c r="J330" t="s">
+        <v>2094</v>
+      </c>
+      <c r="K330" t="s">
+        <v>2095</v>
+      </c>
+      <c r="L330" t="s">
+        <v>1210</v>
+      </c>
+      <c r="M330" t="s">
+        <v>603</v>
+      </c>
+      <c r="N330" t="s">
+        <v>280</v>
+      </c>
+      <c r="O330" t="s">
+        <v>41</v>
+      </c>
+      <c r="P330" t="s">
+        <v>2096</v>
+      </c>
+      <c r="Q330" t="s">
+        <v>773</v>
+      </c>
+      <c r="R330" t="s">
+        <v>38</v>
+      </c>
+      <c r="S330" t="s">
+        <v>41</v>
+      </c>
+      <c r="T330" t="s">
+        <v>38</v>
+      </c>
+      <c r="U330" t="s">
+        <v>41</v>
+      </c>
+      <c r="V330">
+        <v>39</v>
+      </c>
+      <c r="W330">
+        <v>13</v>
+      </c>
+      <c r="X330">
+        <v>20</v>
+      </c>
+      <c r="Y330">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="331" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A331" t="s">
+        <v>202</v>
+      </c>
+      <c r="B331" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C331" t="s">
+        <v>203</v>
+      </c>
+      <c r="D331" t="s">
+        <v>204</v>
+      </c>
+      <c r="E331" t="s">
+        <v>42</v>
+      </c>
+      <c r="F331" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G331" t="s">
+        <v>2097</v>
+      </c>
+      <c r="H331" t="s">
+        <v>2098</v>
+      </c>
+      <c r="I331" t="s">
+        <v>2099</v>
+      </c>
+      <c r="J331" t="s">
+        <v>1425</v>
+      </c>
+      <c r="K331" t="s">
+        <v>2100</v>
+      </c>
+      <c r="L331" t="s">
+        <v>477</v>
+      </c>
+      <c r="M331" t="s">
+        <v>235</v>
+      </c>
+      <c r="N331" t="s">
+        <v>113</v>
+      </c>
+      <c r="O331" t="s">
+        <v>201</v>
+      </c>
+      <c r="P331" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q331" t="s">
+        <v>471</v>
+      </c>
+      <c r="R331" t="s">
+        <v>41</v>
+      </c>
+      <c r="S331" t="s">
+        <v>41</v>
+      </c>
+      <c r="T331" t="s">
+        <v>41</v>
+      </c>
+      <c r="U331" t="s">
+        <v>201</v>
+      </c>
+      <c r="V331">
+        <v>12</v>
+      </c>
+      <c r="W331">
+        <v>6</v>
+      </c>
+      <c r="X331">
+        <v>7</v>
+      </c>
+      <c r="Y331">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="332" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A332" t="s">
+        <v>202</v>
+      </c>
+      <c r="B332" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C332" t="s">
+        <v>203</v>
+      </c>
+      <c r="D332" t="s">
+        <v>204</v>
+      </c>
+      <c r="E332" t="s">
+        <v>54</v>
+      </c>
+      <c r="F332" t="s">
+        <v>2101</v>
+      </c>
+      <c r="G332" t="s">
+        <v>152</v>
+      </c>
+      <c r="H332" t="s">
+        <v>2102</v>
+      </c>
+      <c r="I332" t="s">
+        <v>2103</v>
+      </c>
+      <c r="J332" t="s">
+        <v>2104</v>
+      </c>
+      <c r="K332" t="s">
+        <v>2105</v>
+      </c>
+      <c r="L332" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M332" t="s">
+        <v>1703</v>
+      </c>
+      <c r="N332" t="s">
+        <v>455</v>
+      </c>
+      <c r="O332" t="s">
+        <v>51</v>
+      </c>
+      <c r="P332" t="s">
+        <v>1669</v>
+      </c>
+      <c r="Q332" t="s">
+        <v>1280</v>
+      </c>
+      <c r="R332" t="s">
+        <v>337</v>
+      </c>
+      <c r="S332" t="s">
+        <v>38</v>
+      </c>
+      <c r="T332" t="s">
+        <v>66</v>
+      </c>
+      <c r="U332" t="s">
+        <v>41</v>
+      </c>
+      <c r="V332">
+        <v>52</v>
+      </c>
+      <c r="W332">
+        <v>19</v>
+      </c>
+      <c r="X332">
+        <v>43</v>
+      </c>
+      <c r="Y332">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="333" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A333" t="s">
+        <v>202</v>
+      </c>
+      <c r="B333" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C333" t="s">
+        <v>203</v>
+      </c>
+      <c r="D333" t="s">
+        <v>204</v>
+      </c>
+      <c r="E333" t="s">
+        <v>90</v>
+      </c>
+      <c r="F333" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G333" t="s">
+        <v>2106</v>
+      </c>
+      <c r="H333" t="s">
+        <v>2107</v>
+      </c>
+      <c r="I333" t="s">
+        <v>2108</v>
+      </c>
+      <c r="J333" t="s">
+        <v>2109</v>
+      </c>
+      <c r="K333" t="s">
+        <v>2110</v>
+      </c>
+      <c r="L333" t="s">
+        <v>2111</v>
+      </c>
+      <c r="M333" t="s">
+        <v>823</v>
+      </c>
+      <c r="N333" t="s">
+        <v>604</v>
+      </c>
+      <c r="O333" t="s">
+        <v>38</v>
+      </c>
+      <c r="P333" t="s">
+        <v>2112</v>
+      </c>
+      <c r="Q333" t="s">
+        <v>2113</v>
+      </c>
+      <c r="R333" t="s">
+        <v>40</v>
+      </c>
+      <c r="S333" t="s">
+        <v>39</v>
+      </c>
+      <c r="T333" t="s">
+        <v>40</v>
+      </c>
+      <c r="U333" t="s">
+        <v>41</v>
+      </c>
+      <c r="V333">
+        <v>48</v>
+      </c>
+      <c r="W333">
+        <v>21</v>
+      </c>
+      <c r="X333">
+        <v>42</v>
+      </c>
+      <c r="Y333">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="334" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A334" t="s">
+        <v>202</v>
+      </c>
+      <c r="B334" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C334" t="s">
+        <v>203</v>
+      </c>
+      <c r="D334" t="s">
+        <v>204</v>
+      </c>
+      <c r="E334" t="s">
+        <v>102</v>
+      </c>
+      <c r="F334" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G334" t="s">
+        <v>2114</v>
+      </c>
+      <c r="H334" t="s">
+        <v>2115</v>
+      </c>
+      <c r="I334" t="s">
+        <v>2116</v>
+      </c>
+      <c r="J334" t="s">
+        <v>1571</v>
+      </c>
+      <c r="K334" t="s">
+        <v>2117</v>
+      </c>
+      <c r="L334" t="s">
+        <v>80</v>
+      </c>
+      <c r="M334" t="s">
+        <v>261</v>
+      </c>
+      <c r="N334" t="s">
+        <v>2118</v>
+      </c>
+      <c r="O334" t="s">
+        <v>188</v>
+      </c>
+      <c r="P334" t="s">
+        <v>2119</v>
+      </c>
+      <c r="Q334" t="s">
+        <v>1798</v>
+      </c>
+      <c r="R334" t="s">
+        <v>35</v>
+      </c>
+      <c r="S334" t="s">
+        <v>39</v>
+      </c>
+      <c r="T334" t="s">
+        <v>66</v>
+      </c>
+      <c r="U334" t="s">
+        <v>41</v>
+      </c>
+      <c r="V334">
+        <v>53</v>
+      </c>
+      <c r="W334">
+        <v>20</v>
+      </c>
+      <c r="X334">
+        <v>45</v>
+      </c>
+      <c r="Y334">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="335" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A335" t="s">
+        <v>202</v>
+      </c>
+      <c r="B335" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C335" t="s">
+        <v>203</v>
+      </c>
+      <c r="D335" t="s">
+        <v>204</v>
+      </c>
+      <c r="E335" t="s">
+        <v>895</v>
+      </c>
+      <c r="F335" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G335" t="s">
+        <v>511</v>
+      </c>
+      <c r="H335" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I335" t="s">
+        <v>2121</v>
+      </c>
+      <c r="J335" t="s">
+        <v>2122</v>
+      </c>
+      <c r="K335" t="s">
+        <v>596</v>
+      </c>
+      <c r="L335" t="s">
+        <v>446</v>
+      </c>
+      <c r="M335" t="s">
+        <v>108</v>
+      </c>
+      <c r="N335" t="s">
+        <v>471</v>
+      </c>
+      <c r="O335" t="s">
+        <v>337</v>
+      </c>
+      <c r="P335" t="s">
+        <v>2123</v>
+      </c>
+      <c r="Q335" t="s">
+        <v>1304</v>
+      </c>
+      <c r="R335" t="s">
+        <v>40</v>
+      </c>
+      <c r="S335" t="s">
+        <v>39</v>
+      </c>
+      <c r="T335" t="s">
+        <v>66</v>
+      </c>
+      <c r="U335" t="s">
+        <v>41</v>
+      </c>
+      <c r="V335">
+        <v>45</v>
+      </c>
+      <c r="W335">
+        <v>24</v>
+      </c>
+      <c r="X335">
+        <v>25</v>
+      </c>
+      <c r="Y335">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="336" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A336" t="s">
+        <v>202</v>
+      </c>
+      <c r="B336" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C336" t="s">
+        <v>203</v>
+      </c>
+      <c r="D336" t="s">
+        <v>204</v>
+      </c>
+      <c r="E336" t="s">
+        <v>126</v>
+      </c>
+      <c r="F336" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G336" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H336" t="s">
+        <v>2124</v>
+      </c>
+      <c r="I336" t="s">
+        <v>2125</v>
+      </c>
+      <c r="J336" t="s">
+        <v>1558</v>
+      </c>
+      <c r="K336" t="s">
+        <v>2126</v>
+      </c>
+      <c r="L336" t="s">
+        <v>989</v>
+      </c>
+      <c r="M336" t="s">
+        <v>1825</v>
+      </c>
+      <c r="N336" t="s">
+        <v>902</v>
+      </c>
+      <c r="O336" t="s">
+        <v>555</v>
+      </c>
+      <c r="P336" t="s">
+        <v>2127</v>
+      </c>
+      <c r="Q336" t="s">
+        <v>1934</v>
+      </c>
+      <c r="R336" t="s">
+        <v>66</v>
+      </c>
+      <c r="S336" t="s">
+        <v>39</v>
+      </c>
+      <c r="T336" t="s">
+        <v>38</v>
+      </c>
+      <c r="U336" t="s">
+        <v>41</v>
+      </c>
+      <c r="V336">
+        <v>31</v>
+      </c>
+      <c r="W336">
+        <v>16</v>
+      </c>
+      <c r="X336">
+        <v>38</v>
+      </c>
+      <c r="Y336">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="337" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>202</v>
+      </c>
+      <c r="B337" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C337" t="s">
+        <v>203</v>
+      </c>
+      <c r="D337" t="s">
+        <v>204</v>
+      </c>
+      <c r="E337" t="s">
+        <v>346</v>
+      </c>
+      <c r="F337" t="s">
+        <v>2101</v>
+      </c>
+      <c r="G337" t="s">
+        <v>355</v>
+      </c>
+      <c r="H337" t="s">
+        <v>2128</v>
+      </c>
+      <c r="I337" t="s">
+        <v>2129</v>
+      </c>
+      <c r="J337" t="s">
+        <v>1767</v>
+      </c>
+      <c r="K337" t="s">
+        <v>2130</v>
+      </c>
+      <c r="L337" t="s">
+        <v>505</v>
+      </c>
+      <c r="M337" t="s">
+        <v>503</v>
+      </c>
+      <c r="N337" t="s">
+        <v>641</v>
+      </c>
+      <c r="O337" t="s">
+        <v>488</v>
+      </c>
+      <c r="P337" t="s">
+        <v>2131</v>
+      </c>
+      <c r="Q337" t="s">
+        <v>572</v>
+      </c>
+      <c r="R337" t="s">
+        <v>488</v>
+      </c>
+      <c r="S337" t="s">
+        <v>40</v>
+      </c>
+      <c r="T337" t="s">
+        <v>113</v>
+      </c>
+      <c r="U337" t="s">
+        <v>41</v>
+      </c>
+      <c r="V337">
+        <v>68</v>
+      </c>
+      <c r="W337">
+        <v>24</v>
+      </c>
+      <c r="X337">
+        <v>72</v>
+      </c>
+      <c r="Y337">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="338" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>202</v>
+      </c>
+      <c r="B338" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C338" t="s">
+        <v>203</v>
+      </c>
+      <c r="D338" t="s">
+        <v>204</v>
+      </c>
+      <c r="E338" t="s">
+        <v>137</v>
+      </c>
+      <c r="F338" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G338" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H338" t="s">
+        <v>2132</v>
+      </c>
+      <c r="I338" t="s">
+        <v>2133</v>
+      </c>
+      <c r="J338" t="s">
+        <v>1072</v>
+      </c>
+      <c r="K338" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L338" t="s">
+        <v>1854</v>
+      </c>
+      <c r="M338" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N338" t="s">
+        <v>63</v>
+      </c>
+      <c r="O338" t="s">
+        <v>201</v>
+      </c>
+      <c r="P338" t="s">
+        <v>2135</v>
+      </c>
+      <c r="Q338" t="s">
+        <v>34</v>
+      </c>
+      <c r="R338" t="s">
+        <v>113</v>
+      </c>
+      <c r="S338" t="s">
+        <v>39</v>
+      </c>
+      <c r="T338" t="s">
+        <v>40</v>
+      </c>
+      <c r="U338" t="s">
+        <v>201</v>
+      </c>
+      <c r="V338">
+        <v>52</v>
+      </c>
+      <c r="W338">
+        <v>16</v>
+      </c>
+      <c r="X338">
+        <v>65</v>
+      </c>
+      <c r="Y338">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="339" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>202</v>
+      </c>
+      <c r="B339" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C339" t="s">
+        <v>203</v>
+      </c>
+      <c r="D339" t="s">
+        <v>204</v>
+      </c>
+      <c r="E339" t="s">
+        <v>147</v>
+      </c>
+      <c r="F339" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G339" t="s">
+        <v>891</v>
+      </c>
+      <c r="H339" t="s">
+        <v>2136</v>
+      </c>
+      <c r="I339" t="s">
+        <v>2137</v>
+      </c>
+      <c r="J339" t="s">
+        <v>30</v>
+      </c>
+      <c r="K339" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L339" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M339" t="s">
+        <v>1427</v>
+      </c>
+      <c r="N339" t="s">
+        <v>280</v>
+      </c>
+      <c r="O339" t="s">
+        <v>39</v>
+      </c>
+      <c r="P339" t="s">
+        <v>1603</v>
+      </c>
+      <c r="Q339" t="s">
+        <v>200</v>
+      </c>
+      <c r="R339" t="s">
+        <v>38</v>
+      </c>
+      <c r="S339" t="s">
+        <v>39</v>
+      </c>
+      <c r="T339" t="s">
+        <v>38</v>
+      </c>
+      <c r="U339" t="s">
+        <v>41</v>
+      </c>
+      <c r="V339">
+        <v>39</v>
+      </c>
+      <c r="W339">
+        <v>15</v>
+      </c>
+      <c r="X339">
+        <v>39</v>
+      </c>
+      <c r="Y339">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="340" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>202</v>
+      </c>
+      <c r="B340" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C340" t="s">
+        <v>203</v>
+      </c>
+      <c r="D340" t="s">
+        <v>204</v>
+      </c>
+      <c r="E340" t="s">
+        <v>157</v>
+      </c>
+      <c r="F340" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G340" t="s">
+        <v>867</v>
+      </c>
+      <c r="H340" t="s">
+        <v>2139</v>
+      </c>
+      <c r="I340" t="s">
+        <v>1885</v>
+      </c>
+      <c r="J340" t="s">
+        <v>2140</v>
+      </c>
+      <c r="K340" t="s">
+        <v>2141</v>
+      </c>
+      <c r="L340" t="s">
+        <v>365</v>
+      </c>
+      <c r="M340" t="s">
+        <v>55</v>
+      </c>
+      <c r="N340" t="s">
+        <v>483</v>
+      </c>
+      <c r="O340" t="s">
+        <v>177</v>
+      </c>
+      <c r="P340" t="s">
+        <v>2142</v>
+      </c>
+      <c r="Q340" t="s">
+        <v>2143</v>
+      </c>
+      <c r="R340" t="s">
+        <v>337</v>
+      </c>
+      <c r="S340" t="s">
+        <v>40</v>
+      </c>
+      <c r="T340" t="s">
+        <v>113</v>
+      </c>
+      <c r="U340" t="s">
+        <v>39</v>
+      </c>
+      <c r="V340">
+        <v>46</v>
+      </c>
+      <c r="W340">
+        <v>26</v>
+      </c>
+      <c r="X340">
+        <v>31</v>
+      </c>
+      <c r="Y340">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="341" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>202</v>
+      </c>
+      <c r="B341" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C341" t="s">
+        <v>203</v>
+      </c>
+      <c r="D341" t="s">
+        <v>204</v>
+      </c>
+      <c r="E341" t="s">
+        <v>933</v>
+      </c>
+      <c r="F341" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G341" t="s">
+        <v>212</v>
+      </c>
+      <c r="H341" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I341" t="s">
+        <v>2145</v>
+      </c>
+      <c r="J341" t="s">
+        <v>2146</v>
+      </c>
+      <c r="K341" t="s">
+        <v>2147</v>
+      </c>
+      <c r="L341" t="s">
+        <v>521</v>
+      </c>
+      <c r="M341" t="s">
+        <v>1427</v>
+      </c>
+      <c r="N341" t="s">
+        <v>280</v>
+      </c>
+      <c r="O341" t="s">
+        <v>113</v>
+      </c>
+      <c r="P341" t="s">
+        <v>2148</v>
+      </c>
+      <c r="Q341" t="s">
+        <v>674</v>
+      </c>
+      <c r="R341" t="s">
+        <v>39</v>
+      </c>
+      <c r="S341" t="s">
+        <v>41</v>
+      </c>
+      <c r="T341" t="s">
+        <v>38</v>
+      </c>
+      <c r="U341" t="s">
+        <v>201</v>
+      </c>
+      <c r="V341">
+        <v>30</v>
+      </c>
+      <c r="W341">
+        <v>12</v>
+      </c>
+      <c r="X341">
+        <v>10</v>
+      </c>
+      <c r="Y341">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="342" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>202</v>
+      </c>
+      <c r="B342" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C342" t="s">
+        <v>203</v>
+      </c>
+      <c r="D342" t="s">
+        <v>204</v>
+      </c>
+      <c r="E342" t="s">
+        <v>180</v>
+      </c>
+      <c r="F342" t="s">
+        <v>2101</v>
+      </c>
+      <c r="G342" t="s">
+        <v>2090</v>
+      </c>
+      <c r="H342" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I342" t="s">
+        <v>2150</v>
+      </c>
+      <c r="J342" t="s">
+        <v>58</v>
+      </c>
+      <c r="K342" t="s">
+        <v>2151</v>
+      </c>
+      <c r="L342" t="s">
+        <v>2152</v>
+      </c>
+      <c r="M342" t="s">
+        <v>1830</v>
+      </c>
+      <c r="N342" t="s">
+        <v>1309</v>
+      </c>
+      <c r="O342" t="s">
+        <v>213</v>
+      </c>
+      <c r="P342" t="s">
+        <v>2153</v>
+      </c>
+      <c r="Q342" t="s">
+        <v>2154</v>
+      </c>
+      <c r="R342" t="s">
+        <v>123</v>
+      </c>
+      <c r="S342" t="s">
+        <v>76</v>
+      </c>
+      <c r="T342" t="s">
+        <v>177</v>
+      </c>
+      <c r="U342" t="s">
+        <v>337</v>
+      </c>
+      <c r="V342">
+        <v>118</v>
+      </c>
+      <c r="W342">
+        <v>115</v>
+      </c>
+      <c r="X342">
+        <v>123</v>
+      </c>
+      <c r="Y342">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="343" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>202</v>
+      </c>
+      <c r="B343" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C343" t="s">
+        <v>203</v>
+      </c>
+      <c r="D343" t="s">
+        <v>204</v>
+      </c>
+      <c r="E343" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F343" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G343" t="s">
+        <v>699</v>
+      </c>
+      <c r="H343" t="s">
+        <v>2155</v>
+      </c>
+      <c r="I343" t="s">
+        <v>2156</v>
+      </c>
+      <c r="J343" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K343" t="s">
+        <v>2157</v>
+      </c>
+      <c r="L343" t="s">
+        <v>1796</v>
+      </c>
+      <c r="M343" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N343" t="s">
+        <v>495</v>
+      </c>
+      <c r="O343" t="s">
+        <v>38</v>
+      </c>
+      <c r="P343" t="s">
+        <v>1565</v>
+      </c>
+      <c r="Q343" t="s">
+        <v>2113</v>
+      </c>
+      <c r="R343" t="s">
+        <v>40</v>
+      </c>
+      <c r="S343" t="s">
+        <v>41</v>
+      </c>
+      <c r="T343" t="s">
+        <v>40</v>
+      </c>
+      <c r="U343" t="s">
+        <v>41</v>
+      </c>
+      <c r="V343">
+        <v>47</v>
+      </c>
+      <c r="W343">
+        <v>16</v>
+      </c>
+      <c r="X343">
+        <v>33</v>
+      </c>
+      <c r="Y343">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135A491B-597F-534B-8658-CEE850FFF595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839E06C1-72EF-2648-90B5-C897661D7C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6515" uniqueCount="2159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6775" uniqueCount="2229">
   <si>
     <t>Type</t>
   </si>
@@ -6513,6 +6513,216 @@
   </si>
   <si>
     <t>Jeremy Romany</t>
+  </si>
+  <si>
+    <t>121.1</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>223.48</t>
+  </si>
+  <si>
+    <t>239.82</t>
+  </si>
+  <si>
+    <t>39.64</t>
+  </si>
+  <si>
+    <t>7.48</t>
+  </si>
+  <si>
+    <t>27.4</t>
+  </si>
+  <si>
+    <t>319.87</t>
+  </si>
+  <si>
+    <t>335.63</t>
+  </si>
+  <si>
+    <t>50.77</t>
+  </si>
+  <si>
+    <t>8.61</t>
+  </si>
+  <si>
+    <t>7.93</t>
+  </si>
+  <si>
+    <t>35.6</t>
+  </si>
+  <si>
+    <t>13.5</t>
+  </si>
+  <si>
+    <t>270.39</t>
+  </si>
+  <si>
+    <t>364.23</t>
+  </si>
+  <si>
+    <t>54.99</t>
+  </si>
+  <si>
+    <t>Ismail Mediouna</t>
+  </si>
+  <si>
+    <t>294.25</t>
+  </si>
+  <si>
+    <t>318.13</t>
+  </si>
+  <si>
+    <t>30.83</t>
+  </si>
+  <si>
+    <t>51.94</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>10.6</t>
+  </si>
+  <si>
+    <t>432.22</t>
+  </si>
+  <si>
+    <t>301.64</t>
+  </si>
+  <si>
+    <t>30.99</t>
+  </si>
+  <si>
+    <t>55.9</t>
+  </si>
+  <si>
+    <t>101.75</t>
+  </si>
+  <si>
+    <t>338.85</t>
+  </si>
+  <si>
+    <t>257.34</t>
+  </si>
+  <si>
+    <t>29.55</t>
+  </si>
+  <si>
+    <t>46.62</t>
+  </si>
+  <si>
+    <t>19.6</t>
+  </si>
+  <si>
+    <t>180.04</t>
+  </si>
+  <si>
+    <t>292.04</t>
+  </si>
+  <si>
+    <t>27.99</t>
+  </si>
+  <si>
+    <t>49.71</t>
+  </si>
+  <si>
+    <t>4.75</t>
+  </si>
+  <si>
+    <t>19.2</t>
+  </si>
+  <si>
+    <t>203.51</t>
+  </si>
+  <si>
+    <t>281.69</t>
+  </si>
+  <si>
+    <t>29.39</t>
+  </si>
+  <si>
+    <t>42.16</t>
+  </si>
+  <si>
+    <t>13.7</t>
+  </si>
+  <si>
+    <t>150.99</t>
+  </si>
+  <si>
+    <t>588.02</t>
+  </si>
+  <si>
+    <t>33.68</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
+    <t>244.81</t>
+  </si>
+  <si>
+    <t>252.91</t>
+  </si>
+  <si>
+    <t>43.26</t>
+  </si>
+  <si>
+    <t>329.74</t>
+  </si>
+  <si>
+    <t>321.99</t>
+  </si>
+  <si>
+    <t>28.57</t>
+  </si>
+  <si>
+    <t>48.97</t>
+  </si>
+  <si>
+    <t>7.25</t>
+  </si>
+  <si>
+    <t>41.7</t>
+  </si>
+  <si>
+    <t>10.1</t>
+  </si>
+  <si>
+    <t>103.33</t>
+  </si>
+  <si>
+    <t>306.64</t>
+  </si>
+  <si>
+    <t>432.06</t>
+  </si>
+  <si>
+    <t>48.27</t>
+  </si>
+  <si>
+    <t>7.58</t>
+  </si>
+  <si>
+    <t>32.6</t>
+  </si>
+  <si>
+    <t>44.53</t>
+  </si>
+  <si>
+    <t>227.6</t>
+  </si>
+  <si>
+    <t>25.22</t>
+  </si>
+  <si>
+    <t>40.05</t>
+  </si>
+  <si>
+    <t>4.52</t>
   </si>
 </sst>
 </file>
@@ -6891,7 +7101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y343"/>
+  <dimension ref="A1:Y356"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -32931,6 +33141,1007 @@
         <v>16</v>
       </c>
     </row>
+    <row r="344" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A344" t="s">
+        <v>202</v>
+      </c>
+      <c r="B344" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C344" t="s">
+        <v>203</v>
+      </c>
+      <c r="D344" t="s">
+        <v>345</v>
+      </c>
+      <c r="E344" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F344" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G344" t="s">
+        <v>2160</v>
+      </c>
+      <c r="H344" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I344" t="s">
+        <v>2162</v>
+      </c>
+      <c r="J344" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K344" t="s">
+        <v>2163</v>
+      </c>
+      <c r="L344" t="s">
+        <v>891</v>
+      </c>
+      <c r="M344" t="s">
+        <v>2164</v>
+      </c>
+      <c r="N344" t="s">
+        <v>76</v>
+      </c>
+      <c r="O344" t="s">
+        <v>113</v>
+      </c>
+      <c r="P344" t="s">
+        <v>2165</v>
+      </c>
+      <c r="Q344" t="s">
+        <v>1359</v>
+      </c>
+      <c r="R344" t="s">
+        <v>39</v>
+      </c>
+      <c r="S344" t="s">
+        <v>201</v>
+      </c>
+      <c r="T344" t="s">
+        <v>38</v>
+      </c>
+      <c r="U344" t="s">
+        <v>41</v>
+      </c>
+      <c r="V344">
+        <v>34</v>
+      </c>
+      <c r="W344">
+        <v>19</v>
+      </c>
+      <c r="X344">
+        <v>14</v>
+      </c>
+      <c r="Y344">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A345" t="s">
+        <v>202</v>
+      </c>
+      <c r="B345" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C345" t="s">
+        <v>203</v>
+      </c>
+      <c r="D345" t="s">
+        <v>345</v>
+      </c>
+      <c r="E345" t="s">
+        <v>54</v>
+      </c>
+      <c r="F345" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G345" t="s">
+        <v>86</v>
+      </c>
+      <c r="H345" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I345" t="s">
+        <v>2167</v>
+      </c>
+      <c r="J345" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K345" t="s">
+        <v>2168</v>
+      </c>
+      <c r="L345" t="s">
+        <v>2169</v>
+      </c>
+      <c r="M345" t="s">
+        <v>2170</v>
+      </c>
+      <c r="N345" t="s">
+        <v>554</v>
+      </c>
+      <c r="O345" t="s">
+        <v>488</v>
+      </c>
+      <c r="P345" t="s">
+        <v>2171</v>
+      </c>
+      <c r="Q345" t="s">
+        <v>2172</v>
+      </c>
+      <c r="R345" t="s">
+        <v>113</v>
+      </c>
+      <c r="S345" t="s">
+        <v>39</v>
+      </c>
+      <c r="T345" t="s">
+        <v>66</v>
+      </c>
+      <c r="U345" t="s">
+        <v>39</v>
+      </c>
+      <c r="V345">
+        <v>50</v>
+      </c>
+      <c r="W345">
+        <v>44</v>
+      </c>
+      <c r="X345">
+        <v>39</v>
+      </c>
+      <c r="Y345">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="346" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A346" t="s">
+        <v>202</v>
+      </c>
+      <c r="B346" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C346" t="s">
+        <v>203</v>
+      </c>
+      <c r="D346" t="s">
+        <v>345</v>
+      </c>
+      <c r="E346" t="s">
+        <v>90</v>
+      </c>
+      <c r="F346" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G346" t="s">
+        <v>787</v>
+      </c>
+      <c r="H346" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I346" t="s">
+        <v>2174</v>
+      </c>
+      <c r="J346" t="s">
+        <v>2057</v>
+      </c>
+      <c r="K346" t="s">
+        <v>2175</v>
+      </c>
+      <c r="L346" t="s">
+        <v>541</v>
+      </c>
+      <c r="M346" t="s">
+        <v>80</v>
+      </c>
+      <c r="N346" t="s">
+        <v>672</v>
+      </c>
+      <c r="O346" t="s">
+        <v>113</v>
+      </c>
+      <c r="P346" t="s">
+        <v>1855</v>
+      </c>
+      <c r="Q346" t="s">
+        <v>674</v>
+      </c>
+      <c r="R346" t="s">
+        <v>40</v>
+      </c>
+      <c r="S346" t="s">
+        <v>41</v>
+      </c>
+      <c r="T346" t="s">
+        <v>40</v>
+      </c>
+      <c r="U346" t="s">
+        <v>39</v>
+      </c>
+      <c r="V346">
+        <v>39</v>
+      </c>
+      <c r="W346">
+        <v>32</v>
+      </c>
+      <c r="X346">
+        <v>31</v>
+      </c>
+      <c r="Y346">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="347" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A347" t="s">
+        <v>202</v>
+      </c>
+      <c r="B347" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C347" t="s">
+        <v>203</v>
+      </c>
+      <c r="D347" t="s">
+        <v>345</v>
+      </c>
+      <c r="E347" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F347" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G347" t="s">
+        <v>175</v>
+      </c>
+      <c r="H347" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I347" t="s">
+        <v>2178</v>
+      </c>
+      <c r="J347" t="s">
+        <v>2179</v>
+      </c>
+      <c r="K347" t="s">
+        <v>2180</v>
+      </c>
+      <c r="L347" t="s">
+        <v>891</v>
+      </c>
+      <c r="M347" t="s">
+        <v>1175</v>
+      </c>
+      <c r="N347" t="s">
+        <v>672</v>
+      </c>
+      <c r="O347" t="s">
+        <v>337</v>
+      </c>
+      <c r="P347" t="s">
+        <v>2181</v>
+      </c>
+      <c r="Q347" t="s">
+        <v>2182</v>
+      </c>
+      <c r="R347" t="s">
+        <v>40</v>
+      </c>
+      <c r="S347" t="s">
+        <v>41</v>
+      </c>
+      <c r="T347" t="s">
+        <v>40</v>
+      </c>
+      <c r="U347" t="s">
+        <v>41</v>
+      </c>
+      <c r="V347">
+        <v>38</v>
+      </c>
+      <c r="W347">
+        <v>15</v>
+      </c>
+      <c r="X347">
+        <v>35</v>
+      </c>
+      <c r="Y347">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="348" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A348" t="s">
+        <v>202</v>
+      </c>
+      <c r="B348" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C348" t="s">
+        <v>203</v>
+      </c>
+      <c r="D348" t="s">
+        <v>345</v>
+      </c>
+      <c r="E348" t="s">
+        <v>102</v>
+      </c>
+      <c r="F348" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G348" t="s">
+        <v>742</v>
+      </c>
+      <c r="H348" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I348" t="s">
+        <v>2184</v>
+      </c>
+      <c r="J348" t="s">
+        <v>2185</v>
+      </c>
+      <c r="K348" t="s">
+        <v>1156</v>
+      </c>
+      <c r="L348" t="s">
+        <v>255</v>
+      </c>
+      <c r="M348" t="s">
+        <v>1375</v>
+      </c>
+      <c r="N348" t="s">
+        <v>579</v>
+      </c>
+      <c r="O348" t="s">
+        <v>280</v>
+      </c>
+      <c r="P348" t="s">
+        <v>2186</v>
+      </c>
+      <c r="Q348" t="s">
+        <v>965</v>
+      </c>
+      <c r="R348" t="s">
+        <v>66</v>
+      </c>
+      <c r="S348" t="s">
+        <v>41</v>
+      </c>
+      <c r="T348" t="s">
+        <v>66</v>
+      </c>
+      <c r="U348" t="s">
+        <v>41</v>
+      </c>
+      <c r="V348">
+        <v>44</v>
+      </c>
+      <c r="W348">
+        <v>24</v>
+      </c>
+      <c r="X348">
+        <v>42</v>
+      </c>
+      <c r="Y348">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="349" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A349" t="s">
+        <v>202</v>
+      </c>
+      <c r="B349" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C349" t="s">
+        <v>203</v>
+      </c>
+      <c r="D349" t="s">
+        <v>345</v>
+      </c>
+      <c r="E349" t="s">
+        <v>895</v>
+      </c>
+      <c r="F349" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G349" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H349" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I349" t="s">
+        <v>2189</v>
+      </c>
+      <c r="J349" t="s">
+        <v>2190</v>
+      </c>
+      <c r="K349" t="s">
+        <v>2191</v>
+      </c>
+      <c r="L349" t="s">
+        <v>955</v>
+      </c>
+      <c r="M349" t="s">
+        <v>503</v>
+      </c>
+      <c r="N349" t="s">
+        <v>213</v>
+      </c>
+      <c r="O349" t="s">
+        <v>495</v>
+      </c>
+      <c r="P349" t="s">
+        <v>552</v>
+      </c>
+      <c r="Q349" t="s">
+        <v>2192</v>
+      </c>
+      <c r="R349" t="s">
+        <v>66</v>
+      </c>
+      <c r="S349" t="s">
+        <v>41</v>
+      </c>
+      <c r="T349" t="s">
+        <v>38</v>
+      </c>
+      <c r="U349" t="s">
+        <v>41</v>
+      </c>
+      <c r="V349">
+        <v>28</v>
+      </c>
+      <c r="W349">
+        <v>17</v>
+      </c>
+      <c r="X349">
+        <v>30</v>
+      </c>
+      <c r="Y349">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="350" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
+        <v>202</v>
+      </c>
+      <c r="B350" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C350" t="s">
+        <v>203</v>
+      </c>
+      <c r="D350" t="s">
+        <v>345</v>
+      </c>
+      <c r="E350" t="s">
+        <v>126</v>
+      </c>
+      <c r="F350" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G350" t="s">
+        <v>549</v>
+      </c>
+      <c r="H350" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I350" t="s">
+        <v>2194</v>
+      </c>
+      <c r="J350" t="s">
+        <v>2195</v>
+      </c>
+      <c r="K350" t="s">
+        <v>2196</v>
+      </c>
+      <c r="L350" t="s">
+        <v>748</v>
+      </c>
+      <c r="M350" t="s">
+        <v>2197</v>
+      </c>
+      <c r="N350" t="s">
+        <v>188</v>
+      </c>
+      <c r="O350" t="s">
+        <v>113</v>
+      </c>
+      <c r="P350" t="s">
+        <v>2198</v>
+      </c>
+      <c r="Q350" t="s">
+        <v>1344</v>
+      </c>
+      <c r="R350" t="s">
+        <v>39</v>
+      </c>
+      <c r="S350" t="s">
+        <v>201</v>
+      </c>
+      <c r="T350" t="s">
+        <v>39</v>
+      </c>
+      <c r="U350" t="s">
+        <v>201</v>
+      </c>
+      <c r="V350">
+        <v>32</v>
+      </c>
+      <c r="W350">
+        <v>8</v>
+      </c>
+      <c r="X350">
+        <v>23</v>
+      </c>
+      <c r="Y350">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="351" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>202</v>
+      </c>
+      <c r="B351" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C351" t="s">
+        <v>203</v>
+      </c>
+      <c r="D351" t="s">
+        <v>345</v>
+      </c>
+      <c r="E351" t="s">
+        <v>137</v>
+      </c>
+      <c r="F351" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G351" t="s">
+        <v>982</v>
+      </c>
+      <c r="H351" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I351" t="s">
+        <v>2200</v>
+      </c>
+      <c r="J351" t="s">
+        <v>2201</v>
+      </c>
+      <c r="K351" t="s">
+        <v>2202</v>
+      </c>
+      <c r="L351" t="s">
+        <v>1679</v>
+      </c>
+      <c r="M351" t="s">
+        <v>1457</v>
+      </c>
+      <c r="N351" t="s">
+        <v>488</v>
+      </c>
+      <c r="O351" t="s">
+        <v>488</v>
+      </c>
+      <c r="P351" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q351" t="s">
+        <v>2203</v>
+      </c>
+      <c r="R351" t="s">
+        <v>38</v>
+      </c>
+      <c r="S351" t="s">
+        <v>41</v>
+      </c>
+      <c r="T351" t="s">
+        <v>38</v>
+      </c>
+      <c r="U351" t="s">
+        <v>41</v>
+      </c>
+      <c r="V351">
+        <v>29</v>
+      </c>
+      <c r="W351">
+        <v>14</v>
+      </c>
+      <c r="X351">
+        <v>25</v>
+      </c>
+      <c r="Y351">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="352" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A352" t="s">
+        <v>202</v>
+      </c>
+      <c r="B352" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C352" t="s">
+        <v>203</v>
+      </c>
+      <c r="D352" t="s">
+        <v>345</v>
+      </c>
+      <c r="E352" t="s">
+        <v>147</v>
+      </c>
+      <c r="F352" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G352" t="s">
+        <v>469</v>
+      </c>
+      <c r="H352" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I352" t="s">
+        <v>2205</v>
+      </c>
+      <c r="J352" t="s">
+        <v>2206</v>
+      </c>
+      <c r="K352" t="s">
+        <v>2191</v>
+      </c>
+      <c r="L352" t="s">
+        <v>384</v>
+      </c>
+      <c r="M352" t="s">
+        <v>1609</v>
+      </c>
+      <c r="N352" t="s">
+        <v>188</v>
+      </c>
+      <c r="O352" t="s">
+        <v>38</v>
+      </c>
+      <c r="P352" t="s">
+        <v>2207</v>
+      </c>
+      <c r="Q352" t="s">
+        <v>413</v>
+      </c>
+      <c r="R352" t="s">
+        <v>113</v>
+      </c>
+      <c r="S352" t="s">
+        <v>38</v>
+      </c>
+      <c r="T352" t="s">
+        <v>66</v>
+      </c>
+      <c r="U352" t="s">
+        <v>39</v>
+      </c>
+      <c r="V352">
+        <v>64</v>
+      </c>
+      <c r="W352">
+        <v>27</v>
+      </c>
+      <c r="X352">
+        <v>59</v>
+      </c>
+      <c r="Y352">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="353" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A353" t="s">
+        <v>202</v>
+      </c>
+      <c r="B353" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C353" t="s">
+        <v>203</v>
+      </c>
+      <c r="D353" t="s">
+        <v>345</v>
+      </c>
+      <c r="E353" t="s">
+        <v>157</v>
+      </c>
+      <c r="F353" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G353" t="s">
+        <v>821</v>
+      </c>
+      <c r="H353" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I353" t="s">
+        <v>2209</v>
+      </c>
+      <c r="J353" t="s">
+        <v>547</v>
+      </c>
+      <c r="K353" t="s">
+        <v>2210</v>
+      </c>
+      <c r="L353" t="s">
+        <v>357</v>
+      </c>
+      <c r="M353" t="s">
+        <v>186</v>
+      </c>
+      <c r="N353" t="s">
+        <v>495</v>
+      </c>
+      <c r="O353" t="s">
+        <v>488</v>
+      </c>
+      <c r="P353" t="s">
+        <v>743</v>
+      </c>
+      <c r="Q353" t="s">
+        <v>965</v>
+      </c>
+      <c r="R353" t="s">
+        <v>38</v>
+      </c>
+      <c r="S353" t="s">
+        <v>41</v>
+      </c>
+      <c r="T353" t="s">
+        <v>40</v>
+      </c>
+      <c r="U353" t="s">
+        <v>41</v>
+      </c>
+      <c r="V353">
+        <v>32</v>
+      </c>
+      <c r="W353">
+        <v>19</v>
+      </c>
+      <c r="X353">
+        <v>19</v>
+      </c>
+      <c r="Y353">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="354" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A354" t="s">
+        <v>202</v>
+      </c>
+      <c r="B354" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C354" t="s">
+        <v>203</v>
+      </c>
+      <c r="D354" t="s">
+        <v>345</v>
+      </c>
+      <c r="E354" t="s">
+        <v>933</v>
+      </c>
+      <c r="F354" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G354" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H354" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I354" t="s">
+        <v>2212</v>
+      </c>
+      <c r="J354" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K354" t="s">
+        <v>2214</v>
+      </c>
+      <c r="L354" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M354" t="s">
+        <v>828</v>
+      </c>
+      <c r="N354" t="s">
+        <v>279</v>
+      </c>
+      <c r="O354" t="s">
+        <v>337</v>
+      </c>
+      <c r="P354" t="s">
+        <v>2216</v>
+      </c>
+      <c r="Q354" t="s">
+        <v>2217</v>
+      </c>
+      <c r="R354" t="s">
+        <v>40</v>
+      </c>
+      <c r="S354" t="s">
+        <v>39</v>
+      </c>
+      <c r="T354" t="s">
+        <v>66</v>
+      </c>
+      <c r="U354" t="s">
+        <v>39</v>
+      </c>
+      <c r="V354">
+        <v>52</v>
+      </c>
+      <c r="W354">
+        <v>31</v>
+      </c>
+      <c r="X354">
+        <v>40</v>
+      </c>
+      <c r="Y354">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="355" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A355" t="s">
+        <v>202</v>
+      </c>
+      <c r="B355" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C355" t="s">
+        <v>203</v>
+      </c>
+      <c r="D355" t="s">
+        <v>345</v>
+      </c>
+      <c r="E355" t="s">
+        <v>180</v>
+      </c>
+      <c r="F355" t="s">
+        <v>2218</v>
+      </c>
+      <c r="G355" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H355" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I355" t="s">
+        <v>2220</v>
+      </c>
+      <c r="J355" t="s">
+        <v>2123</v>
+      </c>
+      <c r="K355" t="s">
+        <v>2221</v>
+      </c>
+      <c r="L355" t="s">
+        <v>2222</v>
+      </c>
+      <c r="M355" t="s">
+        <v>1694</v>
+      </c>
+      <c r="N355" t="s">
+        <v>471</v>
+      </c>
+      <c r="O355" t="s">
+        <v>449</v>
+      </c>
+      <c r="P355" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Q355" t="s">
+        <v>2172</v>
+      </c>
+      <c r="R355" t="s">
+        <v>188</v>
+      </c>
+      <c r="S355" t="s">
+        <v>35</v>
+      </c>
+      <c r="T355" t="s">
+        <v>337</v>
+      </c>
+      <c r="U355" t="s">
+        <v>40</v>
+      </c>
+      <c r="V355">
+        <v>70</v>
+      </c>
+      <c r="W355">
+        <v>62</v>
+      </c>
+      <c r="X355">
+        <v>87</v>
+      </c>
+      <c r="Y355">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="356" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A356" t="s">
+        <v>202</v>
+      </c>
+      <c r="B356" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C356" t="s">
+        <v>203</v>
+      </c>
+      <c r="D356" t="s">
+        <v>345</v>
+      </c>
+      <c r="E356" t="s">
+        <v>191</v>
+      </c>
+      <c r="F356" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G356" t="s">
+        <v>571</v>
+      </c>
+      <c r="H356" t="s">
+        <v>2224</v>
+      </c>
+      <c r="I356" t="s">
+        <v>2225</v>
+      </c>
+      <c r="J356" t="s">
+        <v>2226</v>
+      </c>
+      <c r="K356" t="s">
+        <v>2227</v>
+      </c>
+      <c r="L356" t="s">
+        <v>86</v>
+      </c>
+      <c r="M356" t="s">
+        <v>2228</v>
+      </c>
+      <c r="N356" t="s">
+        <v>40</v>
+      </c>
+      <c r="O356" t="s">
+        <v>201</v>
+      </c>
+      <c r="P356" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q356" t="s">
+        <v>34</v>
+      </c>
+      <c r="R356" t="s">
+        <v>41</v>
+      </c>
+      <c r="S356" t="s">
+        <v>201</v>
+      </c>
+      <c r="T356" t="s">
+        <v>41</v>
+      </c>
+      <c r="U356" t="s">
+        <v>201</v>
+      </c>
+      <c r="V356">
+        <v>16</v>
+      </c>
+      <c r="W356">
+        <v>4</v>
+      </c>
+      <c r="X356">
+        <v>9</v>
+      </c>
+      <c r="Y356">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839E06C1-72EF-2648-90B5-C897661D7C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB386165-BD3C-2A4D-959E-8EC8868CF434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6775" uniqueCount="2229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7075" uniqueCount="2289">
   <si>
     <t>Type</t>
   </si>
@@ -6723,6 +6723,186 @@
   </si>
   <si>
     <t>4.52</t>
+  </si>
+  <si>
+    <t>76.58</t>
+  </si>
+  <si>
+    <t>36.65</t>
+  </si>
+  <si>
+    <t>247.59</t>
+  </si>
+  <si>
+    <t>62.11</t>
+  </si>
+  <si>
+    <t>99.04</t>
+  </si>
+  <si>
+    <t>302.16</t>
+  </si>
+  <si>
+    <t>26.61</t>
+  </si>
+  <si>
+    <t>71.7</t>
+  </si>
+  <si>
+    <t>8.13</t>
+  </si>
+  <si>
+    <t>88.24</t>
+  </si>
+  <si>
+    <t>273.64</t>
+  </si>
+  <si>
+    <t>26.02</t>
+  </si>
+  <si>
+    <t>67.66</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>117.5</t>
+  </si>
+  <si>
+    <t>362.13</t>
+  </si>
+  <si>
+    <t>25.25</t>
+  </si>
+  <si>
+    <t>88.1</t>
+  </si>
+  <si>
+    <t>198.6</t>
+  </si>
+  <si>
+    <t>288.47</t>
+  </si>
+  <si>
+    <t>25.9</t>
+  </si>
+  <si>
+    <t>79.62</t>
+  </si>
+  <si>
+    <t>31.4</t>
+  </si>
+  <si>
+    <t>78.87</t>
+  </si>
+  <si>
+    <t>245.94</t>
+  </si>
+  <si>
+    <t>25.97</t>
+  </si>
+  <si>
+    <t>61.44</t>
+  </si>
+  <si>
+    <t>284.18</t>
+  </si>
+  <si>
+    <t>341.39</t>
+  </si>
+  <si>
+    <t>77.6</t>
+  </si>
+  <si>
+    <t>215.27</t>
+  </si>
+  <si>
+    <t>286.26</t>
+  </si>
+  <si>
+    <t>79.6</t>
+  </si>
+  <si>
+    <t>168.32</t>
+  </si>
+  <si>
+    <t>601.83</t>
+  </si>
+  <si>
+    <t>79.8</t>
+  </si>
+  <si>
+    <t>40.21</t>
+  </si>
+  <si>
+    <t>321.93</t>
+  </si>
+  <si>
+    <t>24.17</t>
+  </si>
+  <si>
+    <t>75.17</t>
+  </si>
+  <si>
+    <t>89.32</t>
+  </si>
+  <si>
+    <t>275.75</t>
+  </si>
+  <si>
+    <t>24.51</t>
+  </si>
+  <si>
+    <t>72.1</t>
+  </si>
+  <si>
+    <t>162.18</t>
+  </si>
+  <si>
+    <t>276.78</t>
+  </si>
+  <si>
+    <t>29.92</t>
+  </si>
+  <si>
+    <t>76.17</t>
+  </si>
+  <si>
+    <t>86.14</t>
+  </si>
+  <si>
+    <t>69.11</t>
+  </si>
+  <si>
+    <t>313.61</t>
+  </si>
+  <si>
+    <t>573.33</t>
+  </si>
+  <si>
+    <t>75.0</t>
+  </si>
+  <si>
+    <t>9.68</t>
+  </si>
+  <si>
+    <t>43.0</t>
+  </si>
+  <si>
+    <t>4.94</t>
+  </si>
+  <si>
+    <t>70.5</t>
+  </si>
+  <si>
+    <t>231.59</t>
+  </si>
+  <si>
+    <t>26.29</t>
+  </si>
+  <si>
+    <t>64.56</t>
   </si>
 </sst>
 </file>
@@ -7101,7 +7281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y356"/>
+  <dimension ref="A1:Y371"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -34142,6 +34322,1161 @@
         <v>5</v>
       </c>
     </row>
+    <row r="357" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A357" t="s">
+        <v>202</v>
+      </c>
+      <c r="B357" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C357" t="s">
+        <v>203</v>
+      </c>
+      <c r="D357" t="s">
+        <v>849</v>
+      </c>
+      <c r="E357" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F357" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G357" t="s">
+        <v>115</v>
+      </c>
+      <c r="H357" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I357" t="s">
+        <v>2231</v>
+      </c>
+      <c r="J357" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K357" t="s">
+        <v>2232</v>
+      </c>
+      <c r="L357" t="s">
+        <v>867</v>
+      </c>
+      <c r="M357" t="s">
+        <v>293</v>
+      </c>
+      <c r="N357" t="s">
+        <v>38</v>
+      </c>
+      <c r="O357" t="s">
+        <v>201</v>
+      </c>
+      <c r="P357" t="s">
+        <v>1009</v>
+      </c>
+      <c r="Q357" t="s">
+        <v>34</v>
+      </c>
+      <c r="R357" t="s">
+        <v>66</v>
+      </c>
+      <c r="S357" t="s">
+        <v>41</v>
+      </c>
+      <c r="T357" t="s">
+        <v>40</v>
+      </c>
+      <c r="U357" t="s">
+        <v>41</v>
+      </c>
+      <c r="V357">
+        <v>47</v>
+      </c>
+      <c r="W357">
+        <v>20</v>
+      </c>
+      <c r="X357">
+        <v>36</v>
+      </c>
+      <c r="Y357">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="358" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A358" t="s">
+        <v>202</v>
+      </c>
+      <c r="B358" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C358" t="s">
+        <v>203</v>
+      </c>
+      <c r="D358" t="s">
+        <v>849</v>
+      </c>
+      <c r="E358" t="s">
+        <v>42</v>
+      </c>
+      <c r="F358" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G358" t="s">
+        <v>1704</v>
+      </c>
+      <c r="H358" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I358" t="s">
+        <v>2234</v>
+      </c>
+      <c r="J358" t="s">
+        <v>2235</v>
+      </c>
+      <c r="K358" t="s">
+        <v>2236</v>
+      </c>
+      <c r="L358" t="s">
+        <v>2237</v>
+      </c>
+      <c r="M358" t="s">
+        <v>782</v>
+      </c>
+      <c r="N358" t="s">
+        <v>280</v>
+      </c>
+      <c r="O358" t="s">
+        <v>41</v>
+      </c>
+      <c r="P358" t="s">
+        <v>2096</v>
+      </c>
+      <c r="Q358" t="s">
+        <v>405</v>
+      </c>
+      <c r="R358" t="s">
+        <v>40</v>
+      </c>
+      <c r="S358" t="s">
+        <v>39</v>
+      </c>
+      <c r="T358" t="s">
+        <v>40</v>
+      </c>
+      <c r="U358" t="s">
+        <v>201</v>
+      </c>
+      <c r="V358">
+        <v>59</v>
+      </c>
+      <c r="W358">
+        <v>12</v>
+      </c>
+      <c r="X358">
+        <v>42</v>
+      </c>
+      <c r="Y358">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="359" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A359" t="s">
+        <v>202</v>
+      </c>
+      <c r="B359" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C359" t="s">
+        <v>203</v>
+      </c>
+      <c r="D359" t="s">
+        <v>849</v>
+      </c>
+      <c r="E359" t="s">
+        <v>54</v>
+      </c>
+      <c r="F359" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G359" t="s">
+        <v>823</v>
+      </c>
+      <c r="H359" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I359" t="s">
+        <v>2239</v>
+      </c>
+      <c r="J359" t="s">
+        <v>2240</v>
+      </c>
+      <c r="K359" t="s">
+        <v>2241</v>
+      </c>
+      <c r="L359" t="s">
+        <v>1530</v>
+      </c>
+      <c r="M359" t="s">
+        <v>386</v>
+      </c>
+      <c r="N359" t="s">
+        <v>337</v>
+      </c>
+      <c r="O359" t="s">
+        <v>201</v>
+      </c>
+      <c r="P359" t="s">
+        <v>2242</v>
+      </c>
+      <c r="Q359" t="s">
+        <v>87</v>
+      </c>
+      <c r="R359" t="s">
+        <v>113</v>
+      </c>
+      <c r="S359" t="s">
+        <v>38</v>
+      </c>
+      <c r="T359" t="s">
+        <v>66</v>
+      </c>
+      <c r="U359" t="s">
+        <v>39</v>
+      </c>
+      <c r="V359">
+        <v>49</v>
+      </c>
+      <c r="W359">
+        <v>37</v>
+      </c>
+      <c r="X359">
+        <v>40</v>
+      </c>
+      <c r="Y359">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="360" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A360" t="s">
+        <v>202</v>
+      </c>
+      <c r="B360" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C360" t="s">
+        <v>203</v>
+      </c>
+      <c r="D360" t="s">
+        <v>849</v>
+      </c>
+      <c r="E360" t="s">
+        <v>90</v>
+      </c>
+      <c r="F360" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G360" t="s">
+        <v>343</v>
+      </c>
+      <c r="H360" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I360" t="s">
+        <v>2244</v>
+      </c>
+      <c r="J360" t="s">
+        <v>2245</v>
+      </c>
+      <c r="K360" t="s">
+        <v>2246</v>
+      </c>
+      <c r="L360" t="s">
+        <v>1830</v>
+      </c>
+      <c r="M360" t="s">
+        <v>241</v>
+      </c>
+      <c r="N360" t="s">
+        <v>449</v>
+      </c>
+      <c r="O360" t="s">
+        <v>201</v>
+      </c>
+      <c r="P360" t="s">
+        <v>1690</v>
+      </c>
+      <c r="Q360" t="s">
+        <v>87</v>
+      </c>
+      <c r="R360" t="s">
+        <v>113</v>
+      </c>
+      <c r="S360" t="s">
+        <v>39</v>
+      </c>
+      <c r="T360" t="s">
+        <v>66</v>
+      </c>
+      <c r="U360" t="s">
+        <v>41</v>
+      </c>
+      <c r="V360">
+        <v>81</v>
+      </c>
+      <c r="W360">
+        <v>26</v>
+      </c>
+      <c r="X360">
+        <v>65</v>
+      </c>
+      <c r="Y360">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="361" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A361" t="s">
+        <v>202</v>
+      </c>
+      <c r="B361" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C361" t="s">
+        <v>203</v>
+      </c>
+      <c r="D361" t="s">
+        <v>849</v>
+      </c>
+      <c r="E361" t="s">
+        <v>102</v>
+      </c>
+      <c r="F361" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G361" t="s">
+        <v>241</v>
+      </c>
+      <c r="H361" t="s">
+        <v>2247</v>
+      </c>
+      <c r="I361" t="s">
+        <v>2248</v>
+      </c>
+      <c r="J361" t="s">
+        <v>2249</v>
+      </c>
+      <c r="K361" t="s">
+        <v>2250</v>
+      </c>
+      <c r="L361" t="s">
+        <v>756</v>
+      </c>
+      <c r="M361" t="s">
+        <v>548</v>
+      </c>
+      <c r="N361" t="s">
+        <v>213</v>
+      </c>
+      <c r="O361" t="s">
+        <v>41</v>
+      </c>
+      <c r="P361" t="s">
+        <v>2251</v>
+      </c>
+      <c r="Q361" t="s">
+        <v>773</v>
+      </c>
+      <c r="R361" t="s">
+        <v>113</v>
+      </c>
+      <c r="S361" t="s">
+        <v>41</v>
+      </c>
+      <c r="T361" t="s">
+        <v>113</v>
+      </c>
+      <c r="U361" t="s">
+        <v>41</v>
+      </c>
+      <c r="V361">
+        <v>86</v>
+      </c>
+      <c r="W361">
+        <v>26</v>
+      </c>
+      <c r="X361">
+        <v>59</v>
+      </c>
+      <c r="Y361">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="362" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A362" t="s">
+        <v>202</v>
+      </c>
+      <c r="B362" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C362" t="s">
+        <v>203</v>
+      </c>
+      <c r="D362" t="s">
+        <v>849</v>
+      </c>
+      <c r="E362" t="s">
+        <v>895</v>
+      </c>
+      <c r="F362" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G362" t="s">
+        <v>520</v>
+      </c>
+      <c r="H362" t="s">
+        <v>2252</v>
+      </c>
+      <c r="I362" t="s">
+        <v>2253</v>
+      </c>
+      <c r="J362" t="s">
+        <v>2254</v>
+      </c>
+      <c r="K362" t="s">
+        <v>2255</v>
+      </c>
+      <c r="L362" t="s">
+        <v>86</v>
+      </c>
+      <c r="M362" t="s">
+        <v>1699</v>
+      </c>
+      <c r="N362" t="s">
+        <v>35</v>
+      </c>
+      <c r="O362" t="s">
+        <v>41</v>
+      </c>
+      <c r="P362" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q362" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R362" t="s">
+        <v>40</v>
+      </c>
+      <c r="S362" t="s">
+        <v>41</v>
+      </c>
+      <c r="T362" t="s">
+        <v>40</v>
+      </c>
+      <c r="U362" t="s">
+        <v>41</v>
+      </c>
+      <c r="V362">
+        <v>57</v>
+      </c>
+      <c r="W362">
+        <v>18</v>
+      </c>
+      <c r="X362">
+        <v>46</v>
+      </c>
+      <c r="Y362">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="363" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A363" t="s">
+        <v>202</v>
+      </c>
+      <c r="B363" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C363" t="s">
+        <v>203</v>
+      </c>
+      <c r="D363" t="s">
+        <v>849</v>
+      </c>
+      <c r="E363" t="s">
+        <v>114</v>
+      </c>
+      <c r="F363" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G363" t="s">
+        <v>142</v>
+      </c>
+      <c r="H363" t="s">
+        <v>2256</v>
+      </c>
+      <c r="I363" t="s">
+        <v>2257</v>
+      </c>
+      <c r="J363" t="s">
+        <v>796</v>
+      </c>
+      <c r="K363" t="s">
+        <v>2258</v>
+      </c>
+      <c r="L363" t="s">
+        <v>960</v>
+      </c>
+      <c r="M363" t="s">
+        <v>85</v>
+      </c>
+      <c r="N363" t="s">
+        <v>471</v>
+      </c>
+      <c r="O363" t="s">
+        <v>337</v>
+      </c>
+      <c r="P363" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Q363" t="s">
+        <v>470</v>
+      </c>
+      <c r="R363" t="s">
+        <v>66</v>
+      </c>
+      <c r="S363" t="s">
+        <v>41</v>
+      </c>
+      <c r="T363" t="s">
+        <v>66</v>
+      </c>
+      <c r="U363" t="s">
+        <v>41</v>
+      </c>
+      <c r="V363">
+        <v>55</v>
+      </c>
+      <c r="W363">
+        <v>27</v>
+      </c>
+      <c r="X363">
+        <v>38</v>
+      </c>
+      <c r="Y363">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="364" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A364" t="s">
+        <v>202</v>
+      </c>
+      <c r="B364" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C364" t="s">
+        <v>203</v>
+      </c>
+      <c r="D364" t="s">
+        <v>849</v>
+      </c>
+      <c r="E364" t="s">
+        <v>126</v>
+      </c>
+      <c r="F364" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G364" t="s">
+        <v>241</v>
+      </c>
+      <c r="H364" t="s">
+        <v>2259</v>
+      </c>
+      <c r="I364" t="s">
+        <v>2260</v>
+      </c>
+      <c r="J364" t="s">
+        <v>2051</v>
+      </c>
+      <c r="K364" t="s">
+        <v>2261</v>
+      </c>
+      <c r="L364" t="s">
+        <v>526</v>
+      </c>
+      <c r="M364" t="s">
+        <v>399</v>
+      </c>
+      <c r="N364" t="s">
+        <v>177</v>
+      </c>
+      <c r="O364" t="s">
+        <v>40</v>
+      </c>
+      <c r="P364" t="s">
+        <v>684</v>
+      </c>
+      <c r="Q364" t="s">
+        <v>603</v>
+      </c>
+      <c r="R364" t="s">
+        <v>40</v>
+      </c>
+      <c r="S364" t="s">
+        <v>41</v>
+      </c>
+      <c r="T364" t="s">
+        <v>39</v>
+      </c>
+      <c r="U364" t="s">
+        <v>41</v>
+      </c>
+      <c r="V364">
+        <v>30</v>
+      </c>
+      <c r="W364">
+        <v>16</v>
+      </c>
+      <c r="X364">
+        <v>48</v>
+      </c>
+      <c r="Y364">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="365" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A365" t="s">
+        <v>202</v>
+      </c>
+      <c r="B365" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C365" t="s">
+        <v>203</v>
+      </c>
+      <c r="D365" t="s">
+        <v>849</v>
+      </c>
+      <c r="E365" t="s">
+        <v>346</v>
+      </c>
+      <c r="F365" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G365" t="s">
+        <v>955</v>
+      </c>
+      <c r="H365" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I365" t="s">
+        <v>2263</v>
+      </c>
+      <c r="J365" t="s">
+        <v>1586</v>
+      </c>
+      <c r="K365" t="s">
+        <v>2264</v>
+      </c>
+      <c r="L365" t="s">
+        <v>722</v>
+      </c>
+      <c r="M365" t="s">
+        <v>1062</v>
+      </c>
+      <c r="N365" t="s">
+        <v>76</v>
+      </c>
+      <c r="O365" t="s">
+        <v>41</v>
+      </c>
+      <c r="P365" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q365" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R365" t="s">
+        <v>555</v>
+      </c>
+      <c r="S365" t="s">
+        <v>35</v>
+      </c>
+      <c r="T365" t="s">
+        <v>488</v>
+      </c>
+      <c r="U365" t="s">
+        <v>38</v>
+      </c>
+      <c r="V365">
+        <v>110</v>
+      </c>
+      <c r="W365">
+        <v>65</v>
+      </c>
+      <c r="X365">
+        <v>104</v>
+      </c>
+      <c r="Y365">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="366" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A366" t="s">
+        <v>202</v>
+      </c>
+      <c r="B366" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C366" t="s">
+        <v>203</v>
+      </c>
+      <c r="D366" t="s">
+        <v>849</v>
+      </c>
+      <c r="E366" t="s">
+        <v>137</v>
+      </c>
+      <c r="F366" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G366" t="s">
+        <v>891</v>
+      </c>
+      <c r="H366" t="s">
+        <v>2265</v>
+      </c>
+      <c r="I366" t="s">
+        <v>2266</v>
+      </c>
+      <c r="J366" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K366" t="s">
+        <v>2268</v>
+      </c>
+      <c r="L366" t="s">
+        <v>787</v>
+      </c>
+      <c r="M366" t="s">
+        <v>1197</v>
+      </c>
+      <c r="N366" t="s">
+        <v>40</v>
+      </c>
+      <c r="O366" t="s">
+        <v>201</v>
+      </c>
+      <c r="P366" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q366" t="s">
+        <v>201</v>
+      </c>
+      <c r="R366" t="s">
+        <v>113</v>
+      </c>
+      <c r="S366" t="s">
+        <v>39</v>
+      </c>
+      <c r="T366" t="s">
+        <v>40</v>
+      </c>
+      <c r="U366" t="s">
+        <v>41</v>
+      </c>
+      <c r="V366">
+        <v>54</v>
+      </c>
+      <c r="W366">
+        <v>20</v>
+      </c>
+      <c r="X366">
+        <v>65</v>
+      </c>
+      <c r="Y366">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="367" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A367" t="s">
+        <v>202</v>
+      </c>
+      <c r="B367" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C367" t="s">
+        <v>203</v>
+      </c>
+      <c r="D367" t="s">
+        <v>849</v>
+      </c>
+      <c r="E367" t="s">
+        <v>147</v>
+      </c>
+      <c r="F367" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G367" t="s">
+        <v>926</v>
+      </c>
+      <c r="H367" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I367" t="s">
+        <v>2270</v>
+      </c>
+      <c r="J367" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K367" t="s">
+        <v>2272</v>
+      </c>
+      <c r="L367" t="s">
+        <v>230</v>
+      </c>
+      <c r="M367" t="s">
+        <v>707</v>
+      </c>
+      <c r="N367" t="s">
+        <v>280</v>
+      </c>
+      <c r="O367" t="s">
+        <v>201</v>
+      </c>
+      <c r="P367" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Q367" t="s">
+        <v>201</v>
+      </c>
+      <c r="R367" t="s">
+        <v>66</v>
+      </c>
+      <c r="S367" t="s">
+        <v>41</v>
+      </c>
+      <c r="T367" t="s">
+        <v>40</v>
+      </c>
+      <c r="U367" t="s">
+        <v>41</v>
+      </c>
+      <c r="V367">
+        <v>53</v>
+      </c>
+      <c r="W367">
+        <v>23</v>
+      </c>
+      <c r="X367">
+        <v>45</v>
+      </c>
+      <c r="Y367">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="368" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A368" t="s">
+        <v>202</v>
+      </c>
+      <c r="B368" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C368" t="s">
+        <v>203</v>
+      </c>
+      <c r="D368" t="s">
+        <v>849</v>
+      </c>
+      <c r="E368" t="s">
+        <v>157</v>
+      </c>
+      <c r="F368" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G368" t="s">
+        <v>1670</v>
+      </c>
+      <c r="H368" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I368" t="s">
+        <v>2274</v>
+      </c>
+      <c r="J368" t="s">
+        <v>2275</v>
+      </c>
+      <c r="K368" t="s">
+        <v>2276</v>
+      </c>
+      <c r="L368" t="s">
+        <v>2091</v>
+      </c>
+      <c r="M368" t="s">
+        <v>640</v>
+      </c>
+      <c r="N368" t="s">
+        <v>51</v>
+      </c>
+      <c r="O368" t="s">
+        <v>38</v>
+      </c>
+      <c r="P368" t="s">
+        <v>643</v>
+      </c>
+      <c r="Q368" t="s">
+        <v>344</v>
+      </c>
+      <c r="R368" t="s">
+        <v>113</v>
+      </c>
+      <c r="S368" t="s">
+        <v>38</v>
+      </c>
+      <c r="T368" t="s">
+        <v>35</v>
+      </c>
+      <c r="U368" t="s">
+        <v>39</v>
+      </c>
+      <c r="V368">
+        <v>71</v>
+      </c>
+      <c r="W368">
+        <v>41</v>
+      </c>
+      <c r="X368">
+        <v>40</v>
+      </c>
+      <c r="Y368">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="369" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A369" t="s">
+        <v>202</v>
+      </c>
+      <c r="B369" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C369" t="s">
+        <v>203</v>
+      </c>
+      <c r="D369" t="s">
+        <v>849</v>
+      </c>
+      <c r="E369" t="s">
+        <v>933</v>
+      </c>
+      <c r="F369" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G369" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H369" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I369" t="s">
+        <v>551</v>
+      </c>
+      <c r="J369" t="s">
+        <v>517</v>
+      </c>
+      <c r="K369" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L369" t="s">
+        <v>186</v>
+      </c>
+      <c r="M369" t="s">
+        <v>1375</v>
+      </c>
+      <c r="N369" t="s">
+        <v>337</v>
+      </c>
+      <c r="O369" t="s">
+        <v>201</v>
+      </c>
+      <c r="P369" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q369" t="s">
+        <v>176</v>
+      </c>
+      <c r="R369" t="s">
+        <v>66</v>
+      </c>
+      <c r="S369" t="s">
+        <v>39</v>
+      </c>
+      <c r="T369" t="s">
+        <v>40</v>
+      </c>
+      <c r="U369" t="s">
+        <v>41</v>
+      </c>
+      <c r="V369">
+        <v>45</v>
+      </c>
+      <c r="W369">
+        <v>20</v>
+      </c>
+      <c r="X369">
+        <v>44</v>
+      </c>
+      <c r="Y369">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="370" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A370" t="s">
+        <v>202</v>
+      </c>
+      <c r="B370" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C370" t="s">
+        <v>203</v>
+      </c>
+      <c r="D370" t="s">
+        <v>849</v>
+      </c>
+      <c r="E370" t="s">
+        <v>180</v>
+      </c>
+      <c r="F370" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G370" t="s">
+        <v>699</v>
+      </c>
+      <c r="H370" t="s">
+        <v>2279</v>
+      </c>
+      <c r="I370" t="s">
+        <v>2280</v>
+      </c>
+      <c r="J370" t="s">
+        <v>1887</v>
+      </c>
+      <c r="K370" t="s">
+        <v>2281</v>
+      </c>
+      <c r="L370" t="s">
+        <v>513</v>
+      </c>
+      <c r="M370" t="s">
+        <v>2282</v>
+      </c>
+      <c r="N370" t="s">
+        <v>307</v>
+      </c>
+      <c r="O370" t="s">
+        <v>66</v>
+      </c>
+      <c r="P370" t="s">
+        <v>2283</v>
+      </c>
+      <c r="Q370" t="s">
+        <v>446</v>
+      </c>
+      <c r="R370" t="s">
+        <v>213</v>
+      </c>
+      <c r="S370" t="s">
+        <v>51</v>
+      </c>
+      <c r="T370" t="s">
+        <v>51</v>
+      </c>
+      <c r="U370" t="s">
+        <v>337</v>
+      </c>
+      <c r="V370">
+        <v>119</v>
+      </c>
+      <c r="W370">
+        <v>116</v>
+      </c>
+      <c r="X370">
+        <v>143</v>
+      </c>
+      <c r="Y370">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="371" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A371" t="s">
+        <v>202</v>
+      </c>
+      <c r="B371" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C371" t="s">
+        <v>203</v>
+      </c>
+      <c r="D371" t="s">
+        <v>849</v>
+      </c>
+      <c r="E371" t="s">
+        <v>191</v>
+      </c>
+      <c r="F371" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G371" t="s">
+        <v>2284</v>
+      </c>
+      <c r="H371" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I371" t="s">
+        <v>2286</v>
+      </c>
+      <c r="J371" t="s">
+        <v>2287</v>
+      </c>
+      <c r="K371" t="s">
+        <v>2288</v>
+      </c>
+      <c r="L371" t="s">
+        <v>440</v>
+      </c>
+      <c r="M371" t="s">
+        <v>686</v>
+      </c>
+      <c r="N371" t="s">
+        <v>113</v>
+      </c>
+      <c r="O371" t="s">
+        <v>41</v>
+      </c>
+      <c r="P371" t="s">
+        <v>1856</v>
+      </c>
+      <c r="Q371" t="s">
+        <v>781</v>
+      </c>
+      <c r="R371" t="s">
+        <v>38</v>
+      </c>
+      <c r="S371" t="s">
+        <v>201</v>
+      </c>
+      <c r="T371" t="s">
+        <v>39</v>
+      </c>
+      <c r="U371" t="s">
+        <v>201</v>
+      </c>
+      <c r="V371">
+        <v>37</v>
+      </c>
+      <c r="W371">
+        <v>12</v>
+      </c>
+      <c r="X371">
+        <v>22</v>
+      </c>
+      <c r="Y371">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB386165-BD3C-2A4D-959E-8EC8868CF434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF24FAEB-B2D5-304B-9147-AEC1E975B931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7075" uniqueCount="2289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7455" uniqueCount="2389">
   <si>
     <t>Type</t>
   </si>
@@ -6903,6 +6903,306 @@
   </si>
   <si>
     <t>64.56</t>
+  </si>
+  <si>
+    <t>85.75</t>
+  </si>
+  <si>
+    <t>1026.31</t>
+  </si>
+  <si>
+    <t>438.48</t>
+  </si>
+  <si>
+    <t>29.78</t>
+  </si>
+  <si>
+    <t>111.04</t>
+  </si>
+  <si>
+    <t>36.7</t>
+  </si>
+  <si>
+    <t>11.82</t>
+  </si>
+  <si>
+    <t>1.54</t>
+  </si>
+  <si>
+    <t>202.14</t>
+  </si>
+  <si>
+    <t>65.02</t>
+  </si>
+  <si>
+    <t>130.56</t>
+  </si>
+  <si>
+    <t>26.8</t>
+  </si>
+  <si>
+    <t>98.1</t>
+  </si>
+  <si>
+    <t>12.46</t>
+  </si>
+  <si>
+    <t>1148.49</t>
+  </si>
+  <si>
+    <t>510.49</t>
+  </si>
+  <si>
+    <t>127.03</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>142.6</t>
+  </si>
+  <si>
+    <t>37.4</t>
+  </si>
+  <si>
+    <t>9.92</t>
+  </si>
+  <si>
+    <t>877.6</t>
+  </si>
+  <si>
+    <t>442.98</t>
+  </si>
+  <si>
+    <t>101.15</t>
+  </si>
+  <si>
+    <t>108.9</t>
+  </si>
+  <si>
+    <t>27.9</t>
+  </si>
+  <si>
+    <t>81.37</t>
+  </si>
+  <si>
+    <t>9.44</t>
+  </si>
+  <si>
+    <t>741.96</t>
+  </si>
+  <si>
+    <t>433.91</t>
+  </si>
+  <si>
+    <t>28.69</t>
+  </si>
+  <si>
+    <t>116.02</t>
+  </si>
+  <si>
+    <t>21.6</t>
+  </si>
+  <si>
+    <t>2.97</t>
+  </si>
+  <si>
+    <t>386.91</t>
+  </si>
+  <si>
+    <t>125.51</t>
+  </si>
+  <si>
+    <t>137.5</t>
+  </si>
+  <si>
+    <t>14.6</t>
+  </si>
+  <si>
+    <t>11.85</t>
+  </si>
+  <si>
+    <t>707.57</t>
+  </si>
+  <si>
+    <t>546.62</t>
+  </si>
+  <si>
+    <t>120.81</t>
+  </si>
+  <si>
+    <t>105.7</t>
+  </si>
+  <si>
+    <t>369.89</t>
+  </si>
+  <si>
+    <t>418.45</t>
+  </si>
+  <si>
+    <t>31.89</t>
+  </si>
+  <si>
+    <t>98.27</t>
+  </si>
+  <si>
+    <t>45.3</t>
+  </si>
+  <si>
+    <t>1388.86</t>
+  </si>
+  <si>
+    <t>491.82</t>
+  </si>
+  <si>
+    <t>116.22</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>152.0</t>
+  </si>
+  <si>
+    <t>59.9</t>
+  </si>
+  <si>
+    <t>2.18</t>
+  </si>
+  <si>
+    <t>189.17</t>
+  </si>
+  <si>
+    <t>92.23</t>
+  </si>
+  <si>
+    <t>30.24</t>
+  </si>
+  <si>
+    <t>116.07</t>
+  </si>
+  <si>
+    <t>87.83</t>
+  </si>
+  <si>
+    <t>9.66</t>
+  </si>
+  <si>
+    <t>695.75</t>
+  </si>
+  <si>
+    <t>442.29</t>
+  </si>
+  <si>
+    <t>110.01</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>93.8</t>
+  </si>
+  <si>
+    <t>9.98</t>
+  </si>
+  <si>
+    <t>446.34</t>
+  </si>
+  <si>
+    <t>425.92</t>
+  </si>
+  <si>
+    <t>27.41</t>
+  </si>
+  <si>
+    <t>101.76</t>
+  </si>
+  <si>
+    <t>62.1</t>
+  </si>
+  <si>
+    <t>N1 J7 VS Bourges FC 17/10/2026</t>
+  </si>
+  <si>
+    <t>77.48</t>
+  </si>
+  <si>
+    <t>243.83</t>
+  </si>
+  <si>
+    <t>56.3</t>
+  </si>
+  <si>
+    <t>4.13</t>
+  </si>
+  <si>
+    <t>49.4</t>
+  </si>
+  <si>
+    <t>33.2</t>
+  </si>
+  <si>
+    <t>313.77</t>
+  </si>
+  <si>
+    <t>72.61</t>
+  </si>
+  <si>
+    <t>76.73</t>
+  </si>
+  <si>
+    <t>381.12</t>
+  </si>
+  <si>
+    <t>794.75</t>
+  </si>
+  <si>
+    <t>84.96</t>
+  </si>
+  <si>
+    <t>8.74</t>
+  </si>
+  <si>
+    <t>468.4</t>
+  </si>
+  <si>
+    <t>323.11</t>
+  </si>
+  <si>
+    <t>73.41</t>
+  </si>
+  <si>
+    <t>79.1</t>
+  </si>
+  <si>
+    <t>464.07</t>
+  </si>
+  <si>
+    <t>626.92</t>
+  </si>
+  <si>
+    <t>77.52</t>
+  </si>
+  <si>
+    <t>7.82</t>
+  </si>
+  <si>
+    <t>71.2</t>
+  </si>
+  <si>
+    <t>311.71</t>
+  </si>
+  <si>
+    <t>69.9</t>
+  </si>
+  <si>
+    <t>37.41</t>
+  </si>
+  <si>
+    <t>276.48</t>
+  </si>
+  <si>
+    <t>67.45</t>
   </si>
 </sst>
 </file>
@@ -7281,7 +7581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y371"/>
+  <dimension ref="A1:Y390"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -35477,6 +35777,1469 @@
         <v>8</v>
       </c>
     </row>
+    <row r="372" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A372" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B372" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C372" t="s">
+        <v>203</v>
+      </c>
+      <c r="D372" t="s">
+        <v>348</v>
+      </c>
+      <c r="E372" t="s">
+        <v>54</v>
+      </c>
+      <c r="F372" t="s">
+        <v>2289</v>
+      </c>
+      <c r="G372" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H372" t="s">
+        <v>2290</v>
+      </c>
+      <c r="I372" t="s">
+        <v>2291</v>
+      </c>
+      <c r="J372" t="s">
+        <v>2292</v>
+      </c>
+      <c r="K372" t="s">
+        <v>2293</v>
+      </c>
+      <c r="L372" t="s">
+        <v>315</v>
+      </c>
+      <c r="M372" t="s">
+        <v>1474</v>
+      </c>
+      <c r="N372" t="s">
+        <v>75</v>
+      </c>
+      <c r="O372" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P372" t="s">
+        <v>1913</v>
+      </c>
+      <c r="Q372" t="s">
+        <v>2294</v>
+      </c>
+      <c r="R372" t="s">
+        <v>188</v>
+      </c>
+      <c r="S372" t="s">
+        <v>66</v>
+      </c>
+      <c r="T372" t="s">
+        <v>337</v>
+      </c>
+      <c r="U372" t="s">
+        <v>39</v>
+      </c>
+      <c r="V372">
+        <v>66</v>
+      </c>
+      <c r="W372">
+        <v>48</v>
+      </c>
+      <c r="X372">
+        <v>58</v>
+      </c>
+      <c r="Y372">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="373" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A373" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B373" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C373" t="s">
+        <v>203</v>
+      </c>
+      <c r="D373" t="s">
+        <v>348</v>
+      </c>
+      <c r="E373" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F373" t="s">
+        <v>2295</v>
+      </c>
+      <c r="G373" t="s">
+        <v>2296</v>
+      </c>
+      <c r="H373" t="s">
+        <v>2297</v>
+      </c>
+      <c r="I373" t="s">
+        <v>2298</v>
+      </c>
+      <c r="J373" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K373" t="s">
+        <v>2299</v>
+      </c>
+      <c r="L373" t="s">
+        <v>782</v>
+      </c>
+      <c r="M373" t="s">
+        <v>926</v>
+      </c>
+      <c r="N373" t="s">
+        <v>177</v>
+      </c>
+      <c r="O373" t="s">
+        <v>40</v>
+      </c>
+      <c r="P373" t="s">
+        <v>2300</v>
+      </c>
+      <c r="Q373" t="s">
+        <v>2160</v>
+      </c>
+      <c r="R373" t="s">
+        <v>39</v>
+      </c>
+      <c r="S373" t="s">
+        <v>41</v>
+      </c>
+      <c r="T373" t="s">
+        <v>41</v>
+      </c>
+      <c r="U373" t="s">
+        <v>201</v>
+      </c>
+      <c r="V373">
+        <v>9</v>
+      </c>
+      <c r="W373">
+        <v>2</v>
+      </c>
+      <c r="X373">
+        <v>7</v>
+      </c>
+      <c r="Y373">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="374" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A374" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B374" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C374" t="s">
+        <v>203</v>
+      </c>
+      <c r="D374" t="s">
+        <v>348</v>
+      </c>
+      <c r="E374" t="s">
+        <v>102</v>
+      </c>
+      <c r="F374" t="s">
+        <v>2301</v>
+      </c>
+      <c r="G374" t="s">
+        <v>2302</v>
+      </c>
+      <c r="H374" t="s">
+        <v>2303</v>
+      </c>
+      <c r="I374" t="s">
+        <v>2304</v>
+      </c>
+      <c r="J374" t="s">
+        <v>882</v>
+      </c>
+      <c r="K374" t="s">
+        <v>2305</v>
+      </c>
+      <c r="L374" t="s">
+        <v>1862</v>
+      </c>
+      <c r="M374" t="s">
+        <v>55</v>
+      </c>
+      <c r="N374" t="s">
+        <v>2306</v>
+      </c>
+      <c r="O374" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P374" t="s">
+        <v>2307</v>
+      </c>
+      <c r="Q374" t="s">
+        <v>2308</v>
+      </c>
+      <c r="R374" t="s">
+        <v>188</v>
+      </c>
+      <c r="S374" t="s">
+        <v>40</v>
+      </c>
+      <c r="T374" t="s">
+        <v>35</v>
+      </c>
+      <c r="U374" t="s">
+        <v>39</v>
+      </c>
+      <c r="V374">
+        <v>103</v>
+      </c>
+      <c r="W374">
+        <v>38</v>
+      </c>
+      <c r="X374">
+        <v>76</v>
+      </c>
+      <c r="Y374">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="375" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A375" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B375" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C375" t="s">
+        <v>203</v>
+      </c>
+      <c r="D375" t="s">
+        <v>348</v>
+      </c>
+      <c r="E375" t="s">
+        <v>895</v>
+      </c>
+      <c r="F375" t="s">
+        <v>2301</v>
+      </c>
+      <c r="G375" t="s">
+        <v>2309</v>
+      </c>
+      <c r="H375" t="s">
+        <v>2310</v>
+      </c>
+      <c r="I375" t="s">
+        <v>2311</v>
+      </c>
+      <c r="J375" t="s">
+        <v>832</v>
+      </c>
+      <c r="K375" t="s">
+        <v>2312</v>
+      </c>
+      <c r="L375" t="s">
+        <v>376</v>
+      </c>
+      <c r="M375" t="s">
+        <v>866</v>
+      </c>
+      <c r="N375" t="s">
+        <v>857</v>
+      </c>
+      <c r="O375" t="s">
+        <v>672</v>
+      </c>
+      <c r="P375" t="s">
+        <v>2313</v>
+      </c>
+      <c r="Q375" t="s">
+        <v>2314</v>
+      </c>
+      <c r="R375" t="s">
+        <v>449</v>
+      </c>
+      <c r="S375" t="s">
+        <v>66</v>
+      </c>
+      <c r="T375" t="s">
+        <v>280</v>
+      </c>
+      <c r="U375" t="s">
+        <v>39</v>
+      </c>
+      <c r="V375">
+        <v>75</v>
+      </c>
+      <c r="W375">
+        <v>42</v>
+      </c>
+      <c r="X375">
+        <v>67</v>
+      </c>
+      <c r="Y375">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="376" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A376" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B376" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C376" t="s">
+        <v>203</v>
+      </c>
+      <c r="D376" t="s">
+        <v>348</v>
+      </c>
+      <c r="E376" t="s">
+        <v>126</v>
+      </c>
+      <c r="F376" t="s">
+        <v>2315</v>
+      </c>
+      <c r="G376" t="s">
+        <v>2316</v>
+      </c>
+      <c r="H376" t="s">
+        <v>2317</v>
+      </c>
+      <c r="I376" t="s">
+        <v>2318</v>
+      </c>
+      <c r="J376" t="s">
+        <v>2319</v>
+      </c>
+      <c r="K376" t="s">
+        <v>2320</v>
+      </c>
+      <c r="L376" t="s">
+        <v>415</v>
+      </c>
+      <c r="M376" t="s">
+        <v>1350</v>
+      </c>
+      <c r="N376" t="s">
+        <v>62</v>
+      </c>
+      <c r="O376" t="s">
+        <v>449</v>
+      </c>
+      <c r="P376" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q376" t="s">
+        <v>2148</v>
+      </c>
+      <c r="R376" t="s">
+        <v>35</v>
+      </c>
+      <c r="S376" t="s">
+        <v>40</v>
+      </c>
+      <c r="T376" t="s">
+        <v>40</v>
+      </c>
+      <c r="U376" t="s">
+        <v>41</v>
+      </c>
+      <c r="V376">
+        <v>53</v>
+      </c>
+      <c r="W376">
+        <v>17</v>
+      </c>
+      <c r="X376">
+        <v>45</v>
+      </c>
+      <c r="Y376">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="377" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A377" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B377" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C377" t="s">
+        <v>203</v>
+      </c>
+      <c r="D377" t="s">
+        <v>348</v>
+      </c>
+      <c r="E377" t="s">
+        <v>346</v>
+      </c>
+      <c r="F377" t="s">
+        <v>2321</v>
+      </c>
+      <c r="G377" t="s">
+        <v>2322</v>
+      </c>
+      <c r="H377" t="s">
+        <v>2323</v>
+      </c>
+      <c r="I377" t="s">
+        <v>2324</v>
+      </c>
+      <c r="J377" t="s">
+        <v>832</v>
+      </c>
+      <c r="K377" t="s">
+        <v>2325</v>
+      </c>
+      <c r="L377" t="s">
+        <v>1903</v>
+      </c>
+      <c r="M377" t="s">
+        <v>1476</v>
+      </c>
+      <c r="N377" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O377" t="s">
+        <v>449</v>
+      </c>
+      <c r="P377" t="s">
+        <v>1010</v>
+      </c>
+      <c r="Q377" t="s">
+        <v>2326</v>
+      </c>
+      <c r="R377" t="s">
+        <v>40</v>
+      </c>
+      <c r="S377" t="s">
+        <v>41</v>
+      </c>
+      <c r="T377" t="s">
+        <v>39</v>
+      </c>
+      <c r="U377" t="s">
+        <v>41</v>
+      </c>
+      <c r="V377">
+        <v>19</v>
+      </c>
+      <c r="W377">
+        <v>9</v>
+      </c>
+      <c r="X377">
+        <v>28</v>
+      </c>
+      <c r="Y377">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="378" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A378" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B378" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C378" t="s">
+        <v>203</v>
+      </c>
+      <c r="D378" t="s">
+        <v>348</v>
+      </c>
+      <c r="E378" t="s">
+        <v>137</v>
+      </c>
+      <c r="F378" t="s">
+        <v>2301</v>
+      </c>
+      <c r="G378" t="s">
+        <v>2327</v>
+      </c>
+      <c r="H378" t="s">
+        <v>2328</v>
+      </c>
+      <c r="I378" t="s">
+        <v>2329</v>
+      </c>
+      <c r="J378" t="s">
+        <v>1552</v>
+      </c>
+      <c r="K378" t="s">
+        <v>2330</v>
+      </c>
+      <c r="L378" t="s">
+        <v>251</v>
+      </c>
+      <c r="M378" t="s">
+        <v>821</v>
+      </c>
+      <c r="N378" t="s">
+        <v>2118</v>
+      </c>
+      <c r="O378" t="s">
+        <v>35</v>
+      </c>
+      <c r="P378" t="s">
+        <v>2331</v>
+      </c>
+      <c r="Q378" t="s">
+        <v>1151</v>
+      </c>
+      <c r="R378" t="s">
+        <v>488</v>
+      </c>
+      <c r="S378" t="s">
+        <v>40</v>
+      </c>
+      <c r="T378" t="s">
+        <v>35</v>
+      </c>
+      <c r="U378" t="s">
+        <v>41</v>
+      </c>
+      <c r="V378">
+        <v>87</v>
+      </c>
+      <c r="W378">
+        <v>40</v>
+      </c>
+      <c r="X378">
+        <v>77</v>
+      </c>
+      <c r="Y378">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="379" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A379" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B379" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C379" t="s">
+        <v>203</v>
+      </c>
+      <c r="D379" t="s">
+        <v>348</v>
+      </c>
+      <c r="E379" t="s">
+        <v>147</v>
+      </c>
+      <c r="F379" t="s">
+        <v>2301</v>
+      </c>
+      <c r="G379" t="s">
+        <v>896</v>
+      </c>
+      <c r="H379" t="s">
+        <v>2332</v>
+      </c>
+      <c r="I379" t="s">
+        <v>2333</v>
+      </c>
+      <c r="J379" t="s">
+        <v>2334</v>
+      </c>
+      <c r="K379" t="s">
+        <v>2335</v>
+      </c>
+      <c r="L379" t="s">
+        <v>1617</v>
+      </c>
+      <c r="M379" t="s">
+        <v>828</v>
+      </c>
+      <c r="N379" t="s">
+        <v>110</v>
+      </c>
+      <c r="O379" t="s">
+        <v>488</v>
+      </c>
+      <c r="P379" t="s">
+        <v>2336</v>
+      </c>
+      <c r="Q379" t="s">
+        <v>572</v>
+      </c>
+      <c r="R379" t="s">
+        <v>113</v>
+      </c>
+      <c r="S379" t="s">
+        <v>38</v>
+      </c>
+      <c r="T379" t="s">
+        <v>40</v>
+      </c>
+      <c r="U379" t="s">
+        <v>41</v>
+      </c>
+      <c r="V379">
+        <v>50</v>
+      </c>
+      <c r="W379">
+        <v>25</v>
+      </c>
+      <c r="X379">
+        <v>41</v>
+      </c>
+      <c r="Y379">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="380" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A380" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B380" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C380" t="s">
+        <v>203</v>
+      </c>
+      <c r="D380" t="s">
+        <v>348</v>
+      </c>
+      <c r="E380" t="s">
+        <v>157</v>
+      </c>
+      <c r="F380" t="s">
+        <v>2301</v>
+      </c>
+      <c r="G380" t="s">
+        <v>463</v>
+      </c>
+      <c r="H380" t="s">
+        <v>2337</v>
+      </c>
+      <c r="I380" t="s">
+        <v>2338</v>
+      </c>
+      <c r="J380" t="s">
+        <v>1485</v>
+      </c>
+      <c r="K380" t="s">
+        <v>2339</v>
+      </c>
+      <c r="L380" t="s">
+        <v>1713</v>
+      </c>
+      <c r="M380" t="s">
+        <v>421</v>
+      </c>
+      <c r="N380" t="s">
+        <v>2340</v>
+      </c>
+      <c r="O380" t="s">
+        <v>144</v>
+      </c>
+      <c r="P380" t="s">
+        <v>2341</v>
+      </c>
+      <c r="Q380" t="s">
+        <v>2342</v>
+      </c>
+      <c r="R380" t="s">
+        <v>495</v>
+      </c>
+      <c r="S380" t="s">
+        <v>113</v>
+      </c>
+      <c r="T380" t="s">
+        <v>51</v>
+      </c>
+      <c r="U380" t="s">
+        <v>38</v>
+      </c>
+      <c r="V380">
+        <v>99</v>
+      </c>
+      <c r="W380">
+        <v>52</v>
+      </c>
+      <c r="X380">
+        <v>66</v>
+      </c>
+      <c r="Y380">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="381" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A381" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B381" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C381" t="s">
+        <v>203</v>
+      </c>
+      <c r="D381" t="s">
+        <v>348</v>
+      </c>
+      <c r="E381" t="s">
+        <v>933</v>
+      </c>
+      <c r="F381" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G381" t="s">
+        <v>2343</v>
+      </c>
+      <c r="H381" t="s">
+        <v>2344</v>
+      </c>
+      <c r="I381" t="s">
+        <v>2345</v>
+      </c>
+      <c r="J381" t="s">
+        <v>2346</v>
+      </c>
+      <c r="K381" t="s">
+        <v>2347</v>
+      </c>
+      <c r="L381" t="s">
+        <v>583</v>
+      </c>
+      <c r="M381" t="s">
+        <v>74</v>
+      </c>
+      <c r="N381" t="s">
+        <v>51</v>
+      </c>
+      <c r="O381" t="s">
+        <v>113</v>
+      </c>
+      <c r="P381" t="s">
+        <v>2321</v>
+      </c>
+      <c r="Q381" t="s">
+        <v>398</v>
+      </c>
+      <c r="R381" t="s">
+        <v>39</v>
+      </c>
+      <c r="S381" t="s">
+        <v>41</v>
+      </c>
+      <c r="T381" t="s">
+        <v>41</v>
+      </c>
+      <c r="U381" t="s">
+        <v>201</v>
+      </c>
+      <c r="V381">
+        <v>11</v>
+      </c>
+      <c r="W381">
+        <v>6</v>
+      </c>
+      <c r="X381">
+        <v>14</v>
+      </c>
+      <c r="Y381">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="382" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B382" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C382" t="s">
+        <v>203</v>
+      </c>
+      <c r="D382" t="s">
+        <v>348</v>
+      </c>
+      <c r="E382" t="s">
+        <v>180</v>
+      </c>
+      <c r="F382" t="s">
+        <v>2348</v>
+      </c>
+      <c r="G382" t="s">
+        <v>2349</v>
+      </c>
+      <c r="H382" t="s">
+        <v>2350</v>
+      </c>
+      <c r="I382" t="s">
+        <v>2351</v>
+      </c>
+      <c r="J382" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K382" t="s">
+        <v>2352</v>
+      </c>
+      <c r="L382" t="s">
+        <v>834</v>
+      </c>
+      <c r="M382" t="s">
+        <v>362</v>
+      </c>
+      <c r="N382" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O382" t="s">
+        <v>51</v>
+      </c>
+      <c r="P382" t="s">
+        <v>2354</v>
+      </c>
+      <c r="Q382" t="s">
+        <v>664</v>
+      </c>
+      <c r="R382" t="s">
+        <v>280</v>
+      </c>
+      <c r="S382" t="s">
+        <v>40</v>
+      </c>
+      <c r="T382" t="s">
+        <v>113</v>
+      </c>
+      <c r="U382" t="s">
+        <v>41</v>
+      </c>
+      <c r="V382">
+        <v>68</v>
+      </c>
+      <c r="W382">
+        <v>26</v>
+      </c>
+      <c r="X382">
+        <v>54</v>
+      </c>
+      <c r="Y382">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="383" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B383" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C383" t="s">
+        <v>203</v>
+      </c>
+      <c r="D383" t="s">
+        <v>348</v>
+      </c>
+      <c r="E383" t="s">
+        <v>191</v>
+      </c>
+      <c r="F383" t="s">
+        <v>2301</v>
+      </c>
+      <c r="G383" t="s">
+        <v>2355</v>
+      </c>
+      <c r="H383" t="s">
+        <v>2356</v>
+      </c>
+      <c r="I383" t="s">
+        <v>2357</v>
+      </c>
+      <c r="J383" t="s">
+        <v>2358</v>
+      </c>
+      <c r="K383" t="s">
+        <v>2359</v>
+      </c>
+      <c r="L383" t="s">
+        <v>1316</v>
+      </c>
+      <c r="M383" t="s">
+        <v>399</v>
+      </c>
+      <c r="N383" t="s">
+        <v>242</v>
+      </c>
+      <c r="O383" t="s">
+        <v>113</v>
+      </c>
+      <c r="P383" t="s">
+        <v>2360</v>
+      </c>
+      <c r="Q383" t="s">
+        <v>37</v>
+      </c>
+      <c r="R383" t="s">
+        <v>113</v>
+      </c>
+      <c r="S383" t="s">
+        <v>41</v>
+      </c>
+      <c r="T383" t="s">
+        <v>113</v>
+      </c>
+      <c r="U383" t="s">
+        <v>41</v>
+      </c>
+      <c r="V383">
+        <v>57</v>
+      </c>
+      <c r="W383">
+        <v>27</v>
+      </c>
+      <c r="X383">
+        <v>51</v>
+      </c>
+      <c r="Y383">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="384" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>202</v>
+      </c>
+      <c r="B384" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C384" t="s">
+        <v>203</v>
+      </c>
+      <c r="D384" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E384" t="s">
+        <v>25</v>
+      </c>
+      <c r="F384" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G384" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H384" t="s">
+        <v>1536</v>
+      </c>
+      <c r="I384" t="s">
+        <v>2363</v>
+      </c>
+      <c r="J384" t="s">
+        <v>1589</v>
+      </c>
+      <c r="K384" t="s">
+        <v>2364</v>
+      </c>
+      <c r="L384" t="s">
+        <v>2365</v>
+      </c>
+      <c r="M384" t="s">
+        <v>989</v>
+      </c>
+      <c r="N384" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O384" t="s">
+        <v>201</v>
+      </c>
+      <c r="P384" t="s">
+        <v>2366</v>
+      </c>
+      <c r="Q384" t="s">
+        <v>201</v>
+      </c>
+      <c r="R384" t="s">
+        <v>39</v>
+      </c>
+      <c r="S384" t="s">
+        <v>201</v>
+      </c>
+      <c r="T384" t="s">
+        <v>38</v>
+      </c>
+      <c r="U384" t="s">
+        <v>41</v>
+      </c>
+      <c r="V384">
+        <v>26</v>
+      </c>
+      <c r="W384">
+        <v>23</v>
+      </c>
+      <c r="X384">
+        <v>27</v>
+      </c>
+      <c r="Y384">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="385" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A385" t="s">
+        <v>202</v>
+      </c>
+      <c r="B385" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C385" t="s">
+        <v>203</v>
+      </c>
+      <c r="D385" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E385" t="s">
+        <v>54</v>
+      </c>
+      <c r="F385" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G385" t="s">
+        <v>534</v>
+      </c>
+      <c r="H385" t="s">
+        <v>2367</v>
+      </c>
+      <c r="I385" t="s">
+        <v>2368</v>
+      </c>
+      <c r="J385" t="s">
+        <v>1586</v>
+      </c>
+      <c r="K385" t="s">
+        <v>2369</v>
+      </c>
+      <c r="L385" t="s">
+        <v>1078</v>
+      </c>
+      <c r="M385" t="s">
+        <v>421</v>
+      </c>
+      <c r="N385" t="s">
+        <v>38</v>
+      </c>
+      <c r="O385" t="s">
+        <v>201</v>
+      </c>
+      <c r="P385" t="s">
+        <v>759</v>
+      </c>
+      <c r="Q385" t="s">
+        <v>455</v>
+      </c>
+      <c r="R385" t="s">
+        <v>40</v>
+      </c>
+      <c r="S385" t="s">
+        <v>39</v>
+      </c>
+      <c r="T385" t="s">
+        <v>38</v>
+      </c>
+      <c r="U385" t="s">
+        <v>41</v>
+      </c>
+      <c r="V385">
+        <v>41</v>
+      </c>
+      <c r="W385">
+        <v>22</v>
+      </c>
+      <c r="X385">
+        <v>43</v>
+      </c>
+      <c r="Y385">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="386" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>202</v>
+      </c>
+      <c r="B386" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C386" t="s">
+        <v>203</v>
+      </c>
+      <c r="D386" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E386" t="s">
+        <v>90</v>
+      </c>
+      <c r="F386" t="s">
+        <v>2370</v>
+      </c>
+      <c r="G386" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H386" t="s">
+        <v>2371</v>
+      </c>
+      <c r="I386" t="s">
+        <v>2372</v>
+      </c>
+      <c r="J386" t="s">
+        <v>1948</v>
+      </c>
+      <c r="K386" t="s">
+        <v>2373</v>
+      </c>
+      <c r="L386" t="s">
+        <v>2374</v>
+      </c>
+      <c r="M386" t="s">
+        <v>414</v>
+      </c>
+      <c r="N386" t="s">
+        <v>579</v>
+      </c>
+      <c r="O386" t="s">
+        <v>40</v>
+      </c>
+      <c r="P386" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q386" t="s">
+        <v>264</v>
+      </c>
+      <c r="R386" t="s">
+        <v>495</v>
+      </c>
+      <c r="S386" t="s">
+        <v>35</v>
+      </c>
+      <c r="T386" t="s">
+        <v>280</v>
+      </c>
+      <c r="U386" t="s">
+        <v>40</v>
+      </c>
+      <c r="V386">
+        <v>114</v>
+      </c>
+      <c r="W386">
+        <v>96</v>
+      </c>
+      <c r="X386">
+        <v>177</v>
+      </c>
+      <c r="Y386">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="387" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>202</v>
+      </c>
+      <c r="B387" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C387" t="s">
+        <v>203</v>
+      </c>
+      <c r="D387" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E387" t="s">
+        <v>114</v>
+      </c>
+      <c r="F387" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G387" t="s">
+        <v>782</v>
+      </c>
+      <c r="H387" t="s">
+        <v>2375</v>
+      </c>
+      <c r="I387" t="s">
+        <v>2376</v>
+      </c>
+      <c r="J387" t="s">
+        <v>1189</v>
+      </c>
+      <c r="K387" t="s">
+        <v>2377</v>
+      </c>
+      <c r="L387" t="s">
+        <v>283</v>
+      </c>
+      <c r="M387" t="s">
+        <v>269</v>
+      </c>
+      <c r="N387" t="s">
+        <v>144</v>
+      </c>
+      <c r="O387" t="s">
+        <v>41</v>
+      </c>
+      <c r="P387" t="s">
+        <v>2378</v>
+      </c>
+      <c r="Q387" t="s">
+        <v>1358</v>
+      </c>
+      <c r="R387" t="s">
+        <v>38</v>
+      </c>
+      <c r="S387" t="s">
+        <v>41</v>
+      </c>
+      <c r="T387" t="s">
+        <v>66</v>
+      </c>
+      <c r="U387" t="s">
+        <v>41</v>
+      </c>
+      <c r="V387">
+        <v>52</v>
+      </c>
+      <c r="W387">
+        <v>34</v>
+      </c>
+      <c r="X387">
+        <v>27</v>
+      </c>
+      <c r="Y387">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="388" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
+        <v>202</v>
+      </c>
+      <c r="B388" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C388" t="s">
+        <v>203</v>
+      </c>
+      <c r="D388" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E388" t="s">
+        <v>346</v>
+      </c>
+      <c r="F388" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G388" t="s">
+        <v>121</v>
+      </c>
+      <c r="H388" t="s">
+        <v>2379</v>
+      </c>
+      <c r="I388" t="s">
+        <v>2380</v>
+      </c>
+      <c r="J388" t="s">
+        <v>1362</v>
+      </c>
+      <c r="K388" t="s">
+        <v>2381</v>
+      </c>
+      <c r="L388" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M388" t="s">
+        <v>1694</v>
+      </c>
+      <c r="N388" t="s">
+        <v>324</v>
+      </c>
+      <c r="O388" t="s">
+        <v>38</v>
+      </c>
+      <c r="P388" t="s">
+        <v>2383</v>
+      </c>
+      <c r="Q388" t="s">
+        <v>272</v>
+      </c>
+      <c r="R388" t="s">
+        <v>449</v>
+      </c>
+      <c r="S388" t="s">
+        <v>113</v>
+      </c>
+      <c r="T388" t="s">
+        <v>280</v>
+      </c>
+      <c r="U388" t="s">
+        <v>40</v>
+      </c>
+      <c r="V388">
+        <v>97</v>
+      </c>
+      <c r="W388">
+        <v>65</v>
+      </c>
+      <c r="X388">
+        <v>87</v>
+      </c>
+      <c r="Y388">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="389" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
+        <v>202</v>
+      </c>
+      <c r="B389" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C389" t="s">
+        <v>203</v>
+      </c>
+      <c r="D389" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E389" t="s">
+        <v>137</v>
+      </c>
+      <c r="F389" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G389" t="s">
+        <v>487</v>
+      </c>
+      <c r="H389" t="s">
+        <v>27</v>
+      </c>
+      <c r="I389" t="s">
+        <v>2384</v>
+      </c>
+      <c r="J389" t="s">
+        <v>763</v>
+      </c>
+      <c r="K389" t="s">
+        <v>2385</v>
+      </c>
+      <c r="L389" t="s">
+        <v>707</v>
+      </c>
+      <c r="M389" t="s">
+        <v>391</v>
+      </c>
+      <c r="N389" t="s">
+        <v>41</v>
+      </c>
+      <c r="O389" t="s">
+        <v>201</v>
+      </c>
+      <c r="P389" t="s">
+        <v>781</v>
+      </c>
+      <c r="Q389" t="s">
+        <v>201</v>
+      </c>
+      <c r="R389" t="s">
+        <v>39</v>
+      </c>
+      <c r="S389" t="s">
+        <v>41</v>
+      </c>
+      <c r="T389" t="s">
+        <v>39</v>
+      </c>
+      <c r="U389" t="s">
+        <v>201</v>
+      </c>
+      <c r="V389">
+        <v>20</v>
+      </c>
+      <c r="W389">
+        <v>10</v>
+      </c>
+      <c r="X389">
+        <v>24</v>
+      </c>
+      <c r="Y389">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="390" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>202</v>
+      </c>
+      <c r="B390" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C390" t="s">
+        <v>203</v>
+      </c>
+      <c r="D390" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E390" t="s">
+        <v>191</v>
+      </c>
+      <c r="F390" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G390" t="s">
+        <v>211</v>
+      </c>
+      <c r="H390" t="s">
+        <v>2386</v>
+      </c>
+      <c r="I390" t="s">
+        <v>2387</v>
+      </c>
+      <c r="J390" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K390" t="s">
+        <v>2388</v>
+      </c>
+      <c r="L390" t="s">
+        <v>478</v>
+      </c>
+      <c r="M390" t="s">
+        <v>362</v>
+      </c>
+      <c r="N390" t="s">
+        <v>38</v>
+      </c>
+      <c r="O390" t="s">
+        <v>201</v>
+      </c>
+      <c r="P390" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q390" t="s">
+        <v>455</v>
+      </c>
+      <c r="R390" t="s">
+        <v>41</v>
+      </c>
+      <c r="S390" t="s">
+        <v>201</v>
+      </c>
+      <c r="T390" t="s">
+        <v>39</v>
+      </c>
+      <c r="U390" t="s">
+        <v>41</v>
+      </c>
+      <c r="V390">
+        <v>22</v>
+      </c>
+      <c r="W390">
+        <v>13</v>
+      </c>
+      <c r="X390">
+        <v>9</v>
+      </c>
+      <c r="Y390">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF24FAEB-B2D5-304B-9147-AEC1E975B931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAB64EC-6840-7744-A51A-92D8647F3FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7455" uniqueCount="2389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7655" uniqueCount="2428">
   <si>
     <t>Type</t>
   </si>
@@ -7203,6 +7203,123 @@
   </si>
   <si>
     <t>67.45</t>
+  </si>
+  <si>
+    <t>101.4</t>
+  </si>
+  <si>
+    <t>141.12</t>
+  </si>
+  <si>
+    <t>282.12</t>
+  </si>
+  <si>
+    <t>56.59</t>
+  </si>
+  <si>
+    <t>22.9</t>
+  </si>
+  <si>
+    <t>48.83</t>
+  </si>
+  <si>
+    <t>305.84</t>
+  </si>
+  <si>
+    <t>24.43</t>
+  </si>
+  <si>
+    <t>54.77</t>
+  </si>
+  <si>
+    <t>6.77</t>
+  </si>
+  <si>
+    <t>38.46</t>
+  </si>
+  <si>
+    <t>365.11</t>
+  </si>
+  <si>
+    <t>24.62</t>
+  </si>
+  <si>
+    <t>61.55</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>261.01</t>
+  </si>
+  <si>
+    <t>19.29</t>
+  </si>
+  <si>
+    <t>43.94</t>
+  </si>
+  <si>
+    <t>130.89</t>
+  </si>
+  <si>
+    <t>336.15</t>
+  </si>
+  <si>
+    <t>54.31</t>
+  </si>
+  <si>
+    <t>127.65</t>
+  </si>
+  <si>
+    <t>338.68</t>
+  </si>
+  <si>
+    <t>66.03</t>
+  </si>
+  <si>
+    <t>32.28</t>
+  </si>
+  <si>
+    <t>352.95</t>
+  </si>
+  <si>
+    <t>23.34</t>
+  </si>
+  <si>
+    <t>61.14</t>
+  </si>
+  <si>
+    <t>43.73</t>
+  </si>
+  <si>
+    <t>498.67</t>
+  </si>
+  <si>
+    <t>23.32</t>
+  </si>
+  <si>
+    <t>51.22</t>
+  </si>
+  <si>
+    <t>266.9</t>
+  </si>
+  <si>
+    <t>21.72</t>
+  </si>
+  <si>
+    <t>49.05</t>
+  </si>
+  <si>
+    <t>29.33</t>
+  </si>
+  <si>
+    <t>237.22</t>
+  </si>
+  <si>
+    <t>22.45</t>
+  </si>
+  <si>
+    <t>46.24</t>
   </si>
 </sst>
 </file>
@@ -7581,7 +7698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y390"/>
+  <dimension ref="A1:Y400"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -37240,6 +37357,776 @@
         <v>5</v>
       </c>
     </row>
+    <row r="391" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
+        <v>202</v>
+      </c>
+      <c r="B391" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C391" t="s">
+        <v>203</v>
+      </c>
+      <c r="D391" t="s">
+        <v>848</v>
+      </c>
+      <c r="E391" t="s">
+        <v>25</v>
+      </c>
+      <c r="F391" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G391" t="s">
+        <v>699</v>
+      </c>
+      <c r="H391" t="s">
+        <v>2390</v>
+      </c>
+      <c r="I391" t="s">
+        <v>2391</v>
+      </c>
+      <c r="J391" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K391" t="s">
+        <v>2392</v>
+      </c>
+      <c r="L391" t="s">
+        <v>1966</v>
+      </c>
+      <c r="M391" t="s">
+        <v>278</v>
+      </c>
+      <c r="N391" t="s">
+        <v>555</v>
+      </c>
+      <c r="O391" t="s">
+        <v>201</v>
+      </c>
+      <c r="P391" t="s">
+        <v>2393</v>
+      </c>
+      <c r="Q391" t="s">
+        <v>87</v>
+      </c>
+      <c r="R391" t="s">
+        <v>40</v>
+      </c>
+      <c r="S391" t="s">
+        <v>39</v>
+      </c>
+      <c r="T391" t="s">
+        <v>66</v>
+      </c>
+      <c r="U391" t="s">
+        <v>41</v>
+      </c>
+      <c r="V391">
+        <v>66</v>
+      </c>
+      <c r="W391">
+        <v>29</v>
+      </c>
+      <c r="X391">
+        <v>44</v>
+      </c>
+      <c r="Y391">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="392" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>202</v>
+      </c>
+      <c r="B392" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C392" t="s">
+        <v>203</v>
+      </c>
+      <c r="D392" t="s">
+        <v>848</v>
+      </c>
+      <c r="E392" t="s">
+        <v>54</v>
+      </c>
+      <c r="F392" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G392" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H392" t="s">
+        <v>2394</v>
+      </c>
+      <c r="I392" t="s">
+        <v>2395</v>
+      </c>
+      <c r="J392" t="s">
+        <v>2396</v>
+      </c>
+      <c r="K392" t="s">
+        <v>2397</v>
+      </c>
+      <c r="L392" t="s">
+        <v>2398</v>
+      </c>
+      <c r="M392" t="s">
+        <v>406</v>
+      </c>
+      <c r="N392" t="s">
+        <v>66</v>
+      </c>
+      <c r="O392" t="s">
+        <v>201</v>
+      </c>
+      <c r="P392" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q392" t="s">
+        <v>471</v>
+      </c>
+      <c r="R392" t="s">
+        <v>35</v>
+      </c>
+      <c r="S392" t="s">
+        <v>38</v>
+      </c>
+      <c r="T392" t="s">
+        <v>113</v>
+      </c>
+      <c r="U392" t="s">
+        <v>41</v>
+      </c>
+      <c r="V392">
+        <v>82</v>
+      </c>
+      <c r="W392">
+        <v>36</v>
+      </c>
+      <c r="X392">
+        <v>65</v>
+      </c>
+      <c r="Y392">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="393" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>202</v>
+      </c>
+      <c r="B393" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C393" t="s">
+        <v>203</v>
+      </c>
+      <c r="D393" t="s">
+        <v>848</v>
+      </c>
+      <c r="E393" t="s">
+        <v>90</v>
+      </c>
+      <c r="F393" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G393" t="s">
+        <v>788</v>
+      </c>
+      <c r="H393" t="s">
+        <v>2399</v>
+      </c>
+      <c r="I393" t="s">
+        <v>2400</v>
+      </c>
+      <c r="J393" t="s">
+        <v>2401</v>
+      </c>
+      <c r="K393" t="s">
+        <v>2402</v>
+      </c>
+      <c r="L393" t="s">
+        <v>306</v>
+      </c>
+      <c r="M393" t="s">
+        <v>534</v>
+      </c>
+      <c r="N393" t="s">
+        <v>40</v>
+      </c>
+      <c r="O393" t="s">
+        <v>201</v>
+      </c>
+      <c r="P393" t="s">
+        <v>1903</v>
+      </c>
+      <c r="Q393" t="s">
+        <v>488</v>
+      </c>
+      <c r="R393" t="s">
+        <v>66</v>
+      </c>
+      <c r="S393" t="s">
+        <v>41</v>
+      </c>
+      <c r="T393" t="s">
+        <v>40</v>
+      </c>
+      <c r="U393" t="s">
+        <v>41</v>
+      </c>
+      <c r="V393">
+        <v>71</v>
+      </c>
+      <c r="W393">
+        <v>24</v>
+      </c>
+      <c r="X393">
+        <v>50</v>
+      </c>
+      <c r="Y393">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="394" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>202</v>
+      </c>
+      <c r="B394" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C394" t="s">
+        <v>203</v>
+      </c>
+      <c r="D394" t="s">
+        <v>848</v>
+      </c>
+      <c r="E394" t="s">
+        <v>102</v>
+      </c>
+      <c r="F394" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G394" t="s">
+        <v>215</v>
+      </c>
+      <c r="H394" t="s">
+        <v>2403</v>
+      </c>
+      <c r="I394" t="s">
+        <v>2404</v>
+      </c>
+      <c r="J394" t="s">
+        <v>2405</v>
+      </c>
+      <c r="K394" t="s">
+        <v>2406</v>
+      </c>
+      <c r="L394" t="s">
+        <v>2284</v>
+      </c>
+      <c r="M394" t="s">
+        <v>701</v>
+      </c>
+      <c r="N394" t="s">
+        <v>201</v>
+      </c>
+      <c r="O394" t="s">
+        <v>201</v>
+      </c>
+      <c r="P394" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q394" t="s">
+        <v>201</v>
+      </c>
+      <c r="R394" t="s">
+        <v>38</v>
+      </c>
+      <c r="S394" t="s">
+        <v>41</v>
+      </c>
+      <c r="T394" t="s">
+        <v>38</v>
+      </c>
+      <c r="U394" t="s">
+        <v>201</v>
+      </c>
+      <c r="V394">
+        <v>41</v>
+      </c>
+      <c r="W394">
+        <v>15</v>
+      </c>
+      <c r="X394">
+        <v>31</v>
+      </c>
+      <c r="Y394">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="395" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>202</v>
+      </c>
+      <c r="B395" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C395" t="s">
+        <v>203</v>
+      </c>
+      <c r="D395" t="s">
+        <v>848</v>
+      </c>
+      <c r="E395" t="s">
+        <v>114</v>
+      </c>
+      <c r="F395" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G395" t="s">
+        <v>662</v>
+      </c>
+      <c r="H395" t="s">
+        <v>2407</v>
+      </c>
+      <c r="I395" t="s">
+        <v>2408</v>
+      </c>
+      <c r="J395" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K395" t="s">
+        <v>2409</v>
+      </c>
+      <c r="L395" t="s">
+        <v>2091</v>
+      </c>
+      <c r="M395" t="s">
+        <v>1175</v>
+      </c>
+      <c r="N395" t="s">
+        <v>449</v>
+      </c>
+      <c r="O395" t="s">
+        <v>39</v>
+      </c>
+      <c r="P395" t="s">
+        <v>1934</v>
+      </c>
+      <c r="Q395" t="s">
+        <v>1396</v>
+      </c>
+      <c r="R395" t="s">
+        <v>66</v>
+      </c>
+      <c r="S395" t="s">
+        <v>38</v>
+      </c>
+      <c r="T395" t="s">
+        <v>113</v>
+      </c>
+      <c r="U395" t="s">
+        <v>39</v>
+      </c>
+      <c r="V395">
+        <v>70</v>
+      </c>
+      <c r="W395">
+        <v>37</v>
+      </c>
+      <c r="X395">
+        <v>40</v>
+      </c>
+      <c r="Y395">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="396" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>202</v>
+      </c>
+      <c r="B396" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C396" t="s">
+        <v>203</v>
+      </c>
+      <c r="D396" t="s">
+        <v>848</v>
+      </c>
+      <c r="E396" t="s">
+        <v>126</v>
+      </c>
+      <c r="F396" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G396" t="s">
+        <v>174</v>
+      </c>
+      <c r="H396" t="s">
+        <v>2410</v>
+      </c>
+      <c r="I396" t="s">
+        <v>2411</v>
+      </c>
+      <c r="J396" t="s">
+        <v>2094</v>
+      </c>
+      <c r="K396" t="s">
+        <v>2412</v>
+      </c>
+      <c r="L396" t="s">
+        <v>1350</v>
+      </c>
+      <c r="M396" t="s">
+        <v>511</v>
+      </c>
+      <c r="N396" t="s">
+        <v>188</v>
+      </c>
+      <c r="O396" t="s">
+        <v>41</v>
+      </c>
+      <c r="P396" t="s">
+        <v>1405</v>
+      </c>
+      <c r="Q396" t="s">
+        <v>371</v>
+      </c>
+      <c r="R396" t="s">
+        <v>66</v>
+      </c>
+      <c r="S396" t="s">
+        <v>39</v>
+      </c>
+      <c r="T396" t="s">
+        <v>40</v>
+      </c>
+      <c r="U396" t="s">
+        <v>41</v>
+      </c>
+      <c r="V396">
+        <v>63</v>
+      </c>
+      <c r="W396">
+        <v>15</v>
+      </c>
+      <c r="X396">
+        <v>45</v>
+      </c>
+      <c r="Y396">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="397" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
+        <v>202</v>
+      </c>
+      <c r="B397" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C397" t="s">
+        <v>203</v>
+      </c>
+      <c r="D397" t="s">
+        <v>848</v>
+      </c>
+      <c r="E397" t="s">
+        <v>137</v>
+      </c>
+      <c r="F397" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G397" t="s">
+        <v>289</v>
+      </c>
+      <c r="H397" t="s">
+        <v>2413</v>
+      </c>
+      <c r="I397" t="s">
+        <v>2414</v>
+      </c>
+      <c r="J397" t="s">
+        <v>2415</v>
+      </c>
+      <c r="K397" t="s">
+        <v>2416</v>
+      </c>
+      <c r="L397" t="s">
+        <v>1682</v>
+      </c>
+      <c r="M397" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N397" t="s">
+        <v>38</v>
+      </c>
+      <c r="O397" t="s">
+        <v>201</v>
+      </c>
+      <c r="P397" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q397" t="s">
+        <v>201</v>
+      </c>
+      <c r="R397" t="s">
+        <v>337</v>
+      </c>
+      <c r="S397" t="s">
+        <v>39</v>
+      </c>
+      <c r="T397" t="s">
+        <v>66</v>
+      </c>
+      <c r="U397" t="s">
+        <v>41</v>
+      </c>
+      <c r="V397">
+        <v>82</v>
+      </c>
+      <c r="W397">
+        <v>26</v>
+      </c>
+      <c r="X397">
+        <v>72</v>
+      </c>
+      <c r="Y397">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="398" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A398" t="s">
+        <v>202</v>
+      </c>
+      <c r="B398" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C398" t="s">
+        <v>203</v>
+      </c>
+      <c r="D398" t="s">
+        <v>848</v>
+      </c>
+      <c r="E398" t="s">
+        <v>147</v>
+      </c>
+      <c r="F398" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G398" t="s">
+        <v>663</v>
+      </c>
+      <c r="H398" t="s">
+        <v>2417</v>
+      </c>
+      <c r="I398" t="s">
+        <v>2418</v>
+      </c>
+      <c r="J398" t="s">
+        <v>2419</v>
+      </c>
+      <c r="K398" t="s">
+        <v>2420</v>
+      </c>
+      <c r="L398" t="s">
+        <v>573</v>
+      </c>
+      <c r="M398" t="s">
+        <v>74</v>
+      </c>
+      <c r="N398" t="s">
+        <v>40</v>
+      </c>
+      <c r="O398" t="s">
+        <v>201</v>
+      </c>
+      <c r="P398" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q398" t="s">
+        <v>201</v>
+      </c>
+      <c r="R398" t="s">
+        <v>66</v>
+      </c>
+      <c r="S398" t="s">
+        <v>39</v>
+      </c>
+      <c r="T398" t="s">
+        <v>40</v>
+      </c>
+      <c r="U398" t="s">
+        <v>41</v>
+      </c>
+      <c r="V398">
+        <v>51</v>
+      </c>
+      <c r="W398">
+        <v>22</v>
+      </c>
+      <c r="X398">
+        <v>49</v>
+      </c>
+      <c r="Y398">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="399" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
+        <v>202</v>
+      </c>
+      <c r="B399" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C399" t="s">
+        <v>203</v>
+      </c>
+      <c r="D399" t="s">
+        <v>848</v>
+      </c>
+      <c r="E399" t="s">
+        <v>157</v>
+      </c>
+      <c r="F399" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G399" t="s">
+        <v>391</v>
+      </c>
+      <c r="H399" t="s">
+        <v>443</v>
+      </c>
+      <c r="I399" t="s">
+        <v>2421</v>
+      </c>
+      <c r="J399" t="s">
+        <v>2422</v>
+      </c>
+      <c r="K399" t="s">
+        <v>2423</v>
+      </c>
+      <c r="L399" t="s">
+        <v>699</v>
+      </c>
+      <c r="M399" t="s">
+        <v>494</v>
+      </c>
+      <c r="N399" t="s">
+        <v>39</v>
+      </c>
+      <c r="O399" t="s">
+        <v>201</v>
+      </c>
+      <c r="P399" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Q399" t="s">
+        <v>201</v>
+      </c>
+      <c r="R399" t="s">
+        <v>40</v>
+      </c>
+      <c r="S399" t="s">
+        <v>41</v>
+      </c>
+      <c r="T399" t="s">
+        <v>40</v>
+      </c>
+      <c r="U399" t="s">
+        <v>41</v>
+      </c>
+      <c r="V399">
+        <v>61</v>
+      </c>
+      <c r="W399">
+        <v>27</v>
+      </c>
+      <c r="X399">
+        <v>36</v>
+      </c>
+      <c r="Y399">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="400" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>202</v>
+      </c>
+      <c r="B400" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C400" t="s">
+        <v>203</v>
+      </c>
+      <c r="D400" t="s">
+        <v>848</v>
+      </c>
+      <c r="E400" t="s">
+        <v>191</v>
+      </c>
+      <c r="F400" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G400" t="s">
+        <v>235</v>
+      </c>
+      <c r="H400" t="s">
+        <v>2424</v>
+      </c>
+      <c r="I400" t="s">
+        <v>2425</v>
+      </c>
+      <c r="J400" t="s">
+        <v>2426</v>
+      </c>
+      <c r="K400" t="s">
+        <v>2427</v>
+      </c>
+      <c r="L400" t="s">
+        <v>534</v>
+      </c>
+      <c r="M400" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N400" t="s">
+        <v>38</v>
+      </c>
+      <c r="O400" t="s">
+        <v>201</v>
+      </c>
+      <c r="P400" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q400" t="s">
+        <v>201</v>
+      </c>
+      <c r="R400" t="s">
+        <v>38</v>
+      </c>
+      <c r="S400" t="s">
+        <v>41</v>
+      </c>
+      <c r="T400" t="s">
+        <v>39</v>
+      </c>
+      <c r="U400" t="s">
+        <v>41</v>
+      </c>
+      <c r="V400">
+        <v>30</v>
+      </c>
+      <c r="W400">
+        <v>16</v>
+      </c>
+      <c r="X400">
+        <v>28</v>
+      </c>
+      <c r="Y400">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAB64EC-6840-7744-A51A-92D8647F3FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA04D9E3-E378-2846-A0F1-71FF83080214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7655" uniqueCount="2428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7935" uniqueCount="2491">
   <si>
     <t>Type</t>
   </si>
@@ -7320,6 +7320,195 @@
   </si>
   <si>
     <t>46.24</t>
+  </si>
+  <si>
+    <t>70.87</t>
+  </si>
+  <si>
+    <t>190.4</t>
+  </si>
+  <si>
+    <t>281.02</t>
+  </si>
+  <si>
+    <t>85.57</t>
+  </si>
+  <si>
+    <t>3.78</t>
+  </si>
+  <si>
+    <t>119.86</t>
+  </si>
+  <si>
+    <t>192.77</t>
+  </si>
+  <si>
+    <t>28.13</t>
+  </si>
+  <si>
+    <t>53.38</t>
+  </si>
+  <si>
+    <t>14.8</t>
+  </si>
+  <si>
+    <t>70.88</t>
+  </si>
+  <si>
+    <t>289.39</t>
+  </si>
+  <si>
+    <t>274.32</t>
+  </si>
+  <si>
+    <t>26.72</t>
+  </si>
+  <si>
+    <t>76.26</t>
+  </si>
+  <si>
+    <t>40.9</t>
+  </si>
+  <si>
+    <t>395.08</t>
+  </si>
+  <si>
+    <t>258.77</t>
+  </si>
+  <si>
+    <t>77.83</t>
+  </si>
+  <si>
+    <t>61.9</t>
+  </si>
+  <si>
+    <t>227.21</t>
+  </si>
+  <si>
+    <t>346.19</t>
+  </si>
+  <si>
+    <t>95.97</t>
+  </si>
+  <si>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>298.26</t>
+  </si>
+  <si>
+    <t>241.02</t>
+  </si>
+  <si>
+    <t>28.65</t>
+  </si>
+  <si>
+    <t>72.0</t>
+  </si>
+  <si>
+    <t>3.28</t>
+  </si>
+  <si>
+    <t>119.97</t>
+  </si>
+  <si>
+    <t>150.37</t>
+  </si>
+  <si>
+    <t>28.51</t>
+  </si>
+  <si>
+    <t>46.26</t>
+  </si>
+  <si>
+    <t>4.27</t>
+  </si>
+  <si>
+    <t>429.97</t>
+  </si>
+  <si>
+    <t>287.41</t>
+  </si>
+  <si>
+    <t>30.46</t>
+  </si>
+  <si>
+    <t>75.18</t>
+  </si>
+  <si>
+    <t>52.9</t>
+  </si>
+  <si>
+    <t>345.15</t>
+  </si>
+  <si>
+    <t>276.9</t>
+  </si>
+  <si>
+    <t>82.27</t>
+  </si>
+  <si>
+    <t>5.13</t>
+  </si>
+  <si>
+    <t>53.2</t>
+  </si>
+  <si>
+    <t>407.08</t>
+  </si>
+  <si>
+    <t>311.53</t>
+  </si>
+  <si>
+    <t>88.82</t>
+  </si>
+  <si>
+    <t>72.88</t>
+  </si>
+  <si>
+    <t>252.31</t>
+  </si>
+  <si>
+    <t>422.52</t>
+  </si>
+  <si>
+    <t>67.96</t>
+  </si>
+  <si>
+    <t>384.53</t>
+  </si>
+  <si>
+    <t>238.34</t>
+  </si>
+  <si>
+    <t>31.42</t>
+  </si>
+  <si>
+    <t>73.38</t>
+  </si>
+  <si>
+    <t>43.6</t>
+  </si>
+  <si>
+    <t>287.71</t>
+  </si>
+  <si>
+    <t>488.43</t>
+  </si>
+  <si>
+    <t>4.57</t>
+  </si>
+  <si>
+    <t>83.17</t>
+  </si>
+  <si>
+    <t>197.2</t>
+  </si>
+  <si>
+    <t>64.41</t>
+  </si>
+  <si>
+    <t>4.29</t>
   </si>
 </sst>
 </file>
@@ -7698,7 +7887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y400"/>
+  <dimension ref="A1:Y414"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -38127,6 +38316,1084 @@
         <v>14</v>
       </c>
     </row>
+    <row r="401" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
+        <v>202</v>
+      </c>
+      <c r="B401" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C401" t="s">
+        <v>203</v>
+      </c>
+      <c r="D401" t="s">
+        <v>204</v>
+      </c>
+      <c r="E401" t="s">
+        <v>25</v>
+      </c>
+      <c r="F401" t="s">
+        <v>2428</v>
+      </c>
+      <c r="G401" t="s">
+        <v>306</v>
+      </c>
+      <c r="H401" t="s">
+        <v>2429</v>
+      </c>
+      <c r="I401" t="s">
+        <v>2430</v>
+      </c>
+      <c r="J401" t="s">
+        <v>286</v>
+      </c>
+      <c r="K401" t="s">
+        <v>2431</v>
+      </c>
+      <c r="L401" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M401" t="s">
+        <v>85</v>
+      </c>
+      <c r="N401" t="s">
+        <v>555</v>
+      </c>
+      <c r="O401" t="s">
+        <v>66</v>
+      </c>
+      <c r="P401" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q401" t="s">
+        <v>174</v>
+      </c>
+      <c r="R401" t="s">
+        <v>38</v>
+      </c>
+      <c r="S401" t="s">
+        <v>39</v>
+      </c>
+      <c r="T401" t="s">
+        <v>40</v>
+      </c>
+      <c r="U401" t="s">
+        <v>41</v>
+      </c>
+      <c r="V401">
+        <v>56</v>
+      </c>
+      <c r="W401">
+        <v>14</v>
+      </c>
+      <c r="X401">
+        <v>35</v>
+      </c>
+      <c r="Y401">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="402" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A402" t="s">
+        <v>202</v>
+      </c>
+      <c r="B402" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C402" t="s">
+        <v>203</v>
+      </c>
+      <c r="D402" t="s">
+        <v>204</v>
+      </c>
+      <c r="E402" t="s">
+        <v>42</v>
+      </c>
+      <c r="F402" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G402" t="s">
+        <v>2432</v>
+      </c>
+      <c r="H402" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I402" t="s">
+        <v>2434</v>
+      </c>
+      <c r="J402" t="s">
+        <v>2435</v>
+      </c>
+      <c r="K402" t="s">
+        <v>2436</v>
+      </c>
+      <c r="L402" t="s">
+        <v>397</v>
+      </c>
+      <c r="M402" t="s">
+        <v>1108</v>
+      </c>
+      <c r="N402" t="s">
+        <v>280</v>
+      </c>
+      <c r="O402" t="s">
+        <v>38</v>
+      </c>
+      <c r="P402" t="s">
+        <v>2437</v>
+      </c>
+      <c r="Q402" t="s">
+        <v>344</v>
+      </c>
+      <c r="R402" t="s">
+        <v>39</v>
+      </c>
+      <c r="S402" t="s">
+        <v>41</v>
+      </c>
+      <c r="T402" t="s">
+        <v>39</v>
+      </c>
+      <c r="U402" t="s">
+        <v>201</v>
+      </c>
+      <c r="V402">
+        <v>24</v>
+      </c>
+      <c r="W402">
+        <v>6</v>
+      </c>
+      <c r="X402">
+        <v>18</v>
+      </c>
+      <c r="Y402">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="403" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A403" t="s">
+        <v>202</v>
+      </c>
+      <c r="B403" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C403" t="s">
+        <v>203</v>
+      </c>
+      <c r="D403" t="s">
+        <v>204</v>
+      </c>
+      <c r="E403" t="s">
+        <v>54</v>
+      </c>
+      <c r="F403" t="s">
+        <v>2438</v>
+      </c>
+      <c r="G403" t="s">
+        <v>1474</v>
+      </c>
+      <c r="H403" t="s">
+        <v>2439</v>
+      </c>
+      <c r="I403" t="s">
+        <v>2440</v>
+      </c>
+      <c r="J403" t="s">
+        <v>2441</v>
+      </c>
+      <c r="K403" t="s">
+        <v>2442</v>
+      </c>
+      <c r="L403" t="s">
+        <v>55</v>
+      </c>
+      <c r="M403" t="s">
+        <v>505</v>
+      </c>
+      <c r="N403" t="s">
+        <v>279</v>
+      </c>
+      <c r="O403" t="s">
+        <v>40</v>
+      </c>
+      <c r="P403" t="s">
+        <v>2443</v>
+      </c>
+      <c r="Q403" t="s">
+        <v>526</v>
+      </c>
+      <c r="R403" t="s">
+        <v>40</v>
+      </c>
+      <c r="S403" t="s">
+        <v>41</v>
+      </c>
+      <c r="T403" t="s">
+        <v>40</v>
+      </c>
+      <c r="U403" t="s">
+        <v>41</v>
+      </c>
+      <c r="V403">
+        <v>49</v>
+      </c>
+      <c r="W403">
+        <v>17</v>
+      </c>
+      <c r="X403">
+        <v>33</v>
+      </c>
+      <c r="Y403">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="404" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>202</v>
+      </c>
+      <c r="B404" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C404" t="s">
+        <v>203</v>
+      </c>
+      <c r="D404" t="s">
+        <v>204</v>
+      </c>
+      <c r="E404" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F404" t="s">
+        <v>2438</v>
+      </c>
+      <c r="G404" t="s">
+        <v>926</v>
+      </c>
+      <c r="H404" t="s">
+        <v>2444</v>
+      </c>
+      <c r="I404" t="s">
+        <v>2445</v>
+      </c>
+      <c r="J404" t="s">
+        <v>1948</v>
+      </c>
+      <c r="K404" t="s">
+        <v>2446</v>
+      </c>
+      <c r="L404" t="s">
+        <v>426</v>
+      </c>
+      <c r="M404" t="s">
+        <v>133</v>
+      </c>
+      <c r="N404" t="s">
+        <v>232</v>
+      </c>
+      <c r="O404" t="s">
+        <v>40</v>
+      </c>
+      <c r="P404" t="s">
+        <v>2447</v>
+      </c>
+      <c r="Q404" t="s">
+        <v>264</v>
+      </c>
+      <c r="R404" t="s">
+        <v>66</v>
+      </c>
+      <c r="S404" t="s">
+        <v>39</v>
+      </c>
+      <c r="T404" t="s">
+        <v>40</v>
+      </c>
+      <c r="U404" t="s">
+        <v>41</v>
+      </c>
+      <c r="V404">
+        <v>44</v>
+      </c>
+      <c r="W404">
+        <v>19</v>
+      </c>
+      <c r="X404">
+        <v>42</v>
+      </c>
+      <c r="Y404">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="405" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A405" t="s">
+        <v>202</v>
+      </c>
+      <c r="B405" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C405" t="s">
+        <v>203</v>
+      </c>
+      <c r="D405" t="s">
+        <v>204</v>
+      </c>
+      <c r="E405" t="s">
+        <v>90</v>
+      </c>
+      <c r="F405" t="s">
+        <v>2438</v>
+      </c>
+      <c r="G405" t="s">
+        <v>2090</v>
+      </c>
+      <c r="H405" t="s">
+        <v>2448</v>
+      </c>
+      <c r="I405" t="s">
+        <v>2449</v>
+      </c>
+      <c r="J405" t="s">
+        <v>1810</v>
+      </c>
+      <c r="K405" t="s">
+        <v>2450</v>
+      </c>
+      <c r="L405" t="s">
+        <v>1350</v>
+      </c>
+      <c r="M405" t="s">
+        <v>132</v>
+      </c>
+      <c r="N405" t="s">
+        <v>213</v>
+      </c>
+      <c r="O405" t="s">
+        <v>40</v>
+      </c>
+      <c r="P405" t="s">
+        <v>2451</v>
+      </c>
+      <c r="Q405" t="s">
+        <v>640</v>
+      </c>
+      <c r="R405" t="s">
+        <v>40</v>
+      </c>
+      <c r="S405" t="s">
+        <v>39</v>
+      </c>
+      <c r="T405" t="s">
+        <v>40</v>
+      </c>
+      <c r="U405" t="s">
+        <v>41</v>
+      </c>
+      <c r="V405">
+        <v>57</v>
+      </c>
+      <c r="W405">
+        <v>21</v>
+      </c>
+      <c r="X405">
+        <v>50</v>
+      </c>
+      <c r="Y405">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="406" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A406" t="s">
+        <v>202</v>
+      </c>
+      <c r="B406" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C406" t="s">
+        <v>203</v>
+      </c>
+      <c r="D406" t="s">
+        <v>204</v>
+      </c>
+      <c r="E406" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F406" t="s">
+        <v>2438</v>
+      </c>
+      <c r="G406" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H406" t="s">
+        <v>2452</v>
+      </c>
+      <c r="I406" t="s">
+        <v>2453</v>
+      </c>
+      <c r="J406" t="s">
+        <v>2454</v>
+      </c>
+      <c r="K406" t="s">
+        <v>2455</v>
+      </c>
+      <c r="L406" t="s">
+        <v>821</v>
+      </c>
+      <c r="M406" t="s">
+        <v>1704</v>
+      </c>
+      <c r="N406" t="s">
+        <v>307</v>
+      </c>
+      <c r="O406" t="s">
+        <v>38</v>
+      </c>
+      <c r="P406" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Q406" t="s">
+        <v>225</v>
+      </c>
+      <c r="R406" t="s">
+        <v>40</v>
+      </c>
+      <c r="S406" t="s">
+        <v>41</v>
+      </c>
+      <c r="T406" t="s">
+        <v>40</v>
+      </c>
+      <c r="U406" t="s">
+        <v>41</v>
+      </c>
+      <c r="V406">
+        <v>51</v>
+      </c>
+      <c r="W406">
+        <v>16</v>
+      </c>
+      <c r="X406">
+        <v>36</v>
+      </c>
+      <c r="Y406">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="407" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A407" t="s">
+        <v>202</v>
+      </c>
+      <c r="B407" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C407" t="s">
+        <v>203</v>
+      </c>
+      <c r="D407" t="s">
+        <v>204</v>
+      </c>
+      <c r="E407" t="s">
+        <v>102</v>
+      </c>
+      <c r="F407" t="s">
+        <v>2438</v>
+      </c>
+      <c r="G407" t="s">
+        <v>2456</v>
+      </c>
+      <c r="H407" t="s">
+        <v>2457</v>
+      </c>
+      <c r="I407" t="s">
+        <v>2458</v>
+      </c>
+      <c r="J407" t="s">
+        <v>2459</v>
+      </c>
+      <c r="K407" t="s">
+        <v>2460</v>
+      </c>
+      <c r="L407" t="s">
+        <v>2461</v>
+      </c>
+      <c r="M407" t="s">
+        <v>2011</v>
+      </c>
+      <c r="N407" t="s">
+        <v>337</v>
+      </c>
+      <c r="O407" t="s">
+        <v>40</v>
+      </c>
+      <c r="P407" t="s">
+        <v>1636</v>
+      </c>
+      <c r="Q407" t="s">
+        <v>1009</v>
+      </c>
+      <c r="R407" t="s">
+        <v>41</v>
+      </c>
+      <c r="S407" t="s">
+        <v>201</v>
+      </c>
+      <c r="T407" t="s">
+        <v>39</v>
+      </c>
+      <c r="U407" t="s">
+        <v>201</v>
+      </c>
+      <c r="V407">
+        <v>24</v>
+      </c>
+      <c r="W407">
+        <v>5</v>
+      </c>
+      <c r="X407">
+        <v>12</v>
+      </c>
+      <c r="Y407">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="408" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A408" t="s">
+        <v>202</v>
+      </c>
+      <c r="B408" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C408" t="s">
+        <v>203</v>
+      </c>
+      <c r="D408" t="s">
+        <v>204</v>
+      </c>
+      <c r="E408" t="s">
+        <v>114</v>
+      </c>
+      <c r="F408" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G408" t="s">
+        <v>133</v>
+      </c>
+      <c r="H408" t="s">
+        <v>2462</v>
+      </c>
+      <c r="I408" t="s">
+        <v>2463</v>
+      </c>
+      <c r="J408" t="s">
+        <v>2464</v>
+      </c>
+      <c r="K408" t="s">
+        <v>2465</v>
+      </c>
+      <c r="L408" t="s">
+        <v>469</v>
+      </c>
+      <c r="M408" t="s">
+        <v>503</v>
+      </c>
+      <c r="N408" t="s">
+        <v>290</v>
+      </c>
+      <c r="O408" t="s">
+        <v>449</v>
+      </c>
+      <c r="P408" t="s">
+        <v>2466</v>
+      </c>
+      <c r="Q408" t="s">
+        <v>2242</v>
+      </c>
+      <c r="R408" t="s">
+        <v>66</v>
+      </c>
+      <c r="S408" t="s">
+        <v>39</v>
+      </c>
+      <c r="T408" t="s">
+        <v>66</v>
+      </c>
+      <c r="U408" t="s">
+        <v>39</v>
+      </c>
+      <c r="V408">
+        <v>38</v>
+      </c>
+      <c r="W408">
+        <v>26</v>
+      </c>
+      <c r="X408">
+        <v>28</v>
+      </c>
+      <c r="Y408">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="409" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A409" t="s">
+        <v>202</v>
+      </c>
+      <c r="B409" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C409" t="s">
+        <v>203</v>
+      </c>
+      <c r="D409" t="s">
+        <v>204</v>
+      </c>
+      <c r="E409" t="s">
+        <v>126</v>
+      </c>
+      <c r="F409" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G409" t="s">
+        <v>1670</v>
+      </c>
+      <c r="H409" t="s">
+        <v>2467</v>
+      </c>
+      <c r="I409" t="s">
+        <v>2468</v>
+      </c>
+      <c r="J409" t="s">
+        <v>711</v>
+      </c>
+      <c r="K409" t="s">
+        <v>2469</v>
+      </c>
+      <c r="L409" t="s">
+        <v>699</v>
+      </c>
+      <c r="M409" t="s">
+        <v>2470</v>
+      </c>
+      <c r="N409" t="s">
+        <v>290</v>
+      </c>
+      <c r="O409" t="s">
+        <v>39</v>
+      </c>
+      <c r="P409" t="s">
+        <v>2471</v>
+      </c>
+      <c r="Q409" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R409" t="s">
+        <v>38</v>
+      </c>
+      <c r="S409" t="s">
+        <v>39</v>
+      </c>
+      <c r="T409" t="s">
+        <v>39</v>
+      </c>
+      <c r="U409" t="s">
+        <v>41</v>
+      </c>
+      <c r="V409">
+        <v>22</v>
+      </c>
+      <c r="W409">
+        <v>11</v>
+      </c>
+      <c r="X409">
+        <v>29</v>
+      </c>
+      <c r="Y409">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="410" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A410" t="s">
+        <v>202</v>
+      </c>
+      <c r="B410" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C410" t="s">
+        <v>203</v>
+      </c>
+      <c r="D410" t="s">
+        <v>204</v>
+      </c>
+      <c r="E410" t="s">
+        <v>137</v>
+      </c>
+      <c r="F410" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G410" t="s">
+        <v>439</v>
+      </c>
+      <c r="H410" t="s">
+        <v>2472</v>
+      </c>
+      <c r="I410" t="s">
+        <v>2473</v>
+      </c>
+      <c r="J410" t="s">
+        <v>286</v>
+      </c>
+      <c r="K410" t="s">
+        <v>2474</v>
+      </c>
+      <c r="L410" t="s">
+        <v>1704</v>
+      </c>
+      <c r="M410" t="s">
+        <v>230</v>
+      </c>
+      <c r="N410" t="s">
+        <v>579</v>
+      </c>
+      <c r="O410" t="s">
+        <v>35</v>
+      </c>
+      <c r="P410" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q410" t="s">
+        <v>1089</v>
+      </c>
+      <c r="R410" t="s">
+        <v>66</v>
+      </c>
+      <c r="S410" t="s">
+        <v>41</v>
+      </c>
+      <c r="T410" t="s">
+        <v>40</v>
+      </c>
+      <c r="U410" t="s">
+        <v>41</v>
+      </c>
+      <c r="V410">
+        <v>53</v>
+      </c>
+      <c r="W410">
+        <v>22</v>
+      </c>
+      <c r="X410">
+        <v>53</v>
+      </c>
+      <c r="Y410">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="411" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
+        <v>202</v>
+      </c>
+      <c r="B411" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C411" t="s">
+        <v>203</v>
+      </c>
+      <c r="D411" t="s">
+        <v>204</v>
+      </c>
+      <c r="E411" t="s">
+        <v>147</v>
+      </c>
+      <c r="F411" t="s">
+        <v>2475</v>
+      </c>
+      <c r="G411" t="s">
+        <v>671</v>
+      </c>
+      <c r="H411" t="s">
+        <v>2476</v>
+      </c>
+      <c r="I411" t="s">
+        <v>2477</v>
+      </c>
+      <c r="J411" t="s">
+        <v>1778</v>
+      </c>
+      <c r="K411" t="s">
+        <v>2478</v>
+      </c>
+      <c r="L411" t="s">
+        <v>187</v>
+      </c>
+      <c r="M411" t="s">
+        <v>1144</v>
+      </c>
+      <c r="N411" t="s">
+        <v>672</v>
+      </c>
+      <c r="O411" t="s">
+        <v>40</v>
+      </c>
+      <c r="P411" t="s">
+        <v>1595</v>
+      </c>
+      <c r="Q411" t="s">
+        <v>163</v>
+      </c>
+      <c r="R411" t="s">
+        <v>35</v>
+      </c>
+      <c r="S411" t="s">
+        <v>38</v>
+      </c>
+      <c r="T411" t="s">
+        <v>40</v>
+      </c>
+      <c r="U411" t="s">
+        <v>39</v>
+      </c>
+      <c r="V411">
+        <v>46</v>
+      </c>
+      <c r="W411">
+        <v>20</v>
+      </c>
+      <c r="X411">
+        <v>43</v>
+      </c>
+      <c r="Y411">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="412" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A412" t="s">
+        <v>202</v>
+      </c>
+      <c r="B412" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C412" t="s">
+        <v>203</v>
+      </c>
+      <c r="D412" t="s">
+        <v>204</v>
+      </c>
+      <c r="E412" t="s">
+        <v>157</v>
+      </c>
+      <c r="F412" t="s">
+        <v>2428</v>
+      </c>
+      <c r="G412" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H412" t="s">
+        <v>2479</v>
+      </c>
+      <c r="I412" t="s">
+        <v>2480</v>
+      </c>
+      <c r="J412" t="s">
+        <v>2481</v>
+      </c>
+      <c r="K412" t="s">
+        <v>2482</v>
+      </c>
+      <c r="L412" t="s">
+        <v>397</v>
+      </c>
+      <c r="M412" t="s">
+        <v>1457</v>
+      </c>
+      <c r="N412" t="s">
+        <v>110</v>
+      </c>
+      <c r="O412" t="s">
+        <v>188</v>
+      </c>
+      <c r="P412" t="s">
+        <v>2483</v>
+      </c>
+      <c r="Q412" t="s">
+        <v>2043</v>
+      </c>
+      <c r="R412" t="s">
+        <v>66</v>
+      </c>
+      <c r="S412" t="s">
+        <v>39</v>
+      </c>
+      <c r="T412" t="s">
+        <v>40</v>
+      </c>
+      <c r="U412" t="s">
+        <v>39</v>
+      </c>
+      <c r="V412">
+        <v>47</v>
+      </c>
+      <c r="W412">
+        <v>21</v>
+      </c>
+      <c r="X412">
+        <v>41</v>
+      </c>
+      <c r="Y412">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="413" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A413" t="s">
+        <v>202</v>
+      </c>
+      <c r="B413" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C413" t="s">
+        <v>203</v>
+      </c>
+      <c r="D413" t="s">
+        <v>204</v>
+      </c>
+      <c r="E413" t="s">
+        <v>180</v>
+      </c>
+      <c r="F413" t="s">
+        <v>2438</v>
+      </c>
+      <c r="G413" t="s">
+        <v>541</v>
+      </c>
+      <c r="H413" t="s">
+        <v>2484</v>
+      </c>
+      <c r="I413" t="s">
+        <v>2485</v>
+      </c>
+      <c r="J413" t="s">
+        <v>733</v>
+      </c>
+      <c r="K413" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L413" t="s">
+        <v>1961</v>
+      </c>
+      <c r="M413" t="s">
+        <v>365</v>
+      </c>
+      <c r="N413" t="s">
+        <v>123</v>
+      </c>
+      <c r="O413" t="s">
+        <v>40</v>
+      </c>
+      <c r="P413" t="s">
+        <v>1143</v>
+      </c>
+      <c r="Q413" t="s">
+        <v>163</v>
+      </c>
+      <c r="R413" t="s">
+        <v>51</v>
+      </c>
+      <c r="S413" t="s">
+        <v>35</v>
+      </c>
+      <c r="T413" t="s">
+        <v>280</v>
+      </c>
+      <c r="U413" t="s">
+        <v>40</v>
+      </c>
+      <c r="V413">
+        <v>80</v>
+      </c>
+      <c r="W413">
+        <v>73</v>
+      </c>
+      <c r="X413">
+        <v>106</v>
+      </c>
+      <c r="Y413">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="414" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A414" t="s">
+        <v>202</v>
+      </c>
+      <c r="B414" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C414" t="s">
+        <v>203</v>
+      </c>
+      <c r="D414" t="s">
+        <v>204</v>
+      </c>
+      <c r="E414" t="s">
+        <v>191</v>
+      </c>
+      <c r="F414" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G414" t="s">
+        <v>2486</v>
+      </c>
+      <c r="H414" t="s">
+        <v>2487</v>
+      </c>
+      <c r="I414" t="s">
+        <v>2488</v>
+      </c>
+      <c r="J414" t="s">
+        <v>963</v>
+      </c>
+      <c r="K414" t="s">
+        <v>2489</v>
+      </c>
+      <c r="L414" t="s">
+        <v>2490</v>
+      </c>
+      <c r="M414" t="s">
+        <v>404</v>
+      </c>
+      <c r="N414" t="s">
+        <v>337</v>
+      </c>
+      <c r="O414" t="s">
+        <v>201</v>
+      </c>
+      <c r="P414" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q414" t="s">
+        <v>488</v>
+      </c>
+      <c r="R414" t="s">
+        <v>41</v>
+      </c>
+      <c r="S414" t="s">
+        <v>201</v>
+      </c>
+      <c r="T414" t="s">
+        <v>41</v>
+      </c>
+      <c r="U414" t="s">
+        <v>201</v>
+      </c>
+      <c r="V414">
+        <v>20</v>
+      </c>
+      <c r="W414">
+        <v>9</v>
+      </c>
+      <c r="X414">
+        <v>11</v>
+      </c>
+      <c r="Y414">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA04D9E3-E378-2846-A0F1-71FF83080214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C6F348-63B6-D645-B234-AE9BACF20F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7935" uniqueCount="2491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8417" uniqueCount="2632">
   <si>
     <t>Type</t>
   </si>
@@ -7509,6 +7509,429 @@
   </si>
   <si>
     <t>4.29</t>
+  </si>
+  <si>
+    <t>99.05</t>
+  </si>
+  <si>
+    <t>10.28</t>
+  </si>
+  <si>
+    <t>460.27</t>
+  </si>
+  <si>
+    <t>423.51</t>
+  </si>
+  <si>
+    <t>31.76</t>
+  </si>
+  <si>
+    <t>103.79</t>
+  </si>
+  <si>
+    <t>16.3</t>
+  </si>
+  <si>
+    <t>82.05</t>
+  </si>
+  <si>
+    <t>9.12</t>
+  </si>
+  <si>
+    <t>1332.27</t>
+  </si>
+  <si>
+    <t>420.63</t>
+  </si>
+  <si>
+    <t>111.09</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>153.1</t>
+  </si>
+  <si>
+    <t>51.9</t>
+  </si>
+  <si>
+    <t>78.52</t>
+  </si>
+  <si>
+    <t>8.33</t>
+  </si>
+  <si>
+    <t>809.07</t>
+  </si>
+  <si>
+    <t>386.26</t>
+  </si>
+  <si>
+    <t>31.31</t>
+  </si>
+  <si>
+    <t>106.11</t>
+  </si>
+  <si>
+    <t>104.9</t>
+  </si>
+  <si>
+    <t>20.43</t>
+  </si>
+  <si>
+    <t>399.79</t>
+  </si>
+  <si>
+    <t>105.32</t>
+  </si>
+  <si>
+    <t>27.93</t>
+  </si>
+  <si>
+    <t>120.78</t>
+  </si>
+  <si>
+    <t>63.7</t>
+  </si>
+  <si>
+    <t>26.13</t>
+  </si>
+  <si>
+    <t>2.81</t>
+  </si>
+  <si>
+    <t>125.7</t>
+  </si>
+  <si>
+    <t>32.21</t>
+  </si>
+  <si>
+    <t>107.56</t>
+  </si>
+  <si>
+    <t>6.81</t>
+  </si>
+  <si>
+    <t>17.48</t>
+  </si>
+  <si>
+    <t>2.01</t>
+  </si>
+  <si>
+    <t>96.38</t>
+  </si>
+  <si>
+    <t>31.38</t>
+  </si>
+  <si>
+    <t>114.9</t>
+  </si>
+  <si>
+    <t>99.03</t>
+  </si>
+  <si>
+    <t>10.88</t>
+  </si>
+  <si>
+    <t>741.69</t>
+  </si>
+  <si>
+    <t>489.43</t>
+  </si>
+  <si>
+    <t>109.84</t>
+  </si>
+  <si>
+    <t>89.1</t>
+  </si>
+  <si>
+    <t>9.21</t>
+  </si>
+  <si>
+    <t>893.78</t>
+  </si>
+  <si>
+    <t>400.51</t>
+  </si>
+  <si>
+    <t>29.35</t>
+  </si>
+  <si>
+    <t>117.29</t>
+  </si>
+  <si>
+    <t>8.62</t>
+  </si>
+  <si>
+    <t>104.0</t>
+  </si>
+  <si>
+    <t>474.29</t>
+  </si>
+  <si>
+    <t>520.4</t>
+  </si>
+  <si>
+    <t>110.7</t>
+  </si>
+  <si>
+    <t>72.4</t>
+  </si>
+  <si>
+    <t>9.88</t>
+  </si>
+  <si>
+    <t>544.78</t>
+  </si>
+  <si>
+    <t>425.31</t>
+  </si>
+  <si>
+    <t>30.98</t>
+  </si>
+  <si>
+    <t>99.74</t>
+  </si>
+  <si>
+    <t>8.39</t>
+  </si>
+  <si>
+    <t>63.0</t>
+  </si>
+  <si>
+    <t>73.42</t>
+  </si>
+  <si>
+    <t>7.88</t>
+  </si>
+  <si>
+    <t>871.41</t>
+  </si>
+  <si>
+    <t>337.83</t>
+  </si>
+  <si>
+    <t>107.28</t>
+  </si>
+  <si>
+    <t>41.6</t>
+  </si>
+  <si>
+    <t>98.83</t>
+  </si>
+  <si>
+    <t>10.78</t>
+  </si>
+  <si>
+    <t>1003.06</t>
+  </si>
+  <si>
+    <t>467.51</t>
+  </si>
+  <si>
+    <t>29.18</t>
+  </si>
+  <si>
+    <t>109.06</t>
+  </si>
+  <si>
+    <t>6.98</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>137.7</t>
+  </si>
+  <si>
+    <t>9.47</t>
+  </si>
+  <si>
+    <t>258.22</t>
+  </si>
+  <si>
+    <t>392.08</t>
+  </si>
+  <si>
+    <t>28.21</t>
+  </si>
+  <si>
+    <t>CDF T6 VS Roanne 24/10/2026</t>
+  </si>
+  <si>
+    <t>86.75</t>
+  </si>
+  <si>
+    <t>152.32</t>
+  </si>
+  <si>
+    <t>257.49</t>
+  </si>
+  <si>
+    <t>57.28</t>
+  </si>
+  <si>
+    <t>25.3</t>
+  </si>
+  <si>
+    <t>3.67</t>
+  </si>
+  <si>
+    <t>87.91</t>
+  </si>
+  <si>
+    <t>219.0</t>
+  </si>
+  <si>
+    <t>26.65</t>
+  </si>
+  <si>
+    <t>107.21</t>
+  </si>
+  <si>
+    <t>248.39</t>
+  </si>
+  <si>
+    <t>49.98</t>
+  </si>
+  <si>
+    <t>4.72</t>
+  </si>
+  <si>
+    <t>129.61</t>
+  </si>
+  <si>
+    <t>253.41</t>
+  </si>
+  <si>
+    <t>54.36</t>
+  </si>
+  <si>
+    <t>3.73</t>
+  </si>
+  <si>
+    <t>113.52</t>
+  </si>
+  <si>
+    <t>220.25</t>
+  </si>
+  <si>
+    <t>27.34</t>
+  </si>
+  <si>
+    <t>42.98</t>
+  </si>
+  <si>
+    <t>73.21</t>
+  </si>
+  <si>
+    <t>255.68</t>
+  </si>
+  <si>
+    <t>25.27</t>
+  </si>
+  <si>
+    <t>55.99</t>
+  </si>
+  <si>
+    <t>122.57</t>
+  </si>
+  <si>
+    <t>280.94</t>
+  </si>
+  <si>
+    <t>25.67</t>
+  </si>
+  <si>
+    <t>52.41</t>
+  </si>
+  <si>
+    <t>236.28</t>
+  </si>
+  <si>
+    <t>300.31</t>
+  </si>
+  <si>
+    <t>64.66</t>
+  </si>
+  <si>
+    <t>38.4</t>
+  </si>
+  <si>
+    <t>87.79</t>
+  </si>
+  <si>
+    <t>445.04</t>
+  </si>
+  <si>
+    <t>51.61</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>82.39</t>
+  </si>
+  <si>
+    <t>277.42</t>
+  </si>
+  <si>
+    <t>23.45</t>
+  </si>
+  <si>
+    <t>55.57</t>
+  </si>
+  <si>
+    <t>95.73</t>
+  </si>
+  <si>
+    <t>420.77</t>
+  </si>
+  <si>
+    <t>52.52</t>
+  </si>
+  <si>
+    <t>13.6</t>
+  </si>
+  <si>
+    <t>4.51</t>
+  </si>
+  <si>
+    <t>93.5</t>
+  </si>
+  <si>
+    <t>249.05</t>
+  </si>
+  <si>
+    <t>25.26</t>
+  </si>
+  <si>
+    <t>51.96</t>
+  </si>
+  <si>
+    <t>148.32</t>
+  </si>
+  <si>
+    <t>429.14</t>
+  </si>
+  <si>
+    <t>7.68</t>
+  </si>
+  <si>
+    <t>3.83</t>
+  </si>
+  <si>
+    <t>46.25</t>
+  </si>
+  <si>
+    <t>198.07</t>
+  </si>
+  <si>
+    <t>25.65</t>
+  </si>
+  <si>
+    <t>44.17</t>
   </si>
 </sst>
 </file>
@@ -7887,7 +8310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y414"/>
+  <dimension ref="A1:Y446"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -37017,9 +37440,6 @@
       <c r="C384" t="s">
         <v>203</v>
       </c>
-      <c r="D384" t="s">
-        <v>1724</v>
-      </c>
       <c r="E384" t="s">
         <v>25</v>
       </c>
@@ -37094,9 +37514,6 @@
       <c r="C385" t="s">
         <v>203</v>
       </c>
-      <c r="D385" t="s">
-        <v>1724</v>
-      </c>
       <c r="E385" t="s">
         <v>54</v>
       </c>
@@ -37171,9 +37588,6 @@
       <c r="C386" t="s">
         <v>203</v>
       </c>
-      <c r="D386" t="s">
-        <v>1724</v>
-      </c>
       <c r="E386" t="s">
         <v>90</v>
       </c>
@@ -37248,9 +37662,6 @@
       <c r="C387" t="s">
         <v>203</v>
       </c>
-      <c r="D387" t="s">
-        <v>1724</v>
-      </c>
       <c r="E387" t="s">
         <v>114</v>
       </c>
@@ -37325,9 +37736,6 @@
       <c r="C388" t="s">
         <v>203</v>
       </c>
-      <c r="D388" t="s">
-        <v>1724</v>
-      </c>
       <c r="E388" t="s">
         <v>346</v>
       </c>
@@ -37402,9 +37810,6 @@
       <c r="C389" t="s">
         <v>203</v>
       </c>
-      <c r="D389" t="s">
-        <v>1724</v>
-      </c>
       <c r="E389" t="s">
         <v>137</v>
       </c>
@@ -37479,9 +37884,6 @@
       <c r="C390" t="s">
         <v>203</v>
       </c>
-      <c r="D390" t="s">
-        <v>1724</v>
-      </c>
       <c r="E390" t="s">
         <v>191</v>
       </c>
@@ -37556,9 +37958,6 @@
       <c r="C391" t="s">
         <v>203</v>
       </c>
-      <c r="D391" t="s">
-        <v>848</v>
-      </c>
       <c r="E391" t="s">
         <v>25</v>
       </c>
@@ -37633,9 +38032,6 @@
       <c r="C392" t="s">
         <v>203</v>
       </c>
-      <c r="D392" t="s">
-        <v>848</v>
-      </c>
       <c r="E392" t="s">
         <v>54</v>
       </c>
@@ -37710,9 +38106,6 @@
       <c r="C393" t="s">
         <v>203</v>
       </c>
-      <c r="D393" t="s">
-        <v>848</v>
-      </c>
       <c r="E393" t="s">
         <v>90</v>
       </c>
@@ -37787,9 +38180,6 @@
       <c r="C394" t="s">
         <v>203</v>
       </c>
-      <c r="D394" t="s">
-        <v>848</v>
-      </c>
       <c r="E394" t="s">
         <v>102</v>
       </c>
@@ -37864,9 +38254,6 @@
       <c r="C395" t="s">
         <v>203</v>
       </c>
-      <c r="D395" t="s">
-        <v>848</v>
-      </c>
       <c r="E395" t="s">
         <v>114</v>
       </c>
@@ -37941,9 +38328,6 @@
       <c r="C396" t="s">
         <v>203</v>
       </c>
-      <c r="D396" t="s">
-        <v>848</v>
-      </c>
       <c r="E396" t="s">
         <v>126</v>
       </c>
@@ -38018,9 +38402,6 @@
       <c r="C397" t="s">
         <v>203</v>
       </c>
-      <c r="D397" t="s">
-        <v>848</v>
-      </c>
       <c r="E397" t="s">
         <v>137</v>
       </c>
@@ -38095,9 +38476,6 @@
       <c r="C398" t="s">
         <v>203</v>
       </c>
-      <c r="D398" t="s">
-        <v>848</v>
-      </c>
       <c r="E398" t="s">
         <v>147</v>
       </c>
@@ -38172,9 +38550,6 @@
       <c r="C399" t="s">
         <v>203</v>
       </c>
-      <c r="D399" t="s">
-        <v>848</v>
-      </c>
       <c r="E399" t="s">
         <v>157</v>
       </c>
@@ -38249,9 +38624,6 @@
       <c r="C400" t="s">
         <v>203</v>
       </c>
-      <c r="D400" t="s">
-        <v>848</v>
-      </c>
       <c r="E400" t="s">
         <v>191</v>
       </c>
@@ -38326,9 +38698,6 @@
       <c r="C401" t="s">
         <v>203</v>
       </c>
-      <c r="D401" t="s">
-        <v>204</v>
-      </c>
       <c r="E401" t="s">
         <v>25</v>
       </c>
@@ -38403,9 +38772,6 @@
       <c r="C402" t="s">
         <v>203</v>
       </c>
-      <c r="D402" t="s">
-        <v>204</v>
-      </c>
       <c r="E402" t="s">
         <v>42</v>
       </c>
@@ -38480,9 +38846,6 @@
       <c r="C403" t="s">
         <v>203</v>
       </c>
-      <c r="D403" t="s">
-        <v>204</v>
-      </c>
       <c r="E403" t="s">
         <v>54</v>
       </c>
@@ -38557,9 +38920,6 @@
       <c r="C404" t="s">
         <v>203</v>
       </c>
-      <c r="D404" t="s">
-        <v>204</v>
-      </c>
       <c r="E404" t="s">
         <v>1917</v>
       </c>
@@ -38634,9 +38994,6 @@
       <c r="C405" t="s">
         <v>203</v>
       </c>
-      <c r="D405" t="s">
-        <v>204</v>
-      </c>
       <c r="E405" t="s">
         <v>90</v>
       </c>
@@ -38711,9 +39068,6 @@
       <c r="C406" t="s">
         <v>203</v>
       </c>
-      <c r="D406" t="s">
-        <v>204</v>
-      </c>
       <c r="E406" t="s">
         <v>2158</v>
       </c>
@@ -38788,9 +39142,6 @@
       <c r="C407" t="s">
         <v>203</v>
       </c>
-      <c r="D407" t="s">
-        <v>204</v>
-      </c>
       <c r="E407" t="s">
         <v>102</v>
       </c>
@@ -38865,9 +39216,6 @@
       <c r="C408" t="s">
         <v>203</v>
       </c>
-      <c r="D408" t="s">
-        <v>204</v>
-      </c>
       <c r="E408" t="s">
         <v>114</v>
       </c>
@@ -38942,9 +39290,6 @@
       <c r="C409" t="s">
         <v>203</v>
       </c>
-      <c r="D409" t="s">
-        <v>204</v>
-      </c>
       <c r="E409" t="s">
         <v>126</v>
       </c>
@@ -39019,9 +39364,6 @@
       <c r="C410" t="s">
         <v>203</v>
       </c>
-      <c r="D410" t="s">
-        <v>204</v>
-      </c>
       <c r="E410" t="s">
         <v>137</v>
       </c>
@@ -39096,9 +39438,6 @@
       <c r="C411" t="s">
         <v>203</v>
       </c>
-      <c r="D411" t="s">
-        <v>204</v>
-      </c>
       <c r="E411" t="s">
         <v>147</v>
       </c>
@@ -39173,9 +39512,6 @@
       <c r="C412" t="s">
         <v>203</v>
       </c>
-      <c r="D412" t="s">
-        <v>204</v>
-      </c>
       <c r="E412" t="s">
         <v>157</v>
       </c>
@@ -39250,9 +39586,6 @@
       <c r="C413" t="s">
         <v>203</v>
       </c>
-      <c r="D413" t="s">
-        <v>204</v>
-      </c>
       <c r="E413" t="s">
         <v>180</v>
       </c>
@@ -39327,9 +39660,6 @@
       <c r="C414" t="s">
         <v>203</v>
       </c>
-      <c r="D414" t="s">
-        <v>204</v>
-      </c>
       <c r="E414" t="s">
         <v>191</v>
       </c>
@@ -39393,6 +39723,2019 @@
       <c r="Y414">
         <v>3</v>
       </c>
+    </row>
+    <row r="415" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A415" t="s">
+        <v>202</v>
+      </c>
+      <c r="B415" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C415" t="s">
+        <v>203</v>
+      </c>
+      <c r="E415" t="s">
+        <v>25</v>
+      </c>
+      <c r="F415" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G415" t="s">
+        <v>391</v>
+      </c>
+      <c r="H415" t="s">
+        <v>2575</v>
+      </c>
+      <c r="I415" t="s">
+        <v>2576</v>
+      </c>
+      <c r="J415" t="s">
+        <v>1341</v>
+      </c>
+      <c r="K415" t="s">
+        <v>2577</v>
+      </c>
+      <c r="L415" t="s">
+        <v>548</v>
+      </c>
+      <c r="M415" t="s">
+        <v>960</v>
+      </c>
+      <c r="N415" t="s">
+        <v>495</v>
+      </c>
+      <c r="O415" t="s">
+        <v>201</v>
+      </c>
+      <c r="P415" t="s">
+        <v>2578</v>
+      </c>
+      <c r="Q415" t="s">
+        <v>488</v>
+      </c>
+      <c r="R415" t="s">
+        <v>40</v>
+      </c>
+      <c r="S415" t="s">
+        <v>41</v>
+      </c>
+      <c r="T415" t="s">
+        <v>40</v>
+      </c>
+      <c r="U415" t="s">
+        <v>41</v>
+      </c>
+      <c r="V415">
+        <v>41</v>
+      </c>
+      <c r="W415">
+        <v>27</v>
+      </c>
+      <c r="X415">
+        <v>23</v>
+      </c>
+      <c r="Y415">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="416" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A416" t="s">
+        <v>202</v>
+      </c>
+      <c r="B416" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C416" t="s">
+        <v>203</v>
+      </c>
+      <c r="E416" t="s">
+        <v>42</v>
+      </c>
+      <c r="F416" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G416" t="s">
+        <v>2579</v>
+      </c>
+      <c r="H416" t="s">
+        <v>2580</v>
+      </c>
+      <c r="I416" t="s">
+        <v>2581</v>
+      </c>
+      <c r="J416" t="s">
+        <v>2582</v>
+      </c>
+      <c r="K416" t="s">
+        <v>1503</v>
+      </c>
+      <c r="L416" t="s">
+        <v>469</v>
+      </c>
+      <c r="M416" t="s">
+        <v>628</v>
+      </c>
+      <c r="N416" t="s">
+        <v>35</v>
+      </c>
+      <c r="O416" t="s">
+        <v>41</v>
+      </c>
+      <c r="P416" t="s">
+        <v>965</v>
+      </c>
+      <c r="Q416" t="s">
+        <v>811</v>
+      </c>
+      <c r="R416" t="s">
+        <v>38</v>
+      </c>
+      <c r="S416" t="s">
+        <v>41</v>
+      </c>
+      <c r="T416" t="s">
+        <v>39</v>
+      </c>
+      <c r="U416" t="s">
+        <v>201</v>
+      </c>
+      <c r="V416">
+        <v>24</v>
+      </c>
+      <c r="W416">
+        <v>8</v>
+      </c>
+      <c r="X416">
+        <v>18</v>
+      </c>
+      <c r="Y416">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="417" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A417" t="s">
+        <v>202</v>
+      </c>
+      <c r="B417" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C417" t="s">
+        <v>203</v>
+      </c>
+      <c r="E417" t="s">
+        <v>54</v>
+      </c>
+      <c r="F417" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G417" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H417" t="s">
+        <v>2583</v>
+      </c>
+      <c r="I417" t="s">
+        <v>2584</v>
+      </c>
+      <c r="J417" t="s">
+        <v>1734</v>
+      </c>
+      <c r="K417" t="s">
+        <v>2585</v>
+      </c>
+      <c r="L417" t="s">
+        <v>426</v>
+      </c>
+      <c r="M417" t="s">
+        <v>960</v>
+      </c>
+      <c r="N417" t="s">
+        <v>488</v>
+      </c>
+      <c r="O417" t="s">
+        <v>41</v>
+      </c>
+      <c r="P417" t="s">
+        <v>664</v>
+      </c>
+      <c r="Q417" t="s">
+        <v>781</v>
+      </c>
+      <c r="R417" t="s">
+        <v>40</v>
+      </c>
+      <c r="S417" t="s">
+        <v>41</v>
+      </c>
+      <c r="T417" t="s">
+        <v>40</v>
+      </c>
+      <c r="U417" t="s">
+        <v>41</v>
+      </c>
+      <c r="V417">
+        <v>44</v>
+      </c>
+      <c r="W417">
+        <v>19</v>
+      </c>
+      <c r="X417">
+        <v>41</v>
+      </c>
+      <c r="Y417">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="418" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A418" t="s">
+        <v>202</v>
+      </c>
+      <c r="B418" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C418" t="s">
+        <v>203</v>
+      </c>
+      <c r="E418" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F418" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G418" t="s">
+        <v>2586</v>
+      </c>
+      <c r="H418" t="s">
+        <v>2587</v>
+      </c>
+      <c r="I418" t="s">
+        <v>2588</v>
+      </c>
+      <c r="J418" t="s">
+        <v>1707</v>
+      </c>
+      <c r="K418" t="s">
+        <v>2589</v>
+      </c>
+      <c r="L418" t="s">
+        <v>1055</v>
+      </c>
+      <c r="M418" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N418" t="s">
+        <v>51</v>
+      </c>
+      <c r="O418" t="s">
+        <v>201</v>
+      </c>
+      <c r="P418" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q418" t="s">
+        <v>488</v>
+      </c>
+      <c r="R418" t="s">
+        <v>40</v>
+      </c>
+      <c r="S418" t="s">
+        <v>41</v>
+      </c>
+      <c r="T418" t="s">
+        <v>38</v>
+      </c>
+      <c r="U418" t="s">
+        <v>41</v>
+      </c>
+      <c r="V418">
+        <v>39</v>
+      </c>
+      <c r="W418">
+        <v>14</v>
+      </c>
+      <c r="X418">
+        <v>39</v>
+      </c>
+      <c r="Y418">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="419" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A419" t="s">
+        <v>202</v>
+      </c>
+      <c r="B419" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C419" t="s">
+        <v>203</v>
+      </c>
+      <c r="E419" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F419" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G419" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H419" t="s">
+        <v>2591</v>
+      </c>
+      <c r="I419" t="s">
+        <v>2592</v>
+      </c>
+      <c r="J419" t="s">
+        <v>2593</v>
+      </c>
+      <c r="K419" t="s">
+        <v>2594</v>
+      </c>
+      <c r="L419" t="s">
+        <v>1609</v>
+      </c>
+      <c r="M419" t="s">
+        <v>774</v>
+      </c>
+      <c r="N419" t="s">
+        <v>449</v>
+      </c>
+      <c r="O419" t="s">
+        <v>41</v>
+      </c>
+      <c r="P419" t="s">
+        <v>1048</v>
+      </c>
+      <c r="Q419" t="s">
+        <v>781</v>
+      </c>
+      <c r="R419" t="s">
+        <v>38</v>
+      </c>
+      <c r="S419" t="s">
+        <v>41</v>
+      </c>
+      <c r="T419" t="s">
+        <v>38</v>
+      </c>
+      <c r="U419" t="s">
+        <v>41</v>
+      </c>
+      <c r="V419">
+        <v>31</v>
+      </c>
+      <c r="W419">
+        <v>15</v>
+      </c>
+      <c r="X419">
+        <v>34</v>
+      </c>
+      <c r="Y419">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="420" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A420" t="s">
+        <v>202</v>
+      </c>
+      <c r="B420" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C420" t="s">
+        <v>203</v>
+      </c>
+      <c r="E420" t="s">
+        <v>102</v>
+      </c>
+      <c r="F420" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G420" t="s">
+        <v>489</v>
+      </c>
+      <c r="H420" t="s">
+        <v>2595</v>
+      </c>
+      <c r="I420" t="s">
+        <v>2596</v>
+      </c>
+      <c r="J420" t="s">
+        <v>2597</v>
+      </c>
+      <c r="K420" t="s">
+        <v>2598</v>
+      </c>
+      <c r="L420" t="s">
+        <v>975</v>
+      </c>
+      <c r="M420" t="s">
+        <v>1682</v>
+      </c>
+      <c r="N420" t="s">
+        <v>35</v>
+      </c>
+      <c r="O420" t="s">
+        <v>41</v>
+      </c>
+      <c r="P420" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q420" t="s">
+        <v>1186</v>
+      </c>
+      <c r="R420" t="s">
+        <v>38</v>
+      </c>
+      <c r="S420" t="s">
+        <v>41</v>
+      </c>
+      <c r="T420" t="s">
+        <v>39</v>
+      </c>
+      <c r="U420" t="s">
+        <v>201</v>
+      </c>
+      <c r="V420">
+        <v>35</v>
+      </c>
+      <c r="W420">
+        <v>16</v>
+      </c>
+      <c r="X420">
+        <v>28</v>
+      </c>
+      <c r="Y420">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="421" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A421" t="s">
+        <v>202</v>
+      </c>
+      <c r="B421" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C421" t="s">
+        <v>203</v>
+      </c>
+      <c r="E421" t="s">
+        <v>114</v>
+      </c>
+      <c r="F421" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G421" t="s">
+        <v>506</v>
+      </c>
+      <c r="H421" t="s">
+        <v>2599</v>
+      </c>
+      <c r="I421" t="s">
+        <v>2600</v>
+      </c>
+      <c r="J421" t="s">
+        <v>2601</v>
+      </c>
+      <c r="K421" t="s">
+        <v>2602</v>
+      </c>
+      <c r="L421" t="s">
+        <v>421</v>
+      </c>
+      <c r="M421" t="s">
+        <v>662</v>
+      </c>
+      <c r="N421" t="s">
+        <v>449</v>
+      </c>
+      <c r="O421" t="s">
+        <v>41</v>
+      </c>
+      <c r="P421" t="s">
+        <v>1289</v>
+      </c>
+      <c r="Q421" t="s">
+        <v>263</v>
+      </c>
+      <c r="R421" t="s">
+        <v>38</v>
+      </c>
+      <c r="S421" t="s">
+        <v>41</v>
+      </c>
+      <c r="T421" t="s">
+        <v>40</v>
+      </c>
+      <c r="U421" t="s">
+        <v>41</v>
+      </c>
+      <c r="V421">
+        <v>35</v>
+      </c>
+      <c r="W421">
+        <v>18</v>
+      </c>
+      <c r="X421">
+        <v>37</v>
+      </c>
+      <c r="Y421">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="422" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A422" t="s">
+        <v>202</v>
+      </c>
+      <c r="B422" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C422" t="s">
+        <v>203</v>
+      </c>
+      <c r="E422" t="s">
+        <v>126</v>
+      </c>
+      <c r="F422" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G422" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H422" t="s">
+        <v>2603</v>
+      </c>
+      <c r="I422" t="s">
+        <v>2604</v>
+      </c>
+      <c r="J422" t="s">
+        <v>1964</v>
+      </c>
+      <c r="K422" t="s">
+        <v>2605</v>
+      </c>
+      <c r="L422" t="s">
+        <v>334</v>
+      </c>
+      <c r="M422" t="s">
+        <v>663</v>
+      </c>
+      <c r="N422" t="s">
+        <v>63</v>
+      </c>
+      <c r="O422" t="s">
+        <v>201</v>
+      </c>
+      <c r="P422" t="s">
+        <v>2606</v>
+      </c>
+      <c r="Q422" t="s">
+        <v>34</v>
+      </c>
+      <c r="R422" t="s">
+        <v>113</v>
+      </c>
+      <c r="S422" t="s">
+        <v>41</v>
+      </c>
+      <c r="T422" t="s">
+        <v>38</v>
+      </c>
+      <c r="U422" t="s">
+        <v>41</v>
+      </c>
+      <c r="V422">
+        <v>28</v>
+      </c>
+      <c r="W422">
+        <v>17</v>
+      </c>
+      <c r="X422">
+        <v>50</v>
+      </c>
+      <c r="Y422">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="423" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A423" t="s">
+        <v>202</v>
+      </c>
+      <c r="B423" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C423" t="s">
+        <v>203</v>
+      </c>
+      <c r="E423" t="s">
+        <v>346</v>
+      </c>
+      <c r="F423" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G423" t="s">
+        <v>472</v>
+      </c>
+      <c r="H423" t="s">
+        <v>2607</v>
+      </c>
+      <c r="I423" t="s">
+        <v>2608</v>
+      </c>
+      <c r="J423" t="s">
+        <v>600</v>
+      </c>
+      <c r="K423" t="s">
+        <v>2609</v>
+      </c>
+      <c r="L423" t="s">
+        <v>851</v>
+      </c>
+      <c r="M423" t="s">
+        <v>192</v>
+      </c>
+      <c r="N423" t="s">
+        <v>35</v>
+      </c>
+      <c r="O423" t="s">
+        <v>39</v>
+      </c>
+      <c r="P423" t="s">
+        <v>2610</v>
+      </c>
+      <c r="Q423" t="s">
+        <v>528</v>
+      </c>
+      <c r="R423" t="s">
+        <v>113</v>
+      </c>
+      <c r="S423" t="s">
+        <v>39</v>
+      </c>
+      <c r="T423" t="s">
+        <v>66</v>
+      </c>
+      <c r="U423" t="s">
+        <v>39</v>
+      </c>
+      <c r="V423">
+        <v>55</v>
+      </c>
+      <c r="W423">
+        <v>28</v>
+      </c>
+      <c r="X423">
+        <v>64</v>
+      </c>
+      <c r="Y423">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="424" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A424" t="s">
+        <v>202</v>
+      </c>
+      <c r="B424" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C424" t="s">
+        <v>203</v>
+      </c>
+      <c r="E424" t="s">
+        <v>137</v>
+      </c>
+      <c r="F424" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G424" t="s">
+        <v>43</v>
+      </c>
+      <c r="H424" t="s">
+        <v>2611</v>
+      </c>
+      <c r="I424" t="s">
+        <v>2612</v>
+      </c>
+      <c r="J424" t="s">
+        <v>2613</v>
+      </c>
+      <c r="K424" t="s">
+        <v>2614</v>
+      </c>
+      <c r="L424" t="s">
+        <v>127</v>
+      </c>
+      <c r="M424" t="s">
+        <v>926</v>
+      </c>
+      <c r="N424" t="s">
+        <v>337</v>
+      </c>
+      <c r="O424" t="s">
+        <v>201</v>
+      </c>
+      <c r="P424" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q424" t="s">
+        <v>201</v>
+      </c>
+      <c r="R424" t="s">
+        <v>40</v>
+      </c>
+      <c r="S424" t="s">
+        <v>39</v>
+      </c>
+      <c r="T424" t="s">
+        <v>38</v>
+      </c>
+      <c r="U424" t="s">
+        <v>41</v>
+      </c>
+      <c r="V424">
+        <v>43</v>
+      </c>
+      <c r="W424">
+        <v>17</v>
+      </c>
+      <c r="X424">
+        <v>48</v>
+      </c>
+      <c r="Y424">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="425" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A425" t="s">
+        <v>202</v>
+      </c>
+      <c r="B425" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C425" t="s">
+        <v>203</v>
+      </c>
+      <c r="E425" t="s">
+        <v>147</v>
+      </c>
+      <c r="F425" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G425" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H425" t="s">
+        <v>2615</v>
+      </c>
+      <c r="I425" t="s">
+        <v>2616</v>
+      </c>
+      <c r="J425" t="s">
+        <v>1624</v>
+      </c>
+      <c r="K425" t="s">
+        <v>2617</v>
+      </c>
+      <c r="L425" t="s">
+        <v>1444</v>
+      </c>
+      <c r="M425" t="s">
+        <v>1530</v>
+      </c>
+      <c r="N425" t="s">
+        <v>337</v>
+      </c>
+      <c r="O425" t="s">
+        <v>41</v>
+      </c>
+      <c r="P425" t="s">
+        <v>2618</v>
+      </c>
+      <c r="Q425" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R425" t="s">
+        <v>66</v>
+      </c>
+      <c r="S425" t="s">
+        <v>39</v>
+      </c>
+      <c r="T425" t="s">
+        <v>40</v>
+      </c>
+      <c r="U425" t="s">
+        <v>41</v>
+      </c>
+      <c r="V425">
+        <v>39</v>
+      </c>
+      <c r="W425">
+        <v>23</v>
+      </c>
+      <c r="X425">
+        <v>34</v>
+      </c>
+      <c r="Y425">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="426" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A426" t="s">
+        <v>202</v>
+      </c>
+      <c r="B426" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C426" t="s">
+        <v>203</v>
+      </c>
+      <c r="E426" t="s">
+        <v>157</v>
+      </c>
+      <c r="F426" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G426" t="s">
+        <v>2619</v>
+      </c>
+      <c r="H426" t="s">
+        <v>2620</v>
+      </c>
+      <c r="I426" t="s">
+        <v>2621</v>
+      </c>
+      <c r="J426" t="s">
+        <v>2622</v>
+      </c>
+      <c r="K426" t="s">
+        <v>2623</v>
+      </c>
+      <c r="L426" t="s">
+        <v>612</v>
+      </c>
+      <c r="M426" t="s">
+        <v>707</v>
+      </c>
+      <c r="N426" t="s">
+        <v>280</v>
+      </c>
+      <c r="O426" t="s">
+        <v>41</v>
+      </c>
+      <c r="P426" t="s">
+        <v>2242</v>
+      </c>
+      <c r="Q426" t="s">
+        <v>433</v>
+      </c>
+      <c r="R426" t="s">
+        <v>40</v>
+      </c>
+      <c r="S426" t="s">
+        <v>41</v>
+      </c>
+      <c r="T426" t="s">
+        <v>38</v>
+      </c>
+      <c r="U426" t="s">
+        <v>41</v>
+      </c>
+      <c r="V426">
+        <v>35</v>
+      </c>
+      <c r="W426">
+        <v>19</v>
+      </c>
+      <c r="X426">
+        <v>20</v>
+      </c>
+      <c r="Y426">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="427" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A427" t="s">
+        <v>202</v>
+      </c>
+      <c r="B427" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C427" t="s">
+        <v>203</v>
+      </c>
+      <c r="E427" t="s">
+        <v>180</v>
+      </c>
+      <c r="F427" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G427" t="s">
+        <v>2490</v>
+      </c>
+      <c r="H427" t="s">
+        <v>2624</v>
+      </c>
+      <c r="I427" t="s">
+        <v>2625</v>
+      </c>
+      <c r="J427" t="s">
+        <v>2300</v>
+      </c>
+      <c r="K427" t="s">
+        <v>2366</v>
+      </c>
+      <c r="L427" t="s">
+        <v>2626</v>
+      </c>
+      <c r="M427" t="s">
+        <v>143</v>
+      </c>
+      <c r="N427" t="s">
+        <v>555</v>
+      </c>
+      <c r="O427" t="s">
+        <v>41</v>
+      </c>
+      <c r="P427" t="s">
+        <v>1849</v>
+      </c>
+      <c r="Q427" t="s">
+        <v>811</v>
+      </c>
+      <c r="R427" t="s">
+        <v>337</v>
+      </c>
+      <c r="S427" t="s">
+        <v>113</v>
+      </c>
+      <c r="T427" t="s">
+        <v>35</v>
+      </c>
+      <c r="U427" t="s">
+        <v>38</v>
+      </c>
+      <c r="V427">
+        <v>64</v>
+      </c>
+      <c r="W427">
+        <v>51</v>
+      </c>
+      <c r="X427">
+        <v>55</v>
+      </c>
+      <c r="Y427">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="428" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A428" t="s">
+        <v>202</v>
+      </c>
+      <c r="B428" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C428" t="s">
+        <v>203</v>
+      </c>
+      <c r="E428" t="s">
+        <v>191</v>
+      </c>
+      <c r="F428" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G428" t="s">
+        <v>2627</v>
+      </c>
+      <c r="H428" t="s">
+        <v>2628</v>
+      </c>
+      <c r="I428" t="s">
+        <v>2629</v>
+      </c>
+      <c r="J428" t="s">
+        <v>2630</v>
+      </c>
+      <c r="K428" t="s">
+        <v>2631</v>
+      </c>
+      <c r="L428" t="s">
+        <v>497</v>
+      </c>
+      <c r="M428" t="s">
+        <v>1806</v>
+      </c>
+      <c r="N428" t="s">
+        <v>40</v>
+      </c>
+      <c r="O428" t="s">
+        <v>201</v>
+      </c>
+      <c r="P428" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q428" t="s">
+        <v>165</v>
+      </c>
+      <c r="R428" t="s">
+        <v>41</v>
+      </c>
+      <c r="S428" t="s">
+        <v>201</v>
+      </c>
+      <c r="T428" t="s">
+        <v>41</v>
+      </c>
+      <c r="U428" t="s">
+        <v>201</v>
+      </c>
+      <c r="V428">
+        <v>17</v>
+      </c>
+      <c r="W428">
+        <v>5</v>
+      </c>
+      <c r="X428">
+        <v>10</v>
+      </c>
+      <c r="Y428">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="429" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A429" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B429" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C429" t="s">
+        <v>203</v>
+      </c>
+      <c r="E429" t="s">
+        <v>25</v>
+      </c>
+      <c r="F429" t="s">
+        <v>2491</v>
+      </c>
+      <c r="G429" t="s">
+        <v>2492</v>
+      </c>
+      <c r="H429" t="s">
+        <v>2493</v>
+      </c>
+      <c r="I429" t="s">
+        <v>2494</v>
+      </c>
+      <c r="J429" t="s">
+        <v>2495</v>
+      </c>
+      <c r="K429" t="s">
+        <v>2496</v>
+      </c>
+      <c r="L429" t="s">
+        <v>241</v>
+      </c>
+      <c r="M429" t="s">
+        <v>1699</v>
+      </c>
+      <c r="N429" t="s">
+        <v>912</v>
+      </c>
+      <c r="O429" t="s">
+        <v>51</v>
+      </c>
+      <c r="P429" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q429" t="s">
+        <v>2497</v>
+      </c>
+      <c r="R429" t="s">
+        <v>35</v>
+      </c>
+      <c r="S429" t="s">
+        <v>40</v>
+      </c>
+      <c r="T429" t="s">
+        <v>113</v>
+      </c>
+      <c r="U429" t="s">
+        <v>39</v>
+      </c>
+      <c r="V429">
+        <v>64</v>
+      </c>
+      <c r="W429">
+        <v>37</v>
+      </c>
+      <c r="X429">
+        <v>51</v>
+      </c>
+      <c r="Y429">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="430" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A430" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B430" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C430" t="s">
+        <v>203</v>
+      </c>
+      <c r="E430" t="s">
+        <v>42</v>
+      </c>
+      <c r="F430" t="s">
+        <v>2498</v>
+      </c>
+      <c r="G430" t="s">
+        <v>2499</v>
+      </c>
+      <c r="H430" t="s">
+        <v>2500</v>
+      </c>
+      <c r="I430" t="s">
+        <v>2501</v>
+      </c>
+      <c r="J430" t="s">
+        <v>2346</v>
+      </c>
+      <c r="K430" t="s">
+        <v>2502</v>
+      </c>
+      <c r="L430" t="s">
+        <v>928</v>
+      </c>
+      <c r="M430" t="s">
+        <v>1879</v>
+      </c>
+      <c r="N430" t="s">
+        <v>2503</v>
+      </c>
+      <c r="O430" t="s">
+        <v>1448</v>
+      </c>
+      <c r="P430" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q430" t="s">
+        <v>2505</v>
+      </c>
+      <c r="R430" t="s">
+        <v>488</v>
+      </c>
+      <c r="S430" t="s">
+        <v>113</v>
+      </c>
+      <c r="T430" t="s">
+        <v>113</v>
+      </c>
+      <c r="U430" t="s">
+        <v>39</v>
+      </c>
+      <c r="V430">
+        <v>72</v>
+      </c>
+      <c r="W430">
+        <v>26</v>
+      </c>
+      <c r="X430">
+        <v>49</v>
+      </c>
+      <c r="Y430">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="431" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B431" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C431" t="s">
+        <v>203</v>
+      </c>
+      <c r="E431" t="s">
+        <v>54</v>
+      </c>
+      <c r="F431" t="s">
+        <v>2506</v>
+      </c>
+      <c r="G431" t="s">
+        <v>2507</v>
+      </c>
+      <c r="H431" t="s">
+        <v>2508</v>
+      </c>
+      <c r="I431" t="s">
+        <v>2509</v>
+      </c>
+      <c r="J431" t="s">
+        <v>2510</v>
+      </c>
+      <c r="K431" t="s">
+        <v>2511</v>
+      </c>
+      <c r="L431" t="s">
+        <v>446</v>
+      </c>
+      <c r="M431" t="s">
+        <v>595</v>
+      </c>
+      <c r="N431" t="s">
+        <v>2118</v>
+      </c>
+      <c r="O431" t="s">
+        <v>177</v>
+      </c>
+      <c r="P431" t="s">
+        <v>2512</v>
+      </c>
+      <c r="Q431" t="s">
+        <v>2143</v>
+      </c>
+      <c r="R431" t="s">
+        <v>280</v>
+      </c>
+      <c r="S431" t="s">
+        <v>35</v>
+      </c>
+      <c r="T431" t="s">
+        <v>35</v>
+      </c>
+      <c r="U431" t="s">
+        <v>39</v>
+      </c>
+      <c r="V431">
+        <v>57</v>
+      </c>
+      <c r="W431">
+        <v>40</v>
+      </c>
+      <c r="X431">
+        <v>42</v>
+      </c>
+      <c r="Y431">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="432" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A432" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B432" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C432" t="s">
+        <v>203</v>
+      </c>
+      <c r="E432" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F432" t="s">
+        <v>2513</v>
+      </c>
+      <c r="G432" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H432" t="s">
+        <v>2514</v>
+      </c>
+      <c r="I432" t="s">
+        <v>2515</v>
+      </c>
+      <c r="J432" t="s">
+        <v>2516</v>
+      </c>
+      <c r="K432" t="s">
+        <v>2517</v>
+      </c>
+      <c r="L432" t="s">
+        <v>502</v>
+      </c>
+      <c r="M432" t="s">
+        <v>309</v>
+      </c>
+      <c r="N432" t="s">
+        <v>604</v>
+      </c>
+      <c r="O432" t="s">
+        <v>38</v>
+      </c>
+      <c r="P432" t="s">
+        <v>2518</v>
+      </c>
+      <c r="Q432" t="s">
+        <v>454</v>
+      </c>
+      <c r="R432" t="s">
+        <v>39</v>
+      </c>
+      <c r="S432" t="s">
+        <v>39</v>
+      </c>
+      <c r="T432" t="s">
+        <v>39</v>
+      </c>
+      <c r="U432" t="s">
+        <v>201</v>
+      </c>
+      <c r="V432">
+        <v>20</v>
+      </c>
+      <c r="W432">
+        <v>8</v>
+      </c>
+      <c r="X432">
+        <v>16</v>
+      </c>
+      <c r="Y432">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="433" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A433" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B433" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C433" t="s">
+        <v>203</v>
+      </c>
+      <c r="E433" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F433" t="s">
+        <v>2519</v>
+      </c>
+      <c r="G433" t="s">
+        <v>2520</v>
+      </c>
+      <c r="H433" t="s">
+        <v>1783</v>
+      </c>
+      <c r="I433" t="s">
+        <v>2521</v>
+      </c>
+      <c r="J433" t="s">
+        <v>2522</v>
+      </c>
+      <c r="K433" t="s">
+        <v>2523</v>
+      </c>
+      <c r="L433" t="s">
+        <v>2524</v>
+      </c>
+      <c r="M433" t="s">
+        <v>1205</v>
+      </c>
+      <c r="N433" t="s">
+        <v>495</v>
+      </c>
+      <c r="O433" t="s">
+        <v>188</v>
+      </c>
+      <c r="P433" t="s">
+        <v>1565</v>
+      </c>
+      <c r="Q433" t="s">
+        <v>1603</v>
+      </c>
+      <c r="R433" t="s">
+        <v>38</v>
+      </c>
+      <c r="S433" t="s">
+        <v>39</v>
+      </c>
+      <c r="T433" t="s">
+        <v>39</v>
+      </c>
+      <c r="U433" t="s">
+        <v>201</v>
+      </c>
+      <c r="V433">
+        <v>16</v>
+      </c>
+      <c r="W433">
+        <v>3</v>
+      </c>
+      <c r="X433">
+        <v>12</v>
+      </c>
+      <c r="Y433">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="434" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A434" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B434" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C434" t="s">
+        <v>203</v>
+      </c>
+      <c r="E434" t="s">
+        <v>114</v>
+      </c>
+      <c r="F434" t="s">
+        <v>2525</v>
+      </c>
+      <c r="G434" t="s">
+        <v>2526</v>
+      </c>
+      <c r="H434" t="s">
+        <v>538</v>
+      </c>
+      <c r="I434" t="s">
+        <v>2527</v>
+      </c>
+      <c r="J434" t="s">
+        <v>2528</v>
+      </c>
+      <c r="K434" t="s">
+        <v>2529</v>
+      </c>
+      <c r="L434" t="s">
+        <v>73</v>
+      </c>
+      <c r="M434" t="s">
+        <v>270</v>
+      </c>
+      <c r="N434" t="s">
+        <v>495</v>
+      </c>
+      <c r="O434" t="s">
+        <v>337</v>
+      </c>
+      <c r="P434" t="s">
+        <v>2154</v>
+      </c>
+      <c r="Q434" t="s">
+        <v>1856</v>
+      </c>
+      <c r="R434" t="s">
+        <v>38</v>
+      </c>
+      <c r="S434" t="s">
+        <v>41</v>
+      </c>
+      <c r="T434" t="s">
+        <v>39</v>
+      </c>
+      <c r="U434" t="s">
+        <v>41</v>
+      </c>
+      <c r="V434">
+        <v>21</v>
+      </c>
+      <c r="W434">
+        <v>8</v>
+      </c>
+      <c r="X434">
+        <v>11</v>
+      </c>
+      <c r="Y434">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="435" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A435" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B435" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C435" t="s">
+        <v>203</v>
+      </c>
+      <c r="E435" t="s">
+        <v>126</v>
+      </c>
+      <c r="F435" t="s">
+        <v>2530</v>
+      </c>
+      <c r="G435" t="s">
+        <v>2531</v>
+      </c>
+      <c r="H435" t="s">
+        <v>2532</v>
+      </c>
+      <c r="I435" t="s">
+        <v>2533</v>
+      </c>
+      <c r="J435" t="s">
+        <v>2040</v>
+      </c>
+      <c r="K435" t="s">
+        <v>2534</v>
+      </c>
+      <c r="L435" t="s">
+        <v>513</v>
+      </c>
+      <c r="M435" t="s">
+        <v>80</v>
+      </c>
+      <c r="N435" t="s">
+        <v>483</v>
+      </c>
+      <c r="O435" t="s">
+        <v>471</v>
+      </c>
+      <c r="P435" t="s">
+        <v>2535</v>
+      </c>
+      <c r="Q435" t="s">
+        <v>218</v>
+      </c>
+      <c r="R435" t="s">
+        <v>113</v>
+      </c>
+      <c r="S435" t="s">
+        <v>38</v>
+      </c>
+      <c r="T435" t="s">
+        <v>40</v>
+      </c>
+      <c r="U435" t="s">
+        <v>41</v>
+      </c>
+      <c r="V435">
+        <v>49</v>
+      </c>
+      <c r="W435">
+        <v>20</v>
+      </c>
+      <c r="X435">
+        <v>53</v>
+      </c>
+      <c r="Y435">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="436" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A436" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B436" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C436" t="s">
+        <v>203</v>
+      </c>
+      <c r="E436" t="s">
+        <v>346</v>
+      </c>
+      <c r="F436" t="s">
+        <v>2506</v>
+      </c>
+      <c r="G436" t="s">
+        <v>2536</v>
+      </c>
+      <c r="H436" t="s">
+        <v>2537</v>
+      </c>
+      <c r="I436" t="s">
+        <v>2538</v>
+      </c>
+      <c r="J436" t="s">
+        <v>2539</v>
+      </c>
+      <c r="K436" t="s">
+        <v>2540</v>
+      </c>
+      <c r="L436" t="s">
+        <v>2541</v>
+      </c>
+      <c r="M436" t="s">
+        <v>926</v>
+      </c>
+      <c r="N436" t="s">
+        <v>62</v>
+      </c>
+      <c r="O436" t="s">
+        <v>307</v>
+      </c>
+      <c r="P436" t="s">
+        <v>2542</v>
+      </c>
+      <c r="Q436" t="s">
+        <v>2181</v>
+      </c>
+      <c r="R436" t="s">
+        <v>488</v>
+      </c>
+      <c r="S436" t="s">
+        <v>40</v>
+      </c>
+      <c r="T436" t="s">
+        <v>35</v>
+      </c>
+      <c r="U436" t="s">
+        <v>41</v>
+      </c>
+      <c r="V436">
+        <v>65</v>
+      </c>
+      <c r="W436">
+        <v>35</v>
+      </c>
+      <c r="X436">
+        <v>57</v>
+      </c>
+      <c r="Y436">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="437" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A437" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B437" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C437" t="s">
+        <v>203</v>
+      </c>
+      <c r="E437" t="s">
+        <v>137</v>
+      </c>
+      <c r="F437" t="s">
+        <v>2530</v>
+      </c>
+      <c r="G437" t="s">
+        <v>2007</v>
+      </c>
+      <c r="H437" t="s">
+        <v>2543</v>
+      </c>
+      <c r="I437" t="s">
+        <v>2544</v>
+      </c>
+      <c r="J437" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K437" t="s">
+        <v>2545</v>
+      </c>
+      <c r="L437" t="s">
+        <v>27</v>
+      </c>
+      <c r="M437" t="s">
+        <v>1444</v>
+      </c>
+      <c r="N437" t="s">
+        <v>324</v>
+      </c>
+      <c r="O437" t="s">
+        <v>40</v>
+      </c>
+      <c r="P437" t="s">
+        <v>2546</v>
+      </c>
+      <c r="Q437" t="s">
+        <v>526</v>
+      </c>
+      <c r="R437" t="s">
+        <v>449</v>
+      </c>
+      <c r="S437" t="s">
+        <v>66</v>
+      </c>
+      <c r="T437" t="s">
+        <v>66</v>
+      </c>
+      <c r="U437" t="s">
+        <v>39</v>
+      </c>
+      <c r="V437">
+        <v>73</v>
+      </c>
+      <c r="W437">
+        <v>27</v>
+      </c>
+      <c r="X437">
+        <v>78</v>
+      </c>
+      <c r="Y437">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="438" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A438" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B438" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C438" t="s">
+        <v>203</v>
+      </c>
+      <c r="E438" t="s">
+        <v>147</v>
+      </c>
+      <c r="F438" t="s">
+        <v>2530</v>
+      </c>
+      <c r="G438" t="s">
+        <v>2547</v>
+      </c>
+      <c r="H438" t="s">
+        <v>2548</v>
+      </c>
+      <c r="I438" t="s">
+        <v>2549</v>
+      </c>
+      <c r="J438" t="s">
+        <v>2550</v>
+      </c>
+      <c r="K438" t="s">
+        <v>2551</v>
+      </c>
+      <c r="L438" t="s">
+        <v>2552</v>
+      </c>
+      <c r="M438" t="s">
+        <v>694</v>
+      </c>
+      <c r="N438" t="s">
+        <v>1448</v>
+      </c>
+      <c r="O438" t="s">
+        <v>76</v>
+      </c>
+      <c r="P438" t="s">
+        <v>2553</v>
+      </c>
+      <c r="Q438" t="s">
+        <v>179</v>
+      </c>
+      <c r="R438" t="s">
+        <v>35</v>
+      </c>
+      <c r="S438" t="s">
+        <v>38</v>
+      </c>
+      <c r="T438" t="s">
+        <v>66</v>
+      </c>
+      <c r="U438" t="s">
+        <v>41</v>
+      </c>
+      <c r="V438">
+        <v>70</v>
+      </c>
+      <c r="W438">
+        <v>17</v>
+      </c>
+      <c r="X438">
+        <v>48</v>
+      </c>
+      <c r="Y438">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="439" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A439" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B439" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C439" t="s">
+        <v>203</v>
+      </c>
+      <c r="E439" t="s">
+        <v>157</v>
+      </c>
+      <c r="F439" t="s">
+        <v>2554</v>
+      </c>
+      <c r="G439" t="s">
+        <v>2555</v>
+      </c>
+      <c r="H439" t="s">
+        <v>2556</v>
+      </c>
+      <c r="I439" t="s">
+        <v>2557</v>
+      </c>
+      <c r="J439" t="s">
+        <v>2123</v>
+      </c>
+      <c r="K439" t="s">
+        <v>2558</v>
+      </c>
+      <c r="L439" t="s">
+        <v>398</v>
+      </c>
+      <c r="M439" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N439" t="s">
+        <v>483</v>
+      </c>
+      <c r="O439" t="s">
+        <v>290</v>
+      </c>
+      <c r="P439" t="s">
+        <v>2535</v>
+      </c>
+      <c r="Q439" t="s">
+        <v>2559</v>
+      </c>
+      <c r="R439" t="s">
+        <v>280</v>
+      </c>
+      <c r="S439" t="s">
+        <v>113</v>
+      </c>
+      <c r="T439" t="s">
+        <v>35</v>
+      </c>
+      <c r="U439" t="s">
+        <v>39</v>
+      </c>
+      <c r="V439">
+        <v>53</v>
+      </c>
+      <c r="W439">
+        <v>38</v>
+      </c>
+      <c r="X439">
+        <v>38</v>
+      </c>
+      <c r="Y439">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="440" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B440" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C440" t="s">
+        <v>203</v>
+      </c>
+      <c r="E440" t="s">
+        <v>180</v>
+      </c>
+      <c r="F440" t="s">
+        <v>2560</v>
+      </c>
+      <c r="G440" t="s">
+        <v>2561</v>
+      </c>
+      <c r="H440" t="s">
+        <v>2562</v>
+      </c>
+      <c r="I440" t="s">
+        <v>2563</v>
+      </c>
+      <c r="J440" t="s">
+        <v>2564</v>
+      </c>
+      <c r="K440" t="s">
+        <v>2565</v>
+      </c>
+      <c r="L440" t="s">
+        <v>2566</v>
+      </c>
+      <c r="M440" t="s">
+        <v>707</v>
+      </c>
+      <c r="N440" t="s">
+        <v>2567</v>
+      </c>
+      <c r="O440" t="s">
+        <v>76</v>
+      </c>
+      <c r="P440" t="s">
+        <v>2568</v>
+      </c>
+      <c r="Q440" t="s">
+        <v>885</v>
+      </c>
+      <c r="R440" t="s">
+        <v>280</v>
+      </c>
+      <c r="S440" t="s">
+        <v>40</v>
+      </c>
+      <c r="T440" t="s">
+        <v>113</v>
+      </c>
+      <c r="U440" t="s">
+        <v>41</v>
+      </c>
+      <c r="V440">
+        <v>69</v>
+      </c>
+      <c r="W440">
+        <v>23</v>
+      </c>
+      <c r="X440">
+        <v>60</v>
+      </c>
+      <c r="Y440">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="441" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A441" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B441" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C441" t="s">
+        <v>203</v>
+      </c>
+      <c r="E441" t="s">
+        <v>191</v>
+      </c>
+      <c r="F441" t="s">
+        <v>2530</v>
+      </c>
+      <c r="G441" t="s">
+        <v>2569</v>
+      </c>
+      <c r="H441" t="s">
+        <v>2570</v>
+      </c>
+      <c r="I441" t="s">
+        <v>2571</v>
+      </c>
+      <c r="J441" t="s">
+        <v>2572</v>
+      </c>
+      <c r="K441" t="s">
+        <v>1625</v>
+      </c>
+      <c r="L441" t="s">
+        <v>494</v>
+      </c>
+      <c r="M441" t="s">
+        <v>1835</v>
+      </c>
+      <c r="N441" t="s">
+        <v>63</v>
+      </c>
+      <c r="O441" t="s">
+        <v>38</v>
+      </c>
+      <c r="P441" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q441" t="s">
+        <v>606</v>
+      </c>
+      <c r="R441" t="s">
+        <v>38</v>
+      </c>
+      <c r="S441" t="s">
+        <v>39</v>
+      </c>
+      <c r="T441" t="s">
+        <v>40</v>
+      </c>
+      <c r="U441" t="s">
+        <v>41</v>
+      </c>
+      <c r="V441">
+        <v>55</v>
+      </c>
+      <c r="W441">
+        <v>20</v>
+      </c>
+      <c r="X441">
+        <v>23</v>
+      </c>
+      <c r="Y441">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="442" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B442" s="2"/>
+    </row>
+    <row r="443" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B443" s="2"/>
+    </row>
+    <row r="444" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B444" s="2"/>
+    </row>
+    <row r="445" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B445" s="2"/>
+    </row>
+    <row r="446" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B446" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C6F348-63B6-D645-B234-AE9BACF20F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C56DF1-1E61-2641-8A61-312CFEF7F565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8417" uniqueCount="2632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8645" uniqueCount="2680">
   <si>
     <t>Type</t>
   </si>
@@ -7932,6 +7932,150 @@
   </si>
   <si>
     <t>44.17</t>
+  </si>
+  <si>
+    <t>92.28</t>
+  </si>
+  <si>
+    <t>247.22</t>
+  </si>
+  <si>
+    <t>17.03</t>
+  </si>
+  <si>
+    <t>48.91</t>
+  </si>
+  <si>
+    <t>4.53</t>
+  </si>
+  <si>
+    <t>3.69</t>
+  </si>
+  <si>
+    <t>202.73</t>
+  </si>
+  <si>
+    <t>16.72</t>
+  </si>
+  <si>
+    <t>40.03</t>
+  </si>
+  <si>
+    <t>20.47</t>
+  </si>
+  <si>
+    <t>337.61</t>
+  </si>
+  <si>
+    <t>23.26</t>
+  </si>
+  <si>
+    <t>65.27</t>
+  </si>
+  <si>
+    <t>18.24</t>
+  </si>
+  <si>
+    <t>325.19</t>
+  </si>
+  <si>
+    <t>19.77</t>
+  </si>
+  <si>
+    <t>84.97</t>
+  </si>
+  <si>
+    <t>577.24</t>
+  </si>
+  <si>
+    <t>748.44</t>
+  </si>
+  <si>
+    <t>77.32</t>
+  </si>
+  <si>
+    <t>76.5</t>
+  </si>
+  <si>
+    <t>358.61</t>
+  </si>
+  <si>
+    <t>20.88</t>
+  </si>
+  <si>
+    <t>77.23</t>
+  </si>
+  <si>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>295.13</t>
+  </si>
+  <si>
+    <t>19.46</t>
+  </si>
+  <si>
+    <t>54.01</t>
+  </si>
+  <si>
+    <t>6.35</t>
+  </si>
+  <si>
+    <t>14.57</t>
+  </si>
+  <si>
+    <t>328.45</t>
+  </si>
+  <si>
+    <t>21.94</t>
+  </si>
+  <si>
+    <t>66.31</t>
+  </si>
+  <si>
+    <t>77.9</t>
+  </si>
+  <si>
+    <t>10.5</t>
+  </si>
+  <si>
+    <t>457.28</t>
+  </si>
+  <si>
+    <t>20.82</t>
+  </si>
+  <si>
+    <t>58.58</t>
+  </si>
+  <si>
+    <t>17.98</t>
+  </si>
+  <si>
+    <t>365.08</t>
+  </si>
+  <si>
+    <t>71.41</t>
+  </si>
+  <si>
+    <t>92.27</t>
+  </si>
+  <si>
+    <t>27.89</t>
+  </si>
+  <si>
+    <t>388.74</t>
+  </si>
+  <si>
+    <t>79.47</t>
+  </si>
+  <si>
+    <t>372.01</t>
+  </si>
+  <si>
+    <t>20.66</t>
+  </si>
+  <si>
+    <t>49.49</t>
   </si>
 </sst>
 </file>
@@ -8310,7 +8454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y446"/>
+  <dimension ref="A1:Y453"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -41723,19 +41867,892 @@
       </c>
     </row>
     <row r="442" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B442" s="2"/>
+      <c r="A442" t="s">
+        <v>202</v>
+      </c>
+      <c r="B442" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C442" t="s">
+        <v>203</v>
+      </c>
+      <c r="E442" t="s">
+        <v>25</v>
+      </c>
+      <c r="F442" t="s">
+        <v>2632</v>
+      </c>
+      <c r="G442" t="s">
+        <v>2619</v>
+      </c>
+      <c r="H442" t="s">
+        <v>201</v>
+      </c>
+      <c r="I442" t="s">
+        <v>2633</v>
+      </c>
+      <c r="J442" t="s">
+        <v>2634</v>
+      </c>
+      <c r="K442" t="s">
+        <v>2635</v>
+      </c>
+      <c r="L442" t="s">
+        <v>319</v>
+      </c>
+      <c r="M442" t="s">
+        <v>2636</v>
+      </c>
+      <c r="N442" t="s">
+        <v>201</v>
+      </c>
+      <c r="O442" t="s">
+        <v>201</v>
+      </c>
+      <c r="P442" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q442" t="s">
+        <v>201</v>
+      </c>
+      <c r="R442" t="s">
+        <v>41</v>
+      </c>
+      <c r="S442" t="s">
+        <v>201</v>
+      </c>
+      <c r="T442" t="s">
+        <v>41</v>
+      </c>
+      <c r="U442" t="s">
+        <v>201</v>
+      </c>
+      <c r="V442">
+        <v>10</v>
+      </c>
+      <c r="W442">
+        <v>2</v>
+      </c>
+      <c r="X442">
+        <v>10</v>
+      </c>
+      <c r="Y442">
+        <v>5</v>
+      </c>
     </row>
     <row r="443" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B443" s="2"/>
+      <c r="A443" t="s">
+        <v>202</v>
+      </c>
+      <c r="B443" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C443" t="s">
+        <v>203</v>
+      </c>
+      <c r="E443" t="s">
+        <v>42</v>
+      </c>
+      <c r="F443" t="s">
+        <v>2632</v>
+      </c>
+      <c r="G443" t="s">
+        <v>2637</v>
+      </c>
+      <c r="H443" t="s">
+        <v>201</v>
+      </c>
+      <c r="I443" t="s">
+        <v>2638</v>
+      </c>
+      <c r="J443" t="s">
+        <v>2639</v>
+      </c>
+      <c r="K443" t="s">
+        <v>2640</v>
+      </c>
+      <c r="L443" t="s">
+        <v>2365</v>
+      </c>
+      <c r="M443" t="s">
+        <v>728</v>
+      </c>
+      <c r="N443" t="s">
+        <v>201</v>
+      </c>
+      <c r="O443" t="s">
+        <v>201</v>
+      </c>
+      <c r="P443" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q443" t="s">
+        <v>201</v>
+      </c>
+      <c r="R443" t="s">
+        <v>41</v>
+      </c>
+      <c r="S443" t="s">
+        <v>201</v>
+      </c>
+      <c r="T443" t="s">
+        <v>201</v>
+      </c>
+      <c r="U443" t="s">
+        <v>201</v>
+      </c>
+      <c r="V443">
+        <v>4</v>
+      </c>
+      <c r="W443">
+        <v>3</v>
+      </c>
+      <c r="X443">
+        <v>6</v>
+      </c>
+      <c r="Y443">
+        <v>2</v>
+      </c>
     </row>
     <row r="444" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B444" s="2"/>
+      <c r="A444" t="s">
+        <v>202</v>
+      </c>
+      <c r="B444" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C444" t="s">
+        <v>203</v>
+      </c>
+      <c r="E444" t="s">
+        <v>54</v>
+      </c>
+      <c r="F444" t="s">
+        <v>2632</v>
+      </c>
+      <c r="G444" t="s">
+        <v>549</v>
+      </c>
+      <c r="H444" t="s">
+        <v>2641</v>
+      </c>
+      <c r="I444" t="s">
+        <v>2642</v>
+      </c>
+      <c r="J444" t="s">
+        <v>2643</v>
+      </c>
+      <c r="K444" t="s">
+        <v>2644</v>
+      </c>
+      <c r="L444" t="s">
+        <v>891</v>
+      </c>
+      <c r="M444" t="s">
+        <v>1474</v>
+      </c>
+      <c r="N444" t="s">
+        <v>39</v>
+      </c>
+      <c r="O444" t="s">
+        <v>201</v>
+      </c>
+      <c r="P444" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q444" t="s">
+        <v>201</v>
+      </c>
+      <c r="R444" t="s">
+        <v>40</v>
+      </c>
+      <c r="S444" t="s">
+        <v>41</v>
+      </c>
+      <c r="T444" t="s">
+        <v>38</v>
+      </c>
+      <c r="U444" t="s">
+        <v>41</v>
+      </c>
+      <c r="V444">
+        <v>49</v>
+      </c>
+      <c r="W444">
+        <v>13</v>
+      </c>
+      <c r="X444">
+        <v>48</v>
+      </c>
+      <c r="Y444">
+        <v>12</v>
+      </c>
     </row>
     <row r="445" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B445" s="2"/>
+      <c r="A445" t="s">
+        <v>202</v>
+      </c>
+      <c r="B445" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C445" t="s">
+        <v>203</v>
+      </c>
+      <c r="E445" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F445" t="s">
+        <v>2632</v>
+      </c>
+      <c r="G445" t="s">
+        <v>706</v>
+      </c>
+      <c r="H445" t="s">
+        <v>2645</v>
+      </c>
+      <c r="I445" t="s">
+        <v>2646</v>
+      </c>
+      <c r="J445" t="s">
+        <v>2647</v>
+      </c>
+      <c r="K445" t="s">
+        <v>1374</v>
+      </c>
+      <c r="L445" t="s">
+        <v>27</v>
+      </c>
+      <c r="M445" t="s">
+        <v>526</v>
+      </c>
+      <c r="N445" t="s">
+        <v>39</v>
+      </c>
+      <c r="O445" t="s">
+        <v>201</v>
+      </c>
+      <c r="P445" t="s">
+        <v>1468</v>
+      </c>
+      <c r="Q445" t="s">
+        <v>201</v>
+      </c>
+      <c r="R445" t="s">
+        <v>38</v>
+      </c>
+      <c r="S445" t="s">
+        <v>41</v>
+      </c>
+      <c r="T445" t="s">
+        <v>39</v>
+      </c>
+      <c r="U445" t="s">
+        <v>201</v>
+      </c>
+      <c r="V445">
+        <v>41</v>
+      </c>
+      <c r="W445">
+        <v>13</v>
+      </c>
+      <c r="X445">
+        <v>32</v>
+      </c>
+      <c r="Y445">
+        <v>22</v>
+      </c>
     </row>
     <row r="446" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B446" s="2"/>
+      <c r="A446" t="s">
+        <v>202</v>
+      </c>
+      <c r="B446" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C446" t="s">
+        <v>203</v>
+      </c>
+      <c r="E446" t="s">
+        <v>90</v>
+      </c>
+      <c r="F446" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G446" t="s">
+        <v>181</v>
+      </c>
+      <c r="H446" t="s">
+        <v>2649</v>
+      </c>
+      <c r="I446" t="s">
+        <v>2650</v>
+      </c>
+      <c r="J446" t="s">
+        <v>313</v>
+      </c>
+      <c r="K446" t="s">
+        <v>2651</v>
+      </c>
+      <c r="L446" t="s">
+        <v>519</v>
+      </c>
+      <c r="M446" t="s">
+        <v>398</v>
+      </c>
+      <c r="N446" t="s">
+        <v>902</v>
+      </c>
+      <c r="O446" t="s">
+        <v>488</v>
+      </c>
+      <c r="P446" t="s">
+        <v>2652</v>
+      </c>
+      <c r="Q446" t="s">
+        <v>1401</v>
+      </c>
+      <c r="R446" t="s">
+        <v>495</v>
+      </c>
+      <c r="S446" t="s">
+        <v>280</v>
+      </c>
+      <c r="T446" t="s">
+        <v>449</v>
+      </c>
+      <c r="U446" t="s">
+        <v>66</v>
+      </c>
+      <c r="V446">
+        <v>129</v>
+      </c>
+      <c r="W446">
+        <v>99</v>
+      </c>
+      <c r="X446">
+        <v>133</v>
+      </c>
+      <c r="Y446">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="447" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A447" t="s">
+        <v>202</v>
+      </c>
+      <c r="B447" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C447" t="s">
+        <v>203</v>
+      </c>
+      <c r="E447" t="s">
+        <v>102</v>
+      </c>
+      <c r="F447" t="s">
+        <v>2632</v>
+      </c>
+      <c r="G447" t="s">
+        <v>2077</v>
+      </c>
+      <c r="H447" t="s">
+        <v>1430</v>
+      </c>
+      <c r="I447" t="s">
+        <v>2653</v>
+      </c>
+      <c r="J447" t="s">
+        <v>2654</v>
+      </c>
+      <c r="K447" t="s">
+        <v>2655</v>
+      </c>
+      <c r="L447" t="s">
+        <v>494</v>
+      </c>
+      <c r="M447" t="s">
+        <v>1825</v>
+      </c>
+      <c r="N447" t="s">
+        <v>39</v>
+      </c>
+      <c r="O447" t="s">
+        <v>201</v>
+      </c>
+      <c r="P447" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q447" t="s">
+        <v>201</v>
+      </c>
+      <c r="R447" t="s">
+        <v>39</v>
+      </c>
+      <c r="S447" t="s">
+        <v>41</v>
+      </c>
+      <c r="T447" t="s">
+        <v>39</v>
+      </c>
+      <c r="U447" t="s">
+        <v>201</v>
+      </c>
+      <c r="V447">
+        <v>42</v>
+      </c>
+      <c r="W447">
+        <v>10</v>
+      </c>
+      <c r="X447">
+        <v>27</v>
+      </c>
+      <c r="Y447">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="448" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A448" t="s">
+        <v>202</v>
+      </c>
+      <c r="B448" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C448" t="s">
+        <v>203</v>
+      </c>
+      <c r="E448" t="s">
+        <v>114</v>
+      </c>
+      <c r="F448" t="s">
+        <v>2632</v>
+      </c>
+      <c r="G448" t="s">
+        <v>49</v>
+      </c>
+      <c r="H448" t="s">
+        <v>2656</v>
+      </c>
+      <c r="I448" t="s">
+        <v>2657</v>
+      </c>
+      <c r="J448" t="s">
+        <v>2658</v>
+      </c>
+      <c r="K448" t="s">
+        <v>2659</v>
+      </c>
+      <c r="L448" t="s">
+        <v>1682</v>
+      </c>
+      <c r="M448" t="s">
+        <v>2660</v>
+      </c>
+      <c r="N448" t="s">
+        <v>201</v>
+      </c>
+      <c r="O448" t="s">
+        <v>201</v>
+      </c>
+      <c r="P448" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q448" t="s">
+        <v>201</v>
+      </c>
+      <c r="R448" t="s">
+        <v>41</v>
+      </c>
+      <c r="S448" t="s">
+        <v>201</v>
+      </c>
+      <c r="T448" t="s">
+        <v>41</v>
+      </c>
+      <c r="U448" t="s">
+        <v>201</v>
+      </c>
+      <c r="V448">
+        <v>16</v>
+      </c>
+      <c r="W448">
+        <v>10</v>
+      </c>
+      <c r="X448">
+        <v>13</v>
+      </c>
+      <c r="Y448">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="449" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A449" t="s">
+        <v>202</v>
+      </c>
+      <c r="B449" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C449" t="s">
+        <v>203</v>
+      </c>
+      <c r="E449" t="s">
+        <v>126</v>
+      </c>
+      <c r="F449" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G449" t="s">
+        <v>241</v>
+      </c>
+      <c r="H449" t="s">
+        <v>2661</v>
+      </c>
+      <c r="I449" t="s">
+        <v>2662</v>
+      </c>
+      <c r="J449" t="s">
+        <v>2663</v>
+      </c>
+      <c r="K449" t="s">
+        <v>2664</v>
+      </c>
+      <c r="L449" t="s">
+        <v>1825</v>
+      </c>
+      <c r="M449" t="s">
+        <v>548</v>
+      </c>
+      <c r="N449" t="s">
+        <v>41</v>
+      </c>
+      <c r="O449" t="s">
+        <v>201</v>
+      </c>
+      <c r="P449" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q449" t="s">
+        <v>201</v>
+      </c>
+      <c r="R449" t="s">
+        <v>38</v>
+      </c>
+      <c r="S449" t="s">
+        <v>41</v>
+      </c>
+      <c r="T449" t="s">
+        <v>39</v>
+      </c>
+      <c r="U449" t="s">
+        <v>41</v>
+      </c>
+      <c r="V449">
+        <v>24</v>
+      </c>
+      <c r="W449">
+        <v>13</v>
+      </c>
+      <c r="X449">
+        <v>37</v>
+      </c>
+      <c r="Y449">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="450" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
+        <v>202</v>
+      </c>
+      <c r="B450" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C450" t="s">
+        <v>203</v>
+      </c>
+      <c r="E450" t="s">
+        <v>346</v>
+      </c>
+      <c r="F450" t="s">
+        <v>2665</v>
+      </c>
+      <c r="G450" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H450" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I450" t="s">
+        <v>2667</v>
+      </c>
+      <c r="J450" t="s">
+        <v>2668</v>
+      </c>
+      <c r="K450" t="s">
+        <v>2669</v>
+      </c>
+      <c r="L450" t="s">
+        <v>1682</v>
+      </c>
+      <c r="M450" t="s">
+        <v>158</v>
+      </c>
+      <c r="N450" t="s">
+        <v>41</v>
+      </c>
+      <c r="O450" t="s">
+        <v>201</v>
+      </c>
+      <c r="P450" t="s">
+        <v>811</v>
+      </c>
+      <c r="Q450" t="s">
+        <v>201</v>
+      </c>
+      <c r="R450" t="s">
+        <v>38</v>
+      </c>
+      <c r="S450" t="s">
+        <v>41</v>
+      </c>
+      <c r="T450" t="s">
+        <v>38</v>
+      </c>
+      <c r="U450" t="s">
+        <v>201</v>
+      </c>
+      <c r="V450">
+        <v>52</v>
+      </c>
+      <c r="W450">
+        <v>13</v>
+      </c>
+      <c r="X450">
+        <v>47</v>
+      </c>
+      <c r="Y450">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="451" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
+        <v>202</v>
+      </c>
+      <c r="B451" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C451" t="s">
+        <v>203</v>
+      </c>
+      <c r="E451" t="s">
+        <v>137</v>
+      </c>
+      <c r="F451" t="s">
+        <v>2632</v>
+      </c>
+      <c r="G451" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H451" t="s">
+        <v>2670</v>
+      </c>
+      <c r="I451" t="s">
+        <v>2671</v>
+      </c>
+      <c r="J451" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K451" t="s">
+        <v>2672</v>
+      </c>
+      <c r="L451" t="s">
+        <v>1287</v>
+      </c>
+      <c r="M451" t="s">
+        <v>1195</v>
+      </c>
+      <c r="N451" t="s">
+        <v>39</v>
+      </c>
+      <c r="O451" t="s">
+        <v>201</v>
+      </c>
+      <c r="P451" t="s">
+        <v>1335</v>
+      </c>
+      <c r="Q451" t="s">
+        <v>201</v>
+      </c>
+      <c r="R451" t="s">
+        <v>66</v>
+      </c>
+      <c r="S451" t="s">
+        <v>41</v>
+      </c>
+      <c r="T451" t="s">
+        <v>38</v>
+      </c>
+      <c r="U451" t="s">
+        <v>41</v>
+      </c>
+      <c r="V451">
+        <v>41</v>
+      </c>
+      <c r="W451">
+        <v>15</v>
+      </c>
+      <c r="X451">
+        <v>51</v>
+      </c>
+      <c r="Y451">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="452" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>202</v>
+      </c>
+      <c r="B452" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C452" t="s">
+        <v>203</v>
+      </c>
+      <c r="E452" t="s">
+        <v>157</v>
+      </c>
+      <c r="F452" t="s">
+        <v>2673</v>
+      </c>
+      <c r="G452" t="s">
+        <v>477</v>
+      </c>
+      <c r="H452" t="s">
+        <v>2674</v>
+      </c>
+      <c r="I452" t="s">
+        <v>2675</v>
+      </c>
+      <c r="J452" t="s">
+        <v>179</v>
+      </c>
+      <c r="K452" t="s">
+        <v>2676</v>
+      </c>
+      <c r="L452" t="s">
+        <v>1225</v>
+      </c>
+      <c r="M452" t="s">
+        <v>742</v>
+      </c>
+      <c r="N452" t="s">
+        <v>38</v>
+      </c>
+      <c r="O452" t="s">
+        <v>201</v>
+      </c>
+      <c r="P452" t="s">
+        <v>759</v>
+      </c>
+      <c r="Q452" t="s">
+        <v>201</v>
+      </c>
+      <c r="R452" t="s">
+        <v>40</v>
+      </c>
+      <c r="S452" t="s">
+        <v>41</v>
+      </c>
+      <c r="T452" t="s">
+        <v>40</v>
+      </c>
+      <c r="U452" t="s">
+        <v>41</v>
+      </c>
+      <c r="V452">
+        <v>66</v>
+      </c>
+      <c r="W452">
+        <v>26</v>
+      </c>
+      <c r="X452">
+        <v>44</v>
+      </c>
+      <c r="Y452">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="453" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>202</v>
+      </c>
+      <c r="B453" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C453" t="s">
+        <v>203</v>
+      </c>
+      <c r="E453" t="s">
+        <v>180</v>
+      </c>
+      <c r="F453" t="s">
+        <v>239</v>
+      </c>
+      <c r="G453" t="s">
+        <v>2627</v>
+      </c>
+      <c r="H453" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I453" t="s">
+        <v>2677</v>
+      </c>
+      <c r="J453" t="s">
+        <v>2678</v>
+      </c>
+      <c r="K453" t="s">
+        <v>2679</v>
+      </c>
+      <c r="L453" t="s">
+        <v>414</v>
+      </c>
+      <c r="M453" t="s">
+        <v>1961</v>
+      </c>
+      <c r="N453" t="s">
+        <v>39</v>
+      </c>
+      <c r="O453" t="s">
+        <v>201</v>
+      </c>
+      <c r="P453" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q453" t="s">
+        <v>488</v>
+      </c>
+      <c r="R453" t="s">
+        <v>488</v>
+      </c>
+      <c r="S453" t="s">
+        <v>66</v>
+      </c>
+      <c r="T453" t="s">
+        <v>66</v>
+      </c>
+      <c r="U453" t="s">
+        <v>40</v>
+      </c>
+      <c r="V453">
+        <v>50</v>
+      </c>
+      <c r="W453">
+        <v>53</v>
+      </c>
+      <c r="X453">
+        <v>91</v>
+      </c>
+      <c r="Y453">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C56DF1-1E61-2641-8A61-312CFEF7F565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7972487-FAB0-6046-8EF4-DC35D0A9EBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8645" uniqueCount="2680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8917" uniqueCount="2731">
   <si>
     <t>Type</t>
   </si>
@@ -8076,6 +8076,159 @@
   </si>
   <si>
     <t>49.49</t>
+  </si>
+  <si>
+    <t>102.27</t>
+  </si>
+  <si>
+    <t>123.3</t>
+  </si>
+  <si>
+    <t>300.66</t>
+  </si>
+  <si>
+    <t>57.54</t>
+  </si>
+  <si>
+    <t>68.98</t>
+  </si>
+  <si>
+    <t>309.59</t>
+  </si>
+  <si>
+    <t>22.91</t>
+  </si>
+  <si>
+    <t>51.98</t>
+  </si>
+  <si>
+    <t>166.34</t>
+  </si>
+  <si>
+    <t>322.1</t>
+  </si>
+  <si>
+    <t>58.26</t>
+  </si>
+  <si>
+    <t>30.6</t>
+  </si>
+  <si>
+    <t>80.56</t>
+  </si>
+  <si>
+    <t>335.91</t>
+  </si>
+  <si>
+    <t>25.35</t>
+  </si>
+  <si>
+    <t>56.13</t>
+  </si>
+  <si>
+    <t>4.12</t>
+  </si>
+  <si>
+    <t>35.86</t>
+  </si>
+  <si>
+    <t>210.77</t>
+  </si>
+  <si>
+    <t>23.74</t>
+  </si>
+  <si>
+    <t>40.29</t>
+  </si>
+  <si>
+    <t>106.95</t>
+  </si>
+  <si>
+    <t>314.77</t>
+  </si>
+  <si>
+    <t>170.12</t>
+  </si>
+  <si>
+    <t>296.35</t>
+  </si>
+  <si>
+    <t>27.68</t>
+  </si>
+  <si>
+    <t>59.2</t>
+  </si>
+  <si>
+    <t>64.9</t>
+  </si>
+  <si>
+    <t>325.81</t>
+  </si>
+  <si>
+    <t>22.32</t>
+  </si>
+  <si>
+    <t>54.64</t>
+  </si>
+  <si>
+    <t>125.69</t>
+  </si>
+  <si>
+    <t>325.1</t>
+  </si>
+  <si>
+    <t>57.87</t>
+  </si>
+  <si>
+    <t>124.18</t>
+  </si>
+  <si>
+    <t>551.85</t>
+  </si>
+  <si>
+    <t>26.34</t>
+  </si>
+  <si>
+    <t>52.47</t>
+  </si>
+  <si>
+    <t>102.59</t>
+  </si>
+  <si>
+    <t>274.82</t>
+  </si>
+  <si>
+    <t>24.15</t>
+  </si>
+  <si>
+    <t>53.9</t>
+  </si>
+  <si>
+    <t>17.4</t>
+  </si>
+  <si>
+    <t>485.08</t>
+  </si>
+  <si>
+    <t>48.06</t>
+  </si>
+  <si>
+    <t>15.4</t>
+  </si>
+  <si>
+    <t>3.94</t>
+  </si>
+  <si>
+    <t>12.03</t>
+  </si>
+  <si>
+    <t>207.09</t>
+  </si>
+  <si>
+    <t>20.79</t>
+  </si>
+  <si>
+    <t>38.54</t>
   </si>
 </sst>
 </file>
@@ -8454,7 +8607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y453"/>
+  <dimension ref="A1:Y466"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -41876,6 +42029,9 @@
       <c r="C442" t="s">
         <v>203</v>
       </c>
+      <c r="D442" t="s">
+        <v>1724</v>
+      </c>
       <c r="E442" t="s">
         <v>25</v>
       </c>
@@ -41950,6 +42106,9 @@
       <c r="C443" t="s">
         <v>203</v>
       </c>
+      <c r="D443" t="s">
+        <v>1724</v>
+      </c>
       <c r="E443" t="s">
         <v>42</v>
       </c>
@@ -42024,6 +42183,9 @@
       <c r="C444" t="s">
         <v>203</v>
       </c>
+      <c r="D444" t="s">
+        <v>1724</v>
+      </c>
       <c r="E444" t="s">
         <v>54</v>
       </c>
@@ -42098,6 +42260,9 @@
       <c r="C445" t="s">
         <v>203</v>
       </c>
+      <c r="D445" t="s">
+        <v>1724</v>
+      </c>
       <c r="E445" t="s">
         <v>1917</v>
       </c>
@@ -42172,6 +42337,9 @@
       <c r="C446" t="s">
         <v>203</v>
       </c>
+      <c r="D446" t="s">
+        <v>1724</v>
+      </c>
       <c r="E446" t="s">
         <v>90</v>
       </c>
@@ -42246,6 +42414,9 @@
       <c r="C447" t="s">
         <v>203</v>
       </c>
+      <c r="D447" t="s">
+        <v>1724</v>
+      </c>
       <c r="E447" t="s">
         <v>102</v>
       </c>
@@ -42320,6 +42491,9 @@
       <c r="C448" t="s">
         <v>203</v>
       </c>
+      <c r="D448" t="s">
+        <v>1724</v>
+      </c>
       <c r="E448" t="s">
         <v>114</v>
       </c>
@@ -42394,6 +42568,9 @@
       <c r="C449" t="s">
         <v>203</v>
       </c>
+      <c r="D449" t="s">
+        <v>1724</v>
+      </c>
       <c r="E449" t="s">
         <v>126</v>
       </c>
@@ -42468,6 +42645,9 @@
       <c r="C450" t="s">
         <v>203</v>
       </c>
+      <c r="D450" t="s">
+        <v>1724</v>
+      </c>
       <c r="E450" t="s">
         <v>346</v>
       </c>
@@ -42542,6 +42722,9 @@
       <c r="C451" t="s">
         <v>203</v>
       </c>
+      <c r="D451" t="s">
+        <v>1724</v>
+      </c>
       <c r="E451" t="s">
         <v>137</v>
       </c>
@@ -42616,6 +42799,9 @@
       <c r="C452" t="s">
         <v>203</v>
       </c>
+      <c r="D452" t="s">
+        <v>1724</v>
+      </c>
       <c r="E452" t="s">
         <v>157</v>
       </c>
@@ -42690,6 +42876,9 @@
       <c r="C453" t="s">
         <v>203</v>
       </c>
+      <c r="D453" t="s">
+        <v>1724</v>
+      </c>
       <c r="E453" t="s">
         <v>180</v>
       </c>
@@ -42752,6 +42941,1007 @@
       </c>
       <c r="Y453">
         <v>60</v>
+      </c>
+    </row>
+    <row r="454" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>202</v>
+      </c>
+      <c r="B454" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C454" t="s">
+        <v>203</v>
+      </c>
+      <c r="D454" t="s">
+        <v>848</v>
+      </c>
+      <c r="E454" t="s">
+        <v>25</v>
+      </c>
+      <c r="F454" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G454" t="s">
+        <v>278</v>
+      </c>
+      <c r="H454" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I454" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J454" t="s">
+        <v>2314</v>
+      </c>
+      <c r="K454" t="s">
+        <v>2683</v>
+      </c>
+      <c r="L454" t="s">
+        <v>1350</v>
+      </c>
+      <c r="M454" t="s">
+        <v>362</v>
+      </c>
+      <c r="N454" t="s">
+        <v>449</v>
+      </c>
+      <c r="O454" t="s">
+        <v>41</v>
+      </c>
+      <c r="P454" t="s">
+        <v>1690</v>
+      </c>
+      <c r="Q454" t="s">
+        <v>405</v>
+      </c>
+      <c r="R454" t="s">
+        <v>113</v>
+      </c>
+      <c r="S454" t="s">
+        <v>38</v>
+      </c>
+      <c r="T454" t="s">
+        <v>113</v>
+      </c>
+      <c r="U454" t="s">
+        <v>39</v>
+      </c>
+      <c r="V454">
+        <v>56</v>
+      </c>
+      <c r="W454">
+        <v>41</v>
+      </c>
+      <c r="X454">
+        <v>44</v>
+      </c>
+      <c r="Y454">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="455" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>202</v>
+      </c>
+      <c r="B455" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C455" t="s">
+        <v>203</v>
+      </c>
+      <c r="D455" t="s">
+        <v>848</v>
+      </c>
+      <c r="E455" t="s">
+        <v>54</v>
+      </c>
+      <c r="F455" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G455" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H455" t="s">
+        <v>2684</v>
+      </c>
+      <c r="I455" t="s">
+        <v>2685</v>
+      </c>
+      <c r="J455" t="s">
+        <v>2686</v>
+      </c>
+      <c r="K455" t="s">
+        <v>2687</v>
+      </c>
+      <c r="L455" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M455" t="s">
+        <v>175</v>
+      </c>
+      <c r="N455" t="s">
+        <v>35</v>
+      </c>
+      <c r="O455" t="s">
+        <v>201</v>
+      </c>
+      <c r="P455" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q455" t="s">
+        <v>201</v>
+      </c>
+      <c r="R455" t="s">
+        <v>35</v>
+      </c>
+      <c r="S455" t="s">
+        <v>38</v>
+      </c>
+      <c r="T455" t="s">
+        <v>113</v>
+      </c>
+      <c r="U455" t="s">
+        <v>39</v>
+      </c>
+      <c r="V455">
+        <v>59</v>
+      </c>
+      <c r="W455">
+        <v>38</v>
+      </c>
+      <c r="X455">
+        <v>43</v>
+      </c>
+      <c r="Y455">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="456" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>202</v>
+      </c>
+      <c r="B456" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C456" t="s">
+        <v>203</v>
+      </c>
+      <c r="D456" t="s">
+        <v>848</v>
+      </c>
+      <c r="E456" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F456" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G456" t="s">
+        <v>186</v>
+      </c>
+      <c r="H456" t="s">
+        <v>2688</v>
+      </c>
+      <c r="I456" t="s">
+        <v>2689</v>
+      </c>
+      <c r="J456" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K456" t="s">
+        <v>2690</v>
+      </c>
+      <c r="L456" t="s">
+        <v>1609</v>
+      </c>
+      <c r="M456" t="s">
+        <v>1197</v>
+      </c>
+      <c r="N456" t="s">
+        <v>177</v>
+      </c>
+      <c r="O456" t="s">
+        <v>201</v>
+      </c>
+      <c r="P456" t="s">
+        <v>2691</v>
+      </c>
+      <c r="Q456" t="s">
+        <v>201</v>
+      </c>
+      <c r="R456" t="s">
+        <v>113</v>
+      </c>
+      <c r="S456" t="s">
+        <v>38</v>
+      </c>
+      <c r="T456" t="s">
+        <v>113</v>
+      </c>
+      <c r="U456" t="s">
+        <v>41</v>
+      </c>
+      <c r="V456">
+        <v>84</v>
+      </c>
+      <c r="W456">
+        <v>30</v>
+      </c>
+      <c r="X456">
+        <v>66</v>
+      </c>
+      <c r="Y456">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="457" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>202</v>
+      </c>
+      <c r="B457" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C457" t="s">
+        <v>203</v>
+      </c>
+      <c r="D457" t="s">
+        <v>848</v>
+      </c>
+      <c r="E457" t="s">
+        <v>90</v>
+      </c>
+      <c r="F457" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G457" t="s">
+        <v>699</v>
+      </c>
+      <c r="H457" t="s">
+        <v>2692</v>
+      </c>
+      <c r="I457" t="s">
+        <v>2693</v>
+      </c>
+      <c r="J457" t="s">
+        <v>2694</v>
+      </c>
+      <c r="K457" t="s">
+        <v>2695</v>
+      </c>
+      <c r="L457" t="s">
+        <v>607</v>
+      </c>
+      <c r="M457" t="s">
+        <v>534</v>
+      </c>
+      <c r="N457" t="s">
+        <v>337</v>
+      </c>
+      <c r="O457" t="s">
+        <v>201</v>
+      </c>
+      <c r="P457" t="s">
+        <v>1555</v>
+      </c>
+      <c r="Q457" t="s">
+        <v>87</v>
+      </c>
+      <c r="R457" t="s">
+        <v>40</v>
+      </c>
+      <c r="S457" t="s">
+        <v>38</v>
+      </c>
+      <c r="T457" t="s">
+        <v>113</v>
+      </c>
+      <c r="U457" t="s">
+        <v>41</v>
+      </c>
+      <c r="V457">
+        <v>63</v>
+      </c>
+      <c r="W457">
+        <v>31</v>
+      </c>
+      <c r="X457">
+        <v>26</v>
+      </c>
+      <c r="Y457">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="458" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>202</v>
+      </c>
+      <c r="B458" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C458" t="s">
+        <v>203</v>
+      </c>
+      <c r="D458" t="s">
+        <v>848</v>
+      </c>
+      <c r="E458" t="s">
+        <v>102</v>
+      </c>
+      <c r="F458" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G458" t="s">
+        <v>2696</v>
+      </c>
+      <c r="H458" t="s">
+        <v>2697</v>
+      </c>
+      <c r="I458" t="s">
+        <v>2698</v>
+      </c>
+      <c r="J458" t="s">
+        <v>2699</v>
+      </c>
+      <c r="K458" t="s">
+        <v>2700</v>
+      </c>
+      <c r="L458" t="s">
+        <v>960</v>
+      </c>
+      <c r="M458" t="s">
+        <v>548</v>
+      </c>
+      <c r="N458" t="s">
+        <v>40</v>
+      </c>
+      <c r="O458" t="s">
+        <v>201</v>
+      </c>
+      <c r="P458" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q458" t="s">
+        <v>201</v>
+      </c>
+      <c r="R458" t="s">
+        <v>40</v>
+      </c>
+      <c r="S458" t="s">
+        <v>39</v>
+      </c>
+      <c r="T458" t="s">
+        <v>38</v>
+      </c>
+      <c r="U458" t="s">
+        <v>41</v>
+      </c>
+      <c r="V458">
+        <v>37</v>
+      </c>
+      <c r="W458">
+        <v>18</v>
+      </c>
+      <c r="X458">
+        <v>31</v>
+      </c>
+      <c r="Y458">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="459" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>202</v>
+      </c>
+      <c r="B459" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C459" t="s">
+        <v>203</v>
+      </c>
+      <c r="D459" t="s">
+        <v>848</v>
+      </c>
+      <c r="E459" t="s">
+        <v>114</v>
+      </c>
+      <c r="F459" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G459" t="s">
+        <v>764</v>
+      </c>
+      <c r="H459" t="s">
+        <v>2701</v>
+      </c>
+      <c r="I459" t="s">
+        <v>2702</v>
+      </c>
+      <c r="J459" t="s">
+        <v>2300</v>
+      </c>
+      <c r="K459" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L459" t="s">
+        <v>788</v>
+      </c>
+      <c r="M459" t="s">
+        <v>1795</v>
+      </c>
+      <c r="N459" t="s">
+        <v>488</v>
+      </c>
+      <c r="O459" t="s">
+        <v>41</v>
+      </c>
+      <c r="P459" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q459" t="s">
+        <v>773</v>
+      </c>
+      <c r="R459" t="s">
+        <v>66</v>
+      </c>
+      <c r="S459" t="s">
+        <v>39</v>
+      </c>
+      <c r="T459" t="s">
+        <v>113</v>
+      </c>
+      <c r="U459" t="s">
+        <v>39</v>
+      </c>
+      <c r="V459">
+        <v>61</v>
+      </c>
+      <c r="W459">
+        <v>35</v>
+      </c>
+      <c r="X459">
+        <v>45</v>
+      </c>
+      <c r="Y459">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="460" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>202</v>
+      </c>
+      <c r="B460" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C460" t="s">
+        <v>203</v>
+      </c>
+      <c r="D460" t="s">
+        <v>848</v>
+      </c>
+      <c r="E460" t="s">
+        <v>126</v>
+      </c>
+      <c r="F460" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G460" t="s">
+        <v>689</v>
+      </c>
+      <c r="H460" t="s">
+        <v>2703</v>
+      </c>
+      <c r="I460" t="s">
+        <v>2704</v>
+      </c>
+      <c r="J460" t="s">
+        <v>2705</v>
+      </c>
+      <c r="K460" t="s">
+        <v>2706</v>
+      </c>
+      <c r="L460" t="s">
+        <v>86</v>
+      </c>
+      <c r="M460" t="s">
+        <v>534</v>
+      </c>
+      <c r="N460" t="s">
+        <v>76</v>
+      </c>
+      <c r="O460" t="s">
+        <v>41</v>
+      </c>
+      <c r="P460" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Q460" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R460" t="s">
+        <v>66</v>
+      </c>
+      <c r="S460" t="s">
+        <v>39</v>
+      </c>
+      <c r="T460" t="s">
+        <v>40</v>
+      </c>
+      <c r="U460" t="s">
+        <v>41</v>
+      </c>
+      <c r="V460">
+        <v>45</v>
+      </c>
+      <c r="W460">
+        <v>23</v>
+      </c>
+      <c r="X460">
+        <v>37</v>
+      </c>
+      <c r="Y460">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="461" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>202</v>
+      </c>
+      <c r="B461" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C461" t="s">
+        <v>203</v>
+      </c>
+      <c r="D461" t="s">
+        <v>848</v>
+      </c>
+      <c r="E461" t="s">
+        <v>346</v>
+      </c>
+      <c r="F461" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G461" t="s">
+        <v>707</v>
+      </c>
+      <c r="H461" t="s">
+        <v>2707</v>
+      </c>
+      <c r="I461" t="s">
+        <v>2708</v>
+      </c>
+      <c r="J461" t="s">
+        <v>2709</v>
+      </c>
+      <c r="K461" t="s">
+        <v>2710</v>
+      </c>
+      <c r="L461" t="s">
+        <v>269</v>
+      </c>
+      <c r="M461" t="s">
+        <v>891</v>
+      </c>
+      <c r="N461" t="s">
+        <v>113</v>
+      </c>
+      <c r="O461" t="s">
+        <v>201</v>
+      </c>
+      <c r="P461" t="s">
+        <v>1304</v>
+      </c>
+      <c r="Q461" t="s">
+        <v>201</v>
+      </c>
+      <c r="R461" t="s">
+        <v>66</v>
+      </c>
+      <c r="S461" t="s">
+        <v>39</v>
+      </c>
+      <c r="T461" t="s">
+        <v>40</v>
+      </c>
+      <c r="U461" t="s">
+        <v>41</v>
+      </c>
+      <c r="V461">
+        <v>61</v>
+      </c>
+      <c r="W461">
+        <v>19</v>
+      </c>
+      <c r="X461">
+        <v>34</v>
+      </c>
+      <c r="Y461">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="462" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>202</v>
+      </c>
+      <c r="B462" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C462" t="s">
+        <v>203</v>
+      </c>
+      <c r="D462" t="s">
+        <v>848</v>
+      </c>
+      <c r="E462" t="s">
+        <v>137</v>
+      </c>
+      <c r="F462" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G462" t="s">
+        <v>108</v>
+      </c>
+      <c r="H462" t="s">
+        <v>2711</v>
+      </c>
+      <c r="I462" t="s">
+        <v>2712</v>
+      </c>
+      <c r="J462" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K462" t="s">
+        <v>2713</v>
+      </c>
+      <c r="L462" t="s">
+        <v>2398</v>
+      </c>
+      <c r="M462" t="s">
+        <v>768</v>
+      </c>
+      <c r="N462" t="s">
+        <v>188</v>
+      </c>
+      <c r="O462" t="s">
+        <v>201</v>
+      </c>
+      <c r="P462" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q462" t="s">
+        <v>34</v>
+      </c>
+      <c r="R462" t="s">
+        <v>35</v>
+      </c>
+      <c r="S462" t="s">
+        <v>38</v>
+      </c>
+      <c r="T462" t="s">
+        <v>40</v>
+      </c>
+      <c r="U462" t="s">
+        <v>201</v>
+      </c>
+      <c r="V462">
+        <v>71</v>
+      </c>
+      <c r="W462">
+        <v>13</v>
+      </c>
+      <c r="X462">
+        <v>50</v>
+      </c>
+      <c r="Y462">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="463" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>202</v>
+      </c>
+      <c r="B463" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C463" t="s">
+        <v>203</v>
+      </c>
+      <c r="D463" t="s">
+        <v>848</v>
+      </c>
+      <c r="E463" t="s">
+        <v>147</v>
+      </c>
+      <c r="F463" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G463" t="s">
+        <v>794</v>
+      </c>
+      <c r="H463" t="s">
+        <v>2714</v>
+      </c>
+      <c r="I463" t="s">
+        <v>2715</v>
+      </c>
+      <c r="J463" t="s">
+        <v>2716</v>
+      </c>
+      <c r="K463" t="s">
+        <v>2717</v>
+      </c>
+      <c r="L463" t="s">
+        <v>1144</v>
+      </c>
+      <c r="M463" t="s">
+        <v>120</v>
+      </c>
+      <c r="N463" t="s">
+        <v>188</v>
+      </c>
+      <c r="O463" t="s">
+        <v>41</v>
+      </c>
+      <c r="P463" t="s">
+        <v>1690</v>
+      </c>
+      <c r="Q463" t="s">
+        <v>371</v>
+      </c>
+      <c r="R463" t="s">
+        <v>337</v>
+      </c>
+      <c r="S463" t="s">
+        <v>40</v>
+      </c>
+      <c r="T463" t="s">
+        <v>113</v>
+      </c>
+      <c r="U463" t="s">
+        <v>38</v>
+      </c>
+      <c r="V463">
+        <v>61</v>
+      </c>
+      <c r="W463">
+        <v>46</v>
+      </c>
+      <c r="X463">
+        <v>63</v>
+      </c>
+      <c r="Y463">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="464" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>202</v>
+      </c>
+      <c r="B464" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C464" t="s">
+        <v>203</v>
+      </c>
+      <c r="D464" t="s">
+        <v>848</v>
+      </c>
+      <c r="E464" t="s">
+        <v>157</v>
+      </c>
+      <c r="F464" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G464" t="s">
+        <v>662</v>
+      </c>
+      <c r="H464" t="s">
+        <v>2718</v>
+      </c>
+      <c r="I464" t="s">
+        <v>2719</v>
+      </c>
+      <c r="J464" t="s">
+        <v>2720</v>
+      </c>
+      <c r="K464" t="s">
+        <v>2721</v>
+      </c>
+      <c r="L464" t="s">
+        <v>27</v>
+      </c>
+      <c r="M464" t="s">
+        <v>640</v>
+      </c>
+      <c r="N464" t="s">
+        <v>488</v>
+      </c>
+      <c r="O464" t="s">
+        <v>201</v>
+      </c>
+      <c r="P464" t="s">
+        <v>2722</v>
+      </c>
+      <c r="Q464" t="s">
+        <v>201</v>
+      </c>
+      <c r="R464" t="s">
+        <v>35</v>
+      </c>
+      <c r="S464" t="s">
+        <v>39</v>
+      </c>
+      <c r="T464" t="s">
+        <v>113</v>
+      </c>
+      <c r="U464" t="s">
+        <v>38</v>
+      </c>
+      <c r="V464">
+        <v>56</v>
+      </c>
+      <c r="W464">
+        <v>41</v>
+      </c>
+      <c r="X464">
+        <v>47</v>
+      </c>
+      <c r="Y464">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="465" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>202</v>
+      </c>
+      <c r="B465" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C465" t="s">
+        <v>203</v>
+      </c>
+      <c r="D465" t="s">
+        <v>848</v>
+      </c>
+      <c r="E465" t="s">
+        <v>180</v>
+      </c>
+      <c r="F465" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G465" t="s">
+        <v>497</v>
+      </c>
+      <c r="H465" t="s">
+        <v>1635</v>
+      </c>
+      <c r="I465" t="s">
+        <v>2723</v>
+      </c>
+      <c r="J465" t="s">
+        <v>1142</v>
+      </c>
+      <c r="K465" t="s">
+        <v>2724</v>
+      </c>
+      <c r="L465" t="s">
+        <v>2114</v>
+      </c>
+      <c r="M465" t="s">
+        <v>240</v>
+      </c>
+      <c r="N465" t="s">
+        <v>280</v>
+      </c>
+      <c r="O465" t="s">
+        <v>41</v>
+      </c>
+      <c r="P465" t="s">
+        <v>2725</v>
+      </c>
+      <c r="Q465" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R465" t="s">
+        <v>51</v>
+      </c>
+      <c r="S465" t="s">
+        <v>280</v>
+      </c>
+      <c r="T465" t="s">
+        <v>35</v>
+      </c>
+      <c r="U465" t="s">
+        <v>66</v>
+      </c>
+      <c r="V465">
+        <v>70</v>
+      </c>
+      <c r="W465">
+        <v>75</v>
+      </c>
+      <c r="X465">
+        <v>88</v>
+      </c>
+      <c r="Y465">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="466" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>202</v>
+      </c>
+      <c r="B466" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C466" t="s">
+        <v>203</v>
+      </c>
+      <c r="D466" t="s">
+        <v>848</v>
+      </c>
+      <c r="E466" t="s">
+        <v>191</v>
+      </c>
+      <c r="F466" t="s">
+        <v>2680</v>
+      </c>
+      <c r="G466" t="s">
+        <v>2726</v>
+      </c>
+      <c r="H466" t="s">
+        <v>2727</v>
+      </c>
+      <c r="I466" t="s">
+        <v>2728</v>
+      </c>
+      <c r="J466" t="s">
+        <v>2729</v>
+      </c>
+      <c r="K466" t="s">
+        <v>2730</v>
+      </c>
+      <c r="L466" t="s">
+        <v>926</v>
+      </c>
+      <c r="M466" t="s">
+        <v>821</v>
+      </c>
+      <c r="N466" t="s">
+        <v>41</v>
+      </c>
+      <c r="O466" t="s">
+        <v>201</v>
+      </c>
+      <c r="P466" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q466" t="s">
+        <v>201</v>
+      </c>
+      <c r="R466" t="s">
+        <v>39</v>
+      </c>
+      <c r="S466" t="s">
+        <v>41</v>
+      </c>
+      <c r="T466" t="s">
+        <v>41</v>
+      </c>
+      <c r="U466" t="s">
+        <v>201</v>
+      </c>
+      <c r="V466">
+        <v>18</v>
+      </c>
+      <c r="W466">
+        <v>12</v>
+      </c>
+      <c r="X466">
+        <v>15</v>
+      </c>
+      <c r="Y466">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7972487-FAB0-6046-8EF4-DC35D0A9EBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6305C456-9133-8C42-96F7-92F9734CFB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8917" uniqueCount="2731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9197" uniqueCount="2794">
   <si>
     <t>Type</t>
   </si>
@@ -8229,6 +8229,195 @@
   </si>
   <si>
     <t>38.54</t>
+  </si>
+  <si>
+    <t>80.77</t>
+  </si>
+  <si>
+    <t>98.06</t>
+  </si>
+  <si>
+    <t>249.2</t>
+  </si>
+  <si>
+    <t>23.78</t>
+  </si>
+  <si>
+    <t>64.16</t>
+  </si>
+  <si>
+    <t>81.28</t>
+  </si>
+  <si>
+    <t>275.82</t>
+  </si>
+  <si>
+    <t>266.99</t>
+  </si>
+  <si>
+    <t>65.59</t>
+  </si>
+  <si>
+    <t>35.7</t>
+  </si>
+  <si>
+    <t>81.27</t>
+  </si>
+  <si>
+    <t>335.83</t>
+  </si>
+  <si>
+    <t>267.43</t>
+  </si>
+  <si>
+    <t>59.5</t>
+  </si>
+  <si>
+    <t>233.94</t>
+  </si>
+  <si>
+    <t>396.42</t>
+  </si>
+  <si>
+    <t>95.29</t>
+  </si>
+  <si>
+    <t>393.09</t>
+  </si>
+  <si>
+    <t>520.72</t>
+  </si>
+  <si>
+    <t>27.32</t>
+  </si>
+  <si>
+    <t>70.56</t>
+  </si>
+  <si>
+    <t>54.2</t>
+  </si>
+  <si>
+    <t>449.55</t>
+  </si>
+  <si>
+    <t>268.26</t>
+  </si>
+  <si>
+    <t>26.77</t>
+  </si>
+  <si>
+    <t>71.96</t>
+  </si>
+  <si>
+    <t>75.6</t>
+  </si>
+  <si>
+    <t>734.75</t>
+  </si>
+  <si>
+    <t>316.65</t>
+  </si>
+  <si>
+    <t>31.15</t>
+  </si>
+  <si>
+    <t>73.5</t>
+  </si>
+  <si>
+    <t>110.5</t>
+  </si>
+  <si>
+    <t>213.09</t>
+  </si>
+  <si>
+    <t>289.42</t>
+  </si>
+  <si>
+    <t>76.72</t>
+  </si>
+  <si>
+    <t>4.47</t>
+  </si>
+  <si>
+    <t>28.2</t>
+  </si>
+  <si>
+    <t>271.72</t>
+  </si>
+  <si>
+    <t>318.49</t>
+  </si>
+  <si>
+    <t>28.46</t>
+  </si>
+  <si>
+    <t>80.05</t>
+  </si>
+  <si>
+    <t>37.5</t>
+  </si>
+  <si>
+    <t>171.42</t>
+  </si>
+  <si>
+    <t>324.5</t>
+  </si>
+  <si>
+    <t>24.54</t>
+  </si>
+  <si>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>155.5</t>
+  </si>
+  <si>
+    <t>492.74</t>
+  </si>
+  <si>
+    <t>28.99</t>
+  </si>
+  <si>
+    <t>68.35</t>
+  </si>
+  <si>
+    <t>8.42</t>
+  </si>
+  <si>
+    <t>500.77</t>
+  </si>
+  <si>
+    <t>250.52</t>
+  </si>
+  <si>
+    <t>32.11</t>
+  </si>
+  <si>
+    <t>66.94</t>
+  </si>
+  <si>
+    <t>61.3</t>
+  </si>
+  <si>
+    <t>323.25</t>
+  </si>
+  <si>
+    <t>530.18</t>
+  </si>
+  <si>
+    <t>70.92</t>
+  </si>
+  <si>
+    <t>48.56</t>
+  </si>
+  <si>
+    <t>239.04</t>
+  </si>
+  <si>
+    <t>26.11</t>
+  </si>
+  <si>
+    <t>65.45</t>
   </si>
 </sst>
 </file>
@@ -8607,7 +8796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y466"/>
+  <dimension ref="A1:Y480"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -43944,6 +44133,1084 @@
         <v>7</v>
       </c>
     </row>
+    <row r="467" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>202</v>
+      </c>
+      <c r="B467" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C467" t="s">
+        <v>203</v>
+      </c>
+      <c r="D467" t="s">
+        <v>204</v>
+      </c>
+      <c r="E467" t="s">
+        <v>25</v>
+      </c>
+      <c r="F467" t="s">
+        <v>2731</v>
+      </c>
+      <c r="G467" t="s">
+        <v>823</v>
+      </c>
+      <c r="H467" t="s">
+        <v>2732</v>
+      </c>
+      <c r="I467" t="s">
+        <v>2733</v>
+      </c>
+      <c r="J467" t="s">
+        <v>2734</v>
+      </c>
+      <c r="K467" t="s">
+        <v>2735</v>
+      </c>
+      <c r="L467" t="s">
+        <v>707</v>
+      </c>
+      <c r="M467" t="s">
+        <v>420</v>
+      </c>
+      <c r="N467" t="s">
+        <v>488</v>
+      </c>
+      <c r="O467" t="s">
+        <v>201</v>
+      </c>
+      <c r="P467" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q467" t="s">
+        <v>201</v>
+      </c>
+      <c r="R467" t="s">
+        <v>38</v>
+      </c>
+      <c r="S467" t="s">
+        <v>41</v>
+      </c>
+      <c r="T467" t="s">
+        <v>38</v>
+      </c>
+      <c r="U467" t="s">
+        <v>41</v>
+      </c>
+      <c r="V467">
+        <v>25</v>
+      </c>
+      <c r="W467">
+        <v>19</v>
+      </c>
+      <c r="X467">
+        <v>27</v>
+      </c>
+      <c r="Y467">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="468" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>202</v>
+      </c>
+      <c r="B468" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C468" t="s">
+        <v>203</v>
+      </c>
+      <c r="D468" t="s">
+        <v>204</v>
+      </c>
+      <c r="E468" t="s">
+        <v>54</v>
+      </c>
+      <c r="F468" t="s">
+        <v>2736</v>
+      </c>
+      <c r="G468" t="s">
+        <v>133</v>
+      </c>
+      <c r="H468" t="s">
+        <v>2737</v>
+      </c>
+      <c r="I468" t="s">
+        <v>2738</v>
+      </c>
+      <c r="J468" t="s">
+        <v>711</v>
+      </c>
+      <c r="K468" t="s">
+        <v>2739</v>
+      </c>
+      <c r="L468" t="s">
+        <v>1530</v>
+      </c>
+      <c r="M468" t="s">
+        <v>421</v>
+      </c>
+      <c r="N468" t="s">
+        <v>554</v>
+      </c>
+      <c r="O468" t="s">
+        <v>113</v>
+      </c>
+      <c r="P468" t="s">
+        <v>2740</v>
+      </c>
+      <c r="Q468" t="s">
+        <v>1714</v>
+      </c>
+      <c r="R468" t="s">
+        <v>66</v>
+      </c>
+      <c r="S468" t="s">
+        <v>39</v>
+      </c>
+      <c r="T468" t="s">
+        <v>40</v>
+      </c>
+      <c r="U468" t="s">
+        <v>41</v>
+      </c>
+      <c r="V468">
+        <v>46</v>
+      </c>
+      <c r="W468">
+        <v>26</v>
+      </c>
+      <c r="X468">
+        <v>37</v>
+      </c>
+      <c r="Y468">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="469" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>202</v>
+      </c>
+      <c r="B469" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C469" t="s">
+        <v>203</v>
+      </c>
+      <c r="D469" t="s">
+        <v>204</v>
+      </c>
+      <c r="E469" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F469" t="s">
+        <v>2741</v>
+      </c>
+      <c r="G469" t="s">
+        <v>399</v>
+      </c>
+      <c r="H469" t="s">
+        <v>2742</v>
+      </c>
+      <c r="I469" t="s">
+        <v>2743</v>
+      </c>
+      <c r="J469" t="s">
+        <v>1419</v>
+      </c>
+      <c r="K469" t="s">
+        <v>833</v>
+      </c>
+      <c r="L469" t="s">
+        <v>1350</v>
+      </c>
+      <c r="M469" t="s">
+        <v>926</v>
+      </c>
+      <c r="N469" t="s">
+        <v>912</v>
+      </c>
+      <c r="O469" t="s">
+        <v>201</v>
+      </c>
+      <c r="P469" t="s">
+        <v>2744</v>
+      </c>
+      <c r="Q469" t="s">
+        <v>165</v>
+      </c>
+      <c r="R469" t="s">
+        <v>113</v>
+      </c>
+      <c r="S469" t="s">
+        <v>38</v>
+      </c>
+      <c r="T469" t="s">
+        <v>66</v>
+      </c>
+      <c r="U469" t="s">
+        <v>41</v>
+      </c>
+      <c r="V469">
+        <v>54</v>
+      </c>
+      <c r="W469">
+        <v>15</v>
+      </c>
+      <c r="X469">
+        <v>32</v>
+      </c>
+      <c r="Y469">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="470" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>202</v>
+      </c>
+      <c r="B470" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C470" t="s">
+        <v>203</v>
+      </c>
+      <c r="D470" t="s">
+        <v>204</v>
+      </c>
+      <c r="E470" t="s">
+        <v>90</v>
+      </c>
+      <c r="F470" t="s">
+        <v>2736</v>
+      </c>
+      <c r="G470" t="s">
+        <v>802</v>
+      </c>
+      <c r="H470" t="s">
+        <v>2745</v>
+      </c>
+      <c r="I470" t="s">
+        <v>2746</v>
+      </c>
+      <c r="J470" t="s">
+        <v>1734</v>
+      </c>
+      <c r="K470" t="s">
+        <v>2747</v>
+      </c>
+      <c r="L470" t="s">
+        <v>32</v>
+      </c>
+      <c r="M470" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N470" t="s">
+        <v>63</v>
+      </c>
+      <c r="O470" t="s">
+        <v>41</v>
+      </c>
+      <c r="P470" t="s">
+        <v>721</v>
+      </c>
+      <c r="Q470" t="s">
+        <v>433</v>
+      </c>
+      <c r="R470" t="s">
+        <v>66</v>
+      </c>
+      <c r="S470" t="s">
+        <v>39</v>
+      </c>
+      <c r="T470" t="s">
+        <v>38</v>
+      </c>
+      <c r="U470" t="s">
+        <v>41</v>
+      </c>
+      <c r="V470">
+        <v>47</v>
+      </c>
+      <c r="W470">
+        <v>14</v>
+      </c>
+      <c r="X470">
+        <v>39</v>
+      </c>
+      <c r="Y470">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="471" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A471" t="s">
+        <v>202</v>
+      </c>
+      <c r="B471" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C471" t="s">
+        <v>203</v>
+      </c>
+      <c r="D471" t="s">
+        <v>204</v>
+      </c>
+      <c r="E471" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F471" t="s">
+        <v>2736</v>
+      </c>
+      <c r="G471" t="s">
+        <v>699</v>
+      </c>
+      <c r="H471" t="s">
+        <v>2748</v>
+      </c>
+      <c r="I471" t="s">
+        <v>2749</v>
+      </c>
+      <c r="J471" t="s">
+        <v>2750</v>
+      </c>
+      <c r="K471" t="s">
+        <v>2751</v>
+      </c>
+      <c r="L471" t="s">
+        <v>1504</v>
+      </c>
+      <c r="M471" t="s">
+        <v>940</v>
+      </c>
+      <c r="N471" t="s">
+        <v>912</v>
+      </c>
+      <c r="O471" t="s">
+        <v>113</v>
+      </c>
+      <c r="P471" t="s">
+        <v>2752</v>
+      </c>
+      <c r="Q471" t="s">
+        <v>1211</v>
+      </c>
+      <c r="R471" t="s">
+        <v>449</v>
+      </c>
+      <c r="S471" t="s">
+        <v>66</v>
+      </c>
+      <c r="T471" t="s">
+        <v>280</v>
+      </c>
+      <c r="U471" t="s">
+        <v>40</v>
+      </c>
+      <c r="V471">
+        <v>61</v>
+      </c>
+      <c r="W471">
+        <v>62</v>
+      </c>
+      <c r="X471">
+        <v>74</v>
+      </c>
+      <c r="Y471">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="472" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>202</v>
+      </c>
+      <c r="B472" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C472" t="s">
+        <v>203</v>
+      </c>
+      <c r="D472" t="s">
+        <v>204</v>
+      </c>
+      <c r="E472" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F472" t="s">
+        <v>2741</v>
+      </c>
+      <c r="G472" t="s">
+        <v>61</v>
+      </c>
+      <c r="H472" t="s">
+        <v>2753</v>
+      </c>
+      <c r="I472" t="s">
+        <v>2754</v>
+      </c>
+      <c r="J472" t="s">
+        <v>2755</v>
+      </c>
+      <c r="K472" t="s">
+        <v>2756</v>
+      </c>
+      <c r="L472" t="s">
+        <v>376</v>
+      </c>
+      <c r="M472" t="s">
+        <v>1835</v>
+      </c>
+      <c r="N472" t="s">
+        <v>324</v>
+      </c>
+      <c r="O472" t="s">
+        <v>39</v>
+      </c>
+      <c r="P472" t="s">
+        <v>2757</v>
+      </c>
+      <c r="Q472" t="s">
+        <v>200</v>
+      </c>
+      <c r="R472" t="s">
+        <v>66</v>
+      </c>
+      <c r="S472" t="s">
+        <v>39</v>
+      </c>
+      <c r="T472" t="s">
+        <v>66</v>
+      </c>
+      <c r="U472" t="s">
+        <v>41</v>
+      </c>
+      <c r="V472">
+        <v>64</v>
+      </c>
+      <c r="W472">
+        <v>28</v>
+      </c>
+      <c r="X472">
+        <v>32</v>
+      </c>
+      <c r="Y472">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="473" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A473" t="s">
+        <v>202</v>
+      </c>
+      <c r="B473" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C473" t="s">
+        <v>203</v>
+      </c>
+      <c r="D473" t="s">
+        <v>204</v>
+      </c>
+      <c r="E473" t="s">
+        <v>114</v>
+      </c>
+      <c r="F473" t="s">
+        <v>2741</v>
+      </c>
+      <c r="G473" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H473" t="s">
+        <v>2758</v>
+      </c>
+      <c r="I473" t="s">
+        <v>2759</v>
+      </c>
+      <c r="J473" t="s">
+        <v>2760</v>
+      </c>
+      <c r="K473" t="s">
+        <v>2761</v>
+      </c>
+      <c r="L473" t="s">
+        <v>573</v>
+      </c>
+      <c r="M473" t="s">
+        <v>1617</v>
+      </c>
+      <c r="N473" t="s">
+        <v>892</v>
+      </c>
+      <c r="O473" t="s">
+        <v>35</v>
+      </c>
+      <c r="P473" t="s">
+        <v>2762</v>
+      </c>
+      <c r="Q473" t="s">
+        <v>1504</v>
+      </c>
+      <c r="R473" t="s">
+        <v>39</v>
+      </c>
+      <c r="S473" t="s">
+        <v>39</v>
+      </c>
+      <c r="T473" t="s">
+        <v>40</v>
+      </c>
+      <c r="U473" t="s">
+        <v>39</v>
+      </c>
+      <c r="V473">
+        <v>34</v>
+      </c>
+      <c r="W473">
+        <v>35</v>
+      </c>
+      <c r="X473">
+        <v>23</v>
+      </c>
+      <c r="Y473">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="474" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A474" t="s">
+        <v>202</v>
+      </c>
+      <c r="B474" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C474" t="s">
+        <v>203</v>
+      </c>
+      <c r="D474" t="s">
+        <v>204</v>
+      </c>
+      <c r="E474" t="s">
+        <v>126</v>
+      </c>
+      <c r="F474" t="s">
+        <v>2736</v>
+      </c>
+      <c r="G474" t="s">
+        <v>788</v>
+      </c>
+      <c r="H474" t="s">
+        <v>2763</v>
+      </c>
+      <c r="I474" t="s">
+        <v>2764</v>
+      </c>
+      <c r="J474" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K474" t="s">
+        <v>2765</v>
+      </c>
+      <c r="L474" t="s">
+        <v>764</v>
+      </c>
+      <c r="M474" t="s">
+        <v>2766</v>
+      </c>
+      <c r="N474" t="s">
+        <v>177</v>
+      </c>
+      <c r="O474" t="s">
+        <v>40</v>
+      </c>
+      <c r="P474" t="s">
+        <v>2767</v>
+      </c>
+      <c r="Q474" t="s">
+        <v>1476</v>
+      </c>
+      <c r="R474" t="s">
+        <v>40</v>
+      </c>
+      <c r="S474" t="s">
+        <v>41</v>
+      </c>
+      <c r="T474" t="s">
+        <v>39</v>
+      </c>
+      <c r="U474" t="s">
+        <v>201</v>
+      </c>
+      <c r="V474">
+        <v>28</v>
+      </c>
+      <c r="W474">
+        <v>9</v>
+      </c>
+      <c r="X474">
+        <v>31</v>
+      </c>
+      <c r="Y474">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="475" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A475" t="s">
+        <v>202</v>
+      </c>
+      <c r="B475" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C475" t="s">
+        <v>203</v>
+      </c>
+      <c r="D475" t="s">
+        <v>204</v>
+      </c>
+      <c r="E475" t="s">
+        <v>346</v>
+      </c>
+      <c r="F475" t="s">
+        <v>2736</v>
+      </c>
+      <c r="G475" t="s">
+        <v>426</v>
+      </c>
+      <c r="H475" t="s">
+        <v>2768</v>
+      </c>
+      <c r="I475" t="s">
+        <v>2769</v>
+      </c>
+      <c r="J475" t="s">
+        <v>2770</v>
+      </c>
+      <c r="K475" t="s">
+        <v>2771</v>
+      </c>
+      <c r="L475" t="s">
+        <v>1385</v>
+      </c>
+      <c r="M475" t="s">
+        <v>1009</v>
+      </c>
+      <c r="N475" t="s">
+        <v>63</v>
+      </c>
+      <c r="O475" t="s">
+        <v>66</v>
+      </c>
+      <c r="P475" t="s">
+        <v>2772</v>
+      </c>
+      <c r="Q475" t="s">
+        <v>439</v>
+      </c>
+      <c r="R475" t="s">
+        <v>35</v>
+      </c>
+      <c r="S475" t="s">
+        <v>38</v>
+      </c>
+      <c r="T475" t="s">
+        <v>66</v>
+      </c>
+      <c r="U475" t="s">
+        <v>41</v>
+      </c>
+      <c r="V475">
+        <v>49</v>
+      </c>
+      <c r="W475">
+        <v>31</v>
+      </c>
+      <c r="X475">
+        <v>41</v>
+      </c>
+      <c r="Y475">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="476" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A476" t="s">
+        <v>202</v>
+      </c>
+      <c r="B476" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C476" t="s">
+        <v>203</v>
+      </c>
+      <c r="D476" t="s">
+        <v>204</v>
+      </c>
+      <c r="E476" t="s">
+        <v>137</v>
+      </c>
+      <c r="F476" t="s">
+        <v>2741</v>
+      </c>
+      <c r="G476" t="s">
+        <v>1903</v>
+      </c>
+      <c r="H476" t="s">
+        <v>2773</v>
+      </c>
+      <c r="I476" t="s">
+        <v>2774</v>
+      </c>
+      <c r="J476" t="s">
+        <v>2775</v>
+      </c>
+      <c r="K476" t="s">
+        <v>1322</v>
+      </c>
+      <c r="L476" t="s">
+        <v>788</v>
+      </c>
+      <c r="M476" t="s">
+        <v>1009</v>
+      </c>
+      <c r="N476" t="s">
+        <v>177</v>
+      </c>
+      <c r="O476" t="s">
+        <v>201</v>
+      </c>
+      <c r="P476" t="s">
+        <v>2776</v>
+      </c>
+      <c r="Q476" t="s">
+        <v>488</v>
+      </c>
+      <c r="R476" t="s">
+        <v>66</v>
+      </c>
+      <c r="S476" t="s">
+        <v>39</v>
+      </c>
+      <c r="T476" t="s">
+        <v>38</v>
+      </c>
+      <c r="U476" t="s">
+        <v>41</v>
+      </c>
+      <c r="V476">
+        <v>45</v>
+      </c>
+      <c r="W476">
+        <v>16</v>
+      </c>
+      <c r="X476">
+        <v>39</v>
+      </c>
+      <c r="Y476">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="477" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A477" t="s">
+        <v>202</v>
+      </c>
+      <c r="B477" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C477" t="s">
+        <v>203</v>
+      </c>
+      <c r="D477" t="s">
+        <v>204</v>
+      </c>
+      <c r="E477" t="s">
+        <v>147</v>
+      </c>
+      <c r="F477" t="s">
+        <v>2741</v>
+      </c>
+      <c r="G477" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H477" t="s">
+        <v>2777</v>
+      </c>
+      <c r="I477" t="s">
+        <v>2778</v>
+      </c>
+      <c r="J477" t="s">
+        <v>2779</v>
+      </c>
+      <c r="K477" t="s">
+        <v>2780</v>
+      </c>
+      <c r="L477" t="s">
+        <v>2781</v>
+      </c>
+      <c r="M477" t="s">
+        <v>48</v>
+      </c>
+      <c r="N477" t="s">
+        <v>188</v>
+      </c>
+      <c r="O477" t="s">
+        <v>38</v>
+      </c>
+      <c r="P477" t="s">
+        <v>1246</v>
+      </c>
+      <c r="Q477" t="s">
+        <v>344</v>
+      </c>
+      <c r="R477" t="s">
+        <v>66</v>
+      </c>
+      <c r="S477" t="s">
+        <v>39</v>
+      </c>
+      <c r="T477" t="s">
+        <v>66</v>
+      </c>
+      <c r="U477" t="s">
+        <v>39</v>
+      </c>
+      <c r="V477">
+        <v>55</v>
+      </c>
+      <c r="W477">
+        <v>35</v>
+      </c>
+      <c r="X477">
+        <v>49</v>
+      </c>
+      <c r="Y477">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="478" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A478" t="s">
+        <v>202</v>
+      </c>
+      <c r="B478" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C478" t="s">
+        <v>203</v>
+      </c>
+      <c r="D478" t="s">
+        <v>204</v>
+      </c>
+      <c r="E478" t="s">
+        <v>157</v>
+      </c>
+      <c r="F478" t="s">
+        <v>2736</v>
+      </c>
+      <c r="G478" t="s">
+        <v>221</v>
+      </c>
+      <c r="H478" t="s">
+        <v>2782</v>
+      </c>
+      <c r="I478" t="s">
+        <v>2783</v>
+      </c>
+      <c r="J478" t="s">
+        <v>2784</v>
+      </c>
+      <c r="K478" t="s">
+        <v>2785</v>
+      </c>
+      <c r="L478" t="s">
+        <v>397</v>
+      </c>
+      <c r="M478" t="s">
+        <v>270</v>
+      </c>
+      <c r="N478" t="s">
+        <v>242</v>
+      </c>
+      <c r="O478" t="s">
+        <v>188</v>
+      </c>
+      <c r="P478" t="s">
+        <v>2786</v>
+      </c>
+      <c r="Q478" t="s">
+        <v>1185</v>
+      </c>
+      <c r="R478" t="s">
+        <v>35</v>
+      </c>
+      <c r="S478" t="s">
+        <v>39</v>
+      </c>
+      <c r="T478" t="s">
+        <v>113</v>
+      </c>
+      <c r="U478" t="s">
+        <v>39</v>
+      </c>
+      <c r="V478">
+        <v>38</v>
+      </c>
+      <c r="W478">
+        <v>32</v>
+      </c>
+      <c r="X478">
+        <v>40</v>
+      </c>
+      <c r="Y478">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="479" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A479" t="s">
+        <v>202</v>
+      </c>
+      <c r="B479" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C479" t="s">
+        <v>203</v>
+      </c>
+      <c r="D479" t="s">
+        <v>204</v>
+      </c>
+      <c r="E479" t="s">
+        <v>180</v>
+      </c>
+      <c r="F479" t="s">
+        <v>2741</v>
+      </c>
+      <c r="G479" t="s">
+        <v>891</v>
+      </c>
+      <c r="H479" t="s">
+        <v>2787</v>
+      </c>
+      <c r="I479" t="s">
+        <v>2788</v>
+      </c>
+      <c r="J479" t="s">
+        <v>1896</v>
+      </c>
+      <c r="K479" t="s">
+        <v>2789</v>
+      </c>
+      <c r="L479" t="s">
+        <v>1719</v>
+      </c>
+      <c r="M479" t="s">
+        <v>1308</v>
+      </c>
+      <c r="N479" t="s">
+        <v>307</v>
+      </c>
+      <c r="O479" t="s">
+        <v>35</v>
+      </c>
+      <c r="P479" t="s">
+        <v>1493</v>
+      </c>
+      <c r="Q479" t="s">
+        <v>234</v>
+      </c>
+      <c r="R479" t="s">
+        <v>471</v>
+      </c>
+      <c r="S479" t="s">
+        <v>488</v>
+      </c>
+      <c r="T479" t="s">
+        <v>51</v>
+      </c>
+      <c r="U479" t="s">
+        <v>113</v>
+      </c>
+      <c r="V479">
+        <v>109</v>
+      </c>
+      <c r="W479">
+        <v>98</v>
+      </c>
+      <c r="X479">
+        <v>147</v>
+      </c>
+      <c r="Y479">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="480" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A480" t="s">
+        <v>202</v>
+      </c>
+      <c r="B480" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C480" t="s">
+        <v>203</v>
+      </c>
+      <c r="D480" t="s">
+        <v>204</v>
+      </c>
+      <c r="E480" t="s">
+        <v>191</v>
+      </c>
+      <c r="F480" t="s">
+        <v>2736</v>
+      </c>
+      <c r="G480" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H480" t="s">
+        <v>2790</v>
+      </c>
+      <c r="I480" t="s">
+        <v>2791</v>
+      </c>
+      <c r="J480" t="s">
+        <v>2792</v>
+      </c>
+      <c r="K480" t="s">
+        <v>2793</v>
+      </c>
+      <c r="L480" t="s">
+        <v>385</v>
+      </c>
+      <c r="M480" t="s">
+        <v>1864</v>
+      </c>
+      <c r="N480" t="s">
+        <v>40</v>
+      </c>
+      <c r="O480" t="s">
+        <v>201</v>
+      </c>
+      <c r="P480" t="s">
+        <v>533</v>
+      </c>
+      <c r="Q480" t="s">
+        <v>87</v>
+      </c>
+      <c r="R480" t="s">
+        <v>39</v>
+      </c>
+      <c r="S480" t="s">
+        <v>201</v>
+      </c>
+      <c r="T480" t="s">
+        <v>39</v>
+      </c>
+      <c r="U480" t="s">
+        <v>201</v>
+      </c>
+      <c r="V480">
+        <v>17</v>
+      </c>
+      <c r="W480">
+        <v>7</v>
+      </c>
+      <c r="X480">
+        <v>15</v>
+      </c>
+      <c r="Y480">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Gps propres catapult.xlsx
+++ b/data/2026-2027/Gps propres catapult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6305C456-9133-8C42-96F7-92F9734CFB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8863A6-99A5-C742-B8A2-16D1AC0EFCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16360" xr2:uid="{00696206-4DE9-804C-BC07-569846BD9774}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9197" uniqueCount="2794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9477" uniqueCount="2861">
   <si>
     <t>Type</t>
   </si>
@@ -8418,6 +8418,207 @@
   </si>
   <si>
     <t>65.45</t>
+  </si>
+  <si>
+    <t>80.08</t>
+  </si>
+  <si>
+    <t>3.88</t>
+  </si>
+  <si>
+    <t>52.99</t>
+  </si>
+  <si>
+    <t>206.33</t>
+  </si>
+  <si>
+    <t>24.05</t>
+  </si>
+  <si>
+    <t>48.45</t>
+  </si>
+  <si>
+    <t>Brady Gouandjia</t>
+  </si>
+  <si>
+    <t>186.14</t>
+  </si>
+  <si>
+    <t>211.57</t>
+  </si>
+  <si>
+    <t>47.42</t>
+  </si>
+  <si>
+    <t>279.16</t>
+  </si>
+  <si>
+    <t>195.61</t>
+  </si>
+  <si>
+    <t>27.97</t>
+  </si>
+  <si>
+    <t>46.73</t>
+  </si>
+  <si>
+    <t>35.1</t>
+  </si>
+  <si>
+    <t>227.78</t>
+  </si>
+  <si>
+    <t>53.86</t>
+  </si>
+  <si>
+    <t>26.6</t>
+  </si>
+  <si>
+    <t>3.97</t>
+  </si>
+  <si>
+    <t>439.68</t>
+  </si>
+  <si>
+    <t>209.98</t>
+  </si>
+  <si>
+    <t>49.62</t>
+  </si>
+  <si>
+    <t>53.1</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>268.28</t>
+  </si>
+  <si>
+    <t>342.9</t>
+  </si>
+  <si>
+    <t>28.82</t>
+  </si>
+  <si>
+    <t>54.05</t>
+  </si>
+  <si>
+    <t>522.35</t>
+  </si>
+  <si>
+    <t>214.01</t>
+  </si>
+  <si>
+    <t>28.26</t>
+  </si>
+  <si>
+    <t>56.14</t>
+  </si>
+  <si>
+    <t>59.69</t>
+  </si>
+  <si>
+    <t>282.85</t>
+  </si>
+  <si>
+    <t>382.82</t>
+  </si>
+  <si>
+    <t>30.41</t>
+  </si>
+  <si>
+    <t>50.72</t>
+  </si>
+  <si>
+    <t>32.0</t>
+  </si>
+  <si>
+    <t>457.45</t>
+  </si>
+  <si>
+    <t>272.9</t>
+  </si>
+  <si>
+    <t>30.72</t>
+  </si>
+  <si>
+    <t>64.83</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>19.3</t>
+  </si>
+  <si>
+    <t>135.57</t>
+  </si>
+  <si>
+    <t>224.16</t>
+  </si>
+  <si>
+    <t>28.15</t>
+  </si>
+  <si>
+    <t>51.24</t>
+  </si>
+  <si>
+    <t>17.6</t>
+  </si>
+  <si>
+    <t>279.4</t>
+  </si>
+  <si>
+    <t>412.24</t>
+  </si>
+  <si>
+    <t>51.01</t>
+  </si>
+  <si>
+    <t>4.23</t>
+  </si>
+  <si>
+    <t>307.61</t>
+  </si>
+  <si>
+    <t>213.51</t>
+  </si>
+  <si>
+    <t>29.05</t>
+  </si>
+  <si>
+    <t>52.82</t>
+  </si>
+  <si>
+    <t>4.96</t>
+  </si>
+  <si>
+    <t>33.5</t>
+  </si>
+  <si>
+    <t>13.4</t>
+  </si>
+  <si>
+    <t>63.28</t>
+  </si>
+  <si>
+    <t>3.51</t>
+  </si>
+  <si>
+    <t>394.33</t>
+  </si>
+  <si>
+    <t>331.08</t>
+  </si>
+  <si>
+    <t>31.12</t>
+  </si>
+  <si>
+    <t>55.52</t>
+  </si>
+  <si>
+    <t>20.8</t>
   </si>
 </sst>
 </file>
@@ -8796,7 +8997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC695E1-C828-EE4B-8837-F278E90C9006}">
-  <dimension ref="A1:Y480"/>
+  <dimension ref="A1:Y494"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -45211,6 +45412,1084 @@
         <v>6</v>
       </c>
     </row>
+    <row r="481" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A481" t="s">
+        <v>202</v>
+      </c>
+      <c r="B481" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C481" t="s">
+        <v>203</v>
+      </c>
+      <c r="D481" t="s">
+        <v>345</v>
+      </c>
+      <c r="E481" t="s">
+        <v>25</v>
+      </c>
+      <c r="F481" t="s">
+        <v>2794</v>
+      </c>
+      <c r="G481" t="s">
+        <v>2795</v>
+      </c>
+      <c r="H481" t="s">
+        <v>2796</v>
+      </c>
+      <c r="I481" t="s">
+        <v>2797</v>
+      </c>
+      <c r="J481" t="s">
+        <v>2798</v>
+      </c>
+      <c r="K481" t="s">
+        <v>2799</v>
+      </c>
+      <c r="L481" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M481" t="s">
+        <v>254</v>
+      </c>
+      <c r="N481" t="s">
+        <v>66</v>
+      </c>
+      <c r="O481" t="s">
+        <v>201</v>
+      </c>
+      <c r="P481" t="s">
+        <v>1047</v>
+      </c>
+      <c r="Q481" t="s">
+        <v>488</v>
+      </c>
+      <c r="R481" t="s">
+        <v>201</v>
+      </c>
+      <c r="S481" t="s">
+        <v>201</v>
+      </c>
+      <c r="T481" t="s">
+        <v>41</v>
+      </c>
+      <c r="U481" t="s">
+        <v>201</v>
+      </c>
+      <c r="V481">
+        <v>13</v>
+      </c>
+      <c r="W481">
+        <v>1</v>
+      </c>
+      <c r="X481">
+        <v>5</v>
+      </c>
+      <c r="Y481">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>202</v>
+      </c>
+      <c r="B482" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C482" t="s">
+        <v>203</v>
+      </c>
+      <c r="D482" t="s">
+        <v>345</v>
+      </c>
+      <c r="E482" t="s">
+        <v>2800</v>
+      </c>
+      <c r="F482" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G482" t="s">
+        <v>606</v>
+      </c>
+      <c r="H482" t="s">
+        <v>2801</v>
+      </c>
+      <c r="I482" t="s">
+        <v>2802</v>
+      </c>
+      <c r="J482" t="s">
+        <v>1552</v>
+      </c>
+      <c r="K482" t="s">
+        <v>2803</v>
+      </c>
+      <c r="L482" t="s">
+        <v>55</v>
+      </c>
+      <c r="M482" t="s">
+        <v>487</v>
+      </c>
+      <c r="N482" t="s">
+        <v>555</v>
+      </c>
+      <c r="O482" t="s">
+        <v>40</v>
+      </c>
+      <c r="P482" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q482" t="s">
+        <v>603</v>
+      </c>
+      <c r="R482" t="s">
+        <v>39</v>
+      </c>
+      <c r="S482" t="s">
+        <v>201</v>
+      </c>
+      <c r="T482" t="s">
+        <v>38</v>
+      </c>
+      <c r="U482" t="s">
+        <v>41</v>
+      </c>
+      <c r="V482">
+        <v>21</v>
+      </c>
+      <c r="W482">
+        <v>12</v>
+      </c>
+      <c r="X482">
+        <v>9</v>
+      </c>
+      <c r="Y482">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="483" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>202</v>
+      </c>
+      <c r="B483" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C483" t="s">
+        <v>203</v>
+      </c>
+      <c r="D483" t="s">
+        <v>345</v>
+      </c>
+      <c r="E483" t="s">
+        <v>54</v>
+      </c>
+      <c r="F483" t="s">
+        <v>2794</v>
+      </c>
+      <c r="G483" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H483" t="s">
+        <v>2804</v>
+      </c>
+      <c r="I483" t="s">
+        <v>2805</v>
+      </c>
+      <c r="J483" t="s">
+        <v>2806</v>
+      </c>
+      <c r="K483" t="s">
+        <v>2807</v>
+      </c>
+      <c r="L483" t="s">
+        <v>534</v>
+      </c>
+      <c r="M483" t="s">
+        <v>1474</v>
+      </c>
+      <c r="N483" t="s">
+        <v>554</v>
+      </c>
+      <c r="O483" t="s">
+        <v>113</v>
+      </c>
+      <c r="P483" t="s">
+        <v>2808</v>
+      </c>
+      <c r="Q483" t="s">
+        <v>1255</v>
+      </c>
+      <c r="R483" t="s">
+        <v>40</v>
+      </c>
+      <c r="S483" t="s">
+        <v>41</v>
+      </c>
+      <c r="T483" t="s">
+        <v>41</v>
+      </c>
+      <c r="U483" t="s">
+        <v>201</v>
+      </c>
+      <c r="V483">
+        <v>17</v>
+      </c>
+      <c r="W483">
+        <v>6</v>
+      </c>
+      <c r="X483">
+        <v>26</v>
+      </c>
+      <c r="Y483">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="484" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>202</v>
+      </c>
+      <c r="B484" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C484" t="s">
+        <v>203</v>
+      </c>
+      <c r="D484" t="s">
+        <v>345</v>
+      </c>
+      <c r="E484" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F484" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G484" t="s">
+        <v>847</v>
+      </c>
+      <c r="H484" t="s">
+        <v>523</v>
+      </c>
+      <c r="I484" t="s">
+        <v>2809</v>
+      </c>
+      <c r="J484" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K484" t="s">
+        <v>2810</v>
+      </c>
+      <c r="L484" t="s">
+        <v>115</v>
+      </c>
+      <c r="M484" t="s">
+        <v>1108</v>
+      </c>
+      <c r="N484" t="s">
+        <v>177</v>
+      </c>
+      <c r="O484" t="s">
+        <v>337</v>
+      </c>
+      <c r="P484" t="s">
+        <v>2811</v>
+      </c>
+      <c r="Q484" t="s">
+        <v>427</v>
+      </c>
+      <c r="R484" t="s">
+        <v>39</v>
+      </c>
+      <c r="S484" t="s">
+        <v>201</v>
+      </c>
+      <c r="T484" t="s">
+        <v>41</v>
+      </c>
+      <c r="U484" t="s">
+        <v>201</v>
+      </c>
+      <c r="V484">
+        <v>17</v>
+      </c>
+      <c r="W484">
+        <v>2</v>
+      </c>
+      <c r="X484">
+        <v>15</v>
+      </c>
+      <c r="Y484">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="485" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A485" t="s">
+        <v>202</v>
+      </c>
+      <c r="B485" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C485" t="s">
+        <v>203</v>
+      </c>
+      <c r="D485" t="s">
+        <v>345</v>
+      </c>
+      <c r="E485" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F485" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G485" t="s">
+        <v>2812</v>
+      </c>
+      <c r="H485" t="s">
+        <v>2813</v>
+      </c>
+      <c r="I485" t="s">
+        <v>2814</v>
+      </c>
+      <c r="J485" t="s">
+        <v>1647</v>
+      </c>
+      <c r="K485" t="s">
+        <v>2815</v>
+      </c>
+      <c r="L485" t="s">
+        <v>494</v>
+      </c>
+      <c r="M485" t="s">
+        <v>1864</v>
+      </c>
+      <c r="N485" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O485" t="s">
+        <v>51</v>
+      </c>
+      <c r="P485" t="s">
+        <v>2816</v>
+      </c>
+      <c r="Q485" t="s">
+        <v>2817</v>
+      </c>
+      <c r="R485" t="s">
+        <v>39</v>
+      </c>
+      <c r="S485" t="s">
+        <v>39</v>
+      </c>
+      <c r="T485" t="s">
+        <v>41</v>
+      </c>
+      <c r="U485" t="s">
+        <v>41</v>
+      </c>
+      <c r="V485">
+        <v>13</v>
+      </c>
+      <c r="W485">
+        <v>6</v>
+      </c>
+      <c r="X485">
+        <v>12</v>
+      </c>
+      <c r="Y485">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="486" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>202</v>
+      </c>
+      <c r="B486" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C486" t="s">
+        <v>203</v>
+      </c>
+      <c r="D486" t="s">
+        <v>345</v>
+      </c>
+      <c r="E486" t="s">
+        <v>90</v>
+      </c>
+      <c r="F486" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G486" t="s">
+        <v>241</v>
+      </c>
+      <c r="H486" t="s">
+        <v>2818</v>
+      </c>
+      <c r="I486" t="s">
+        <v>2819</v>
+      </c>
+      <c r="J486" t="s">
+        <v>2820</v>
+      </c>
+      <c r="K486" t="s">
+        <v>2821</v>
+      </c>
+      <c r="L486" t="s">
+        <v>1400</v>
+      </c>
+      <c r="M486" t="s">
+        <v>1864</v>
+      </c>
+      <c r="N486" t="s">
+        <v>554</v>
+      </c>
+      <c r="O486" t="s">
+        <v>66</v>
+      </c>
+      <c r="P486" t="s">
+        <v>2171</v>
+      </c>
+      <c r="Q486" t="s">
+        <v>766</v>
+      </c>
+      <c r="R486" t="s">
+        <v>39</v>
+      </c>
+      <c r="S486" t="s">
+        <v>201</v>
+      </c>
+      <c r="T486" t="s">
+        <v>38</v>
+      </c>
+      <c r="U486" t="s">
+        <v>41</v>
+      </c>
+      <c r="V486">
+        <v>35</v>
+      </c>
+      <c r="W486">
+        <v>13</v>
+      </c>
+      <c r="X486">
+        <v>25</v>
+      </c>
+      <c r="Y486">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="487" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A487" t="s">
+        <v>202</v>
+      </c>
+      <c r="B487" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C487" t="s">
+        <v>203</v>
+      </c>
+      <c r="D487" t="s">
+        <v>345</v>
+      </c>
+      <c r="E487" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F487" t="s">
+        <v>2794</v>
+      </c>
+      <c r="G487" t="s">
+        <v>225</v>
+      </c>
+      <c r="H487" t="s">
+        <v>2822</v>
+      </c>
+      <c r="I487" t="s">
+        <v>2823</v>
+      </c>
+      <c r="J487" t="s">
+        <v>2824</v>
+      </c>
+      <c r="K487" t="s">
+        <v>2825</v>
+      </c>
+      <c r="L487" t="s">
+        <v>494</v>
+      </c>
+      <c r="M487" t="s">
+        <v>759</v>
+      </c>
+      <c r="N487" t="s">
+        <v>50</v>
+      </c>
+      <c r="O487" t="s">
+        <v>337</v>
+      </c>
+      <c r="P487" t="s">
+        <v>903</v>
+      </c>
+      <c r="Q487" t="s">
+        <v>2666</v>
+      </c>
+      <c r="R487" t="s">
+        <v>41</v>
+      </c>
+      <c r="S487" t="s">
+        <v>41</v>
+      </c>
+      <c r="T487" t="s">
+        <v>41</v>
+      </c>
+      <c r="U487" t="s">
+        <v>201</v>
+      </c>
+      <c r="V487">
+        <v>27</v>
+      </c>
+      <c r="W487">
+        <v>5</v>
+      </c>
+      <c r="X487">
+        <v>12</v>
+      </c>
+      <c r="Y487">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="488" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A488" t="s">
+        <v>202</v>
+      </c>
+      <c r="B488" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C488" t="s">
+        <v>203</v>
+      </c>
+      <c r="D488" t="s">
+        <v>345</v>
+      </c>
+      <c r="E488" t="s">
+        <v>126</v>
+      </c>
+      <c r="F488" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G488" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H488" t="s">
+        <v>1557</v>
+      </c>
+      <c r="I488" t="s">
+        <v>237</v>
+      </c>
+      <c r="J488" t="s">
+        <v>313</v>
+      </c>
+      <c r="K488" t="s">
+        <v>2826</v>
+      </c>
+      <c r="L488" t="s">
+        <v>454</v>
+      </c>
+      <c r="M488" t="s">
+        <v>675</v>
+      </c>
+      <c r="N488" t="s">
+        <v>213</v>
+      </c>
+      <c r="O488" t="s">
+        <v>337</v>
+      </c>
+      <c r="P488" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q488" t="s">
+        <v>2182</v>
+      </c>
+      <c r="R488" t="s">
+        <v>39</v>
+      </c>
+      <c r="S488" t="s">
+        <v>201</v>
+      </c>
+      <c r="T488" t="s">
+        <v>39</v>
+      </c>
+      <c r="U488" t="s">
+        <v>201</v>
+      </c>
+      <c r="V488">
+        <v>25</v>
+      </c>
+      <c r="W488">
+        <v>8</v>
+      </c>
+      <c r="X488">
+        <v>24</v>
+      </c>
+      <c r="Y488">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="489" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A489" t="s">
+        <v>202</v>
+      </c>
+      <c r="B489" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C489" t="s">
+        <v>203</v>
+      </c>
+      <c r="D489" t="s">
+        <v>345</v>
+      </c>
+      <c r="E489" t="s">
+        <v>346</v>
+      </c>
+      <c r="F489" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G489" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H489" t="s">
+        <v>2827</v>
+      </c>
+      <c r="I489" t="s">
+        <v>2828</v>
+      </c>
+      <c r="J489" t="s">
+        <v>2829</v>
+      </c>
+      <c r="K489" t="s">
+        <v>2830</v>
+      </c>
+      <c r="L489" t="s">
+        <v>876</v>
+      </c>
+      <c r="M489" t="s">
+        <v>497</v>
+      </c>
+      <c r="N489" t="s">
+        <v>471</v>
+      </c>
+      <c r="O489" t="s">
+        <v>280</v>
+      </c>
+      <c r="P489" t="s">
+        <v>2831</v>
+      </c>
+      <c r="Q489" t="s">
+        <v>2610</v>
+      </c>
+      <c r="R489" t="s">
+        <v>66</v>
+      </c>
+      <c r="S489" t="s">
+        <v>39</v>
+      </c>
+      <c r="T489" t="s">
+        <v>40</v>
+      </c>
+      <c r="U489" t="s">
+        <v>41</v>
+      </c>
+      <c r="V489">
+        <v>34</v>
+      </c>
+      <c r="W489">
+        <v>20</v>
+      </c>
+      <c r="X489">
+        <v>38</v>
+      </c>
+      <c r="Y489">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="490" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A490" t="s">
+        <v>202</v>
+      </c>
+      <c r="B490" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C490" t="s">
+        <v>203</v>
+      </c>
+      <c r="D490" t="s">
+        <v>345</v>
+      </c>
+      <c r="E490" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F490" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G490" t="s">
+        <v>663</v>
+      </c>
+      <c r="H490" t="s">
+        <v>2832</v>
+      </c>
+      <c r="I490" t="s">
+        <v>2833</v>
+      </c>
+      <c r="J490" t="s">
+        <v>2834</v>
+      </c>
+      <c r="K490" t="s">
+        <v>2835</v>
+      </c>
+      <c r="L490" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M490" t="s">
+        <v>269</v>
+      </c>
+      <c r="N490" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O490" t="s">
+        <v>495</v>
+      </c>
+      <c r="P490" t="s">
+        <v>2836</v>
+      </c>
+      <c r="Q490" t="s">
+        <v>2837</v>
+      </c>
+      <c r="R490" t="s">
+        <v>38</v>
+      </c>
+      <c r="S490" t="s">
+        <v>39</v>
+      </c>
+      <c r="T490" t="s">
+        <v>38</v>
+      </c>
+      <c r="U490" t="s">
+        <v>41</v>
+      </c>
+      <c r="V490">
+        <v>27</v>
+      </c>
+      <c r="W490">
+        <v>12</v>
+      </c>
+      <c r="X490">
+        <v>26</v>
+      </c>
+      <c r="Y490">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="491" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A491" t="s">
+        <v>202</v>
+      </c>
+      <c r="B491" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C491" t="s">
+        <v>203</v>
+      </c>
+      <c r="D491" t="s">
+        <v>345</v>
+      </c>
+      <c r="E491" t="s">
+        <v>137</v>
+      </c>
+      <c r="F491" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G491" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H491" t="s">
+        <v>2838</v>
+      </c>
+      <c r="I491" t="s">
+        <v>2839</v>
+      </c>
+      <c r="J491" t="s">
+        <v>2840</v>
+      </c>
+      <c r="K491" t="s">
+        <v>2841</v>
+      </c>
+      <c r="L491" t="s">
+        <v>823</v>
+      </c>
+      <c r="M491" t="s">
+        <v>211</v>
+      </c>
+      <c r="N491" t="s">
+        <v>449</v>
+      </c>
+      <c r="O491" t="s">
+        <v>38</v>
+      </c>
+      <c r="P491" t="s">
+        <v>2842</v>
+      </c>
+      <c r="Q491" t="s">
+        <v>670</v>
+      </c>
+      <c r="R491" t="s">
+        <v>38</v>
+      </c>
+      <c r="S491" t="s">
+        <v>201</v>
+      </c>
+      <c r="T491" t="s">
+        <v>39</v>
+      </c>
+      <c r="U491" t="s">
+        <v>201</v>
+      </c>
+      <c r="V491">
+        <v>22</v>
+      </c>
+      <c r="W491">
+        <v>12</v>
+      </c>
+      <c r="X491">
+        <v>25</v>
+      </c>
+      <c r="Y491">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="492" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A492" t="s">
+        <v>202</v>
+      </c>
+      <c r="B492" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C492" t="s">
+        <v>203</v>
+      </c>
+      <c r="D492" t="s">
+        <v>345</v>
+      </c>
+      <c r="E492" t="s">
+        <v>147</v>
+      </c>
+      <c r="F492" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G492" t="s">
+        <v>338</v>
+      </c>
+      <c r="H492" t="s">
+        <v>2843</v>
+      </c>
+      <c r="I492" t="s">
+        <v>2844</v>
+      </c>
+      <c r="J492" t="s">
+        <v>899</v>
+      </c>
+      <c r="K492" t="s">
+        <v>2845</v>
+      </c>
+      <c r="L492" t="s">
+        <v>782</v>
+      </c>
+      <c r="M492" t="s">
+        <v>270</v>
+      </c>
+      <c r="N492" t="s">
+        <v>213</v>
+      </c>
+      <c r="O492" t="s">
+        <v>337</v>
+      </c>
+      <c r="P492" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q492" t="s">
+        <v>836</v>
+      </c>
+      <c r="R492" t="s">
+        <v>39</v>
+      </c>
+      <c r="S492" t="s">
+        <v>41</v>
+      </c>
+      <c r="T492" t="s">
+        <v>40</v>
+      </c>
+      <c r="U492" t="s">
+        <v>41</v>
+      </c>
+      <c r="V492">
+        <v>25</v>
+      </c>
+      <c r="W492">
+        <v>17</v>
+      </c>
+      <c r="X492">
+        <v>22</v>
+      </c>
+      <c r="Y492">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="493" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A493" t="s">
+        <v>202</v>
+      </c>
+      <c r="B493" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C493" t="s">
+        <v>203</v>
+      </c>
+      <c r="D493" t="s">
+        <v>345</v>
+      </c>
+      <c r="E493" t="s">
+        <v>157</v>
+      </c>
+      <c r="F493" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G493" t="s">
+        <v>2846</v>
+      </c>
+      <c r="H493" t="s">
+        <v>2847</v>
+      </c>
+      <c r="I493" t="s">
+        <v>2848</v>
+      </c>
+      <c r="J493" t="s">
+        <v>2849</v>
+      </c>
+      <c r="K493" t="s">
+        <v>2850</v>
+      </c>
+      <c r="L493" t="s">
+        <v>306</v>
+      </c>
+      <c r="M493" t="s">
+        <v>2851</v>
+      </c>
+      <c r="N493" t="s">
+        <v>672</v>
+      </c>
+      <c r="O493" t="s">
+        <v>488</v>
+      </c>
+      <c r="P493" t="s">
+        <v>2852</v>
+      </c>
+      <c r="Q493" t="s">
+        <v>2853</v>
+      </c>
+      <c r="R493" t="s">
+        <v>41</v>
+      </c>
+      <c r="S493" t="s">
+        <v>41</v>
+      </c>
+      <c r="T493" t="s">
+        <v>39</v>
+      </c>
+      <c r="U493" t="s">
+        <v>201</v>
+      </c>
+      <c r="V493">
+        <v>23</v>
+      </c>
+      <c r="W493">
+        <v>6</v>
+      </c>
+      <c r="X493">
+        <v>11</v>
+      </c>
+      <c r="Y493">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="494" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A494" t="s">
+        <v>202</v>
+      </c>
+      <c r="B494" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C494" t="s">
+        <v>203</v>
+      </c>
+      <c r="D494" t="s">
+        <v>345</v>
+      </c>
+      <c r="E494" t="s">
+        <v>180</v>
+      </c>
+      <c r="F494" t="s">
+        <v>2854</v>
+      </c>
+      <c r="G494" t="s">
+        <v>2855</v>
+      </c>
+      <c r="H494" t="s">
+        <v>2856</v>
+      </c>
+      <c r="I494" t="s">
+        <v>2857</v>
+      </c>
+      <c r="J494" t="s">
+        <v>2858</v>
+      </c>
+      <c r="K494" t="s">
+        <v>2859</v>
+      </c>
+      <c r="L494" t="s">
+        <v>96</v>
+      </c>
+      <c r="M494" t="s">
+        <v>2215</v>
+      </c>
+      <c r="N494" t="s">
+        <v>63</v>
+      </c>
+      <c r="O494" t="s">
+        <v>76</v>
+      </c>
+      <c r="P494" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q494" t="s">
+        <v>2860</v>
+      </c>
+      <c r="R494" t="s">
+        <v>280</v>
+      </c>
+      <c r="S494" t="s">
+        <v>66</v>
+      </c>
+      <c r="T494" t="s">
+        <v>113</v>
+      </c>
+      <c r="U494" t="s">
+        <v>38</v>
+      </c>
+      <c r="V494">
+        <v>39</v>
+      </c>
+      <c r="W494">
+        <v>40</v>
+      </c>
+      <c r="X494">
+        <v>44</v>
+      </c>
+      <c r="Y494">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
